--- a/Dados/table_PROD_BR_1_aux.xlsx
+++ b/Dados/table_PROD_BR_1_aux.xlsx
@@ -36480,37 +36480,37 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Atividades imobiliárias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Outras atividades de serviços</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Comércio</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Transporte, armazenagem e correio</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Informação e comunicação</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Atividades financeiras, de seguros e serviços relacionados</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -36554,25 +36554,25 @@
         <v>637571800396.7791</v>
       </c>
       <c r="H2">
+        <v>279765824417.143</v>
+      </c>
+      <c r="I2">
+        <v>83131292509.8862</v>
+      </c>
+      <c r="J2">
+        <v>54023454352.0709</v>
+      </c>
+      <c r="K2">
+        <v>54023454352.0709</v>
+      </c>
+      <c r="L2">
         <v>165837871843.276</v>
       </c>
-      <c r="I2">
+      <c r="M2">
         <v>326111277597.997</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <v>366390231816.905</v>
-      </c>
-      <c r="K2">
-        <v>279765824417.143</v>
-      </c>
-      <c r="L2">
-        <v>83131292509.8862</v>
-      </c>
-      <c r="M2">
-        <v>54023454352.0709</v>
-      </c>
-      <c r="N2">
-        <v>54023454352.0709</v>
       </c>
       <c r="O2">
         <v>1430040474172.02</v>
@@ -36609,25 +36609,25 @@
         <v>639455362714.452</v>
       </c>
       <c r="H3">
+        <v>284926728423.338</v>
+      </c>
+      <c r="I3">
+        <v>84013092041.60381</v>
+      </c>
+      <c r="J3">
+        <v>55054058632.8966</v>
+      </c>
+      <c r="K3">
+        <v>55054058632.8966</v>
+      </c>
+      <c r="L3">
         <v>170240070747.132</v>
       </c>
-      <c r="I3">
+      <c r="M3">
         <v>330880258658.099</v>
       </c>
-      <c r="J3">
+      <c r="N3">
         <v>366455328828.085</v>
-      </c>
-      <c r="K3">
-        <v>284926728423.338</v>
-      </c>
-      <c r="L3">
-        <v>84013092041.60381</v>
-      </c>
-      <c r="M3">
-        <v>55054058632.8966</v>
-      </c>
-      <c r="N3">
-        <v>55054058632.8966</v>
       </c>
       <c r="O3">
         <v>1449335797250.06</v>
@@ -36664,25 +36664,25 @@
         <v>642083665663.684</v>
       </c>
       <c r="H4">
+        <v>287678218251.441</v>
+      </c>
+      <c r="I4">
+        <v>85124674285.53709</v>
+      </c>
+      <c r="J4">
+        <v>57227851704.3203</v>
+      </c>
+      <c r="K4">
+        <v>57227851704.3203</v>
+      </c>
+      <c r="L4">
         <v>172511288998.636</v>
       </c>
-      <c r="I4">
+      <c r="M4">
         <v>335683015574.517</v>
       </c>
-      <c r="J4">
+      <c r="N4">
         <v>364152501721.101</v>
-      </c>
-      <c r="K4">
-        <v>287678218251.441</v>
-      </c>
-      <c r="L4">
-        <v>85124674285.53709</v>
-      </c>
-      <c r="M4">
-        <v>57227851704.3203</v>
-      </c>
-      <c r="N4">
-        <v>57227851704.3203</v>
       </c>
       <c r="O4">
         <v>1462541121384.11</v>
@@ -36719,25 +36719,25 @@
         <v>637980985700.4659</v>
       </c>
       <c r="H5">
+        <v>286389135352.144</v>
+      </c>
+      <c r="I5">
+        <v>85284214974.94749</v>
+      </c>
+      <c r="J5">
+        <v>57570067264.2328</v>
+      </c>
+      <c r="K5">
+        <v>57570067264.2328</v>
+      </c>
+      <c r="L5">
         <v>172440776911.828</v>
       </c>
-      <c r="I5">
+      <c r="M5">
         <v>340818654287.079</v>
       </c>
-      <c r="J5">
+      <c r="N5">
         <v>364858683311.858</v>
-      </c>
-      <c r="K5">
-        <v>286389135352.144</v>
-      </c>
-      <c r="L5">
-        <v>85284214974.94749</v>
-      </c>
-      <c r="M5">
-        <v>57570067264.2328</v>
-      </c>
-      <c r="N5">
-        <v>57570067264.2328</v>
       </c>
       <c r="O5">
         <v>1469258086162.08</v>
@@ -36774,25 +36774,25 @@
         <v>630620617799.213</v>
       </c>
       <c r="H6">
+        <v>289094252606.195</v>
+      </c>
+      <c r="I6">
+        <v>84188491538.2701</v>
+      </c>
+      <c r="J6">
+        <v>56824178440.0216</v>
+      </c>
+      <c r="K6">
+        <v>56824178440.0216</v>
+      </c>
+      <c r="L6">
         <v>177681757174.175</v>
       </c>
-      <c r="I6">
+      <c r="M6">
         <v>333638657090.956</v>
       </c>
-      <c r="J6">
+      <c r="N6">
         <v>372208422321.788</v>
-      </c>
-      <c r="K6">
-        <v>289094252606.195</v>
-      </c>
-      <c r="L6">
-        <v>84188491538.2701</v>
-      </c>
-      <c r="M6">
-        <v>56824178440.0216</v>
-      </c>
-      <c r="N6">
-        <v>56824178440.0216</v>
       </c>
       <c r="O6">
         <v>1472952627710.12</v>
@@ -36829,25 +36829,25 @@
         <v>665353651239.655</v>
       </c>
       <c r="H7">
+        <v>296629961450.031</v>
+      </c>
+      <c r="I7">
+        <v>88590656816.257</v>
+      </c>
+      <c r="J7">
+        <v>58192122671.6981</v>
+      </c>
+      <c r="K7">
+        <v>58192122671.6981</v>
+      </c>
+      <c r="L7">
         <v>178621480488.854</v>
       </c>
-      <c r="I7">
+      <c r="M7">
         <v>335629335175.395</v>
       </c>
-      <c r="J7">
+      <c r="N7">
         <v>371583730581.693</v>
-      </c>
-      <c r="K7">
-        <v>296629961450.031</v>
-      </c>
-      <c r="L7">
-        <v>88590656816.257</v>
-      </c>
-      <c r="M7">
-        <v>58192122671.6981</v>
-      </c>
-      <c r="N7">
-        <v>58192122671.6981</v>
       </c>
       <c r="O7">
         <v>1493922481391.33</v>
@@ -36884,25 +36884,25 @@
         <v>661273850771.198</v>
       </c>
       <c r="H8">
+        <v>296412355194.451</v>
+      </c>
+      <c r="I8">
+        <v>86693490627.8736</v>
+      </c>
+      <c r="J8">
+        <v>57856188186.5946</v>
+      </c>
+      <c r="K8">
+        <v>57856188186.5946</v>
+      </c>
+      <c r="L8">
         <v>179704752157.497</v>
       </c>
-      <c r="I8">
+      <c r="M8">
         <v>341120906511.165</v>
       </c>
-      <c r="J8">
+      <c r="N8">
         <v>374294866111.894</v>
-      </c>
-      <c r="K8">
-        <v>296412355194.451</v>
-      </c>
-      <c r="L8">
-        <v>86693490627.8736</v>
-      </c>
-      <c r="M8">
-        <v>57856188186.5946</v>
-      </c>
-      <c r="N8">
-        <v>57856188186.5946</v>
       </c>
       <c r="O8">
         <v>1502064598096.48</v>
@@ -36939,25 +36939,25 @@
         <v>655411988008.059</v>
       </c>
       <c r="H9">
+        <v>295524529081.136</v>
+      </c>
+      <c r="I9">
+        <v>86955287381.6301</v>
+      </c>
+      <c r="J9">
+        <v>59984450460.965</v>
+      </c>
+      <c r="K9">
+        <v>59984450460.965</v>
+      </c>
+      <c r="L9">
         <v>179845122929.328</v>
       </c>
-      <c r="I9">
+      <c r="M9">
         <v>345142646887.486</v>
       </c>
-      <c r="J9">
+      <c r="N9">
         <v>374962251926.655</v>
-      </c>
-      <c r="K9">
-        <v>295524529081.136</v>
-      </c>
-      <c r="L9">
-        <v>86955287381.6301</v>
-      </c>
-      <c r="M9">
-        <v>59984450460.965</v>
-      </c>
-      <c r="N9">
-        <v>59984450460.965</v>
       </c>
       <c r="O9">
         <v>1505539485141.38</v>
@@ -36994,25 +36994,25 @@
         <v>652535572637.2271</v>
       </c>
       <c r="H10">
+        <v>300590593180.776</v>
+      </c>
+      <c r="I10">
+        <v>87623097698.77451</v>
+      </c>
+      <c r="J10">
+        <v>60574051124.6059</v>
+      </c>
+      <c r="K10">
+        <v>60574051124.6059</v>
+      </c>
+      <c r="L10">
         <v>180363912024.8</v>
       </c>
-      <c r="I10">
+      <c r="M10">
         <v>346101768170.724</v>
       </c>
-      <c r="J10">
+      <c r="N10">
         <v>373091304838.482</v>
-      </c>
-      <c r="K10">
-        <v>300590593180.776</v>
-      </c>
-      <c r="L10">
-        <v>87623097698.77451</v>
-      </c>
-      <c r="M10">
-        <v>60574051124.6059</v>
-      </c>
-      <c r="N10">
-        <v>60574051124.6059</v>
       </c>
       <c r="O10">
         <v>1511860285396.43</v>
@@ -37049,25 +37049,25 @@
         <v>643263212440.183</v>
       </c>
       <c r="H11">
+        <v>292701228960.928</v>
+      </c>
+      <c r="I11">
+        <v>87408694705.8119</v>
+      </c>
+      <c r="J11">
+        <v>61383736386.2711</v>
+      </c>
+      <c r="K11">
+        <v>61383736386.2711</v>
+      </c>
+      <c r="L11">
         <v>179858702983.735</v>
       </c>
-      <c r="I11">
+      <c r="M11">
         <v>345868980415.314</v>
       </c>
-      <c r="J11">
+      <c r="N11">
         <v>373827103343.929</v>
-      </c>
-      <c r="K11">
-        <v>292701228960.928</v>
-      </c>
-      <c r="L11">
-        <v>87408694705.8119</v>
-      </c>
-      <c r="M11">
-        <v>61383736386.2711</v>
-      </c>
-      <c r="N11">
-        <v>61383736386.2711</v>
       </c>
       <c r="O11">
         <v>1504805164592.47</v>
@@ -37104,25 +37104,25 @@
         <v>636997502051.475</v>
       </c>
       <c r="H12">
+        <v>294690786171.163</v>
+      </c>
+      <c r="I12">
+        <v>87977569526.6087</v>
+      </c>
+      <c r="J12">
+        <v>61628203915.3239</v>
+      </c>
+      <c r="K12">
+        <v>61628203915.3239</v>
+      </c>
+      <c r="L12">
         <v>180003567861.504</v>
       </c>
-      <c r="I12">
+      <c r="M12">
         <v>345257990856.123</v>
       </c>
-      <c r="J12">
+      <c r="N12">
         <v>373507980999.913</v>
-      </c>
-      <c r="K12">
-        <v>294690786171.163</v>
-      </c>
-      <c r="L12">
-        <v>87977569526.6087</v>
-      </c>
-      <c r="M12">
-        <v>61628203915.3239</v>
-      </c>
-      <c r="N12">
-        <v>61628203915.3239</v>
       </c>
       <c r="O12">
         <v>1507883741917.52</v>
@@ -37159,25 +37159,25 @@
         <v>640503280302.585</v>
       </c>
       <c r="H13">
+        <v>296178407718.025</v>
+      </c>
+      <c r="I13">
+        <v>88634138723.8423</v>
+      </c>
+      <c r="J13">
+        <v>61617858001.4104</v>
+      </c>
+      <c r="K13">
+        <v>61617858001.4104</v>
+      </c>
+      <c r="L13">
         <v>180798574221.132</v>
       </c>
-      <c r="I13">
+      <c r="M13">
         <v>343711689763.695</v>
       </c>
-      <c r="J13">
+      <c r="N13">
         <v>374024792864.499</v>
-      </c>
-      <c r="K13">
-        <v>296178407718.025</v>
-      </c>
-      <c r="L13">
-        <v>88634138723.8423</v>
-      </c>
-      <c r="M13">
-        <v>61617858001.4104</v>
-      </c>
-      <c r="N13">
-        <v>61617858001.4104</v>
       </c>
       <c r="O13">
         <v>1508814670073.73</v>
@@ -37214,25 +37214,25 @@
         <v>627605105210.781</v>
       </c>
       <c r="H14">
+        <v>288621316790.213</v>
+      </c>
+      <c r="I14">
+        <v>85957304368.39371</v>
+      </c>
+      <c r="J14">
+        <v>62301394530.5768</v>
+      </c>
+      <c r="K14">
+        <v>62301394530.5768</v>
+      </c>
+      <c r="L14">
         <v>180217907911.726</v>
       </c>
-      <c r="I14">
+      <c r="M14">
         <v>339513454740.307</v>
       </c>
-      <c r="J14">
+      <c r="N14">
         <v>374861219779.688</v>
-      </c>
-      <c r="K14">
-        <v>288621316790.213</v>
-      </c>
-      <c r="L14">
-        <v>85957304368.39371</v>
-      </c>
-      <c r="M14">
-        <v>62301394530.5768</v>
-      </c>
-      <c r="N14">
-        <v>62301394530.5768</v>
       </c>
       <c r="O14">
         <v>1493871066257.31</v>
@@ -37269,25 +37269,25 @@
         <v>611384718455.373</v>
       </c>
       <c r="H15">
+        <v>277078409066.733</v>
+      </c>
+      <c r="I15">
+        <v>84229294499.8531</v>
+      </c>
+      <c r="J15">
+        <v>60884440380.9337</v>
+      </c>
+      <c r="K15">
+        <v>60884440380.9337</v>
+      </c>
+      <c r="L15">
         <v>179278420293.535</v>
       </c>
-      <c r="I15">
+      <c r="M15">
         <v>335297316860.083</v>
       </c>
-      <c r="J15">
+      <c r="N15">
         <v>373140293816.238</v>
-      </c>
-      <c r="K15">
-        <v>277078409066.733</v>
-      </c>
-      <c r="L15">
-        <v>84229294499.8531</v>
-      </c>
-      <c r="M15">
-        <v>60884440380.9337</v>
-      </c>
-      <c r="N15">
-        <v>60884440380.9337</v>
       </c>
       <c r="O15">
         <v>1471268781868.9</v>
@@ -37324,25 +37324,25 @@
         <v>598924181785.813</v>
       </c>
       <c r="H16">
+        <v>268984564672.613</v>
+      </c>
+      <c r="I16">
+        <v>83660424637.0316</v>
+      </c>
+      <c r="J16">
+        <v>60358914085.6659</v>
+      </c>
+      <c r="K16">
+        <v>60358914085.6659</v>
+      </c>
+      <c r="L16">
         <v>179394362020.183</v>
       </c>
-      <c r="I16">
+      <c r="M16">
         <v>327246623855.846</v>
       </c>
-      <c r="J16">
+      <c r="N16">
         <v>374665720423.435</v>
-      </c>
-      <c r="K16">
-        <v>268984564672.613</v>
-      </c>
-      <c r="L16">
-        <v>83660424637.0316</v>
-      </c>
-      <c r="M16">
-        <v>60358914085.6659</v>
-      </c>
-      <c r="N16">
-        <v>60358914085.6659</v>
       </c>
       <c r="O16">
         <v>1455528793100.3</v>
@@ -37379,25 +37379,25 @@
         <v>586921442021.172</v>
       </c>
       <c r="H17">
+        <v>263094342771.076</v>
+      </c>
+      <c r="I17">
+        <v>82680289271.49809</v>
+      </c>
+      <c r="J17">
+        <v>59443988293.876</v>
+      </c>
+      <c r="K17">
+        <v>59443988293.876</v>
+      </c>
+      <c r="L17">
         <v>179352539513.816</v>
       </c>
-      <c r="I17">
+      <c r="M17">
         <v>327533645123.234</v>
       </c>
-      <c r="J17">
+      <c r="N17">
         <v>375454669046.696</v>
-      </c>
-      <c r="K17">
-        <v>263094342771.076</v>
-      </c>
-      <c r="L17">
-        <v>82680289271.49809</v>
-      </c>
-      <c r="M17">
-        <v>59443988293.876</v>
-      </c>
-      <c r="N17">
-        <v>59443988293.876</v>
       </c>
       <c r="O17">
         <v>1447835243331.76</v>
@@ -37434,25 +37434,25 @@
         <v>584249449645.139</v>
       </c>
       <c r="H18">
+        <v>259606118229.241</v>
+      </c>
+      <c r="I18">
+        <v>81104810420.57401</v>
+      </c>
+      <c r="J18">
+        <v>59751856106.9046</v>
+      </c>
+      <c r="K18">
+        <v>59751856106.9046</v>
+      </c>
+      <c r="L18">
         <v>180403042469.301</v>
       </c>
-      <c r="I18">
+      <c r="M18">
         <v>329664331963.583</v>
       </c>
-      <c r="J18">
+      <c r="N18">
         <v>376064408462.106</v>
-      </c>
-      <c r="K18">
-        <v>259606118229.241</v>
-      </c>
-      <c r="L18">
-        <v>81104810420.57401</v>
-      </c>
-      <c r="M18">
-        <v>59751856106.9046</v>
-      </c>
-      <c r="N18">
-        <v>59751856106.9046</v>
       </c>
       <c r="O18">
         <v>1442888330883.51</v>
@@ -37489,25 +37489,25 @@
         <v>586121531984.703</v>
       </c>
       <c r="H19">
+        <v>258035182882.067</v>
+      </c>
+      <c r="I19">
+        <v>80230163877.5766</v>
+      </c>
+      <c r="J19">
+        <v>59737479686.7278</v>
+      </c>
+      <c r="K19">
+        <v>59737479686.7278</v>
+      </c>
+      <c r="L19">
         <v>179966158211.71</v>
       </c>
-      <c r="I19">
+      <c r="M19">
         <v>328647339517.458</v>
       </c>
-      <c r="J19">
+      <c r="N19">
         <v>376506956634.678</v>
-      </c>
-      <c r="K19">
-        <v>258035182882.067</v>
-      </c>
-      <c r="L19">
-        <v>80230163877.5766</v>
-      </c>
-      <c r="M19">
-        <v>59737479686.7278</v>
-      </c>
-      <c r="N19">
-        <v>59737479686.7278</v>
       </c>
       <c r="O19">
         <v>1439302051353.53</v>
@@ -37544,25 +37544,25 @@
         <v>577350680476.542</v>
       </c>
       <c r="H20">
+        <v>254262371177.979</v>
+      </c>
+      <c r="I20">
+        <v>78535718831.9144</v>
+      </c>
+      <c r="J20">
+        <v>60440608082.0945</v>
+      </c>
+      <c r="K20">
+        <v>60440608082.0945</v>
+      </c>
+      <c r="L20">
         <v>179212926906.196</v>
       </c>
-      <c r="I20">
+      <c r="M20">
         <v>327416939144.487</v>
       </c>
-      <c r="J20">
+      <c r="N20">
         <v>376119164707.825</v>
-      </c>
-      <c r="K20">
-        <v>254262371177.979</v>
-      </c>
-      <c r="L20">
-        <v>78535718831.9144</v>
-      </c>
-      <c r="M20">
-        <v>60440608082.0945</v>
-      </c>
-      <c r="N20">
-        <v>60440608082.0945</v>
       </c>
       <c r="O20">
         <v>1430365691895.15</v>
@@ -37599,25 +37599,25 @@
         <v>566214229743.6379</v>
       </c>
       <c r="H21">
+        <v>253113248204.112</v>
+      </c>
+      <c r="I21">
+        <v>77902628539.9482</v>
+      </c>
+      <c r="J21">
+        <v>58055004532.7724</v>
+      </c>
+      <c r="K21">
+        <v>58055004532.7724</v>
+      </c>
+      <c r="L21">
         <v>179813429493.321</v>
       </c>
-      <c r="I21">
+      <c r="M21">
         <v>325400980279.761</v>
       </c>
-      <c r="J21">
+      <c r="N21">
         <v>374375200436.171</v>
-      </c>
-      <c r="K21">
-        <v>253113248204.112</v>
-      </c>
-      <c r="L21">
-        <v>77902628539.9482</v>
-      </c>
-      <c r="M21">
-        <v>58055004532.7724</v>
-      </c>
-      <c r="N21">
-        <v>58055004532.7724</v>
       </c>
       <c r="O21">
         <v>1422077321586.45</v>
@@ -37654,25 +37654,25 @@
         <v>572410350533.363</v>
       </c>
       <c r="H22">
+        <v>255025588287.381</v>
+      </c>
+      <c r="I22">
+        <v>79150914912.0575</v>
+      </c>
+      <c r="J22">
+        <v>60418964849.1751</v>
+      </c>
+      <c r="K22">
+        <v>60418964849.1751</v>
+      </c>
+      <c r="L22">
         <v>180058438912.216</v>
       </c>
-      <c r="I22">
+      <c r="M22">
         <v>325829775655.527</v>
       </c>
-      <c r="J22">
+      <c r="N22">
         <v>373760823940.046</v>
-      </c>
-      <c r="K22">
-        <v>255025588287.381</v>
-      </c>
-      <c r="L22">
-        <v>79150914912.0575</v>
-      </c>
-      <c r="M22">
-        <v>60418964849.1751</v>
-      </c>
-      <c r="N22">
-        <v>60418964849.1751</v>
       </c>
       <c r="O22">
         <v>1428368774081.69</v>
@@ -37709,25 +37709,25 @@
         <v>574067935584.828</v>
       </c>
       <c r="H23">
+        <v>261645213586.231</v>
+      </c>
+      <c r="I23">
+        <v>80284840085.634</v>
+      </c>
+      <c r="J23">
+        <v>60026776777.9761</v>
+      </c>
+      <c r="K23">
+        <v>60026776777.9761</v>
+      </c>
+      <c r="L23">
         <v>181727743005.919</v>
       </c>
-      <c r="I23">
+      <c r="M23">
         <v>330669579904.641</v>
       </c>
-      <c r="J23">
+      <c r="N23">
         <v>375886210191.087</v>
-      </c>
-      <c r="K23">
-        <v>261645213586.231</v>
-      </c>
-      <c r="L23">
-        <v>80284840085.634</v>
-      </c>
-      <c r="M23">
-        <v>60026776777.9761</v>
-      </c>
-      <c r="N23">
-        <v>60026776777.9761</v>
       </c>
       <c r="O23">
         <v>1444257212531.26</v>
@@ -37764,25 +37764,25 @@
         <v>574945390119.582</v>
       </c>
       <c r="H24">
+        <v>264906613204.404</v>
+      </c>
+      <c r="I24">
+        <v>80422460021.2941</v>
+      </c>
+      <c r="J24">
+        <v>60235361492.289</v>
+      </c>
+      <c r="K24">
+        <v>60235361492.289</v>
+      </c>
+      <c r="L24">
         <v>183169756635.274</v>
       </c>
-      <c r="I24">
+      <c r="M24">
         <v>333294708275.494</v>
       </c>
-      <c r="J24">
+      <c r="N24">
         <v>377691711681.583</v>
-      </c>
-      <c r="K24">
-        <v>264906613204.404</v>
-      </c>
-      <c r="L24">
-        <v>80422460021.2941</v>
-      </c>
-      <c r="M24">
-        <v>60235361492.289</v>
-      </c>
-      <c r="N24">
-        <v>60235361492.289</v>
       </c>
       <c r="O24">
         <v>1452247330206.94</v>
@@ -37819,25 +37819,25 @@
         <v>580871667104.741</v>
       </c>
       <c r="H25">
+        <v>267146697193.309</v>
+      </c>
+      <c r="I25">
+        <v>80958755668.08569</v>
+      </c>
+      <c r="J25">
+        <v>60444925061.1939</v>
+      </c>
+      <c r="K25">
+        <v>60444925061.1939</v>
+      </c>
+      <c r="L25">
         <v>184067538694.502</v>
       </c>
-      <c r="I25">
+      <c r="M25">
         <v>331542111150.565</v>
       </c>
-      <c r="J25">
+      <c r="N25">
         <v>377131471146.273</v>
-      </c>
-      <c r="K25">
-        <v>267146697193.309</v>
-      </c>
-      <c r="L25">
-        <v>80958755668.08569</v>
-      </c>
-      <c r="M25">
-        <v>60444925061.1939</v>
-      </c>
-      <c r="N25">
-        <v>60444925061.1939</v>
       </c>
       <c r="O25">
         <v>1457292534023.9</v>
@@ -37874,25 +37874,25 @@
         <v>582350793044.2209</v>
       </c>
       <c r="H26">
+        <v>269667660548.798</v>
+      </c>
+      <c r="I26">
+        <v>81569351187.56441</v>
+      </c>
+      <c r="J26">
+        <v>60300988222.2464</v>
+      </c>
+      <c r="K26">
+        <v>60300988222.2464</v>
+      </c>
+      <c r="L26">
         <v>185567988198.093</v>
       </c>
-      <c r="I26">
+      <c r="M26">
         <v>337011180905.377</v>
       </c>
-      <c r="J26">
+      <c r="N26">
         <v>376504588772.503</v>
-      </c>
-      <c r="K26">
-        <v>269667660548.798</v>
-      </c>
-      <c r="L26">
-        <v>81569351187.56441</v>
-      </c>
-      <c r="M26">
-        <v>60300988222.2464</v>
-      </c>
-      <c r="N26">
-        <v>60300988222.2464</v>
       </c>
       <c r="O26">
         <v>1466572059653.42</v>
@@ -37929,25 +37929,25 @@
         <v>578148541502.356</v>
       </c>
       <c r="H27">
+        <v>268765158483.948</v>
+      </c>
+      <c r="I27">
+        <v>80673326872.2905</v>
+      </c>
+      <c r="J27">
+        <v>61608088510.4464</v>
+      </c>
+      <c r="K27">
+        <v>61608088510.4464</v>
+      </c>
+      <c r="L27">
         <v>187587316243.982</v>
       </c>
-      <c r="I27">
+      <c r="M27">
         <v>341297051890.037</v>
       </c>
-      <c r="J27">
+      <c r="N27">
         <v>376954861609.212</v>
-      </c>
-      <c r="K27">
-        <v>268765158483.948</v>
-      </c>
-      <c r="L27">
-        <v>80673326872.2905</v>
-      </c>
-      <c r="M27">
-        <v>61608088510.4464</v>
-      </c>
-      <c r="N27">
-        <v>61608088510.4464</v>
       </c>
       <c r="O27">
         <v>1474843716825.15</v>
@@ -37984,25 +37984,25 @@
         <v>580756991322.031</v>
       </c>
       <c r="H28">
+        <v>269272062187.011</v>
+      </c>
+      <c r="I28">
+        <v>83014954479.8174</v>
+      </c>
+      <c r="J28">
+        <v>61644747417.7672</v>
+      </c>
+      <c r="K28">
+        <v>61644747417.7672</v>
+      </c>
+      <c r="L28">
         <v>189386538518.298</v>
       </c>
-      <c r="I28">
+      <c r="M28">
         <v>345179968168.137</v>
       </c>
-      <c r="J28">
+      <c r="N28">
         <v>377258809237.111</v>
-      </c>
-      <c r="K28">
-        <v>269272062187.011</v>
-      </c>
-      <c r="L28">
-        <v>83014954479.8174</v>
-      </c>
-      <c r="M28">
-        <v>61644747417.7672</v>
-      </c>
-      <c r="N28">
-        <v>61644747417.7672</v>
       </c>
       <c r="O28">
         <v>1482292818806.53</v>
@@ -38039,25 +38039,25 @@
         <v>577722461016.627</v>
       </c>
       <c r="H29">
+        <v>268459333570.647</v>
+      </c>
+      <c r="I29">
+        <v>82411834381.86279</v>
+      </c>
+      <c r="J29">
+        <v>61851575344.5494</v>
+      </c>
+      <c r="K29">
+        <v>61851575344.5494</v>
+      </c>
+      <c r="L29">
         <v>190635137659.139</v>
       </c>
-      <c r="I29">
+      <c r="M29">
         <v>342708780477.813</v>
       </c>
-      <c r="J29">
+      <c r="N29">
         <v>373966305914.173</v>
-      </c>
-      <c r="K29">
-        <v>268459333570.647</v>
-      </c>
-      <c r="L29">
-        <v>82411834381.86279</v>
-      </c>
-      <c r="M29">
-        <v>61851575344.5494</v>
-      </c>
-      <c r="N29">
-        <v>61851575344.5494</v>
       </c>
       <c r="O29">
         <v>1477148523897.47</v>
@@ -38094,25 +38094,25 @@
         <v>572809903135.103</v>
       </c>
       <c r="H30">
+        <v>269848143316.237</v>
+      </c>
+      <c r="I30">
+        <v>82005934893.76801</v>
+      </c>
+      <c r="J30">
+        <v>63350316248.7792</v>
+      </c>
+      <c r="K30">
+        <v>63350316248.7792</v>
+      </c>
+      <c r="L30">
         <v>191906640950.649</v>
       </c>
-      <c r="I30">
+      <c r="M30">
         <v>348785721320.932</v>
       </c>
-      <c r="J30">
+      <c r="N30">
         <v>376623350986.378</v>
-      </c>
-      <c r="K30">
-        <v>269848143316.237</v>
-      </c>
-      <c r="L30">
-        <v>82005934893.76801</v>
-      </c>
-      <c r="M30">
-        <v>63350316248.7792</v>
-      </c>
-      <c r="N30">
-        <v>63350316248.7792</v>
       </c>
       <c r="O30">
         <v>1490453198505.56</v>
@@ -38149,25 +38149,25 @@
         <v>577301955263.333</v>
       </c>
       <c r="H31">
+        <v>272957252283.115</v>
+      </c>
+      <c r="I31">
+        <v>82092443824.2348</v>
+      </c>
+      <c r="J31">
+        <v>63946778758.1133</v>
+      </c>
+      <c r="K31">
+        <v>63946778758.1133</v>
+      </c>
+      <c r="L31">
         <v>193475480031.415</v>
       </c>
-      <c r="I31">
+      <c r="M31">
         <v>350585583390.36</v>
       </c>
-      <c r="J31">
+      <c r="N31">
         <v>375044130169.686</v>
-      </c>
-      <c r="K31">
-        <v>272957252283.115</v>
-      </c>
-      <c r="L31">
-        <v>82092443824.2348</v>
-      </c>
-      <c r="M31">
-        <v>63946778758.1133</v>
-      </c>
-      <c r="N31">
-        <v>63946778758.1133</v>
       </c>
       <c r="O31">
         <v>1497256036183.33</v>
@@ -38204,25 +38204,25 @@
         <v>576056028898.2371</v>
       </c>
       <c r="H32">
+        <v>274919065282.52</v>
+      </c>
+      <c r="I32">
+        <v>82408309273.91299</v>
+      </c>
+      <c r="J32">
+        <v>64415443282.474</v>
+      </c>
+      <c r="K32">
+        <v>64415443282.474</v>
+      </c>
+      <c r="L32">
         <v>193377582457.117</v>
       </c>
-      <c r="I32">
+      <c r="M32">
         <v>350118850948.18</v>
       </c>
-      <c r="J32">
+      <c r="N32">
         <v>372810339764.343</v>
-      </c>
-      <c r="K32">
-        <v>274919065282.52</v>
-      </c>
-      <c r="L32">
-        <v>82408309273.91299</v>
-      </c>
-      <c r="M32">
-        <v>64415443282.474</v>
-      </c>
-      <c r="N32">
-        <v>64415443282.474</v>
       </c>
       <c r="O32">
         <v>1498753823909.59</v>
@@ -38259,25 +38259,25 @@
         <v>577424384907.2889</v>
       </c>
       <c r="H33">
+        <v>275864520214.406</v>
+      </c>
+      <c r="I33">
+        <v>81370451695.7025</v>
+      </c>
+      <c r="J33">
+        <v>64613397025.8235</v>
+      </c>
+      <c r="K33">
+        <v>64613397025.8235</v>
+      </c>
+      <c r="L33">
         <v>192696126377.793</v>
       </c>
-      <c r="I33">
+      <c r="M33">
         <v>354296234804.731</v>
       </c>
-      <c r="J33">
+      <c r="N33">
         <v>373872900277.486</v>
-      </c>
-      <c r="K33">
-        <v>275864520214.406</v>
-      </c>
-      <c r="L33">
-        <v>81370451695.7025</v>
-      </c>
-      <c r="M33">
-        <v>64613397025.8235</v>
-      </c>
-      <c r="N33">
-        <v>64613397025.8235</v>
       </c>
       <c r="O33">
         <v>1502868141837.58</v>
@@ -38314,25 +38314,25 @@
         <v>566691770425.55</v>
       </c>
       <c r="H34">
+        <v>276523901292.979</v>
+      </c>
+      <c r="I34">
+        <v>78847297147.6777</v>
+      </c>
+      <c r="J34">
+        <v>65888988736.3008</v>
+      </c>
+      <c r="K34">
+        <v>65888988736.3008</v>
+      </c>
+      <c r="L34">
         <v>195002261960.811</v>
       </c>
-      <c r="I34">
+      <c r="M34">
         <v>344585584198.586</v>
       </c>
-      <c r="J34">
+      <c r="N34">
         <v>375128168876.269</v>
-      </c>
-      <c r="K34">
-        <v>276523901292.979</v>
-      </c>
-      <c r="L34">
-        <v>78847297147.6777</v>
-      </c>
-      <c r="M34">
-        <v>65888988736.3008</v>
-      </c>
-      <c r="N34">
-        <v>65888988736.3008</v>
       </c>
       <c r="O34">
         <v>1492229743298.52</v>
@@ -38369,25 +38369,25 @@
         <v>501405727755.582</v>
       </c>
       <c r="H35">
+        <v>239615623953.131</v>
+      </c>
+      <c r="I35">
+        <v>63234898862.907</v>
+      </c>
+      <c r="J35">
+        <v>63088727556.0352</v>
+      </c>
+      <c r="K35">
+        <v>63088727556.0352</v>
+      </c>
+      <c r="L35">
         <v>195330509319.059</v>
       </c>
-      <c r="I35">
+      <c r="M35">
         <v>287042190184.794</v>
       </c>
-      <c r="J35">
+      <c r="N35">
         <v>341433832195.367</v>
-      </c>
-      <c r="K35">
-        <v>239615623953.131</v>
-      </c>
-      <c r="L35">
-        <v>63234898862.907</v>
-      </c>
-      <c r="M35">
-        <v>63088727556.0352</v>
-      </c>
-      <c r="N35">
-        <v>63088727556.0352</v>
       </c>
       <c r="O35">
         <v>1355383705016.02</v>
@@ -38424,25 +38424,25 @@
         <v>575999044665.546</v>
       </c>
       <c r="H36">
+        <v>276190928550.693</v>
+      </c>
+      <c r="I36">
+        <v>69719907502.6716</v>
+      </c>
+      <c r="J36">
+        <v>64782314675.7013</v>
+      </c>
+      <c r="K36">
+        <v>64782314675.7013</v>
+      </c>
+      <c r="L36">
         <v>196566463860.616</v>
       </c>
-      <c r="I36">
+      <c r="M36">
         <v>311007003014.077</v>
       </c>
-      <c r="J36">
+      <c r="N36">
         <v>352319576525.709</v>
-      </c>
-      <c r="K36">
-        <v>276190928550.693</v>
-      </c>
-      <c r="L36">
-        <v>69719907502.6716</v>
-      </c>
-      <c r="M36">
-        <v>64782314675.7013</v>
-      </c>
-      <c r="N36">
-        <v>64782314675.7013</v>
       </c>
       <c r="O36">
         <v>1434883238320.34</v>
@@ -38479,25 +38479,25 @@
         <v>591159203601.786</v>
       </c>
       <c r="H37">
+        <v>285399523018.216</v>
+      </c>
+      <c r="I37">
+        <v>74496614795.43069</v>
+      </c>
+      <c r="J37">
+        <v>67775195255.2055</v>
+      </c>
+      <c r="K37">
+        <v>67775195255.2055</v>
+      </c>
+      <c r="L37">
         <v>197839257271.68</v>
       </c>
-      <c r="I37">
+      <c r="M37">
         <v>329372993186.103</v>
       </c>
-      <c r="J37">
+      <c r="N37">
         <v>361528136392.997</v>
-      </c>
-      <c r="K37">
-        <v>285399523018.216</v>
-      </c>
-      <c r="L37">
-        <v>74496614795.43069</v>
-      </c>
-      <c r="M37">
-        <v>67775195255.2055</v>
-      </c>
-      <c r="N37">
-        <v>67775195255.2055</v>
       </c>
       <c r="O37">
         <v>1478832225922.96</v>
@@ -38534,25 +38534,25 @@
         <v>602128674190.726</v>
       </c>
       <c r="H38">
+        <v>284457861616.198</v>
+      </c>
+      <c r="I38">
+        <v>76088789069.1671</v>
+      </c>
+      <c r="J38">
+        <v>70843925236.41769</v>
+      </c>
+      <c r="K38">
+        <v>70843925236.41769</v>
+      </c>
+      <c r="L38">
         <v>199256186179.295</v>
       </c>
-      <c r="I38">
+      <c r="M38">
         <v>335735657783.166</v>
       </c>
-      <c r="J38">
+      <c r="N38">
         <v>361642696933.046</v>
-      </c>
-      <c r="K38">
-        <v>284457861616.198</v>
-      </c>
-      <c r="L38">
-        <v>76088789069.1671</v>
-      </c>
-      <c r="M38">
-        <v>70843925236.41769</v>
-      </c>
-      <c r="N38">
-        <v>70843925236.41769</v>
       </c>
       <c r="O38">
         <v>1492258800482.94</v>
@@ -38589,25 +38589,25 @@
         <v>591900255144.649</v>
       </c>
       <c r="H39">
+        <v>279849270483.663</v>
+      </c>
+      <c r="I39">
+        <v>75227871489.5896</v>
+      </c>
+      <c r="J39">
+        <v>74215479249.71069</v>
+      </c>
+      <c r="K39">
+        <v>74215479249.71069</v>
+      </c>
+      <c r="L39">
         <v>199609176197.223</v>
       </c>
-      <c r="I39">
+      <c r="M39">
         <v>340424612720.04</v>
       </c>
-      <c r="J39">
+      <c r="N39">
         <v>364433604524.974</v>
-      </c>
-      <c r="K39">
-        <v>279849270483.663</v>
-      </c>
-      <c r="L39">
-        <v>75227871489.5896</v>
-      </c>
-      <c r="M39">
-        <v>74215479249.71069</v>
-      </c>
-      <c r="N39">
-        <v>74215479249.71069</v>
       </c>
       <c r="O39">
         <v>1500188931380.13</v>
@@ -38644,25 +38644,25 @@
         <v>584264464269.438</v>
       </c>
       <c r="H40">
+        <v>280080360831.386</v>
+      </c>
+      <c r="I40">
+        <v>75794429741.2155</v>
+      </c>
+      <c r="J40">
+        <v>75295948796.3976</v>
+      </c>
+      <c r="K40">
+        <v>75295948796.3976</v>
+      </c>
+      <c r="L40">
         <v>199363866837.548</v>
       </c>
-      <c r="I40">
+      <c r="M40">
         <v>355228263614.787</v>
       </c>
-      <c r="J40">
+      <c r="N40">
         <v>367897101010.03</v>
-      </c>
-      <c r="K40">
-        <v>280080360831.386</v>
-      </c>
-      <c r="L40">
-        <v>75794429741.2155</v>
-      </c>
-      <c r="M40">
-        <v>75295948796.3976</v>
-      </c>
-      <c r="N40">
-        <v>75295948796.3976</v>
       </c>
       <c r="O40">
         <v>1515420037386.83</v>
@@ -38699,25 +38699,25 @@
         <v>569553733883.561</v>
       </c>
       <c r="H41">
+        <v>281826264959.61</v>
+      </c>
+      <c r="I41">
+        <v>77616837130.8671</v>
+      </c>
+      <c r="J41">
+        <v>77592636518.24561</v>
+      </c>
+      <c r="K41">
+        <v>77592636518.24561</v>
+      </c>
+      <c r="L41">
         <v>201030932837.768</v>
       </c>
-      <c r="I41">
+      <c r="M41">
         <v>357159884280.83</v>
       </c>
-      <c r="J41">
+      <c r="N41">
         <v>374398978271.37</v>
-      </c>
-      <c r="K41">
-        <v>281826264959.61</v>
-      </c>
-      <c r="L41">
-        <v>77616837130.8671</v>
-      </c>
-      <c r="M41">
-        <v>77592636518.24561</v>
-      </c>
-      <c r="N41">
-        <v>77592636518.24561</v>
       </c>
       <c r="O41">
         <v>1535429179707.85</v>
@@ -38754,25 +38754,25 @@
         <v>588247331917.877</v>
       </c>
       <c r="H42">
+        <v>280899173602.724</v>
+      </c>
+      <c r="I42">
+        <v>80078583319.403</v>
+      </c>
+      <c r="J42">
+        <v>75266137577.13589</v>
+      </c>
+      <c r="K42">
+        <v>75266137577.13589</v>
+      </c>
+      <c r="L42">
         <v>200814021284.105</v>
       </c>
-      <c r="I42">
+      <c r="M42">
         <v>372793106803.758</v>
       </c>
-      <c r="J42">
+      <c r="N42">
         <v>375619607064.28</v>
-      </c>
-      <c r="K42">
-        <v>280899173602.724</v>
-      </c>
-      <c r="L42">
-        <v>80078583319.403</v>
-      </c>
-      <c r="M42">
-        <v>75266137577.13589</v>
-      </c>
-      <c r="N42">
-        <v>75266137577.13589</v>
       </c>
       <c r="O42">
         <v>1550001433922.62</v>
@@ -38809,25 +38809,25 @@
         <v>598377246637.678</v>
       </c>
       <c r="H43">
+        <v>285424420754.859</v>
+      </c>
+      <c r="I43">
+        <v>82116964291.9725</v>
+      </c>
+      <c r="J43">
+        <v>77335766598.81171</v>
+      </c>
+      <c r="K43">
+        <v>77335766598.81171</v>
+      </c>
+      <c r="L43">
         <v>202521700378.932</v>
       </c>
-      <c r="I43">
+      <c r="M43">
         <v>385436839306.446</v>
       </c>
-      <c r="J43">
+      <c r="N43">
         <v>369853365515.181</v>
-      </c>
-      <c r="K43">
-        <v>285424420754.859</v>
-      </c>
-      <c r="L43">
-        <v>82116964291.9725</v>
-      </c>
-      <c r="M43">
-        <v>77335766598.81171</v>
-      </c>
-      <c r="N43">
-        <v>77335766598.81171</v>
       </c>
       <c r="O43">
         <v>1569532559305.97</v>
@@ -38864,25 +38864,25 @@
         <v>600132265661.811</v>
       </c>
       <c r="H44">
+        <v>285531605578.954</v>
+      </c>
+      <c r="I44">
+        <v>83154348789.1145</v>
+      </c>
+      <c r="J44">
+        <v>79687870185.134</v>
+      </c>
+      <c r="K44">
+        <v>79687870185.134</v>
+      </c>
+      <c r="L44">
         <v>204228091399.097</v>
       </c>
-      <c r="I44">
+      <c r="M44">
         <v>393968741275.502</v>
       </c>
-      <c r="J44">
+      <c r="N44">
         <v>374618934969.845</v>
-      </c>
-      <c r="K44">
-        <v>285531605578.954</v>
-      </c>
-      <c r="L44">
-        <v>83154348789.1145</v>
-      </c>
-      <c r="M44">
-        <v>79687870185.134</v>
-      </c>
-      <c r="N44">
-        <v>79687870185.134</v>
       </c>
       <c r="O44">
         <v>1587539035982.98</v>
@@ -38919,25 +38919,25 @@
         <v>596647267637.053</v>
       </c>
       <c r="H45">
+        <v>284785045523.719</v>
+      </c>
+      <c r="I45">
+        <v>83816527590.9194</v>
+      </c>
+      <c r="J45">
+        <v>81181152071.1483</v>
+      </c>
+      <c r="K45">
+        <v>81181152071.1483</v>
+      </c>
+      <c r="L45">
         <v>206729905051.363</v>
       </c>
-      <c r="I45">
+      <c r="M45">
         <v>395335452729.499</v>
       </c>
-      <c r="J45">
+      <c r="N45">
         <v>373330306286.295</v>
-      </c>
-      <c r="K45">
-        <v>284785045523.719</v>
-      </c>
-      <c r="L45">
-        <v>83816527590.9194</v>
-      </c>
-      <c r="M45">
-        <v>81181152071.1483</v>
-      </c>
-      <c r="N45">
-        <v>81181152071.1483</v>
       </c>
       <c r="O45">
         <v>1595576850057.82</v>
@@ -38974,25 +38974,25 @@
         <v>597724945492.214</v>
       </c>
       <c r="H46">
+        <v>285967205251.207</v>
+      </c>
+      <c r="I46">
+        <v>84348820750.6357</v>
+      </c>
+      <c r="J46">
+        <v>79982756578.0387</v>
+      </c>
+      <c r="K46">
+        <v>79982756578.0387</v>
+      </c>
+      <c r="L46">
         <v>206702832525.279</v>
       </c>
-      <c r="I46">
+      <c r="M46">
         <v>393199845988.054</v>
       </c>
-      <c r="J46">
+      <c r="N46">
         <v>376544296559.195</v>
-      </c>
-      <c r="K46">
-        <v>285967205251.207</v>
-      </c>
-      <c r="L46">
-        <v>84348820750.6357</v>
-      </c>
-      <c r="M46">
-        <v>79982756578.0387</v>
-      </c>
-      <c r="N46">
-        <v>79982756578.0387</v>
       </c>
       <c r="O46">
         <v>1604218301127.64</v>
@@ -39029,25 +39029,25 @@
         <v>603250306022.068</v>
       </c>
       <c r="H47">
+        <v>286996258545.758</v>
+      </c>
+      <c r="I47">
+        <v>85648635739.05721</v>
+      </c>
+      <c r="J47">
+        <v>80756893660.6149</v>
+      </c>
+      <c r="K47">
+        <v>80756893660.6149</v>
+      </c>
+      <c r="L47">
         <v>208482210956.883</v>
       </c>
-      <c r="I47">
+      <c r="M47">
         <v>397882903508.288</v>
       </c>
-      <c r="J47">
+      <c r="N47">
         <v>379600035742.677</v>
-      </c>
-      <c r="K47">
-        <v>286996258545.758</v>
-      </c>
-      <c r="L47">
-        <v>85648635739.05721</v>
-      </c>
-      <c r="M47">
-        <v>80756893660.6149</v>
-      </c>
-      <c r="N47">
-        <v>80756893660.6149</v>
       </c>
       <c r="O47">
         <v>1616444323747.29</v>
@@ -39084,25 +39084,25 @@
         <v>607035365981.79</v>
       </c>
       <c r="H48">
+        <v>287390931567.697</v>
+      </c>
+      <c r="I48">
+        <v>84107340497.8988</v>
+      </c>
+      <c r="J48">
+        <v>80793021487.1552</v>
+      </c>
+      <c r="K48">
+        <v>80793021487.1552</v>
+      </c>
+      <c r="L48">
         <v>211141833804.043</v>
       </c>
-      <c r="I48">
+      <c r="M48">
         <v>401027154196.132</v>
       </c>
-      <c r="J48">
+      <c r="N48">
         <v>380865130762.265</v>
-      </c>
-      <c r="K48">
-        <v>287390931567.697</v>
-      </c>
-      <c r="L48">
-        <v>84107340497.8988</v>
-      </c>
-      <c r="M48">
-        <v>80793021487.1552</v>
-      </c>
-      <c r="N48">
-        <v>80793021487.1552</v>
       </c>
       <c r="O48">
         <v>1622307852296.04</v>
@@ -39139,25 +39139,25 @@
         <v>615186059409.975</v>
       </c>
       <c r="H49">
+        <v>285397591466.808</v>
+      </c>
+      <c r="I49">
+        <v>82970520902.1288</v>
+      </c>
+      <c r="J49">
+        <v>81427460666.3</v>
+      </c>
+      <c r="K49">
+        <v>81427460666.3</v>
+      </c>
+      <c r="L49">
         <v>212562995272.36</v>
       </c>
-      <c r="I49">
+      <c r="M49">
         <v>407506208316.611</v>
       </c>
-      <c r="J49">
+      <c r="N49">
         <v>380211836665.34</v>
-      </c>
-      <c r="K49">
-        <v>285397591466.808</v>
-      </c>
-      <c r="L49">
-        <v>82970520902.1288</v>
-      </c>
-      <c r="M49">
-        <v>81427460666.3</v>
-      </c>
-      <c r="N49">
-        <v>81427460666.3</v>
       </c>
       <c r="O49">
         <v>1635086882331.72</v>
@@ -39194,25 +39194,25 @@
         <v>617046103924.256</v>
       </c>
       <c r="H50">
+        <v>293097236081.933</v>
+      </c>
+      <c r="I50">
+        <v>85346374391.73689</v>
+      </c>
+      <c r="J50">
+        <v>83734543791.4713</v>
+      </c>
+      <c r="K50">
+        <v>83734543791.4713</v>
+      </c>
+      <c r="L50">
         <v>214602912328</v>
       </c>
-      <c r="I50">
+      <c r="M50">
         <v>413709186291.466</v>
       </c>
-      <c r="J50">
+      <c r="N50">
         <v>383452207529.112</v>
-      </c>
-      <c r="K50">
-        <v>293097236081.933</v>
-      </c>
-      <c r="L50">
-        <v>85346374391.73689</v>
-      </c>
-      <c r="M50">
-        <v>83734543791.4713</v>
-      </c>
-      <c r="N50">
-        <v>83734543791.4713</v>
       </c>
       <c r="O50">
         <v>1658588905585.71</v>
@@ -39249,25 +39249,25 @@
         <v>624729436634.068</v>
       </c>
       <c r="H51">
+        <v>297418989181.205</v>
+      </c>
+      <c r="I51">
+        <v>85757931701.4861</v>
+      </c>
+      <c r="J51">
+        <v>85027054035.4995</v>
+      </c>
+      <c r="K51">
+        <v>85027054035.4995</v>
+      </c>
+      <c r="L51">
         <v>215950843041.725</v>
       </c>
-      <c r="I51">
+      <c r="M51">
         <v>417803757160.649</v>
       </c>
-      <c r="J51">
+      <c r="N51">
         <v>385815066059.142</v>
-      </c>
-      <c r="K51">
-        <v>297418989181.205</v>
-      </c>
-      <c r="L51">
-        <v>85757931701.4861</v>
-      </c>
-      <c r="M51">
-        <v>85027054035.4995</v>
-      </c>
-      <c r="N51">
-        <v>85027054035.4995</v>
       </c>
       <c r="O51">
         <v>1675308771555.05</v>
@@ -39304,25 +39304,25 @@
         <v>627586042563.499</v>
       </c>
       <c r="H52">
+        <v>299306694592.133</v>
+      </c>
+      <c r="I52">
+        <v>85987354999.0847</v>
+      </c>
+      <c r="J52">
+        <v>87074840623.8365</v>
+      </c>
+      <c r="K52">
+        <v>87074840623.8365</v>
+      </c>
+      <c r="L52">
         <v>216994198099.569</v>
       </c>
-      <c r="I52">
+      <c r="M52">
         <v>424750963707.06</v>
       </c>
-      <c r="J52">
+      <c r="N52">
         <v>387093024929.194</v>
-      </c>
-      <c r="K52">
-        <v>299306694592.133</v>
-      </c>
-      <c r="L52">
-        <v>85987354999.0847</v>
-      </c>
-      <c r="M52">
-        <v>87074840623.8365</v>
-      </c>
-      <c r="N52">
-        <v>87074840623.8365</v>
       </c>
       <c r="O52">
         <v>1689393663614.49</v>
@@ -39359,25 +39359,25 @@
         <v>628449249784.02</v>
       </c>
       <c r="H53">
+        <v>299001519882.98</v>
+      </c>
+      <c r="I53">
+        <v>86319343660.7023</v>
+      </c>
+      <c r="J53">
+        <v>86658007336.55209</v>
+      </c>
+      <c r="K53">
+        <v>86658007336.55209</v>
+      </c>
+      <c r="L53">
         <v>217608171794.045</v>
       </c>
-      <c r="I53">
+      <c r="M53">
         <v>424791277676.532</v>
       </c>
-      <c r="J53">
+      <c r="N53">
         <v>385583190441.643</v>
-      </c>
-      <c r="K53">
-        <v>299001519882.98</v>
-      </c>
-      <c r="L53">
-        <v>86319343660.7023</v>
-      </c>
-      <c r="M53">
-        <v>86658007336.55209</v>
-      </c>
-      <c r="N53">
-        <v>86658007336.55209</v>
       </c>
       <c r="O53">
         <v>1693978994745.57</v>
@@ -39414,25 +39414,25 @@
         <v>629792871782.5031</v>
       </c>
       <c r="H54">
+        <v>299755843607.784</v>
+      </c>
+      <c r="I54">
+        <v>85872280681.8154</v>
+      </c>
+      <c r="J54">
+        <v>89507308843.7003</v>
+      </c>
+      <c r="K54">
+        <v>89507308843.7003</v>
+      </c>
+      <c r="L54">
         <v>218823509449.926</v>
       </c>
-      <c r="I54">
+      <c r="M54">
         <v>424117813751.547</v>
       </c>
-      <c r="J54">
+      <c r="N54">
         <v>385964238471.55</v>
-      </c>
-      <c r="K54">
-        <v>299755843607.784</v>
-      </c>
-      <c r="L54">
-        <v>85872280681.8154</v>
-      </c>
-      <c r="M54">
-        <v>89507308843.7003</v>
-      </c>
-      <c r="N54">
-        <v>89507308843.7003</v>
       </c>
       <c r="O54">
         <v>1697945611980.6</v>
@@ -39469,25 +39469,25 @@
         <v>633337179773.764</v>
       </c>
       <c r="H55">
+        <v>300384362558.508</v>
+      </c>
+      <c r="I55">
+        <v>87503485104.2542</v>
+      </c>
+      <c r="J55">
+        <v>90526750916.44341</v>
+      </c>
+      <c r="K55">
+        <v>90526750916.44341</v>
+      </c>
+      <c r="L55">
         <v>220214762804.729</v>
       </c>
-      <c r="I55">
+      <c r="M55">
         <v>428857413875.328</v>
       </c>
-      <c r="J55">
+      <c r="N55">
         <v>386095178615.24</v>
-      </c>
-      <c r="K55">
-        <v>300384362558.508</v>
-      </c>
-      <c r="L55">
-        <v>87503485104.2542</v>
-      </c>
-      <c r="M55">
-        <v>90526750916.44341</v>
-      </c>
-      <c r="N55">
-        <v>90526750916.44341</v>
       </c>
       <c r="O55">
         <v>1706264522197.18</v>
@@ -39524,25 +39524,25 @@
         <v>638631186749.124</v>
       </c>
       <c r="H56">
+        <v>302019654953.556</v>
+      </c>
+      <c r="I56">
+        <v>89501930202.02251</v>
+      </c>
+      <c r="J56">
+        <v>91612133911.7009</v>
+      </c>
+      <c r="K56">
+        <v>91612133911.7009</v>
+      </c>
+      <c r="L56">
         <v>221157185143.062</v>
       </c>
-      <c r="I56">
+      <c r="M56">
         <v>429300265872.069</v>
       </c>
-      <c r="J56">
+      <c r="N56">
         <v>387975010867.307</v>
-      </c>
-      <c r="K56">
-        <v>302019654953.556</v>
-      </c>
-      <c r="L56">
-        <v>89501930202.02251</v>
-      </c>
-      <c r="M56">
-        <v>91612133911.7009</v>
-      </c>
-      <c r="N56">
-        <v>91612133911.7009</v>
       </c>
       <c r="O56">
         <v>1710506914846.92</v>
@@ -39602,37 +39602,37 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Atividades imobiliárias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Outras atividades de serviços</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Comércio</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Transporte, armazenagem e correio</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Informação e comunicação</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Atividades financeiras, de seguros e serviços relacionados</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -39676,25 +39676,25 @@
         <v>20659576.3533457</v>
       </c>
       <c r="H2">
+        <v>16951142.7769976</v>
+      </c>
+      <c r="I2">
+        <v>4126044.80809643</v>
+      </c>
+      <c r="J2">
+        <v>1226393.69863743</v>
+      </c>
+      <c r="K2">
+        <v>1219550.80015771</v>
+      </c>
+      <c r="L2">
         <v>523406.098672419</v>
       </c>
-      <c r="I2">
+      <c r="M2">
         <v>25574648.6393908</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <v>10616182.5794095</v>
-      </c>
-      <c r="K2">
-        <v>16951142.7769976</v>
-      </c>
-      <c r="L2">
-        <v>4126044.80809643</v>
-      </c>
-      <c r="M2">
-        <v>1226393.69863743</v>
-      </c>
-      <c r="N2">
-        <v>1219550.80015771</v>
       </c>
       <c r="O2">
         <v>60265570.0887747</v>
@@ -39731,25 +39731,25 @@
         <v>21090969.9374508</v>
       </c>
       <c r="H3">
+        <v>17117660.9315074</v>
+      </c>
+      <c r="I3">
+        <v>4165211.90394523</v>
+      </c>
+      <c r="J3">
+        <v>1289472.87385262</v>
+      </c>
+      <c r="K3">
+        <v>1268972.5149248</v>
+      </c>
+      <c r="L3">
         <v>553085.757046178</v>
       </c>
-      <c r="I3">
+      <c r="M3">
         <v>25407797.55579</v>
       </c>
-      <c r="J3">
+      <c r="N3">
         <v>10722395.5516146</v>
-      </c>
-      <c r="K3">
-        <v>17117660.9315074</v>
-      </c>
-      <c r="L3">
-        <v>4165211.90394523</v>
-      </c>
-      <c r="M3">
-        <v>1289472.87385262</v>
-      </c>
-      <c r="N3">
-        <v>1268972.5149248</v>
       </c>
       <c r="O3">
         <v>60481556.881957</v>
@@ -39786,25 +39786,25 @@
         <v>21248643.1798195</v>
       </c>
       <c r="H4">
+        <v>17091058.1268873</v>
+      </c>
+      <c r="I4">
+        <v>4290749.76149983</v>
+      </c>
+      <c r="J4">
+        <v>1295967.69645605</v>
+      </c>
+      <c r="K4">
+        <v>1274470.18763735</v>
+      </c>
+      <c r="L4">
         <v>552806.2918842071</v>
       </c>
-      <c r="I4">
+      <c r="M4">
         <v>25492483.9860168</v>
       </c>
-      <c r="J4">
+      <c r="N4">
         <v>10775864.2782025</v>
-      </c>
-      <c r="K4">
-        <v>17091058.1268873</v>
-      </c>
-      <c r="L4">
-        <v>4290749.76149983</v>
-      </c>
-      <c r="M4">
-        <v>1295967.69645605</v>
-      </c>
-      <c r="N4">
-        <v>1274470.18763735</v>
       </c>
       <c r="O4">
         <v>60872265.9536512</v>
@@ -39841,25 +39841,25 @@
         <v>21237555.4840948</v>
       </c>
       <c r="H5">
+        <v>17243596.9580886</v>
+      </c>
+      <c r="I5">
+        <v>4364860.94853833</v>
+      </c>
+      <c r="J5">
+        <v>1271142.14390721</v>
+      </c>
+      <c r="K5">
+        <v>1329646.77930227</v>
+      </c>
+      <c r="L5">
         <v>569102.6064779391</v>
       </c>
-      <c r="I5">
+      <c r="M5">
         <v>25556754.3776373</v>
       </c>
-      <c r="J5">
+      <c r="N5">
         <v>10603915.0990007</v>
-      </c>
-      <c r="K5">
-        <v>17243596.9580886</v>
-      </c>
-      <c r="L5">
-        <v>4364860.94853833</v>
-      </c>
-      <c r="M5">
-        <v>1271142.14390721</v>
-      </c>
-      <c r="N5">
-        <v>1329646.77930227</v>
       </c>
       <c r="O5">
         <v>60935130.776865</v>
@@ -39896,25 +39896,25 @@
         <v>21320628.9226897</v>
       </c>
       <c r="H6">
+        <v>17322119.2274578</v>
+      </c>
+      <c r="I6">
+        <v>4359469.28186737</v>
+      </c>
+      <c r="J6">
+        <v>1289734.98639672</v>
+      </c>
+      <c r="K6">
+        <v>1299735.95062161</v>
+      </c>
+      <c r="L6">
         <v>569791.164035844</v>
       </c>
-      <c r="I6">
+      <c r="M6">
         <v>25666953.7939646</v>
       </c>
-      <c r="J6">
+      <c r="N6">
         <v>10611120.4719241</v>
-      </c>
-      <c r="K6">
-        <v>17322119.2274578</v>
-      </c>
-      <c r="L6">
-        <v>4359469.28186737</v>
-      </c>
-      <c r="M6">
-        <v>1289734.98639672</v>
-      </c>
-      <c r="N6">
-        <v>1299735.95062161</v>
       </c>
       <c r="O6">
         <v>61182604.9844321</v>
@@ -39951,25 +39951,25 @@
         <v>21356747.9596826</v>
       </c>
       <c r="H7">
+        <v>17427910.3564868</v>
+      </c>
+      <c r="I7">
+        <v>4401247.07309149</v>
+      </c>
+      <c r="J7">
+        <v>1284010.83234687</v>
+      </c>
+      <c r="K7">
+        <v>1333226.67773756</v>
+      </c>
+      <c r="L7">
         <v>588881.368797048</v>
       </c>
-      <c r="I7">
+      <c r="M7">
         <v>25801735.3001011</v>
       </c>
-      <c r="J7">
+      <c r="N7">
         <v>10642699.813902</v>
-      </c>
-      <c r="K7">
-        <v>17427910.3564868</v>
-      </c>
-      <c r="L7">
-        <v>4401247.07309149</v>
-      </c>
-      <c r="M7">
-        <v>1284010.83234687</v>
-      </c>
-      <c r="N7">
-        <v>1333226.67773756</v>
       </c>
       <c r="O7">
         <v>61432783.0792561</v>
@@ -40006,25 +40006,25 @@
         <v>21341522.6936424</v>
       </c>
       <c r="H8">
+        <v>17780027.4141001</v>
+      </c>
+      <c r="I8">
+        <v>4385362.37769838</v>
+      </c>
+      <c r="J8">
+        <v>1287052.90965347</v>
+      </c>
+      <c r="K8">
+        <v>1306591.18210176</v>
+      </c>
+      <c r="L8">
         <v>603139.785336617</v>
       </c>
-      <c r="I8">
+      <c r="M8">
         <v>25868102.074248</v>
       </c>
-      <c r="J8">
+      <c r="N8">
         <v>10579184.795188</v>
-      </c>
-      <c r="K8">
-        <v>17780027.4141001</v>
-      </c>
-      <c r="L8">
-        <v>4385362.37769838</v>
-      </c>
-      <c r="M8">
-        <v>1287052.90965347</v>
-      </c>
-      <c r="N8">
-        <v>1306591.18210176</v>
       </c>
       <c r="O8">
         <v>61758840.0876468</v>
@@ -40061,25 +40061,25 @@
         <v>21312459.9140999</v>
       </c>
       <c r="H9">
+        <v>17813371.1905286</v>
+      </c>
+      <c r="I9">
+        <v>4267415.69673552</v>
+      </c>
+      <c r="J9">
+        <v>1314889.72896873</v>
+      </c>
+      <c r="K9">
+        <v>1299323.05266057</v>
+      </c>
+      <c r="L9">
         <v>546051.488859775</v>
       </c>
-      <c r="I9">
+      <c r="M9">
         <v>26208288.6733943</v>
       </c>
-      <c r="J9">
+      <c r="N9">
         <v>10629081.4833582</v>
-      </c>
-      <c r="K9">
-        <v>17813371.1905286</v>
-      </c>
-      <c r="L9">
-        <v>4267415.69673552</v>
-      </c>
-      <c r="M9">
-        <v>1314889.72896873</v>
-      </c>
-      <c r="N9">
-        <v>1299323.05266057</v>
       </c>
       <c r="O9">
         <v>62054437.1394697</v>
@@ -40116,25 +40116,25 @@
         <v>21733292.8090245</v>
       </c>
       <c r="H10">
+        <v>17952803.0743852</v>
+      </c>
+      <c r="I10">
+        <v>4276898.69684144</v>
+      </c>
+      <c r="J10">
+        <v>1334114.25960403</v>
+      </c>
+      <c r="K10">
+        <v>1321996.82949237</v>
+      </c>
+      <c r="L10">
         <v>543690.508338687</v>
       </c>
-      <c r="I10">
+      <c r="M10">
         <v>26462432.1194963</v>
       </c>
-      <c r="J10">
+      <c r="N10">
         <v>10789949.6408539</v>
-      </c>
-      <c r="K10">
-        <v>17952803.0743852</v>
-      </c>
-      <c r="L10">
-        <v>4276898.69684144</v>
-      </c>
-      <c r="M10">
-        <v>1334114.25960403</v>
-      </c>
-      <c r="N10">
-        <v>1321996.82949237</v>
       </c>
       <c r="O10">
         <v>62751459.1848207</v>
@@ -40171,25 +40171,25 @@
         <v>21419399.6276619</v>
       </c>
       <c r="H11">
+        <v>17845381.2221517</v>
+      </c>
+      <c r="I11">
+        <v>4312560.06350141</v>
+      </c>
+      <c r="J11">
+        <v>1312287.96843159</v>
+      </c>
+      <c r="K11">
+        <v>1301788.6728175</v>
+      </c>
+      <c r="L11">
         <v>532743.280920003</v>
       </c>
-      <c r="I11">
+      <c r="M11">
         <v>26842839.7112702</v>
       </c>
-      <c r="J11">
+      <c r="N11">
         <v>10736004.8851842</v>
-      </c>
-      <c r="K11">
-        <v>17845381.2221517</v>
-      </c>
-      <c r="L11">
-        <v>4312560.06350141</v>
-      </c>
-      <c r="M11">
-        <v>1312287.96843159</v>
-      </c>
-      <c r="N11">
-        <v>1301788.6728175</v>
       </c>
       <c r="O11">
         <v>62828082.2072136</v>
@@ -40226,25 +40226,25 @@
         <v>21447746.3283565</v>
       </c>
       <c r="H12">
+        <v>17684477.8291205</v>
+      </c>
+      <c r="I12">
+        <v>4272531.67908124</v>
+      </c>
+      <c r="J12">
+        <v>1299164.75103807</v>
+      </c>
+      <c r="K12">
+        <v>1366421.74495647</v>
+      </c>
+      <c r="L12">
         <v>554379.204467527</v>
       </c>
-      <c r="I12">
+      <c r="M12">
         <v>27260953.5028119</v>
       </c>
-      <c r="J12">
+      <c r="N12">
         <v>10752492.5337126</v>
-      </c>
-      <c r="K12">
-        <v>17684477.8291205</v>
-      </c>
-      <c r="L12">
-        <v>4272531.67908124</v>
-      </c>
-      <c r="M12">
-        <v>1299164.75103807</v>
-      </c>
-      <c r="N12">
-        <v>1366421.74495647</v>
       </c>
       <c r="O12">
         <v>63168668.3352119</v>
@@ -40281,25 +40281,25 @@
         <v>21451223.0504745</v>
       </c>
       <c r="H13">
+        <v>17777748.1521204</v>
+      </c>
+      <c r="I13">
+        <v>4311169.92976361</v>
+      </c>
+      <c r="J13">
+        <v>1319467.8923731</v>
+      </c>
+      <c r="K13">
+        <v>1334616.97751234</v>
+      </c>
+      <c r="L13">
         <v>619162.658956599</v>
       </c>
-      <c r="I13">
+      <c r="M13">
         <v>27372060.2344641</v>
       </c>
-      <c r="J13">
+      <c r="N13">
         <v>10846660.373387</v>
-      </c>
-      <c r="K13">
-        <v>17777748.1521204</v>
-      </c>
-      <c r="L13">
-        <v>4311169.92976361</v>
-      </c>
-      <c r="M13">
-        <v>1319467.8923731</v>
-      </c>
-      <c r="N13">
-        <v>1334616.97751234</v>
       </c>
       <c r="O13">
         <v>63518773.5660122</v>
@@ -40336,25 +40336,25 @@
         <v>21576360.7051937</v>
       </c>
       <c r="H14">
+        <v>17882497.0859434</v>
+      </c>
+      <c r="I14">
+        <v>4404119.61801795</v>
+      </c>
+      <c r="J14">
+        <v>1284929.01365306</v>
+      </c>
+      <c r="K14">
+        <v>1287948.36990242</v>
+      </c>
+      <c r="L14">
         <v>580273.489530907</v>
       </c>
-      <c r="I14">
+      <c r="M14">
         <v>27200894.0094121</v>
       </c>
-      <c r="J14">
+      <c r="N14">
         <v>10867341.0941509</v>
-      </c>
-      <c r="K14">
-        <v>17882497.0859434</v>
-      </c>
-      <c r="L14">
-        <v>4404119.61801795</v>
-      </c>
-      <c r="M14">
-        <v>1284929.01365306</v>
-      </c>
-      <c r="N14">
-        <v>1287948.36990242</v>
       </c>
       <c r="O14">
         <v>63595394.646793</v>
@@ -40391,25 +40391,25 @@
         <v>20743410.1237035</v>
       </c>
       <c r="H15">
+        <v>18034030.1728388</v>
+      </c>
+      <c r="I15">
+        <v>4356247.42536909</v>
+      </c>
+      <c r="J15">
+        <v>1300888.90254037</v>
+      </c>
+      <c r="K15">
+        <v>1285933.39806588</v>
+      </c>
+      <c r="L15">
         <v>611900.845687682</v>
       </c>
-      <c r="I15">
+      <c r="M15">
         <v>27700628.3378806</v>
       </c>
-      <c r="J15">
+      <c r="N15">
         <v>10788223.72297</v>
-      </c>
-      <c r="K15">
-        <v>18034030.1728388</v>
-      </c>
-      <c r="L15">
-        <v>4356247.42536909</v>
-      </c>
-      <c r="M15">
-        <v>1300888.90254037</v>
-      </c>
-      <c r="N15">
-        <v>1285933.39806588</v>
       </c>
       <c r="O15">
         <v>64034002.1014564</v>
@@ -40446,25 +40446,25 @@
         <v>20649703.075096</v>
       </c>
       <c r="H16">
+        <v>18092504.5938858</v>
+      </c>
+      <c r="I16">
+        <v>4397096.56821396</v>
+      </c>
+      <c r="J16">
+        <v>1353460.68027136</v>
+      </c>
+      <c r="K16">
+        <v>1217208.05478462</v>
+      </c>
+      <c r="L16">
         <v>595263.8400161701</v>
       </c>
-      <c r="I16">
+      <c r="M16">
         <v>27556106.3705744</v>
       </c>
-      <c r="J16">
+      <c r="N16">
         <v>10817394.5620818</v>
-      </c>
-      <c r="K16">
-        <v>18092504.5938858</v>
-      </c>
-      <c r="L16">
-        <v>4397096.56821396</v>
-      </c>
-      <c r="M16">
-        <v>1353460.68027136</v>
-      </c>
-      <c r="N16">
-        <v>1217208.05478462</v>
       </c>
       <c r="O16">
         <v>64004686.9138405</v>
@@ -40501,25 +40501,25 @@
         <v>20468040.7935806</v>
       </c>
       <c r="H17">
+        <v>17893480.3986572</v>
+      </c>
+      <c r="I17">
+        <v>4522921.74759182</v>
+      </c>
+      <c r="J17">
+        <v>1235496.77489789</v>
+      </c>
+      <c r="K17">
+        <v>1197891.25485556</v>
+      </c>
+      <c r="L17">
         <v>576787.44308706</v>
       </c>
-      <c r="I17">
+      <c r="M17">
         <v>27545378.5018038</v>
       </c>
-      <c r="J17">
+      <c r="N17">
         <v>10781970.6339382</v>
-      </c>
-      <c r="K17">
-        <v>17893480.3986572</v>
-      </c>
-      <c r="L17">
-        <v>4522921.74759182</v>
-      </c>
-      <c r="M17">
-        <v>1235496.77489789</v>
-      </c>
-      <c r="N17">
-        <v>1197891.25485556</v>
       </c>
       <c r="O17">
         <v>63653335.8310197</v>
@@ -40556,25 +40556,25 @@
         <v>19886832.8173539</v>
       </c>
       <c r="H18">
+        <v>17843872.965623</v>
+      </c>
+      <c r="I18">
+        <v>4503590.25525543</v>
+      </c>
+      <c r="J18">
+        <v>1217428.84591505</v>
+      </c>
+      <c r="K18">
+        <v>1244380.21518025</v>
+      </c>
+      <c r="L18">
         <v>569677.053615722</v>
       </c>
-      <c r="I18">
+      <c r="M18">
         <v>27576286.2211536</v>
       </c>
-      <c r="J18">
+      <c r="N18">
         <v>10663924.7714425</v>
-      </c>
-      <c r="K18">
-        <v>17843872.965623</v>
-      </c>
-      <c r="L18">
-        <v>4503590.25525543</v>
-      </c>
-      <c r="M18">
-        <v>1217428.84591505</v>
-      </c>
-      <c r="N18">
-        <v>1244380.21518025</v>
       </c>
       <c r="O18">
         <v>63730544.2579042</v>
@@ -40611,25 +40611,25 @@
         <v>19412486.1355341</v>
       </c>
       <c r="H19">
+        <v>17741152.378136</v>
+      </c>
+      <c r="I19">
+        <v>4523167.246389</v>
+      </c>
+      <c r="J19">
+        <v>1231499.26440769</v>
+      </c>
+      <c r="K19">
+        <v>1207431.95800479</v>
+      </c>
+      <c r="L19">
         <v>539443.759395193</v>
       </c>
-      <c r="I19">
+      <c r="M19">
         <v>27617377.6613477</v>
       </c>
-      <c r="J19">
+      <c r="N19">
         <v>10679407.6964562</v>
-      </c>
-      <c r="K19">
-        <v>17741152.378136</v>
-      </c>
-      <c r="L19">
-        <v>4523167.246389</v>
-      </c>
-      <c r="M19">
-        <v>1231499.26440769</v>
-      </c>
-      <c r="N19">
-        <v>1207431.95800479</v>
       </c>
       <c r="O19">
         <v>63484162.7358348</v>
@@ -40666,25 +40666,25 @@
         <v>18923491.8590408</v>
       </c>
       <c r="H20">
+        <v>17379272.9747188</v>
+      </c>
+      <c r="I20">
+        <v>4583335.24539911</v>
+      </c>
+      <c r="J20">
+        <v>1237360.87525679</v>
+      </c>
+      <c r="K20">
+        <v>1226563.73317635</v>
+      </c>
+      <c r="L20">
         <v>530561.940666915</v>
       </c>
-      <c r="I20">
+      <c r="M20">
         <v>27511121.319138</v>
       </c>
-      <c r="J20">
+      <c r="N20">
         <v>10669249.4342907</v>
-      </c>
-      <c r="K20">
-        <v>17379272.9747188</v>
-      </c>
-      <c r="L20">
-        <v>4583335.24539911</v>
-      </c>
-      <c r="M20">
-        <v>1237360.87525679</v>
-      </c>
-      <c r="N20">
-        <v>1226563.73317635</v>
       </c>
       <c r="O20">
         <v>63091409.9798459</v>
@@ -40721,25 +40721,25 @@
         <v>18511392.1842752</v>
       </c>
       <c r="H21">
+        <v>17677886.8930759</v>
+      </c>
+      <c r="I21">
+        <v>4608291.20909879</v>
+      </c>
+      <c r="J21">
+        <v>1256656.45801725</v>
+      </c>
+      <c r="K21">
+        <v>1253711.10022423</v>
+      </c>
+      <c r="L21">
         <v>576155.060255614</v>
       </c>
-      <c r="I21">
+      <c r="M21">
         <v>27400342.8921747</v>
       </c>
-      <c r="J21">
+      <c r="N21">
         <v>10591719.7786223</v>
-      </c>
-      <c r="K21">
-        <v>17677886.8930759</v>
-      </c>
-      <c r="L21">
-        <v>4608291.20909879</v>
-      </c>
-      <c r="M21">
-        <v>1256656.45801725</v>
-      </c>
-      <c r="N21">
-        <v>1253711.10022423</v>
       </c>
       <c r="O21">
         <v>63415213.5507181</v>
@@ -40776,25 +40776,25 @@
         <v>18773526.989369</v>
       </c>
       <c r="H22">
+        <v>17505010.016458</v>
+      </c>
+      <c r="I22">
+        <v>4569726.31568632</v>
+      </c>
+      <c r="J22">
+        <v>1263113.01560002</v>
+      </c>
+      <c r="K22">
+        <v>1265259.96455566</v>
+      </c>
+      <c r="L22">
         <v>591767.851043044</v>
       </c>
-      <c r="I22">
+      <c r="M22">
         <v>27904212.213944</v>
       </c>
-      <c r="J22">
+      <c r="N22">
         <v>10489701.3328623</v>
-      </c>
-      <c r="K22">
-        <v>17505010.016458</v>
-      </c>
-      <c r="L22">
-        <v>4569726.31568632</v>
-      </c>
-      <c r="M22">
-        <v>1263113.01560002</v>
-      </c>
-      <c r="N22">
-        <v>1265259.96455566</v>
       </c>
       <c r="O22">
         <v>63602958.3790649</v>
@@ -40831,25 +40831,25 @@
         <v>18850263.209484</v>
       </c>
       <c r="H23">
+        <v>17737676.5392401</v>
+      </c>
+      <c r="I23">
+        <v>4667560.08960727</v>
+      </c>
+      <c r="J23">
+        <v>1255586.65445623</v>
+      </c>
+      <c r="K23">
+        <v>1200531.33640502</v>
+      </c>
+      <c r="L23">
         <v>558628.757224738</v>
       </c>
-      <c r="I23">
+      <c r="M23">
         <v>28345917.856871</v>
       </c>
-      <c r="J23">
+      <c r="N23">
         <v>10634716.3628547</v>
-      </c>
-      <c r="K23">
-        <v>17737676.5392401</v>
-      </c>
-      <c r="L23">
-        <v>4667560.08960727</v>
-      </c>
-      <c r="M23">
-        <v>1255586.65445623</v>
-      </c>
-      <c r="N23">
-        <v>1200531.33640502</v>
       </c>
       <c r="O23">
         <v>64361170.6256325</v>
@@ -40886,25 +40886,25 @@
         <v>18937951.2036995</v>
       </c>
       <c r="H24">
+        <v>17862923.1543947</v>
+      </c>
+      <c r="I24">
+        <v>4724397.79622807</v>
+      </c>
+      <c r="J24">
+        <v>1269801.21938148</v>
+      </c>
+      <c r="K24">
+        <v>1254436.61539316</v>
+      </c>
+      <c r="L24">
         <v>577748.122908899</v>
       </c>
-      <c r="I24">
+      <c r="M24">
         <v>28689143.0783535</v>
       </c>
-      <c r="J24">
+      <c r="N24">
         <v>10688910.5983022</v>
-      </c>
-      <c r="K24">
-        <v>17862923.1543947</v>
-      </c>
-      <c r="L24">
-        <v>4724397.79622807</v>
-      </c>
-      <c r="M24">
-        <v>1269801.21938148</v>
-      </c>
-      <c r="N24">
-        <v>1254436.61539316</v>
       </c>
       <c r="O24">
         <v>65138170.4279773</v>
@@ -40941,25 +40941,25 @@
         <v>18985319.6636112</v>
       </c>
       <c r="H25">
+        <v>17985796.7657274</v>
+      </c>
+      <c r="I25">
+        <v>4585830.07260005</v>
+      </c>
+      <c r="J25">
+        <v>1219945.34809755</v>
+      </c>
+      <c r="K25">
+        <v>1263602.79058951</v>
+      </c>
+      <c r="L25">
         <v>558056.184040283</v>
       </c>
-      <c r="I25">
+      <c r="M25">
         <v>29090030.8189911</v>
       </c>
-      <c r="J25">
+      <c r="N25">
         <v>10808327.1165763</v>
-      </c>
-      <c r="K25">
-        <v>17985796.7657274</v>
-      </c>
-      <c r="L25">
-        <v>4585830.07260005</v>
-      </c>
-      <c r="M25">
-        <v>1219945.34809755</v>
-      </c>
-      <c r="N25">
-        <v>1263602.79058951</v>
       </c>
       <c r="O25">
         <v>65581956.6749989</v>
@@ -40996,25 +40996,25 @@
         <v>18786695.9770477</v>
       </c>
       <c r="H26">
+        <v>17942129.8992399</v>
+      </c>
+      <c r="I26">
+        <v>4736227.6142679</v>
+      </c>
+      <c r="J26">
+        <v>1237682.34761247</v>
+      </c>
+      <c r="K26">
+        <v>1239285.80170869</v>
+      </c>
+      <c r="L26">
         <v>559202.167311094</v>
       </c>
-      <c r="I26">
+      <c r="M26">
         <v>29484210.6103324</v>
       </c>
-      <c r="J26">
+      <c r="N26">
         <v>10855010.6282756</v>
-      </c>
-      <c r="K26">
-        <v>17942129.8992399</v>
-      </c>
-      <c r="L26">
-        <v>4736227.6142679</v>
-      </c>
-      <c r="M26">
-        <v>1237682.34761247</v>
-      </c>
-      <c r="N26">
-        <v>1239285.80170869</v>
       </c>
       <c r="O26">
         <v>66058517.8046902</v>
@@ -41051,25 +41051,25 @@
         <v>18851989.4687904</v>
       </c>
       <c r="H27">
+        <v>17836877.0932995</v>
+      </c>
+      <c r="I27">
+        <v>4741820.52570486</v>
+      </c>
+      <c r="J27">
+        <v>1236902.95262919</v>
+      </c>
+      <c r="K27">
+        <v>1251337.43350371</v>
+      </c>
+      <c r="L27">
         <v>588817.71504436</v>
       </c>
-      <c r="I27">
+      <c r="M27">
         <v>29403976.885699</v>
       </c>
-      <c r="J27">
+      <c r="N27">
         <v>10852996.6948479</v>
-      </c>
-      <c r="K27">
-        <v>17836877.0932995</v>
-      </c>
-      <c r="L27">
-        <v>4741820.52570486</v>
-      </c>
-      <c r="M27">
-        <v>1236902.95262919</v>
-      </c>
-      <c r="N27">
-        <v>1251337.43350371</v>
       </c>
       <c r="O27">
         <v>65897385.1912259</v>
@@ -41106,25 +41106,25 @@
         <v>18930072.2289771</v>
       </c>
       <c r="H28">
+        <v>17957636.5205169</v>
+      </c>
+      <c r="I28">
+        <v>4747605.70074746</v>
+      </c>
+      <c r="J28">
+        <v>1269436.61513546</v>
+      </c>
+      <c r="K28">
+        <v>1269915.54576248</v>
+      </c>
+      <c r="L28">
         <v>596871.7580676971</v>
       </c>
-      <c r="I28">
+      <c r="M28">
         <v>29775990.535302</v>
       </c>
-      <c r="J28">
+      <c r="N28">
         <v>10924858.693294</v>
-      </c>
-      <c r="K28">
-        <v>17957636.5205169</v>
-      </c>
-      <c r="L28">
-        <v>4747605.70074746</v>
-      </c>
-      <c r="M28">
-        <v>1269436.61513546</v>
-      </c>
-      <c r="N28">
-        <v>1269915.54576248</v>
       </c>
       <c r="O28">
         <v>66574439.7728216</v>
@@ -41161,25 +41161,25 @@
         <v>18792691.2720155</v>
       </c>
       <c r="H29">
+        <v>17944145.737936</v>
+      </c>
+      <c r="I29">
+        <v>4854144.68474681</v>
+      </c>
+      <c r="J29">
+        <v>1311574.09547054</v>
+      </c>
+      <c r="K29">
+        <v>1255620.19426801</v>
+      </c>
+      <c r="L29">
         <v>584725.037313245</v>
       </c>
-      <c r="I29">
+      <c r="M29">
         <v>30170876.0256255</v>
       </c>
-      <c r="J29">
+      <c r="N29">
         <v>10979653.342727</v>
-      </c>
-      <c r="K29">
-        <v>17944145.737936</v>
-      </c>
-      <c r="L29">
-        <v>4854144.68474681</v>
-      </c>
-      <c r="M29">
-        <v>1311574.09547054</v>
-      </c>
-      <c r="N29">
-        <v>1255620.19426801</v>
       </c>
       <c r="O29">
         <v>67052697.9566367</v>
@@ -41216,25 +41216,25 @@
         <v>18901675.2714847</v>
       </c>
       <c r="H30">
+        <v>18131639.5871101</v>
+      </c>
+      <c r="I30">
+        <v>4944015.54098047</v>
+      </c>
+      <c r="J30">
+        <v>1333557.41344423</v>
+      </c>
+      <c r="K30">
+        <v>1277775.34229025</v>
+      </c>
+      <c r="L30">
         <v>589198.866460145</v>
       </c>
-      <c r="I30">
+      <c r="M30">
         <v>30327142.1542751</v>
       </c>
-      <c r="J30">
+      <c r="N30">
         <v>11003839.8030153</v>
-      </c>
-      <c r="K30">
-        <v>18131639.5871101</v>
-      </c>
-      <c r="L30">
-        <v>4944015.54098047</v>
-      </c>
-      <c r="M30">
-        <v>1333557.41344423</v>
-      </c>
-      <c r="N30">
-        <v>1277775.34229025</v>
       </c>
       <c r="O30">
         <v>67719647.36529</v>
@@ -41271,25 +41271,25 @@
         <v>19114725.3321689</v>
       </c>
       <c r="H31">
+        <v>18084481.7785028</v>
+      </c>
+      <c r="I31">
+        <v>5008747.57162123</v>
+      </c>
+      <c r="J31">
+        <v>1328907.12317759</v>
+      </c>
+      <c r="K31">
+        <v>1318182.52892508</v>
+      </c>
+      <c r="L31">
         <v>597500.694114874</v>
       </c>
-      <c r="I31">
+      <c r="M31">
         <v>30864286.4374065</v>
       </c>
-      <c r="J31">
+      <c r="N31">
         <v>10949504.1603574</v>
-      </c>
-      <c r="K31">
-        <v>18084481.7785028</v>
-      </c>
-      <c r="L31">
-        <v>5008747.57162123</v>
-      </c>
-      <c r="M31">
-        <v>1328907.12317759</v>
-      </c>
-      <c r="N31">
-        <v>1318182.52892508</v>
       </c>
       <c r="O31">
         <v>68191261.16364001</v>
@@ -41326,25 +41326,25 @@
         <v>19288604.2736199</v>
       </c>
       <c r="H32">
+        <v>18170392.1735457</v>
+      </c>
+      <c r="I32">
+        <v>5052934.1053877</v>
+      </c>
+      <c r="J32">
+        <v>1338453.45933326</v>
+      </c>
+      <c r="K32">
+        <v>1300750.688587</v>
+      </c>
+      <c r="L32">
         <v>585801.5608821081</v>
       </c>
-      <c r="I32">
+      <c r="M32">
         <v>30966222.67993</v>
       </c>
-      <c r="J32">
+      <c r="N32">
         <v>10965397.8987257</v>
-      </c>
-      <c r="K32">
-        <v>18170392.1735457</v>
-      </c>
-      <c r="L32">
-        <v>5052934.1053877</v>
-      </c>
-      <c r="M32">
-        <v>1338453.45933326</v>
-      </c>
-      <c r="N32">
-        <v>1300750.688587</v>
       </c>
       <c r="O32">
         <v>68209037.91995139</v>
@@ -41381,25 +41381,25 @@
         <v>19218692.5090613</v>
       </c>
       <c r="H33">
+        <v>18184996.8570288</v>
+      </c>
+      <c r="I33">
+        <v>5017108.51621763</v>
+      </c>
+      <c r="J33">
+        <v>1382541.6954084</v>
+      </c>
+      <c r="K33">
+        <v>1260970.53115044</v>
+      </c>
+      <c r="L33">
         <v>578043.612565306</v>
       </c>
-      <c r="I33">
+      <c r="M33">
         <v>30988986.8567683</v>
       </c>
-      <c r="J33">
+      <c r="N33">
         <v>11041515.1912586</v>
-      </c>
-      <c r="K33">
-        <v>18184996.8570288</v>
-      </c>
-      <c r="L33">
-        <v>5017108.51621763</v>
-      </c>
-      <c r="M33">
-        <v>1382541.6954084</v>
-      </c>
-      <c r="N33">
-        <v>1260970.53115044</v>
       </c>
       <c r="O33">
         <v>68433201.2184961</v>
@@ -41436,25 +41436,25 @@
         <v>18949190.5306156</v>
       </c>
       <c r="H34">
+        <v>17952392.2445475</v>
+      </c>
+      <c r="I34">
+        <v>4964944.67755548</v>
+      </c>
+      <c r="J34">
+        <v>1420023.30476986</v>
+      </c>
+      <c r="K34">
+        <v>1256473.36807506</v>
+      </c>
+      <c r="L34">
         <v>562032.9320318199</v>
       </c>
-      <c r="I34">
+      <c r="M34">
         <v>30661766.3034127</v>
       </c>
-      <c r="J34">
+      <c r="N34">
         <v>11262436.3400438</v>
-      </c>
-      <c r="K34">
-        <v>17952392.2445475</v>
-      </c>
-      <c r="L34">
-        <v>4964944.67755548</v>
-      </c>
-      <c r="M34">
-        <v>1420023.30476986</v>
-      </c>
-      <c r="N34">
-        <v>1256473.36807506</v>
       </c>
       <c r="O34">
         <v>68127157.7981925</v>
@@ -41491,25 +41491,25 @@
         <v>16603091.7249511</v>
       </c>
       <c r="H35">
+        <v>15687823.109982</v>
+      </c>
+      <c r="I35">
+        <v>4443617.41671727</v>
+      </c>
+      <c r="J35">
+        <v>1351135.59162174</v>
+      </c>
+      <c r="K35">
+        <v>1234144.33269609</v>
+      </c>
+      <c r="L35">
         <v>535248.9720877199</v>
       </c>
-      <c r="I35">
+      <c r="M35">
         <v>25718993.5085489</v>
       </c>
-      <c r="J35">
+      <c r="N35">
         <v>11398065.2696748</v>
-      </c>
-      <c r="K35">
-        <v>15687823.109982</v>
-      </c>
-      <c r="L35">
-        <v>4443617.41671727</v>
-      </c>
-      <c r="M35">
-        <v>1351135.59162174</v>
-      </c>
-      <c r="N35">
-        <v>1234144.33269609</v>
       </c>
       <c r="O35">
         <v>60431902.3860825</v>
@@ -41546,25 +41546,25 @@
         <v>16855996.1622296</v>
       </c>
       <c r="H36">
+        <v>15763393.0904358</v>
+      </c>
+      <c r="I36">
+        <v>4285643.12213893</v>
+      </c>
+      <c r="J36">
+        <v>1430265.17809408</v>
+      </c>
+      <c r="K36">
+        <v>1203693.07564693</v>
+      </c>
+      <c r="L36">
         <v>579138.8693015761</v>
       </c>
-      <c r="I36">
+      <c r="M36">
         <v>24800171.6810076</v>
       </c>
-      <c r="J36">
+      <c r="N36">
         <v>10822642.922282</v>
-      </c>
-      <c r="K36">
-        <v>15763393.0904358</v>
-      </c>
-      <c r="L36">
-        <v>4285643.12213893</v>
-      </c>
-      <c r="M36">
-        <v>1430265.17809408</v>
-      </c>
-      <c r="N36">
-        <v>1203693.07564693</v>
       </c>
       <c r="O36">
         <v>58723949.3875384</v>
@@ -41601,25 +41601,25 @@
         <v>17388002.5777577</v>
       </c>
       <c r="H37">
+        <v>16201491.5653976</v>
+      </c>
+      <c r="I37">
+        <v>4404671.30596352</v>
+      </c>
+      <c r="J37">
+        <v>1427527.64071968</v>
+      </c>
+      <c r="K37">
+        <v>1344495.12695506</v>
+      </c>
+      <c r="L37">
         <v>529614.8396141391</v>
       </c>
-      <c r="I37">
+      <c r="M37">
         <v>26006267.6643859</v>
       </c>
-      <c r="J37">
+      <c r="N37">
         <v>11273787.7225208</v>
-      </c>
-      <c r="K37">
-        <v>16201491.5653976</v>
-      </c>
-      <c r="L37">
-        <v>4404671.30596352</v>
-      </c>
-      <c r="M37">
-        <v>1427527.64071968</v>
-      </c>
-      <c r="N37">
-        <v>1344495.12695506</v>
       </c>
       <c r="O37">
         <v>61156707.9553464</v>
@@ -41656,25 +41656,25 @@
         <v>17935317.8077751</v>
       </c>
       <c r="H38">
+        <v>16495823.8329928</v>
+      </c>
+      <c r="I38">
+        <v>4533828.2284433</v>
+      </c>
+      <c r="J38">
+        <v>1475892.44547878</v>
+      </c>
+      <c r="K38">
+        <v>1348225.3064507</v>
+      </c>
+      <c r="L38">
         <v>600796.697508966</v>
       </c>
-      <c r="I38">
+      <c r="M38">
         <v>26671199.5320878</v>
       </c>
-      <c r="J38">
+      <c r="N38">
         <v>11305651.9291921</v>
-      </c>
-      <c r="K38">
-        <v>16495823.8329928</v>
-      </c>
-      <c r="L38">
-        <v>4533828.2284433</v>
-      </c>
-      <c r="M38">
-        <v>1475892.44547878</v>
-      </c>
-      <c r="N38">
-        <v>1348225.3064507</v>
       </c>
       <c r="O38">
         <v>62487836.7557047</v>
@@ -41711,25 +41711,25 @@
         <v>18190140.2886766</v>
       </c>
       <c r="H39">
+        <v>16667682.4588009</v>
+      </c>
+      <c r="I39">
+        <v>4675780.8733016</v>
+      </c>
+      <c r="J39">
+        <v>1583637.30091329</v>
+      </c>
+      <c r="K39">
+        <v>1356569.43346114</v>
+      </c>
+      <c r="L39">
         <v>568945.841470971</v>
       </c>
-      <c r="I39">
+      <c r="M39">
         <v>27439959.9724894</v>
       </c>
-      <c r="J39">
+      <c r="N39">
         <v>10941377.030384</v>
-      </c>
-      <c r="K39">
-        <v>16667682.4588009</v>
-      </c>
-      <c r="L39">
-        <v>4675780.8733016</v>
-      </c>
-      <c r="M39">
-        <v>1583637.30091329</v>
-      </c>
-      <c r="N39">
-        <v>1356569.43346114</v>
       </c>
       <c r="O39">
         <v>63306485.9310963</v>
@@ -41766,25 +41766,25 @@
         <v>19297254.2882928</v>
       </c>
       <c r="H40">
+        <v>17891755.8230495</v>
+      </c>
+      <c r="I40">
+        <v>4840395.68296194</v>
+      </c>
+      <c r="J40">
+        <v>1542087.29529403</v>
+      </c>
+      <c r="K40">
+        <v>1345385.92300966</v>
+      </c>
+      <c r="L40">
         <v>599368.940274547</v>
       </c>
-      <c r="I40">
+      <c r="M40">
         <v>28605579.0054034</v>
       </c>
-      <c r="J40">
+      <c r="N40">
         <v>10617536.9030144</v>
-      </c>
-      <c r="K40">
-        <v>17891755.8230495</v>
-      </c>
-      <c r="L40">
-        <v>4840395.68296194</v>
-      </c>
-      <c r="M40">
-        <v>1542087.29529403</v>
-      </c>
-      <c r="N40">
-        <v>1345385.92300966</v>
       </c>
       <c r="O40">
         <v>65297195.8375225</v>
@@ -41821,25 +41821,25 @@
         <v>19519800.8236551</v>
       </c>
       <c r="H41">
+        <v>18216816.3983856</v>
+      </c>
+      <c r="I41">
+        <v>4865535.49125814</v>
+      </c>
+      <c r="J41">
+        <v>1691759.01460919</v>
+      </c>
+      <c r="K41">
+        <v>1404185.51480844</v>
+      </c>
+      <c r="L41">
         <v>596499.1230785199</v>
       </c>
-      <c r="I41">
+      <c r="M41">
         <v>29752784.2625108</v>
       </c>
-      <c r="J41">
+      <c r="N41">
         <v>10933164.0695314</v>
-      </c>
-      <c r="K41">
-        <v>18216816.3983856</v>
-      </c>
-      <c r="L41">
-        <v>4865535.49125814</v>
-      </c>
-      <c r="M41">
-        <v>1691759.01460919</v>
-      </c>
-      <c r="N41">
-        <v>1404185.51480844</v>
       </c>
       <c r="O41">
         <v>67401961.8160581</v>
@@ -41876,25 +41876,25 @@
         <v>19629721.6276589</v>
       </c>
       <c r="H42">
+        <v>18477106.8891996</v>
+      </c>
+      <c r="I42">
+        <v>5022030.31849784</v>
+      </c>
+      <c r="J42">
+        <v>1635160.26851615</v>
+      </c>
+      <c r="K42">
+        <v>1408130.25556317</v>
+      </c>
+      <c r="L42">
         <v>603856.497522323</v>
       </c>
-      <c r="I42">
+      <c r="M42">
         <v>30392945.3725697</v>
       </c>
-      <c r="J42">
+      <c r="N42">
         <v>11117614.3611073</v>
-      </c>
-      <c r="K42">
-        <v>18477106.8891996</v>
-      </c>
-      <c r="L42">
-        <v>5022030.31849784</v>
-      </c>
-      <c r="M42">
-        <v>1635160.26851615</v>
-      </c>
-      <c r="N42">
-        <v>1408130.25556317</v>
       </c>
       <c r="O42">
         <v>68725022.4384196</v>
@@ -41931,25 +41931,25 @@
         <v>20104869.2117003</v>
       </c>
       <c r="H43">
+        <v>19017165.5435924</v>
+      </c>
+      <c r="I43">
+        <v>5169709.37275897</v>
+      </c>
+      <c r="J43">
+        <v>1783205.77321407</v>
+      </c>
+      <c r="K43">
+        <v>1472660.33334858</v>
+      </c>
+      <c r="L43">
         <v>665082.642163678</v>
       </c>
-      <c r="I43">
+      <c r="M43">
         <v>31073925.1098813</v>
       </c>
-      <c r="J43">
+      <c r="N43">
         <v>11279813.7091826</v>
-      </c>
-      <c r="K43">
-        <v>19017165.5435924</v>
-      </c>
-      <c r="L43">
-        <v>5169709.37275897</v>
-      </c>
-      <c r="M43">
-        <v>1783205.77321407</v>
-      </c>
-      <c r="N43">
-        <v>1472660.33334858</v>
       </c>
       <c r="O43">
         <v>70524600.52057479</v>
@@ -41986,25 +41986,25 @@
         <v>19994591.9717066</v>
       </c>
       <c r="H44">
+        <v>19254627.9358992</v>
+      </c>
+      <c r="I44">
+        <v>5298458.65979789</v>
+      </c>
+      <c r="J44">
+        <v>1697057.29089906</v>
+      </c>
+      <c r="K44">
+        <v>1518486.42004113</v>
+      </c>
+      <c r="L44">
         <v>666505.022986312</v>
       </c>
-      <c r="I44">
+      <c r="M44">
         <v>31472638.2595426</v>
       </c>
-      <c r="J44">
+      <c r="N44">
         <v>11570208.119012</v>
-      </c>
-      <c r="K44">
-        <v>19254627.9358992</v>
-      </c>
-      <c r="L44">
-        <v>5298458.65979789</v>
-      </c>
-      <c r="M44">
-        <v>1697057.29089906</v>
-      </c>
-      <c r="N44">
-        <v>1518486.42004113</v>
       </c>
       <c r="O44">
         <v>71378116.89511991</v>
@@ -42041,25 +42041,25 @@
         <v>19828381.4961064</v>
       </c>
       <c r="H45">
+        <v>18995006.3079807</v>
+      </c>
+      <c r="I45">
+        <v>5335709.46065974</v>
+      </c>
+      <c r="J45">
+        <v>1652999.09427369</v>
+      </c>
+      <c r="K45">
+        <v>1560090.69040179</v>
+      </c>
+      <c r="L45">
         <v>665037.255065436</v>
       </c>
-      <c r="I45">
+      <c r="M45">
         <v>31324865.6755407</v>
       </c>
-      <c r="J45">
+      <c r="N45">
         <v>11670672.6463675</v>
-      </c>
-      <c r="K45">
-        <v>18995006.3079807</v>
-      </c>
-      <c r="L45">
-        <v>5335709.46065974</v>
-      </c>
-      <c r="M45">
-        <v>1652999.09427369</v>
-      </c>
-      <c r="N45">
-        <v>1560090.69040179</v>
       </c>
       <c r="O45">
         <v>71294541.45601819</v>
@@ -42096,25 +42096,25 @@
         <v>19831768.7232548</v>
       </c>
       <c r="H46">
+        <v>19033030.3409656</v>
+      </c>
+      <c r="I46">
+        <v>5411431.08697296</v>
+      </c>
+      <c r="J46">
+        <v>1706213.39625611</v>
+      </c>
+      <c r="K46">
+        <v>1562263.27862626</v>
+      </c>
+      <c r="L46">
         <v>664328.131992612</v>
       </c>
-      <c r="I46">
+      <c r="M46">
         <v>31699242.803851</v>
       </c>
-      <c r="J46">
+      <c r="N46">
         <v>11638833.236205</v>
-      </c>
-      <c r="K46">
-        <v>19033030.3409656</v>
-      </c>
-      <c r="L46">
-        <v>5411431.08697296</v>
-      </c>
-      <c r="M46">
-        <v>1706213.39625611</v>
-      </c>
-      <c r="N46">
-        <v>1562263.27862626</v>
       </c>
       <c r="O46">
         <v>71608813.3561386</v>
@@ -42151,25 +42151,25 @@
         <v>19792840.5143389</v>
       </c>
       <c r="H47">
+        <v>18813673.5546832</v>
+      </c>
+      <c r="I47">
+        <v>5388995.60957964</v>
+      </c>
+      <c r="J47">
+        <v>1691403.86837373</v>
+      </c>
+      <c r="K47">
+        <v>1528068.5353158</v>
+      </c>
+      <c r="L47">
         <v>676582.95829757</v>
       </c>
-      <c r="I47">
+      <c r="M47">
         <v>31988334.7467215</v>
       </c>
-      <c r="J47">
+      <c r="N47">
         <v>11606200.6895701</v>
-      </c>
-      <c r="K47">
-        <v>18813673.5546832</v>
-      </c>
-      <c r="L47">
-        <v>5388995.60957964</v>
-      </c>
-      <c r="M47">
-        <v>1691403.86837373</v>
-      </c>
-      <c r="N47">
-        <v>1528068.5353158</v>
       </c>
       <c r="O47">
         <v>71744921.38560461</v>
@@ -42206,25 +42206,25 @@
         <v>19760106.675937</v>
       </c>
       <c r="H48">
+        <v>18873827.0374895</v>
+      </c>
+      <c r="I48">
+        <v>5506900.43689634</v>
+      </c>
+      <c r="J48">
+        <v>1776905.54799475</v>
+      </c>
+      <c r="K48">
+        <v>1607713.53808844</v>
+      </c>
+      <c r="L48">
         <v>682533.071382034</v>
       </c>
-      <c r="I48">
+      <c r="M48">
         <v>32135615.0124319</v>
       </c>
-      <c r="J48">
+      <c r="N48">
         <v>11580166.8376016</v>
-      </c>
-      <c r="K48">
-        <v>18873827.0374895</v>
-      </c>
-      <c r="L48">
-        <v>5506900.43689634</v>
-      </c>
-      <c r="M48">
-        <v>1776905.54799475</v>
-      </c>
-      <c r="N48">
-        <v>1607713.53808844</v>
       </c>
       <c r="O48">
         <v>72224769.06872369</v>
@@ -42261,25 +42261,25 @@
         <v>20057892.5262197</v>
       </c>
       <c r="H49">
+        <v>18928001.8999622</v>
+      </c>
+      <c r="I49">
+        <v>5701188.22688781</v>
+      </c>
+      <c r="J49">
+        <v>1812872.70843897</v>
+      </c>
+      <c r="K49">
+        <v>1551440.15541446</v>
+      </c>
+      <c r="L49">
         <v>729531.554190411</v>
       </c>
-      <c r="I49">
+      <c r="M49">
         <v>32613806.9656151</v>
       </c>
-      <c r="J49">
+      <c r="N49">
         <v>11701133.7222002</v>
-      </c>
-      <c r="K49">
-        <v>18928001.8999622</v>
-      </c>
-      <c r="L49">
-        <v>5701188.22688781</v>
-      </c>
-      <c r="M49">
-        <v>1812872.70843897</v>
-      </c>
-      <c r="N49">
-        <v>1551440.15541446</v>
       </c>
       <c r="O49">
         <v>73170599.2982441</v>
@@ -42316,25 +42316,25 @@
         <v>20352372.6776097</v>
       </c>
       <c r="H50">
+        <v>19148632.972078</v>
+      </c>
+      <c r="I50">
+        <v>5717081.38478276</v>
+      </c>
+      <c r="J50">
+        <v>1791337.476956</v>
+      </c>
+      <c r="K50">
+        <v>1522955.62904294</v>
+      </c>
+      <c r="L50">
         <v>740157.555114345</v>
       </c>
-      <c r="I50">
+      <c r="M50">
         <v>33128461.859054</v>
       </c>
-      <c r="J50">
+      <c r="N50">
         <v>11921311.3215513</v>
-      </c>
-      <c r="K50">
-        <v>19148632.972078</v>
-      </c>
-      <c r="L50">
-        <v>5717081.38478276</v>
-      </c>
-      <c r="M50">
-        <v>1791337.476956</v>
-      </c>
-      <c r="N50">
-        <v>1522955.62904294</v>
       </c>
       <c r="O50">
         <v>74009328.2384644</v>
@@ -42371,25 +42371,25 @@
         <v>20341005.5312047</v>
       </c>
       <c r="H51">
+        <v>19315503.8794836</v>
+      </c>
+      <c r="I51">
+        <v>5809715.96675455</v>
+      </c>
+      <c r="J51">
+        <v>1849541.94750954</v>
+      </c>
+      <c r="K51">
+        <v>1523105.4288702</v>
+      </c>
+      <c r="L51">
         <v>743004.917034945</v>
       </c>
-      <c r="I51">
+      <c r="M51">
         <v>33272131.4985843</v>
       </c>
-      <c r="J51">
+      <c r="N51">
         <v>12105506.3328135</v>
-      </c>
-      <c r="K51">
-        <v>19315503.8794836</v>
-      </c>
-      <c r="L51">
-        <v>5809715.96675455</v>
-      </c>
-      <c r="M51">
-        <v>1849541.94750954</v>
-      </c>
-      <c r="N51">
-        <v>1523105.4288702</v>
       </c>
       <c r="O51">
         <v>74638547.8548422</v>
@@ -42426,25 +42426,25 @@
         <v>20685020.2948753</v>
       </c>
       <c r="H52">
+        <v>19573138.3180033</v>
+      </c>
+      <c r="I52">
+        <v>5848366.80061393</v>
+      </c>
+      <c r="J52">
+        <v>1868266.70565767</v>
+      </c>
+      <c r="K52">
+        <v>1585790.55290773</v>
+      </c>
+      <c r="L52">
         <v>721032.764381655</v>
       </c>
-      <c r="I52">
+      <c r="M52">
         <v>33594893.8910979</v>
       </c>
-      <c r="J52">
+      <c r="N52">
         <v>12228067.7128397</v>
-      </c>
-      <c r="K52">
-        <v>19573138.3180033</v>
-      </c>
-      <c r="L52">
-        <v>5848366.80061393</v>
-      </c>
-      <c r="M52">
-        <v>1868266.70565767</v>
-      </c>
-      <c r="N52">
-        <v>1585790.55290773</v>
       </c>
       <c r="O52">
         <v>75310230.9948388</v>
@@ -42481,25 +42481,25 @@
         <v>20847070.9859361</v>
       </c>
       <c r="H53">
+        <v>19578176.7169029</v>
+      </c>
+      <c r="I53">
+        <v>6009782.77856726</v>
+      </c>
+      <c r="J53">
+        <v>1840056.74467639</v>
+      </c>
+      <c r="K53">
+        <v>1540998.38513455</v>
+      </c>
+      <c r="L53">
         <v>736900.383275105</v>
       </c>
-      <c r="I53">
+      <c r="M53">
         <v>33688964.2139399</v>
       </c>
-      <c r="J53">
+      <c r="N53">
         <v>12343637.3391549</v>
-      </c>
-      <c r="K53">
-        <v>19578176.7169029</v>
-      </c>
-      <c r="L53">
-        <v>6009782.77856726</v>
-      </c>
-      <c r="M53">
-        <v>1840056.74467639</v>
-      </c>
-      <c r="N53">
-        <v>1540998.38513455</v>
       </c>
       <c r="O53">
         <v>75750238.2274279</v>
@@ -42536,25 +42536,25 @@
         <v>20849738.9549847</v>
       </c>
       <c r="H54">
+        <v>19713224.3921011</v>
+      </c>
+      <c r="I54">
+        <v>6048001.36285103</v>
+      </c>
+      <c r="J54">
+        <v>1858648.58142128</v>
+      </c>
+      <c r="K54">
+        <v>1611653.88945755</v>
+      </c>
+      <c r="L54">
         <v>764116.601527776</v>
       </c>
-      <c r="I54">
+      <c r="M54">
         <v>33715557.9082867</v>
       </c>
-      <c r="J54">
+      <c r="N54">
         <v>12372826.1138609</v>
-      </c>
-      <c r="K54">
-        <v>19713224.3921011</v>
-      </c>
-      <c r="L54">
-        <v>6048001.36285103</v>
-      </c>
-      <c r="M54">
-        <v>1858648.58142128</v>
-      </c>
-      <c r="N54">
-        <v>1611653.88945755</v>
       </c>
       <c r="O54">
         <v>76107076.594192</v>
@@ -42591,25 +42591,25 @@
         <v>20919849.1354006</v>
       </c>
       <c r="H55">
+        <v>19932977.2618415</v>
+      </c>
+      <c r="I55">
+        <v>6189357.59120588</v>
+      </c>
+      <c r="J55">
+        <v>1815660.50738984</v>
+      </c>
+      <c r="K55">
+        <v>1675652.73299301</v>
+      </c>
+      <c r="L55">
         <v>764302.037314081</v>
       </c>
-      <c r="I55">
+      <c r="M55">
         <v>34089338.8429245</v>
       </c>
-      <c r="J55">
+      <c r="N55">
         <v>12456589.8209393</v>
-      </c>
-      <c r="K55">
-        <v>19932977.2618415</v>
-      </c>
-      <c r="L55">
-        <v>6189357.59120588</v>
-      </c>
-      <c r="M55">
-        <v>1815660.50738984</v>
-      </c>
-      <c r="N55">
-        <v>1675652.73299301</v>
       </c>
       <c r="O55">
         <v>76932225.66446491</v>
@@ -42646,25 +42646,25 @@
         <v>21042091.4016669</v>
       </c>
       <c r="H56">
+        <v>19544066.5228163</v>
+      </c>
+      <c r="I56">
+        <v>6269412.89464465</v>
+      </c>
+      <c r="J56">
+        <v>1810291.82415117</v>
+      </c>
+      <c r="K56">
+        <v>1648289.17263579</v>
+      </c>
+      <c r="L56">
         <v>822006.3518675989</v>
       </c>
-      <c r="I56">
+      <c r="M56">
         <v>33856838.7577957</v>
       </c>
-      <c r="J56">
+      <c r="N56">
         <v>12495227.6437415</v>
-      </c>
-      <c r="K56">
-        <v>19544066.5228163</v>
-      </c>
-      <c r="L56">
-        <v>6269412.89464465</v>
-      </c>
-      <c r="M56">
-        <v>1810291.82415117</v>
-      </c>
-      <c r="N56">
-        <v>1648289.17263579</v>
       </c>
       <c r="O56">
         <v>76313042.45936459</v>
@@ -42724,37 +42724,37 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Atividades imobiliárias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Outras atividades de serviços</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Comércio</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Transporte, armazenagem e correio</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Informação e comunicação</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Atividades financeiras, de seguros e serviços relacionados</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -42798,25 +42798,25 @@
         <v>11133476759.995</v>
       </c>
       <c r="H2">
+        <v>9468234691.08684</v>
+      </c>
+      <c r="I2">
+        <v>2424758679.75739</v>
+      </c>
+      <c r="J2">
+        <v>621568600.703119</v>
+      </c>
+      <c r="K2">
+        <v>603308292.4198821</v>
+      </c>
+      <c r="L2">
         <v>267309515.923085</v>
       </c>
-      <c r="I2">
+      <c r="M2">
         <v>12318480131.6502</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <v>4826194424.48059</v>
-      </c>
-      <c r="K2">
-        <v>9468234691.08684</v>
-      </c>
-      <c r="L2">
-        <v>2424758679.75739</v>
-      </c>
-      <c r="M2">
-        <v>621568600.703119</v>
-      </c>
-      <c r="N2">
-        <v>603308292.4198821</v>
       </c>
       <c r="O2">
         <v>30667411185.0957</v>
@@ -42853,25 +42853,25 @@
         <v>11256813243.3636</v>
       </c>
       <c r="H3">
+        <v>9477901718.36068</v>
+      </c>
+      <c r="I3">
+        <v>2435692193.32601</v>
+      </c>
+      <c r="J3">
+        <v>660163547.6161751</v>
+      </c>
+      <c r="K3">
+        <v>621470734.04265</v>
+      </c>
+      <c r="L3">
         <v>293217716.790335</v>
       </c>
-      <c r="I3">
+      <c r="M3">
         <v>12291487260.0999</v>
       </c>
-      <c r="J3">
+      <c r="N3">
         <v>4847172694.70684</v>
-      </c>
-      <c r="K3">
-        <v>9477901718.36068</v>
-      </c>
-      <c r="L3">
-        <v>2435692193.32601</v>
-      </c>
-      <c r="M3">
-        <v>660163547.6161751</v>
-      </c>
-      <c r="N3">
-        <v>621470734.04265</v>
       </c>
       <c r="O3">
         <v>30621823392.3729</v>
@@ -42908,25 +42908,25 @@
         <v>11355096262.6188</v>
       </c>
       <c r="H4">
+        <v>9418571387.471359</v>
+      </c>
+      <c r="I4">
+        <v>2490967285.39778</v>
+      </c>
+      <c r="J4">
+        <v>665094221.4564331</v>
+      </c>
+      <c r="K4">
+        <v>622231166.533797</v>
+      </c>
+      <c r="L4">
         <v>284999209.443087</v>
       </c>
-      <c r="I4">
+      <c r="M4">
         <v>12397124825.8449</v>
       </c>
-      <c r="J4">
+      <c r="N4">
         <v>4874971288.16813</v>
-      </c>
-      <c r="K4">
-        <v>9418571387.471359</v>
-      </c>
-      <c r="L4">
-        <v>2490967285.39778</v>
-      </c>
-      <c r="M4">
-        <v>665094221.4564331</v>
-      </c>
-      <c r="N4">
-        <v>622231166.533797</v>
       </c>
       <c r="O4">
         <v>30614276962.2102</v>
@@ -42963,25 +42963,25 @@
         <v>11366032533.003</v>
       </c>
       <c r="H5">
+        <v>9518623733.06126</v>
+      </c>
+      <c r="I5">
+        <v>2530371987.52481</v>
+      </c>
+      <c r="J5">
+        <v>658075374.707419</v>
+      </c>
+      <c r="K5">
+        <v>650255472.916069</v>
+      </c>
+      <c r="L5">
         <v>298238131.04532</v>
       </c>
-      <c r="I5">
+      <c r="M5">
         <v>12337026379.9249</v>
       </c>
-      <c r="J5">
+      <c r="N5">
         <v>4826538845.83536</v>
-      </c>
-      <c r="K5">
-        <v>9518623733.06126</v>
-      </c>
-      <c r="L5">
-        <v>2530371987.52481</v>
-      </c>
-      <c r="M5">
-        <v>658075374.707419</v>
-      </c>
-      <c r="N5">
-        <v>650255472.916069</v>
       </c>
       <c r="O5">
         <v>30837876798.1293</v>
@@ -43018,25 +43018,25 @@
         <v>11349707379.486</v>
       </c>
       <c r="H6">
+        <v>9538815024.294861</v>
+      </c>
+      <c r="I6">
+        <v>2525866841.08151</v>
+      </c>
+      <c r="J6">
+        <v>666988849.5489531</v>
+      </c>
+      <c r="K6">
+        <v>642272048.011905</v>
+      </c>
+      <c r="L6">
         <v>303312922.73585</v>
       </c>
-      <c r="I6">
+      <c r="M6">
         <v>12371822005.9973</v>
       </c>
-      <c r="J6">
+      <c r="N6">
         <v>4814988240.97851</v>
-      </c>
-      <c r="K6">
-        <v>9538815024.294861</v>
-      </c>
-      <c r="L6">
-        <v>2525866841.08151</v>
-      </c>
-      <c r="M6">
-        <v>666988849.5489531</v>
-      </c>
-      <c r="N6">
-        <v>642272048.011905</v>
       </c>
       <c r="O6">
         <v>30836386925.6841</v>
@@ -43073,25 +43073,25 @@
         <v>11343567490.5503</v>
       </c>
       <c r="H7">
+        <v>9620928346.64459</v>
+      </c>
+      <c r="I7">
+        <v>2542326070.36659</v>
+      </c>
+      <c r="J7">
+        <v>657085011.454499</v>
+      </c>
+      <c r="K7">
+        <v>658809149.228552</v>
+      </c>
+      <c r="L7">
         <v>309988798.866667</v>
       </c>
-      <c r="I7">
+      <c r="M7">
         <v>12388093327.2126</v>
       </c>
-      <c r="J7">
+      <c r="N7">
         <v>4819423882.71218</v>
-      </c>
-      <c r="K7">
-        <v>9620928346.64459</v>
-      </c>
-      <c r="L7">
-        <v>2542326070.36659</v>
-      </c>
-      <c r="M7">
-        <v>657085011.454499</v>
-      </c>
-      <c r="N7">
-        <v>658809149.228552</v>
       </c>
       <c r="O7">
         <v>30996947411.8676</v>
@@ -43128,25 +43128,25 @@
         <v>11324610688.7809</v>
       </c>
       <c r="H8">
+        <v>9791125153.231159</v>
+      </c>
+      <c r="I8">
+        <v>2531777492.55948</v>
+      </c>
+      <c r="J8">
+        <v>664125588.539569</v>
+      </c>
+      <c r="K8">
+        <v>646406926.513364</v>
+      </c>
+      <c r="L8">
         <v>319180692.768251</v>
       </c>
-      <c r="I8">
+      <c r="M8">
         <v>12492729384.1837</v>
       </c>
-      <c r="J8">
+      <c r="N8">
         <v>4807829246.89874</v>
-      </c>
-      <c r="K8">
-        <v>9791125153.231159</v>
-      </c>
-      <c r="L8">
-        <v>2531777492.55948</v>
-      </c>
-      <c r="M8">
-        <v>664125588.539569</v>
-      </c>
-      <c r="N8">
-        <v>646406926.513364</v>
       </c>
       <c r="O8">
         <v>31278995527.955</v>
@@ -43183,25 +43183,25 @@
         <v>11317566245.9631</v>
       </c>
       <c r="H9">
+        <v>9772984975.359529</v>
+      </c>
+      <c r="I9">
+        <v>2436825271.45257</v>
+      </c>
+      <c r="J9">
+        <v>678769023.7631249</v>
+      </c>
+      <c r="K9">
+        <v>639803404.622761</v>
+      </c>
+      <c r="L9">
         <v>291864539.630202</v>
       </c>
-      <c r="I9">
+      <c r="M9">
         <v>12638190048.1542</v>
       </c>
-      <c r="J9">
+      <c r="N9">
         <v>4821418398.82938</v>
-      </c>
-      <c r="K9">
-        <v>9772984975.359529</v>
-      </c>
-      <c r="L9">
-        <v>2436825271.45257</v>
-      </c>
-      <c r="M9">
-        <v>678769023.7631249</v>
-      </c>
-      <c r="N9">
-        <v>639803404.622761</v>
       </c>
       <c r="O9">
         <v>31316618475.0224</v>
@@ -43238,25 +43238,25 @@
         <v>11581828847.7706</v>
       </c>
       <c r="H10">
+        <v>9846393722.077181</v>
+      </c>
+      <c r="I10">
+        <v>2442344681.3032</v>
+      </c>
+      <c r="J10">
+        <v>690664273.400481</v>
+      </c>
+      <c r="K10">
+        <v>649531562.375863</v>
+      </c>
+      <c r="L10">
         <v>284309177.639578</v>
       </c>
-      <c r="I10">
+      <c r="M10">
         <v>12803516775.2929</v>
       </c>
-      <c r="J10">
+      <c r="N10">
         <v>4875361381.78042</v>
-      </c>
-      <c r="K10">
-        <v>9846393722.077181</v>
-      </c>
-      <c r="L10">
-        <v>2442344681.3032</v>
-      </c>
-      <c r="M10">
-        <v>690664273.400481</v>
-      </c>
-      <c r="N10">
-        <v>649531562.375863</v>
       </c>
       <c r="O10">
         <v>31543825812.6243</v>
@@ -43293,25 +43293,25 @@
         <v>11311601479.0838</v>
       </c>
       <c r="H11">
+        <v>9739873117.32486</v>
+      </c>
+      <c r="I11">
+        <v>2451008022.05394</v>
+      </c>
+      <c r="J11">
+        <v>680593582.443869</v>
+      </c>
+      <c r="K11">
+        <v>641506396.823149</v>
+      </c>
+      <c r="L11">
         <v>280211788.82298</v>
       </c>
-      <c r="I11">
+      <c r="M11">
         <v>12973697507.3033</v>
       </c>
-      <c r="J11">
+      <c r="N11">
         <v>4881990728.13583</v>
-      </c>
-      <c r="K11">
-        <v>9739873117.32486</v>
-      </c>
-      <c r="L11">
-        <v>2451008022.05394</v>
-      </c>
-      <c r="M11">
-        <v>680593582.443869</v>
-      </c>
-      <c r="N11">
-        <v>641506396.823149</v>
       </c>
       <c r="O11">
         <v>31654266626.7966</v>
@@ -43348,25 +43348,25 @@
         <v>11297573917.4132</v>
       </c>
       <c r="H12">
+        <v>9676488811.58345</v>
+      </c>
+      <c r="I12">
+        <v>2423097662.613</v>
+      </c>
+      <c r="J12">
+        <v>672249203.48098</v>
+      </c>
+      <c r="K12">
+        <v>666210698.009572</v>
+      </c>
+      <c r="L12">
         <v>285939262.287721</v>
       </c>
-      <c r="I12">
+      <c r="M12">
         <v>13066561626.0437</v>
       </c>
-      <c r="J12">
+      <c r="N12">
         <v>4876389087.16321</v>
-      </c>
-      <c r="K12">
-        <v>9676488811.58345</v>
-      </c>
-      <c r="L12">
-        <v>2423097662.613</v>
-      </c>
-      <c r="M12">
-        <v>672249203.48098</v>
-      </c>
-      <c r="N12">
-        <v>666210698.009572</v>
       </c>
       <c r="O12">
         <v>31689328327.3811</v>
@@ -43403,25 +43403,25 @@
         <v>11313863543.3333</v>
       </c>
       <c r="H13">
+        <v>9670463964.199909</v>
+      </c>
+      <c r="I13">
+        <v>2439825783.16956</v>
+      </c>
+      <c r="J13">
+        <v>679091505.2024339</v>
+      </c>
+      <c r="K13">
+        <v>650596149.479745</v>
+      </c>
+      <c r="L13">
         <v>327016934.007616</v>
       </c>
-      <c r="I13">
+      <c r="M13">
         <v>13092490404.1545</v>
       </c>
-      <c r="J13">
+      <c r="N13">
         <v>4903051743.0258</v>
-      </c>
-      <c r="K13">
-        <v>9670463964.199909</v>
-      </c>
-      <c r="L13">
-        <v>2439825783.16956</v>
-      </c>
-      <c r="M13">
-        <v>679091505.2024339</v>
-      </c>
-      <c r="N13">
-        <v>650596149.479745</v>
       </c>
       <c r="O13">
         <v>31827756642.4585</v>
@@ -43458,25 +43458,25 @@
         <v>11351716040.5986</v>
       </c>
       <c r="H14">
+        <v>9705090727.36256</v>
+      </c>
+      <c r="I14">
+        <v>2492897016.28519</v>
+      </c>
+      <c r="J14">
+        <v>663700328.8239681</v>
+      </c>
+      <c r="K14">
+        <v>629574357.29615</v>
+      </c>
+      <c r="L14">
         <v>298551904.684134</v>
       </c>
-      <c r="I14">
+      <c r="M14">
         <v>13004683680.1104</v>
       </c>
-      <c r="J14">
+      <c r="N14">
         <v>4897875897.13835</v>
-      </c>
-      <c r="K14">
-        <v>9705090727.36256</v>
-      </c>
-      <c r="L14">
-        <v>2492897016.28519</v>
-      </c>
-      <c r="M14">
-        <v>663700328.8239681</v>
-      </c>
-      <c r="N14">
-        <v>629574357.29615</v>
       </c>
       <c r="O14">
         <v>31609853663.2382</v>
@@ -43513,25 +43513,25 @@
         <v>10842520170.1068</v>
       </c>
       <c r="H15">
+        <v>9773445059.816071</v>
+      </c>
+      <c r="I15">
+        <v>2452119891.00216</v>
+      </c>
+      <c r="J15">
+        <v>672139296.335008</v>
+      </c>
+      <c r="K15">
+        <v>629503560.51133</v>
+      </c>
+      <c r="L15">
         <v>314076697.996991</v>
       </c>
-      <c r="I15">
+      <c r="M15">
         <v>13181338250.49</v>
       </c>
-      <c r="J15">
+      <c r="N15">
         <v>4882632196.52407</v>
-      </c>
-      <c r="K15">
-        <v>9773445059.816071</v>
-      </c>
-      <c r="L15">
-        <v>2452119891.00216</v>
-      </c>
-      <c r="M15">
-        <v>672139296.335008</v>
-      </c>
-      <c r="N15">
-        <v>629503560.51133</v>
       </c>
       <c r="O15">
         <v>31918002217.1956</v>
@@ -43568,25 +43568,25 @@
         <v>10721102054.0624</v>
       </c>
       <c r="H16">
+        <v>9775923013.48317</v>
+      </c>
+      <c r="I16">
+        <v>2459000415.77828</v>
+      </c>
+      <c r="J16">
+        <v>693972659.031625</v>
+      </c>
+      <c r="K16">
+        <v>593939133.525977</v>
+      </c>
+      <c r="L16">
         <v>308457238.355414</v>
       </c>
-      <c r="I16">
+      <c r="M16">
         <v>13051346352.0924</v>
       </c>
-      <c r="J16">
+      <c r="N16">
         <v>4889899624.18502</v>
-      </c>
-      <c r="K16">
-        <v>9775923013.48317</v>
-      </c>
-      <c r="L16">
-        <v>2459000415.77828</v>
-      </c>
-      <c r="M16">
-        <v>693972659.031625</v>
-      </c>
-      <c r="N16">
-        <v>593939133.525977</v>
       </c>
       <c r="O16">
         <v>31798837565.0875</v>
@@ -43623,25 +43623,25 @@
         <v>10691699854.2567</v>
       </c>
       <c r="H17">
+        <v>9505990667.98958</v>
+      </c>
+      <c r="I17">
+        <v>2497904049.71816</v>
+      </c>
+      <c r="J17">
+        <v>631131998.588446</v>
+      </c>
+      <c r="K17">
+        <v>583008906.429347</v>
+      </c>
+      <c r="L17">
         <v>293906722.438573</v>
       </c>
-      <c r="I17">
+      <c r="M17">
         <v>13010273318.1549</v>
       </c>
-      <c r="J17">
+      <c r="N17">
         <v>4930995809.052</v>
-      </c>
-      <c r="K17">
-        <v>9505990667.98958</v>
-      </c>
-      <c r="L17">
-        <v>2497904049.71816</v>
-      </c>
-      <c r="M17">
-        <v>631131998.588446</v>
-      </c>
-      <c r="N17">
-        <v>583008906.429347</v>
       </c>
       <c r="O17">
         <v>31536906164.3674</v>
@@ -43678,25 +43678,25 @@
         <v>10373141632.6752</v>
       </c>
       <c r="H18">
+        <v>9525620723.3127</v>
+      </c>
+      <c r="I18">
+        <v>2485043549.09674</v>
+      </c>
+      <c r="J18">
+        <v>620225186.164392</v>
+      </c>
+      <c r="K18">
+        <v>624060741.144049</v>
+      </c>
+      <c r="L18">
         <v>288277764.028081</v>
       </c>
-      <c r="I18">
+      <c r="M18">
         <v>13028913639.6762</v>
       </c>
-      <c r="J18">
+      <c r="N18">
         <v>4910681327.06581</v>
-      </c>
-      <c r="K18">
-        <v>9525620723.3127</v>
-      </c>
-      <c r="L18">
-        <v>2485043549.09674</v>
-      </c>
-      <c r="M18">
-        <v>620225186.164392</v>
-      </c>
-      <c r="N18">
-        <v>624060741.144049</v>
       </c>
       <c r="O18">
         <v>31531031140.1044</v>
@@ -43733,25 +43733,25 @@
         <v>10134727284.6642</v>
       </c>
       <c r="H19">
+        <v>9461476708.195999</v>
+      </c>
+      <c r="I19">
+        <v>2501382388.21623</v>
+      </c>
+      <c r="J19">
+        <v>633741983.54944</v>
+      </c>
+      <c r="K19">
+        <v>600949884.802603</v>
+      </c>
+      <c r="L19">
         <v>280741606.752387</v>
       </c>
-      <c r="I19">
+      <c r="M19">
         <v>13045789727.7716</v>
       </c>
-      <c r="J19">
+      <c r="N19">
         <v>4943478561.71952</v>
-      </c>
-      <c r="K19">
-        <v>9461476708.195999</v>
-      </c>
-      <c r="L19">
-        <v>2501382388.21623</v>
-      </c>
-      <c r="M19">
-        <v>633741983.54944</v>
-      </c>
-      <c r="N19">
-        <v>600949884.802603</v>
       </c>
       <c r="O19">
         <v>31483131393.671</v>
@@ -43788,25 +43788,25 @@
         <v>9879306989.027889</v>
       </c>
       <c r="H20">
+        <v>9294731397.932421</v>
+      </c>
+      <c r="I20">
+        <v>2538534195.65453</v>
+      </c>
+      <c r="J20">
+        <v>633687166.944786</v>
+      </c>
+      <c r="K20">
+        <v>610645043.477697</v>
+      </c>
+      <c r="L20">
         <v>279899023.631829</v>
       </c>
-      <c r="I20">
+      <c r="M20">
         <v>13011821443.7326</v>
       </c>
-      <c r="J20">
+      <c r="N20">
         <v>4968009867.85239</v>
-      </c>
-      <c r="K20">
-        <v>9294731397.932421</v>
-      </c>
-      <c r="L20">
-        <v>2538534195.65453</v>
-      </c>
-      <c r="M20">
-        <v>633687166.944786</v>
-      </c>
-      <c r="N20">
-        <v>610645043.477697</v>
       </c>
       <c r="O20">
         <v>31374047696.1514</v>
@@ -43843,25 +43843,25 @@
         <v>9680545481.810711</v>
       </c>
       <c r="H21">
+        <v>9364267817.416941</v>
+      </c>
+      <c r="I21">
+        <v>2545631493.97483</v>
+      </c>
+      <c r="J21">
+        <v>642337791.2932431</v>
+      </c>
+      <c r="K21">
+        <v>629725427.578037</v>
+      </c>
+      <c r="L21">
         <v>302437147.699397</v>
       </c>
-      <c r="I21">
+      <c r="M21">
         <v>13027861717.2718</v>
       </c>
-      <c r="J21">
+      <c r="N21">
         <v>4913812057.41171</v>
-      </c>
-      <c r="K21">
-        <v>9364267817.416941</v>
-      </c>
-      <c r="L21">
-        <v>2545631493.97483</v>
-      </c>
-      <c r="M21">
-        <v>642337791.2932431</v>
-      </c>
-      <c r="N21">
-        <v>629725427.578037</v>
       </c>
       <c r="O21">
         <v>31335593509.3069</v>
@@ -43898,25 +43898,25 @@
         <v>9741082385.85417</v>
       </c>
       <c r="H22">
+        <v>9316796281.7598</v>
+      </c>
+      <c r="I22">
+        <v>2514916876.69573</v>
+      </c>
+      <c r="J22">
+        <v>649953889.893831</v>
+      </c>
+      <c r="K22">
+        <v>631722670.360651</v>
+      </c>
+      <c r="L22">
         <v>308520399.188823</v>
       </c>
-      <c r="I22">
+      <c r="M22">
         <v>13133305137.5045</v>
       </c>
-      <c r="J22">
+      <c r="N22">
         <v>4887126537.90613</v>
-      </c>
-      <c r="K22">
-        <v>9316796281.7598</v>
-      </c>
-      <c r="L22">
-        <v>2514916876.69573</v>
-      </c>
-      <c r="M22">
-        <v>649953889.893831</v>
-      </c>
-      <c r="N22">
-        <v>631722670.360651</v>
       </c>
       <c r="O22">
         <v>31503284062.4726</v>
@@ -43953,25 +43953,25 @@
         <v>9744993525.727171</v>
       </c>
       <c r="H23">
+        <v>9385318448.30689</v>
+      </c>
+      <c r="I23">
+        <v>2551141088.04483</v>
+      </c>
+      <c r="J23">
+        <v>642131089.040795</v>
+      </c>
+      <c r="K23">
+        <v>605051762.352767</v>
+      </c>
+      <c r="L23">
         <v>292217060.233782</v>
       </c>
-      <c r="I23">
+      <c r="M23">
         <v>13328511205.9164</v>
       </c>
-      <c r="J23">
+      <c r="N23">
         <v>4904206061.95992</v>
-      </c>
-      <c r="K23">
-        <v>9385318448.30689</v>
-      </c>
-      <c r="L23">
-        <v>2551141088.04483</v>
-      </c>
-      <c r="M23">
-        <v>642131089.040795</v>
-      </c>
-      <c r="N23">
-        <v>605051762.352767</v>
       </c>
       <c r="O23">
         <v>31723152006.6386</v>
@@ -44008,25 +44008,25 @@
         <v>9791727019.62516</v>
       </c>
       <c r="H24">
+        <v>9405528331.73794</v>
+      </c>
+      <c r="I24">
+        <v>2589879829.61606</v>
+      </c>
+      <c r="J24">
+        <v>659299017.659781</v>
+      </c>
+      <c r="K24">
+        <v>630563193.721296</v>
+      </c>
+      <c r="L24">
         <v>290439870.316877</v>
       </c>
-      <c r="I24">
+      <c r="M24">
         <v>13503592496.426</v>
       </c>
-      <c r="J24">
+      <c r="N24">
         <v>4929096179.92703</v>
-      </c>
-      <c r="K24">
-        <v>9405528331.73794</v>
-      </c>
-      <c r="L24">
-        <v>2589879829.61606</v>
-      </c>
-      <c r="M24">
-        <v>659299017.659781</v>
-      </c>
-      <c r="N24">
-        <v>630563193.721296</v>
       </c>
       <c r="O24">
         <v>31880256769.0368</v>
@@ -44063,25 +44063,25 @@
         <v>9831017690.122761</v>
       </c>
       <c r="H25">
+        <v>9475311247.33363</v>
+      </c>
+      <c r="I25">
+        <v>2501567823.10785</v>
+      </c>
+      <c r="J25">
+        <v>636990744.903989</v>
+      </c>
+      <c r="K25">
+        <v>634318406.162843</v>
+      </c>
+      <c r="L25">
         <v>278995458.581196</v>
       </c>
-      <c r="I25">
+      <c r="M25">
         <v>13656033105.8561</v>
       </c>
-      <c r="J25">
+      <c r="N25">
         <v>4976049274.22755</v>
-      </c>
-      <c r="K25">
-        <v>9475311247.33363</v>
-      </c>
-      <c r="L25">
-        <v>2501567823.10785</v>
-      </c>
-      <c r="M25">
-        <v>636990744.903989</v>
-      </c>
-      <c r="N25">
-        <v>634318406.162843</v>
       </c>
       <c r="O25">
         <v>32051601119.4183</v>
@@ -44118,25 +44118,25 @@
         <v>9649617040.916571</v>
       </c>
       <c r="H26">
+        <v>9487432768.274349</v>
+      </c>
+      <c r="I26">
+        <v>2587476792.24668</v>
+      </c>
+      <c r="J26">
+        <v>641318339.942822</v>
+      </c>
+      <c r="K26">
+        <v>616882048.148896</v>
+      </c>
+      <c r="L26">
         <v>284911951.661802</v>
       </c>
-      <c r="I26">
+      <c r="M26">
         <v>13745464737.6183</v>
       </c>
-      <c r="J26">
+      <c r="N26">
         <v>4998978604.6458</v>
-      </c>
-      <c r="K26">
-        <v>9487432768.274349</v>
-      </c>
-      <c r="L26">
-        <v>2587476792.24668</v>
-      </c>
-      <c r="M26">
-        <v>641318339.942822</v>
-      </c>
-      <c r="N26">
-        <v>616882048.148896</v>
       </c>
       <c r="O26">
         <v>32431003410.3564</v>
@@ -44173,25 +44173,25 @@
         <v>9716386264.132271</v>
       </c>
       <c r="H27">
+        <v>9444610681.09584</v>
+      </c>
+      <c r="I27">
+        <v>2610222438.91558</v>
+      </c>
+      <c r="J27">
+        <v>642626309.9533041</v>
+      </c>
+      <c r="K27">
+        <v>629212141.335487</v>
+      </c>
+      <c r="L27">
         <v>303137541.049725</v>
       </c>
-      <c r="I27">
+      <c r="M27">
         <v>13632786631.3839</v>
       </c>
-      <c r="J27">
+      <c r="N27">
         <v>5001297959.87242</v>
-      </c>
-      <c r="K27">
-        <v>9444610681.09584</v>
-      </c>
-      <c r="L27">
-        <v>2610222438.91558</v>
-      </c>
-      <c r="M27">
-        <v>642626309.9533041</v>
-      </c>
-      <c r="N27">
-        <v>629212141.335487</v>
       </c>
       <c r="O27">
         <v>32283980027.9577</v>
@@ -44228,25 +44228,25 @@
         <v>9751245364.78171</v>
       </c>
       <c r="H28">
+        <v>9533662181.915409</v>
+      </c>
+      <c r="I28">
+        <v>2614440141.17146</v>
+      </c>
+      <c r="J28">
+        <v>658246770.678561</v>
+      </c>
+      <c r="K28">
+        <v>639317701.617398</v>
+      </c>
+      <c r="L28">
         <v>302985584.527665</v>
       </c>
-      <c r="I28">
+      <c r="M28">
         <v>13859028776.5263</v>
       </c>
-      <c r="J28">
+      <c r="N28">
         <v>5033667575.57827</v>
-      </c>
-      <c r="K28">
-        <v>9533662181.915409</v>
-      </c>
-      <c r="L28">
-        <v>2614440141.17146</v>
-      </c>
-      <c r="M28">
-        <v>658246770.678561</v>
-      </c>
-      <c r="N28">
-        <v>639317701.617398</v>
       </c>
       <c r="O28">
         <v>32517902625.4459</v>
@@ -44283,25 +44283,25 @@
         <v>9685762907.638769</v>
       </c>
       <c r="H29">
+        <v>9482373050.15604</v>
+      </c>
+      <c r="I29">
+        <v>2660178379.00688</v>
+      </c>
+      <c r="J29">
+        <v>681846539.293787</v>
+      </c>
+      <c r="K29">
+        <v>623793653.804024</v>
+      </c>
+      <c r="L29">
         <v>299273194.502671</v>
       </c>
-      <c r="I29">
+      <c r="M29">
         <v>13992627402.1007</v>
       </c>
-      <c r="J29">
+      <c r="N29">
         <v>5061926914.27519</v>
-      </c>
-      <c r="K29">
-        <v>9482373050.15604</v>
-      </c>
-      <c r="L29">
-        <v>2660178379.00688</v>
-      </c>
-      <c r="M29">
-        <v>681846539.293787</v>
-      </c>
-      <c r="N29">
-        <v>623793653.804024</v>
       </c>
       <c r="O29">
         <v>32843787952.875</v>
@@ -44338,25 +44338,25 @@
         <v>9722209282.56419</v>
       </c>
       <c r="H30">
+        <v>9565695130.601259</v>
+      </c>
+      <c r="I30">
+        <v>2711295357.57505</v>
+      </c>
+      <c r="J30">
+        <v>690267102.127741</v>
+      </c>
+      <c r="K30">
+        <v>645085411.406635</v>
+      </c>
+      <c r="L30">
         <v>298133179.894997</v>
       </c>
-      <c r="I30">
+      <c r="M30">
         <v>14167025177.7593</v>
       </c>
-      <c r="J30">
+      <c r="N30">
         <v>5083847011.78189</v>
-      </c>
-      <c r="K30">
-        <v>9565695130.601259</v>
-      </c>
-      <c r="L30">
-        <v>2711295357.57505</v>
-      </c>
-      <c r="M30">
-        <v>690267102.127741</v>
-      </c>
-      <c r="N30">
-        <v>645085411.406635</v>
       </c>
       <c r="O30">
         <v>33069971948.7713</v>
@@ -44393,25 +44393,25 @@
         <v>9823842917.02417</v>
       </c>
       <c r="H31">
+        <v>9553004930.14016</v>
+      </c>
+      <c r="I31">
+        <v>2751535388.27916</v>
+      </c>
+      <c r="J31">
+        <v>689053672.08912</v>
+      </c>
+      <c r="K31">
+        <v>665275683.7265691</v>
+      </c>
+      <c r="L31">
         <v>298835506.162579</v>
       </c>
-      <c r="I31">
+      <c r="M31">
         <v>14285836441.8371</v>
       </c>
-      <c r="J31">
+      <c r="N31">
         <v>5048830074.7346</v>
-      </c>
-      <c r="K31">
-        <v>9553004930.14016</v>
-      </c>
-      <c r="L31">
-        <v>2751535388.27916</v>
-      </c>
-      <c r="M31">
-        <v>689053672.08912</v>
-      </c>
-      <c r="N31">
-        <v>665275683.7265691</v>
       </c>
       <c r="O31">
         <v>33324757118.3699</v>
@@ -44448,25 +44448,25 @@
         <v>9921754179.66678</v>
       </c>
       <c r="H32">
+        <v>9598050287.69718</v>
+      </c>
+      <c r="I32">
+        <v>2781191147.77825</v>
+      </c>
+      <c r="J32">
+        <v>697590434.797124</v>
+      </c>
+      <c r="K32">
+        <v>655449039.855772</v>
+      </c>
+      <c r="L32">
         <v>294945127.062846</v>
       </c>
-      <c r="I32">
+      <c r="M32">
         <v>14356102326.6753</v>
       </c>
-      <c r="J32">
+      <c r="N32">
         <v>5055664119.74914</v>
-      </c>
-      <c r="K32">
-        <v>9598050287.69718</v>
-      </c>
-      <c r="L32">
-        <v>2781191147.77825</v>
-      </c>
-      <c r="M32">
-        <v>697590434.797124</v>
-      </c>
-      <c r="N32">
-        <v>655449039.855772</v>
       </c>
       <c r="O32">
         <v>33479747381.0336</v>
@@ -44503,25 +44503,25 @@
         <v>9867463452.35659</v>
       </c>
       <c r="H33">
+        <v>9601632423.81687</v>
+      </c>
+      <c r="I33">
+        <v>2775087879.27776</v>
+      </c>
+      <c r="J33">
+        <v>713296926.001755</v>
+      </c>
+      <c r="K33">
+        <v>626520266.971172</v>
+      </c>
+      <c r="L33">
         <v>294162424.411544</v>
       </c>
-      <c r="I33">
+      <c r="M33">
         <v>14497664618.2139</v>
       </c>
-      <c r="J33">
+      <c r="N33">
         <v>5114168748.53895</v>
-      </c>
-      <c r="K33">
-        <v>9601632423.81687</v>
-      </c>
-      <c r="L33">
-        <v>2775087879.27776</v>
-      </c>
-      <c r="M33">
-        <v>713296926.001755</v>
-      </c>
-      <c r="N33">
-        <v>626520266.971172</v>
       </c>
       <c r="O33">
         <v>33648355174.6221</v>
@@ -44558,25 +44558,25 @@
         <v>9820859921.17935</v>
       </c>
       <c r="H34">
+        <v>9512633533.709749</v>
+      </c>
+      <c r="I34">
+        <v>2755629825.61677</v>
+      </c>
+      <c r="J34">
+        <v>749220137.932524</v>
+      </c>
+      <c r="K34">
+        <v>642956078.512243</v>
+      </c>
+      <c r="L34">
         <v>285443688.214909</v>
       </c>
-      <c r="I34">
+      <c r="M34">
         <v>14291386432.9529</v>
       </c>
-      <c r="J34">
+      <c r="N34">
         <v>5221603602.52858</v>
-      </c>
-      <c r="K34">
-        <v>9512633533.709749</v>
-      </c>
-      <c r="L34">
-        <v>2755629825.61677</v>
-      </c>
-      <c r="M34">
-        <v>749220137.932524</v>
-      </c>
-      <c r="N34">
-        <v>642956078.512243</v>
       </c>
       <c r="O34">
         <v>33537499038.9809</v>
@@ -44613,25 +44613,25 @@
         <v>8598607803.592421</v>
       </c>
       <c r="H35">
+        <v>8339270713.33477</v>
+      </c>
+      <c r="I35">
+        <v>2478518726.08386</v>
+      </c>
+      <c r="J35">
+        <v>694147330.549677</v>
+      </c>
+      <c r="K35">
+        <v>607356917.103449</v>
+      </c>
+      <c r="L35">
         <v>273182133.855289</v>
       </c>
-      <c r="I35">
+      <c r="M35">
         <v>12111091266.0959</v>
       </c>
-      <c r="J35">
+      <c r="N35">
         <v>5327959506.49646</v>
-      </c>
-      <c r="K35">
-        <v>8339270713.33477</v>
-      </c>
-      <c r="L35">
-        <v>2478518726.08386</v>
-      </c>
-      <c r="M35">
-        <v>694147330.549677</v>
-      </c>
-      <c r="N35">
-        <v>607356917.103449</v>
       </c>
       <c r="O35">
         <v>29876165041.7302</v>
@@ -44668,25 +44668,25 @@
         <v>8728057364.24535</v>
       </c>
       <c r="H36">
+        <v>8392223231.22813</v>
+      </c>
+      <c r="I36">
+        <v>2379249074.19513</v>
+      </c>
+      <c r="J36">
+        <v>735221362.962387</v>
+      </c>
+      <c r="K36">
+        <v>608264517.453096</v>
+      </c>
+      <c r="L36">
         <v>289473476.642286</v>
       </c>
-      <c r="I36">
+      <c r="M36">
         <v>11562448565.0624</v>
       </c>
-      <c r="J36">
+      <c r="N36">
         <v>5084027913.28508</v>
-      </c>
-      <c r="K36">
-        <v>8392223231.22813</v>
-      </c>
-      <c r="L36">
-        <v>2379249074.19513</v>
-      </c>
-      <c r="M36">
-        <v>735221362.962387</v>
-      </c>
-      <c r="N36">
-        <v>608264517.453096</v>
       </c>
       <c r="O36">
         <v>29084694354.7551</v>
@@ -44723,25 +44723,25 @@
         <v>9008668481.20232</v>
       </c>
       <c r="H37">
+        <v>8615516247.23521</v>
+      </c>
+      <c r="I37">
+        <v>2434158769.56591</v>
+      </c>
+      <c r="J37">
+        <v>733845942.530916</v>
+      </c>
+      <c r="K37">
+        <v>675937236.649142</v>
+      </c>
+      <c r="L37">
         <v>276020869.081004</v>
       </c>
-      <c r="I37">
+      <c r="M37">
         <v>12059840398.1187</v>
       </c>
-      <c r="J37">
+      <c r="N37">
         <v>5279616503.27922</v>
-      </c>
-      <c r="K37">
-        <v>8615516247.23521</v>
-      </c>
-      <c r="L37">
-        <v>2434158769.56591</v>
-      </c>
-      <c r="M37">
-        <v>733845942.530916</v>
-      </c>
-      <c r="N37">
-        <v>675937236.649142</v>
       </c>
       <c r="O37">
         <v>30098137086.6041</v>
@@ -44778,25 +44778,25 @@
         <v>9265252382.089081</v>
       </c>
       <c r="H38">
+        <v>8721801579.946051</v>
+      </c>
+      <c r="I38">
+        <v>2524010447.93271</v>
+      </c>
+      <c r="J38">
+        <v>760838410.243255</v>
+      </c>
+      <c r="K38">
+        <v>692481142.74727</v>
+      </c>
+      <c r="L38">
         <v>311898782.415158</v>
       </c>
-      <c r="I38">
+      <c r="M38">
         <v>12367090966.508</v>
       </c>
-      <c r="J38">
+      <c r="N38">
         <v>5296334987.84729</v>
-      </c>
-      <c r="K38">
-        <v>8721801579.946051</v>
-      </c>
-      <c r="L38">
-        <v>2524010447.93271</v>
-      </c>
-      <c r="M38">
-        <v>760838410.243255</v>
-      </c>
-      <c r="N38">
-        <v>692481142.74727</v>
       </c>
       <c r="O38">
         <v>30593375274.7125</v>
@@ -44833,25 +44833,25 @@
         <v>9382126240.176041</v>
       </c>
       <c r="H39">
+        <v>8808211607.425871</v>
+      </c>
+      <c r="I39">
+        <v>2553579645.46517</v>
+      </c>
+      <c r="J39">
+        <v>814337221.696561</v>
+      </c>
+      <c r="K39">
+        <v>692838455.386579</v>
+      </c>
+      <c r="L39">
         <v>293696055.062127</v>
       </c>
-      <c r="I39">
+      <c r="M39">
         <v>12766261243.8065</v>
       </c>
-      <c r="J39">
+      <c r="N39">
         <v>5141799195.58427</v>
-      </c>
-      <c r="K39">
-        <v>8808211607.425871</v>
-      </c>
-      <c r="L39">
-        <v>2553579645.46517</v>
-      </c>
-      <c r="M39">
-        <v>814337221.696561</v>
-      </c>
-      <c r="N39">
-        <v>692838455.386579</v>
       </c>
       <c r="O39">
         <v>31117831531.9736</v>
@@ -44888,25 +44888,25 @@
         <v>9970878518.57659</v>
       </c>
       <c r="H40">
+        <v>9481041322.67037</v>
+      </c>
+      <c r="I40">
+        <v>2677059214.56657</v>
+      </c>
+      <c r="J40">
+        <v>805156973.967401</v>
+      </c>
+      <c r="K40">
+        <v>684340869.033801</v>
+      </c>
+      <c r="L40">
         <v>304142837.73656</v>
       </c>
-      <c r="I40">
+      <c r="M40">
         <v>13277091569.7279</v>
       </c>
-      <c r="J40">
+      <c r="N40">
         <v>4985485025.35508</v>
-      </c>
-      <c r="K40">
-        <v>9481041322.67037</v>
-      </c>
-      <c r="L40">
-        <v>2677059214.56657</v>
-      </c>
-      <c r="M40">
-        <v>805156973.967401</v>
-      </c>
-      <c r="N40">
-        <v>684340869.033801</v>
       </c>
       <c r="O40">
         <v>32233873904.6573</v>
@@ -44943,25 +44943,25 @@
         <v>10141879158.7196</v>
       </c>
       <c r="H41">
+        <v>9682874092.828609</v>
+      </c>
+      <c r="I41">
+        <v>2695851704.02767</v>
+      </c>
+      <c r="J41">
+        <v>887297292.357748</v>
+      </c>
+      <c r="K41">
+        <v>702548524.3066</v>
+      </c>
+      <c r="L41">
         <v>301710201.897171</v>
       </c>
-      <c r="I41">
+      <c r="M41">
         <v>13857476936.1423</v>
       </c>
-      <c r="J41">
+      <c r="N41">
         <v>5148418930.67196</v>
-      </c>
-      <c r="K41">
-        <v>9682874092.828609</v>
-      </c>
-      <c r="L41">
-        <v>2695851704.02767</v>
-      </c>
-      <c r="M41">
-        <v>887297292.357748</v>
-      </c>
-      <c r="N41">
-        <v>702548524.3066</v>
       </c>
       <c r="O41">
         <v>33312607582.0079</v>
@@ -44998,25 +44998,25 @@
         <v>10191765840.307</v>
       </c>
       <c r="H42">
+        <v>9865967432.22621</v>
+      </c>
+      <c r="I42">
+        <v>2741268901.89934</v>
+      </c>
+      <c r="J42">
+        <v>851893860.668146</v>
+      </c>
+      <c r="K42">
+        <v>708493950.685114</v>
+      </c>
+      <c r="L42">
         <v>309115229.173361</v>
       </c>
-      <c r="I42">
+      <c r="M42">
         <v>14286564259.3507</v>
       </c>
-      <c r="J42">
+      <c r="N42">
         <v>5218848286.58593</v>
-      </c>
-      <c r="K42">
-        <v>9865967432.22621</v>
-      </c>
-      <c r="L42">
-        <v>2741268901.89934</v>
-      </c>
-      <c r="M42">
-        <v>851893860.668146</v>
-      </c>
-      <c r="N42">
-        <v>708493950.685114</v>
       </c>
       <c r="O42">
         <v>33894456489.9594</v>
@@ -45053,25 +45053,25 @@
         <v>10473215151.8692</v>
       </c>
       <c r="H43">
+        <v>10153408835.3436</v>
+      </c>
+      <c r="I43">
+        <v>2837662555.57793</v>
+      </c>
+      <c r="J43">
+        <v>915987785.9458899</v>
+      </c>
+      <c r="K43">
+        <v>748602656.2019939</v>
+      </c>
+      <c r="L43">
         <v>340006501.184314</v>
       </c>
-      <c r="I43">
+      <c r="M43">
         <v>14510449463.6793</v>
       </c>
-      <c r="J43">
+      <c r="N43">
         <v>5306958410.68237</v>
-      </c>
-      <c r="K43">
-        <v>10153408835.3436</v>
-      </c>
-      <c r="L43">
-        <v>2837662555.57793</v>
-      </c>
-      <c r="M43">
-        <v>915987785.9458899</v>
-      </c>
-      <c r="N43">
-        <v>748602656.2019939</v>
       </c>
       <c r="O43">
         <v>34863770836.884</v>
@@ -45108,25 +45108,25 @@
         <v>10399263799.036</v>
       </c>
       <c r="H44">
+        <v>10263706930.3625</v>
+      </c>
+      <c r="I44">
+        <v>2922501062.89023</v>
+      </c>
+      <c r="J44">
+        <v>873975633.126022</v>
+      </c>
+      <c r="K44">
+        <v>772677592.547459</v>
+      </c>
+      <c r="L44">
         <v>339949149.185839</v>
       </c>
-      <c r="I44">
+      <c r="M44">
         <v>14665528012.3387</v>
       </c>
-      <c r="J44">
+      <c r="N44">
         <v>5412626585.27547</v>
-      </c>
-      <c r="K44">
-        <v>10263706930.3625</v>
-      </c>
-      <c r="L44">
-        <v>2922501062.89023</v>
-      </c>
-      <c r="M44">
-        <v>873975633.126022</v>
-      </c>
-      <c r="N44">
-        <v>772677592.547459</v>
       </c>
       <c r="O44">
         <v>35274589625.0592</v>
@@ -45163,25 +45163,25 @@
         <v>10307062788.2867</v>
       </c>
       <c r="H45">
+        <v>10121077224.5835</v>
+      </c>
+      <c r="I45">
+        <v>2930103520.56378</v>
+      </c>
+      <c r="J45">
+        <v>858738558.325689</v>
+      </c>
+      <c r="K45">
+        <v>790185042.0418071</v>
+      </c>
+      <c r="L45">
         <v>338779919.245493</v>
       </c>
-      <c r="I45">
+      <c r="M45">
         <v>14692625216.4977</v>
       </c>
-      <c r="J45">
+      <c r="N45">
         <v>5458772050.91628</v>
-      </c>
-      <c r="K45">
-        <v>10121077224.5835</v>
-      </c>
-      <c r="L45">
-        <v>2930103520.56378</v>
-      </c>
-      <c r="M45">
-        <v>858738558.325689</v>
-      </c>
-      <c r="N45">
-        <v>790185042.0418071</v>
       </c>
       <c r="O45">
         <v>35064455166.5946</v>
@@ -45218,25 +45218,25 @@
         <v>10253146026.4644</v>
       </c>
       <c r="H46">
+        <v>10140057002.6306</v>
+      </c>
+      <c r="I46">
+        <v>2954042628.82615</v>
+      </c>
+      <c r="J46">
+        <v>879651237.5998189</v>
+      </c>
+      <c r="K46">
+        <v>786612954.837934</v>
+      </c>
+      <c r="L46">
         <v>338030379.520859</v>
       </c>
-      <c r="I46">
+      <c r="M46">
         <v>14752292490.4036</v>
       </c>
-      <c r="J46">
+      <c r="N46">
         <v>5461207186.68328</v>
-      </c>
-      <c r="K46">
-        <v>10140057002.6306</v>
-      </c>
-      <c r="L46">
-        <v>2954042628.82615</v>
-      </c>
-      <c r="M46">
-        <v>879651237.5998189</v>
-      </c>
-      <c r="N46">
-        <v>786612954.837934</v>
       </c>
       <c r="O46">
         <v>35375312442.3417</v>
@@ -45273,25 +45273,25 @@
         <v>10236617013.5254</v>
       </c>
       <c r="H47">
+        <v>10022285423.3735</v>
+      </c>
+      <c r="I47">
+        <v>2935308842.30234</v>
+      </c>
+      <c r="J47">
+        <v>870874549.238392</v>
+      </c>
+      <c r="K47">
+        <v>779477060.829031</v>
+      </c>
+      <c r="L47">
         <v>339549902.354795</v>
       </c>
-      <c r="I47">
+      <c r="M47">
         <v>14922253764.2577</v>
       </c>
-      <c r="J47">
+      <c r="N47">
         <v>5450163555.17058</v>
-      </c>
-      <c r="K47">
-        <v>10022285423.3735</v>
-      </c>
-      <c r="L47">
-        <v>2935308842.30234</v>
-      </c>
-      <c r="M47">
-        <v>870874549.238392</v>
-      </c>
-      <c r="N47">
-        <v>779477060.829031</v>
       </c>
       <c r="O47">
         <v>35379083319.2793</v>
@@ -45328,25 +45328,25 @@
         <v>10200278358.7208</v>
       </c>
       <c r="H48">
+        <v>10073518927.6953</v>
+      </c>
+      <c r="I48">
+        <v>2988888644.06531</v>
+      </c>
+      <c r="J48">
+        <v>917607914.887072</v>
+      </c>
+      <c r="K48">
+        <v>818772325.800249</v>
+      </c>
+      <c r="L48">
         <v>342579206.827817</v>
       </c>
-      <c r="I48">
+      <c r="M48">
         <v>15047681326.038</v>
       </c>
-      <c r="J48">
+      <c r="N48">
         <v>5445461426.54518</v>
-      </c>
-      <c r="K48">
-        <v>10073518927.6953</v>
-      </c>
-      <c r="L48">
-        <v>2988888644.06531</v>
-      </c>
-      <c r="M48">
-        <v>917607914.887072</v>
-      </c>
-      <c r="N48">
-        <v>818772325.800249</v>
       </c>
       <c r="O48">
         <v>35488280176.5162</v>
@@ -45383,25 +45383,25 @@
         <v>10354871723.8703</v>
       </c>
       <c r="H49">
+        <v>10107852158.21</v>
+      </c>
+      <c r="I49">
+        <v>3088653577.2636</v>
+      </c>
+      <c r="J49">
+        <v>938862937.838699</v>
+      </c>
+      <c r="K49">
+        <v>783468760.244848</v>
+      </c>
+      <c r="L49">
         <v>369011280.444004</v>
       </c>
-      <c r="I49">
+      <c r="M49">
         <v>15180440899.9081</v>
       </c>
-      <c r="J49">
+      <c r="N49">
         <v>5499561384.66893</v>
-      </c>
-      <c r="K49">
-        <v>10107852158.21</v>
-      </c>
-      <c r="L49">
-        <v>3088653577.2636</v>
-      </c>
-      <c r="M49">
-        <v>938862937.838699</v>
-      </c>
-      <c r="N49">
-        <v>783468760.244848</v>
       </c>
       <c r="O49">
         <v>35848122940.1682</v>
@@ -45438,25 +45438,25 @@
         <v>10503900276.5308</v>
       </c>
       <c r="H50">
+        <v>10218014772.184</v>
+      </c>
+      <c r="I50">
+        <v>3122422761.2326</v>
+      </c>
+      <c r="J50">
+        <v>934812756.667485</v>
+      </c>
+      <c r="K50">
+        <v>778046919.632817</v>
+      </c>
+      <c r="L50">
         <v>370216389.124042</v>
       </c>
-      <c r="I50">
+      <c r="M50">
         <v>15374412036.2338</v>
       </c>
-      <c r="J50">
+      <c r="N50">
         <v>5593122283.62349</v>
-      </c>
-      <c r="K50">
-        <v>10218014772.184</v>
-      </c>
-      <c r="L50">
-        <v>3122422761.2326</v>
-      </c>
-      <c r="M50">
-        <v>934812756.667485</v>
-      </c>
-      <c r="N50">
-        <v>778046919.632817</v>
       </c>
       <c r="O50">
         <v>36433782669.0039</v>
@@ -45493,25 +45493,25 @@
         <v>10545014275.2446</v>
       </c>
       <c r="H51">
+        <v>10295559924.9207</v>
+      </c>
+      <c r="I51">
+        <v>3174309354.75328</v>
+      </c>
+      <c r="J51">
+        <v>964595822.383848</v>
+      </c>
+      <c r="K51">
+        <v>770080787.518213</v>
+      </c>
+      <c r="L51">
         <v>373976421.65377</v>
       </c>
-      <c r="I51">
+      <c r="M51">
         <v>15489150193.093</v>
       </c>
-      <c r="J51">
+      <c r="N51">
         <v>5685816351.41656</v>
-      </c>
-      <c r="K51">
-        <v>10295559924.9207</v>
-      </c>
-      <c r="L51">
-        <v>3174309354.75328</v>
-      </c>
-      <c r="M51">
-        <v>964595822.383848</v>
-      </c>
-      <c r="N51">
-        <v>770080787.518213</v>
       </c>
       <c r="O51">
         <v>36819949994.7914</v>
@@ -45548,25 +45548,25 @@
         <v>10708748671.8926</v>
       </c>
       <c r="H52">
+        <v>10395934693.3553</v>
+      </c>
+      <c r="I52">
+        <v>3186789996.20811</v>
+      </c>
+      <c r="J52">
+        <v>973718886.831341</v>
+      </c>
+      <c r="K52">
+        <v>807565242.007517</v>
+      </c>
+      <c r="L52">
         <v>362869519.544392</v>
       </c>
-      <c r="I52">
+      <c r="M52">
         <v>15594987721.8723</v>
       </c>
-      <c r="J52">
+      <c r="N52">
         <v>5713595200.49905</v>
-      </c>
-      <c r="K52">
-        <v>10395934693.3553</v>
-      </c>
-      <c r="L52">
-        <v>3186789996.20811</v>
-      </c>
-      <c r="M52">
-        <v>973718886.831341</v>
-      </c>
-      <c r="N52">
-        <v>807565242.007517</v>
       </c>
       <c r="O52">
         <v>37066316245.141</v>
@@ -45603,25 +45603,25 @@
         <v>10757628122.6834</v>
       </c>
       <c r="H53">
+        <v>10391497466.4976</v>
+      </c>
+      <c r="I53">
+        <v>3256639381.83466</v>
+      </c>
+      <c r="J53">
+        <v>950350543.23893</v>
+      </c>
+      <c r="K53">
+        <v>777630154.392269</v>
+      </c>
+      <c r="L53">
         <v>369875442.194489</v>
       </c>
-      <c r="I53">
+      <c r="M53">
         <v>15707194208.2505</v>
       </c>
-      <c r="J53">
+      <c r="N53">
         <v>5761761253.83787</v>
-      </c>
-      <c r="K53">
-        <v>10391497466.4976</v>
-      </c>
-      <c r="L53">
-        <v>3256639381.83466</v>
-      </c>
-      <c r="M53">
-        <v>950350543.23893</v>
-      </c>
-      <c r="N53">
-        <v>777630154.392269</v>
       </c>
       <c r="O53">
         <v>37265784425.2771</v>
@@ -45658,25 +45658,25 @@
         <v>10801934583.6769</v>
       </c>
       <c r="H54">
+        <v>10484221091.1112</v>
+      </c>
+      <c r="I54">
+        <v>3288678692.05559</v>
+      </c>
+      <c r="J54">
+        <v>957359679.698217</v>
+      </c>
+      <c r="K54">
+        <v>820323722.406406</v>
+      </c>
+      <c r="L54">
         <v>387406676.700413</v>
       </c>
-      <c r="I54">
+      <c r="M54">
         <v>15763118920.2927</v>
       </c>
-      <c r="J54">
+      <c r="N54">
         <v>5798366962.69495</v>
-      </c>
-      <c r="K54">
-        <v>10484221091.1112</v>
-      </c>
-      <c r="L54">
-        <v>3288678692.05559</v>
-      </c>
-      <c r="M54">
-        <v>957359679.698217</v>
-      </c>
-      <c r="N54">
-        <v>820323722.406406</v>
       </c>
       <c r="O54">
         <v>37362488594.5646</v>
@@ -45713,25 +45713,25 @@
         <v>10830836099.0678</v>
       </c>
       <c r="H55">
+        <v>10610484296.5981</v>
+      </c>
+      <c r="I55">
+        <v>3359832499.95385</v>
+      </c>
+      <c r="J55">
+        <v>934472822.973532</v>
+      </c>
+      <c r="K55">
+        <v>855535230.653097</v>
+      </c>
+      <c r="L55">
         <v>386873789.265354</v>
       </c>
-      <c r="I55">
+      <c r="M55">
         <v>15863761634.7683</v>
       </c>
-      <c r="J55">
+      <c r="N55">
         <v>5818577989.61801</v>
-      </c>
-      <c r="K55">
-        <v>10610484296.5981</v>
-      </c>
-      <c r="L55">
-        <v>3359832499.95385</v>
-      </c>
-      <c r="M55">
-        <v>934472822.973532</v>
-      </c>
-      <c r="N55">
-        <v>855535230.653097</v>
       </c>
       <c r="O55">
         <v>37901312905.2826</v>
@@ -45768,25 +45768,25 @@
         <v>10919996876.7559</v>
       </c>
       <c r="H56">
+        <v>10398512634.8695</v>
+      </c>
+      <c r="I56">
+        <v>3384262984.91709</v>
+      </c>
+      <c r="J56">
+        <v>935223276.813377</v>
+      </c>
+      <c r="K56">
+        <v>836835200.8871239</v>
+      </c>
+      <c r="L56">
         <v>411871749.726311</v>
       </c>
-      <c r="I56">
+      <c r="M56">
         <v>15778403172.6152</v>
       </c>
-      <c r="J56">
+      <c r="N56">
         <v>5834966150.97459</v>
-      </c>
-      <c r="K56">
-        <v>10398512634.8695</v>
-      </c>
-      <c r="L56">
-        <v>3384262984.91709</v>
-      </c>
-      <c r="M56">
-        <v>935223276.813377</v>
-      </c>
-      <c r="N56">
-        <v>836835200.8871239</v>
       </c>
       <c r="O56">
         <v>37615476620.8762</v>
@@ -45846,37 +45846,37 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Atividades imobiliárias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Outras atividades de serviços</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Comércio</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Transporte, armazenagem e correio</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Informação e comunicação</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Atividades financeiras, de seguros e serviços relacionados</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -45920,25 +45920,25 @@
         <v>10608681140.6181</v>
       </c>
       <c r="H2">
+        <v>9146800158.51989</v>
+      </c>
+      <c r="I2">
+        <v>2342646337.71266</v>
+      </c>
+      <c r="J2">
+        <v>603115805.290084</v>
+      </c>
+      <c r="K2">
+        <v>571788067.8179539</v>
+      </c>
+      <c r="L2">
         <v>260383313.535038</v>
       </c>
-      <c r="I2">
+      <c r="M2">
         <v>11854373025.3271</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <v>4481772410.66826</v>
-      </c>
-      <c r="K2">
-        <v>9146800158.51989</v>
-      </c>
-      <c r="L2">
-        <v>2342646337.71266</v>
-      </c>
-      <c r="M2">
-        <v>603115805.290084</v>
-      </c>
-      <c r="N2">
-        <v>571788067.8179539</v>
       </c>
       <c r="O2">
         <v>29507281708.4974</v>
@@ -45975,25 +45975,25 @@
         <v>10740345473.5898</v>
       </c>
       <c r="H3">
+        <v>9197592111.22809</v>
+      </c>
+      <c r="I3">
+        <v>2336170641.23651</v>
+      </c>
+      <c r="J3">
+        <v>640134728.772626</v>
+      </c>
+      <c r="K3">
+        <v>600058654.2462341</v>
+      </c>
+      <c r="L3">
         <v>283039833.163486</v>
       </c>
-      <c r="I3">
+      <c r="M3">
         <v>11826104652.8317</v>
       </c>
-      <c r="J3">
+      <c r="N3">
         <v>4535382767.36108</v>
-      </c>
-      <c r="K3">
-        <v>9197592111.22809</v>
-      </c>
-      <c r="L3">
-        <v>2336170641.23651</v>
-      </c>
-      <c r="M3">
-        <v>640134728.772626</v>
-      </c>
-      <c r="N3">
-        <v>600058654.2462341</v>
       </c>
       <c r="O3">
         <v>29393054734.5283</v>
@@ -46030,25 +46030,25 @@
         <v>10839546871.7555</v>
       </c>
       <c r="H4">
+        <v>9145474688.158859</v>
+      </c>
+      <c r="I4">
+        <v>2398518925.43642</v>
+      </c>
+      <c r="J4">
+        <v>653718397.8987449</v>
+      </c>
+      <c r="K4">
+        <v>602785203.1198471</v>
+      </c>
+      <c r="L4">
         <v>275944193.074716</v>
       </c>
-      <c r="I4">
+      <c r="M4">
         <v>11946172385.189</v>
       </c>
-      <c r="J4">
+      <c r="N4">
         <v>4563586410.34743</v>
-      </c>
-      <c r="K4">
-        <v>9145474688.158859</v>
-      </c>
-      <c r="L4">
-        <v>2398518925.43642</v>
-      </c>
-      <c r="M4">
-        <v>653718397.8987449</v>
-      </c>
-      <c r="N4">
-        <v>602785203.1198471</v>
       </c>
       <c r="O4">
         <v>29518581308.6577</v>
@@ -46085,25 +46085,25 @@
         <v>10776234113.3776</v>
       </c>
       <c r="H5">
+        <v>9223902068.56859</v>
+      </c>
+      <c r="I5">
+        <v>2420104023.22673</v>
+      </c>
+      <c r="J5">
+        <v>634750509.17967</v>
+      </c>
+      <c r="K5">
+        <v>625875738.5689</v>
+      </c>
+      <c r="L5">
         <v>284110399.650582</v>
       </c>
-      <c r="I5">
+      <c r="M5">
         <v>11836276006.3594</v>
       </c>
-      <c r="J5">
+      <c r="N5">
         <v>4450500434.93909</v>
-      </c>
-      <c r="K5">
-        <v>9223902068.56859</v>
-      </c>
-      <c r="L5">
-        <v>2420104023.22673</v>
-      </c>
-      <c r="M5">
-        <v>634750509.17967</v>
-      </c>
-      <c r="N5">
-        <v>625875738.5689</v>
       </c>
       <c r="O5">
         <v>29380009981.6502</v>
@@ -46140,25 +46140,25 @@
         <v>10628290216.1556</v>
       </c>
       <c r="H6">
+        <v>9229647222.54051</v>
+      </c>
+      <c r="I6">
+        <v>2401346115.25599</v>
+      </c>
+      <c r="J6">
+        <v>644922264.427624</v>
+      </c>
+      <c r="K6">
+        <v>612761627.2855</v>
+      </c>
+      <c r="L6">
         <v>288688560.353468</v>
       </c>
-      <c r="I6">
+      <c r="M6">
         <v>11870467001.0963</v>
       </c>
-      <c r="J6">
+      <c r="N6">
         <v>4478881006.77006</v>
-      </c>
-      <c r="K6">
-        <v>9229647222.54051</v>
-      </c>
-      <c r="L6">
-        <v>2401346115.25599</v>
-      </c>
-      <c r="M6">
-        <v>644922264.427624</v>
-      </c>
-      <c r="N6">
-        <v>612761627.2855</v>
       </c>
       <c r="O6">
         <v>29538175128.26</v>
@@ -46195,25 +46195,25 @@
         <v>10879451566.2048</v>
       </c>
       <c r="H7">
+        <v>9371259923.2321</v>
+      </c>
+      <c r="I7">
+        <v>2438594079.54807</v>
+      </c>
+      <c r="J7">
+        <v>635962691.09232</v>
+      </c>
+      <c r="K7">
+        <v>643587954.0561889</v>
+      </c>
+      <c r="L7">
         <v>301959135.090164</v>
       </c>
-      <c r="I7">
+      <c r="M7">
         <v>12001578736.2275</v>
       </c>
-      <c r="J7">
+      <c r="N7">
         <v>4554417480.91818</v>
-      </c>
-      <c r="K7">
-        <v>9371259923.2321</v>
-      </c>
-      <c r="L7">
-        <v>2438594079.54807</v>
-      </c>
-      <c r="M7">
-        <v>635962691.09232</v>
-      </c>
-      <c r="N7">
-        <v>643587954.0561889</v>
       </c>
       <c r="O7">
         <v>29980059563.8707</v>
@@ -46250,25 +46250,25 @@
         <v>10956872771.8593</v>
       </c>
       <c r="H8">
+        <v>9587413062.950211</v>
+      </c>
+      <c r="I8">
+        <v>2451749766.1275</v>
+      </c>
+      <c r="J8">
+        <v>646965155.808744</v>
+      </c>
+      <c r="K8">
+        <v>629924612.458873</v>
+      </c>
+      <c r="L8">
         <v>308527570.891261</v>
       </c>
-      <c r="I8">
+      <c r="M8">
         <v>12155862540.5628</v>
       </c>
-      <c r="J8">
+      <c r="N8">
         <v>4556435112.29097</v>
-      </c>
-      <c r="K8">
-        <v>9587413062.950211</v>
-      </c>
-      <c r="L8">
-        <v>2451749766.1275</v>
-      </c>
-      <c r="M8">
-        <v>646965155.808744</v>
-      </c>
-      <c r="N8">
-        <v>629924612.458873</v>
       </c>
       <c r="O8">
         <v>30232353031.1055</v>
@@ -46305,25 +46305,25 @@
         <v>10970385007.1273</v>
       </c>
       <c r="H9">
+        <v>9613465476.30703</v>
+      </c>
+      <c r="I9">
+        <v>2385169390.65399</v>
+      </c>
+      <c r="J9">
+        <v>667200649.679898</v>
+      </c>
+      <c r="K9">
+        <v>628341561.304727</v>
+      </c>
+      <c r="L9">
         <v>288574708.688754</v>
       </c>
-      <c r="I9">
+      <c r="M9">
         <v>12339552173.8234</v>
       </c>
-      <c r="J9">
+      <c r="N9">
         <v>4604721761.78548</v>
-      </c>
-      <c r="K9">
-        <v>9613465476.30703</v>
-      </c>
-      <c r="L9">
-        <v>2385169390.65399</v>
-      </c>
-      <c r="M9">
-        <v>667200649.679898</v>
-      </c>
-      <c r="N9">
-        <v>628341561.304727</v>
       </c>
       <c r="O9">
         <v>30542699152.7452</v>
@@ -46360,25 +46360,25 @@
         <v>11097956937.1513</v>
       </c>
       <c r="H10">
+        <v>9647658954.842421</v>
+      </c>
+      <c r="I10">
+        <v>2360815905.6244</v>
+      </c>
+      <c r="J10">
+        <v>665136417.767483</v>
+      </c>
+      <c r="K10">
+        <v>633532434.83295</v>
+      </c>
+      <c r="L10">
         <v>278750638.295955</v>
       </c>
-      <c r="I10">
+      <c r="M10">
         <v>12502232307.2046</v>
       </c>
-      <c r="J10">
+      <c r="N10">
         <v>4652527298.14761</v>
-      </c>
-      <c r="K10">
-        <v>9647658954.842421</v>
-      </c>
-      <c r="L10">
-        <v>2360815905.6244</v>
-      </c>
-      <c r="M10">
-        <v>665136417.767483</v>
-      </c>
-      <c r="N10">
-        <v>633532434.83295</v>
       </c>
       <c r="O10">
         <v>30710350281.9357</v>
@@ -46415,25 +46415,25 @@
         <v>10934399826.7324</v>
       </c>
       <c r="H11">
+        <v>9505650360.218081</v>
+      </c>
+      <c r="I11">
+        <v>2374790786.0276</v>
+      </c>
+      <c r="J11">
+        <v>670777930.566033</v>
+      </c>
+      <c r="K11">
+        <v>621061467.061254</v>
+      </c>
+      <c r="L11">
         <v>271727140.599882</v>
       </c>
-      <c r="I11">
+      <c r="M11">
         <v>12594409992.5364</v>
       </c>
-      <c r="J11">
+      <c r="N11">
         <v>4599271953.21393</v>
-      </c>
-      <c r="K11">
-        <v>9505650360.218081</v>
-      </c>
-      <c r="L11">
-        <v>2374790786.0276</v>
-      </c>
-      <c r="M11">
-        <v>670777930.566033</v>
-      </c>
-      <c r="N11">
-        <v>621061467.061254</v>
       </c>
       <c r="O11">
         <v>30598708215.711</v>
@@ -46470,25 +46470,25 @@
         <v>10868076359.3557</v>
       </c>
       <c r="H12">
+        <v>9412500578.149549</v>
+      </c>
+      <c r="I12">
+        <v>2343150274.26397</v>
+      </c>
+      <c r="J12">
+        <v>655181542.146883</v>
+      </c>
+      <c r="K12">
+        <v>647245850.08885</v>
+      </c>
+      <c r="L12">
         <v>274762393.810079</v>
       </c>
-      <c r="I12">
+      <c r="M12">
         <v>12671982599.9353</v>
       </c>
-      <c r="J12">
+      <c r="N12">
         <v>4605387073.54266</v>
-      </c>
-      <c r="K12">
-        <v>9412500578.149549</v>
-      </c>
-      <c r="L12">
-        <v>2343150274.26397</v>
-      </c>
-      <c r="M12">
-        <v>655181542.146883</v>
-      </c>
-      <c r="N12">
-        <v>647245850.08885</v>
       </c>
       <c r="O12">
         <v>30614112140.7228</v>
@@ -46525,25 +46525,25 @@
         <v>10871297595.3798</v>
       </c>
       <c r="H13">
+        <v>9437710980.300791</v>
+      </c>
+      <c r="I13">
+        <v>2367389486.20338</v>
+      </c>
+      <c r="J13">
+        <v>658274777.731145</v>
+      </c>
+      <c r="K13">
+        <v>635542181.335292</v>
+      </c>
+      <c r="L13">
         <v>318403186.688545</v>
       </c>
-      <c r="I13">
+      <c r="M13">
         <v>12684917432.8165</v>
       </c>
-      <c r="J13">
+      <c r="N13">
         <v>4613652622.90233</v>
-      </c>
-      <c r="K13">
-        <v>9437710980.300791</v>
-      </c>
-      <c r="L13">
-        <v>2367389486.20338</v>
-      </c>
-      <c r="M13">
-        <v>658274777.731145</v>
-      </c>
-      <c r="N13">
-        <v>635542181.335292</v>
       </c>
       <c r="O13">
         <v>30948749860.6433</v>
@@ -46580,25 +46580,25 @@
         <v>10913342779.4181</v>
       </c>
       <c r="H14">
+        <v>9522817942.354309</v>
+      </c>
+      <c r="I14">
+        <v>2417193475.38637</v>
+      </c>
+      <c r="J14">
+        <v>656590114.096514</v>
+      </c>
+      <c r="K14">
+        <v>615687771.678596</v>
+      </c>
+      <c r="L14">
         <v>298996315.644005</v>
       </c>
-      <c r="I14">
+      <c r="M14">
         <v>12683745910.1251</v>
       </c>
-      <c r="J14">
+      <c r="N14">
         <v>4596752414.71799</v>
-      </c>
-      <c r="K14">
-        <v>9522817942.354309</v>
-      </c>
-      <c r="L14">
-        <v>2417193475.38637</v>
-      </c>
-      <c r="M14">
-        <v>656590114.096514</v>
-      </c>
-      <c r="N14">
-        <v>615687771.678596</v>
       </c>
       <c r="O14">
         <v>30540128436.2976</v>
@@ -46635,25 +46635,25 @@
         <v>10388418108.1315</v>
       </c>
       <c r="H15">
+        <v>9532810562.88023</v>
+      </c>
+      <c r="I15">
+        <v>2372246841.28243</v>
+      </c>
+      <c r="J15">
+        <v>652789194.78738</v>
+      </c>
+      <c r="K15">
+        <v>609050937.99182</v>
+      </c>
+      <c r="L15">
         <v>303970197.526069</v>
       </c>
-      <c r="I15">
+      <c r="M15">
         <v>12759642981.746</v>
       </c>
-      <c r="J15">
+      <c r="N15">
         <v>4618015797.69833</v>
-      </c>
-      <c r="K15">
-        <v>9532810562.88023</v>
-      </c>
-      <c r="L15">
-        <v>2372246841.28243</v>
-      </c>
-      <c r="M15">
-        <v>652789194.78738</v>
-      </c>
-      <c r="N15">
-        <v>609050937.99182</v>
       </c>
       <c r="O15">
         <v>30817903795.7402</v>
@@ -46690,25 +46690,25 @@
         <v>10211726569.1954</v>
       </c>
       <c r="H16">
+        <v>9497427730.43055</v>
+      </c>
+      <c r="I16">
+        <v>2357164321.26095</v>
+      </c>
+      <c r="J16">
+        <v>668165105.605286</v>
+      </c>
+      <c r="K16">
+        <v>572686368.857489</v>
+      </c>
+      <c r="L16">
         <v>295953830.939219</v>
       </c>
-      <c r="I16">
+      <c r="M16">
         <v>12624252249.7572</v>
       </c>
-      <c r="J16">
+      <c r="N16">
         <v>4566489372.94399</v>
-      </c>
-      <c r="K16">
-        <v>9497427730.43055</v>
-      </c>
-      <c r="L16">
-        <v>2357164321.26095</v>
-      </c>
-      <c r="M16">
-        <v>668165105.605286</v>
-      </c>
-      <c r="N16">
-        <v>572686368.857489</v>
       </c>
       <c r="O16">
         <v>30790354022.7986</v>
@@ -46745,25 +46745,25 @@
         <v>10341480188.202</v>
       </c>
       <c r="H17">
+        <v>9309552660.31476</v>
+      </c>
+      <c r="I17">
+        <v>2417623770.49469</v>
+      </c>
+      <c r="J17">
+        <v>614374386.637745</v>
+      </c>
+      <c r="K17">
+        <v>563766474.86322</v>
+      </c>
+      <c r="L17">
         <v>285263872.927715</v>
       </c>
-      <c r="I17">
+      <c r="M17">
         <v>12685450305.0958</v>
       </c>
-      <c r="J17">
+      <c r="N17">
         <v>4698825798.49714</v>
-      </c>
-      <c r="K17">
-        <v>9309552660.31476</v>
-      </c>
-      <c r="L17">
-        <v>2417623770.49469</v>
-      </c>
-      <c r="M17">
-        <v>614374386.637745</v>
-      </c>
-      <c r="N17">
-        <v>563766474.86322</v>
       </c>
       <c r="O17">
         <v>30610999499.9496</v>
@@ -46800,25 +46800,25 @@
         <v>10111587204.4606</v>
       </c>
       <c r="H18">
+        <v>9253314644.73914</v>
+      </c>
+      <c r="I18">
+        <v>2428881806.19709</v>
+      </c>
+      <c r="J18">
+        <v>623678158.048301</v>
+      </c>
+      <c r="K18">
+        <v>583324257.359429</v>
+      </c>
+      <c r="L18">
         <v>286799681.780511</v>
       </c>
-      <c r="I18">
+      <c r="M18">
         <v>12668997185.7662</v>
       </c>
-      <c r="J18">
+      <c r="N18">
         <v>4714841195.35662</v>
-      </c>
-      <c r="K18">
-        <v>9253314644.73914</v>
-      </c>
-      <c r="L18">
-        <v>2428881806.19709</v>
-      </c>
-      <c r="M18">
-        <v>623678158.048301</v>
-      </c>
-      <c r="N18">
-        <v>583324257.359429</v>
       </c>
       <c r="O18">
         <v>30747572298.6016</v>
@@ -46855,25 +46855,25 @@
         <v>9752136853.52593</v>
       </c>
       <c r="H19">
+        <v>9215025476.16256</v>
+      </c>
+      <c r="I19">
+        <v>2410207703.52513</v>
+      </c>
+      <c r="J19">
+        <v>616177246.310585</v>
+      </c>
+      <c r="K19">
+        <v>573058551.706923</v>
+      </c>
+      <c r="L19">
         <v>272486677.581798</v>
       </c>
-      <c r="I19">
+      <c r="M19">
         <v>12671309520.7505</v>
       </c>
-      <c r="J19">
+      <c r="N19">
         <v>4648620131.76698</v>
-      </c>
-      <c r="K19">
-        <v>9215025476.16256</v>
-      </c>
-      <c r="L19">
-        <v>2410207703.52513</v>
-      </c>
-      <c r="M19">
-        <v>616177246.310585</v>
-      </c>
-      <c r="N19">
-        <v>573058551.706923</v>
       </c>
       <c r="O19">
         <v>30441015269.3842</v>
@@ -46910,25 +46910,25 @@
         <v>9449041100.72097</v>
       </c>
       <c r="H20">
+        <v>9039921306.18899</v>
+      </c>
+      <c r="I20">
+        <v>2441978226.24852</v>
+      </c>
+      <c r="J20">
+        <v>613079695.733613</v>
+      </c>
+      <c r="K20">
+        <v>592304418.178002</v>
+      </c>
+      <c r="L20">
         <v>268501826.982207</v>
       </c>
-      <c r="I20">
+      <c r="M20">
         <v>12592933858.5684</v>
       </c>
-      <c r="J20">
+      <c r="N20">
         <v>4670977825.47347</v>
-      </c>
-      <c r="K20">
-        <v>9039921306.18899</v>
-      </c>
-      <c r="L20">
-        <v>2441978226.24852</v>
-      </c>
-      <c r="M20">
-        <v>613079695.733613</v>
-      </c>
-      <c r="N20">
-        <v>592304418.178002</v>
       </c>
       <c r="O20">
         <v>30056546480.1035</v>
@@ -46965,25 +46965,25 @@
         <v>9318418636.819521</v>
       </c>
       <c r="H21">
+        <v>9153799182.3067</v>
+      </c>
+      <c r="I21">
+        <v>2437025028.78113</v>
+      </c>
+      <c r="J21">
+        <v>629594443.194762</v>
+      </c>
+      <c r="K21">
+        <v>603845545.534363</v>
+      </c>
+      <c r="L21">
         <v>293801556.392374</v>
       </c>
-      <c r="I21">
+      <c r="M21">
         <v>12644600587.5533</v>
       </c>
-      <c r="J21">
+      <c r="N21">
         <v>4639205414.19097</v>
-      </c>
-      <c r="K21">
-        <v>9153799182.3067</v>
-      </c>
-      <c r="L21">
-        <v>2437025028.78113</v>
-      </c>
-      <c r="M21">
-        <v>629594443.194762</v>
-      </c>
-      <c r="N21">
-        <v>603845545.534363</v>
       </c>
       <c r="O21">
         <v>30403339113.8599</v>
@@ -47020,25 +47020,25 @@
         <v>9315057504.316401</v>
       </c>
       <c r="H22">
+        <v>9070756152.22674</v>
+      </c>
+      <c r="I22">
+        <v>2408626840.37131</v>
+      </c>
+      <c r="J22">
+        <v>624578732.651566</v>
+      </c>
+      <c r="K22">
+        <v>611199965.173559</v>
+      </c>
+      <c r="L22">
         <v>304349387.930851</v>
       </c>
-      <c r="I22">
+      <c r="M22">
         <v>12772465764.6819</v>
       </c>
-      <c r="J22">
+      <c r="N22">
         <v>4591185879.67558</v>
-      </c>
-      <c r="K22">
-        <v>9070756152.22674</v>
-      </c>
-      <c r="L22">
-        <v>2408626840.37131</v>
-      </c>
-      <c r="M22">
-        <v>624578732.651566</v>
-      </c>
-      <c r="N22">
-        <v>611199965.173559</v>
       </c>
       <c r="O22">
         <v>30397310360.3676</v>
@@ -47075,25 +47075,25 @@
         <v>9296709058.76256</v>
       </c>
       <c r="H23">
+        <v>9075885131.51827</v>
+      </c>
+      <c r="I23">
+        <v>2447804407.67334</v>
+      </c>
+      <c r="J23">
+        <v>621426783.860549</v>
+      </c>
+      <c r="K23">
+        <v>572154551.556422</v>
+      </c>
+      <c r="L23">
         <v>280123116.310657</v>
       </c>
-      <c r="I23">
+      <c r="M23">
         <v>12842293871.706</v>
       </c>
-      <c r="J23">
+      <c r="N23">
         <v>4604207702.62574</v>
-      </c>
-      <c r="K23">
-        <v>9075885131.51827</v>
-      </c>
-      <c r="L23">
-        <v>2447804407.67334</v>
-      </c>
-      <c r="M23">
-        <v>621426783.860549</v>
-      </c>
-      <c r="N23">
-        <v>572154551.556422</v>
       </c>
       <c r="O23">
         <v>30425745259.1353</v>
@@ -47130,25 +47130,25 @@
         <v>9310037368.34096</v>
       </c>
       <c r="H24">
+        <v>9111720394.162979</v>
+      </c>
+      <c r="I24">
+        <v>2482822588.7468</v>
+      </c>
+      <c r="J24">
+        <v>639062723.823559</v>
+      </c>
+      <c r="K24">
+        <v>600698678.0572571</v>
+      </c>
+      <c r="L24">
         <v>279869071.419836</v>
       </c>
-      <c r="I24">
+      <c r="M24">
         <v>12973177090.5745</v>
       </c>
-      <c r="J24">
+      <c r="N24">
         <v>4631024264.77021</v>
-      </c>
-      <c r="K24">
-        <v>9111720394.162979</v>
-      </c>
-      <c r="L24">
-        <v>2482822588.7468</v>
-      </c>
-      <c r="M24">
-        <v>639062723.823559</v>
-      </c>
-      <c r="N24">
-        <v>600698678.0572571</v>
       </c>
       <c r="O24">
         <v>30620178910.9569</v>
@@ -47185,25 +47185,25 @@
         <v>9233856581.80312</v>
       </c>
       <c r="H25">
+        <v>9151081870.40807</v>
+      </c>
+      <c r="I25">
+        <v>2374632636.2032</v>
+      </c>
+      <c r="J25">
+        <v>611459157.77494</v>
+      </c>
+      <c r="K25">
+        <v>592174434.9785579</v>
+      </c>
+      <c r="L25">
         <v>263408652.415264</v>
       </c>
-      <c r="I25">
+      <c r="M25">
         <v>13049214064.8572</v>
       </c>
-      <c r="J25">
+      <c r="N25">
         <v>4605645455.38766</v>
-      </c>
-      <c r="K25">
-        <v>9151081870.40807</v>
-      </c>
-      <c r="L25">
-        <v>2374632636.2032</v>
-      </c>
-      <c r="M25">
-        <v>611459157.77494</v>
-      </c>
-      <c r="N25">
-        <v>592174434.9785579</v>
       </c>
       <c r="O25">
         <v>30631193223.7321</v>
@@ -47240,25 +47240,25 @@
         <v>9152353120.83667</v>
       </c>
       <c r="H26">
+        <v>9129094757.955839</v>
+      </c>
+      <c r="I26">
+        <v>2455744873.03371</v>
+      </c>
+      <c r="J26">
+        <v>609258191.642458</v>
+      </c>
+      <c r="K26">
+        <v>578410038.397591</v>
+      </c>
+      <c r="L26">
         <v>273481714.505151</v>
       </c>
-      <c r="I26">
+      <c r="M26">
         <v>13126008612.7327</v>
       </c>
-      <c r="J26">
+      <c r="N26">
         <v>4625739841.7805</v>
-      </c>
-      <c r="K26">
-        <v>9129094757.955839</v>
-      </c>
-      <c r="L26">
-        <v>2455744873.03371</v>
-      </c>
-      <c r="M26">
-        <v>609258191.642458</v>
-      </c>
-      <c r="N26">
-        <v>578410038.397591</v>
       </c>
       <c r="O26">
         <v>30774061936.3263</v>
@@ -47295,25 +47295,25 @@
         <v>9278424416.989719</v>
       </c>
       <c r="H27">
+        <v>9106738718.627951</v>
+      </c>
+      <c r="I27">
+        <v>2475659468.00614</v>
+      </c>
+      <c r="J27">
+        <v>616640367.2785</v>
+      </c>
+      <c r="K27">
+        <v>599808660.4203449</v>
+      </c>
+      <c r="L27">
         <v>288059328.199859</v>
       </c>
-      <c r="I27">
+      <c r="M27">
         <v>13153299567.9267</v>
       </c>
-      <c r="J27">
+      <c r="N27">
         <v>4669322545.79346</v>
-      </c>
-      <c r="K27">
-        <v>9106738718.627951</v>
-      </c>
-      <c r="L27">
-        <v>2475659468.00614</v>
-      </c>
-      <c r="M27">
-        <v>616640367.2785</v>
-      </c>
-      <c r="N27">
-        <v>599808660.4203449</v>
       </c>
       <c r="O27">
         <v>30981980801.5147</v>
@@ -47350,25 +47350,25 @@
         <v>9265040924.550421</v>
       </c>
       <c r="H28">
+        <v>9212185669.379379</v>
+      </c>
+      <c r="I28">
+        <v>2502411181.47115</v>
+      </c>
+      <c r="J28">
+        <v>643481726.424035</v>
+      </c>
+      <c r="K28">
+        <v>605213642.242316</v>
+      </c>
+      <c r="L28">
         <v>291520526.313698</v>
       </c>
-      <c r="I28">
+      <c r="M28">
         <v>13321441672.4913</v>
       </c>
-      <c r="J28">
+      <c r="N28">
         <v>4739299308.14335</v>
-      </c>
-      <c r="K28">
-        <v>9212185669.379379</v>
-      </c>
-      <c r="L28">
-        <v>2502411181.47115</v>
-      </c>
-      <c r="M28">
-        <v>643481726.424035</v>
-      </c>
-      <c r="N28">
-        <v>605213642.242316</v>
       </c>
       <c r="O28">
         <v>31160105127.6287</v>
@@ -47405,25 +47405,25 @@
         <v>9111334330.626631</v>
       </c>
       <c r="H29">
+        <v>9158187106.472919</v>
+      </c>
+      <c r="I29">
+        <v>2515554271.88929</v>
+      </c>
+      <c r="J29">
+        <v>647243722.737466</v>
+      </c>
+      <c r="K29">
+        <v>589011792.817012</v>
+      </c>
+      <c r="L29">
         <v>286001738.132495</v>
       </c>
-      <c r="I29">
+      <c r="M29">
         <v>13414719792.7242</v>
       </c>
-      <c r="J29">
+      <c r="N29">
         <v>4664969525.65088</v>
-      </c>
-      <c r="K29">
-        <v>9158187106.472919</v>
-      </c>
-      <c r="L29">
-        <v>2515554271.88929</v>
-      </c>
-      <c r="M29">
-        <v>647243722.737466</v>
-      </c>
-      <c r="N29">
-        <v>589011792.817012</v>
       </c>
       <c r="O29">
         <v>31224242923.3924</v>
@@ -47460,25 +47460,25 @@
         <v>9156026881.961399</v>
       </c>
       <c r="H30">
+        <v>9192286076.06216</v>
+      </c>
+      <c r="I30">
+        <v>2569430168.60422</v>
+      </c>
+      <c r="J30">
+        <v>658526515.639581</v>
+      </c>
+      <c r="K30">
+        <v>603105874.9369169</v>
+      </c>
+      <c r="L30">
         <v>289822076.398565</v>
       </c>
-      <c r="I30">
+      <c r="M30">
         <v>13527586543.762</v>
       </c>
-      <c r="J30">
+      <c r="N30">
         <v>4662866585.09943</v>
-      </c>
-      <c r="K30">
-        <v>9192286076.06216</v>
-      </c>
-      <c r="L30">
-        <v>2569430168.60422</v>
-      </c>
-      <c r="M30">
-        <v>658526515.639581</v>
-      </c>
-      <c r="N30">
-        <v>603105874.9369169</v>
       </c>
       <c r="O30">
         <v>31575490920.4697</v>
@@ -47515,25 +47515,25 @@
         <v>9369716472.96159</v>
       </c>
       <c r="H31">
+        <v>9241223562.90646</v>
+      </c>
+      <c r="I31">
+        <v>2639401804.179</v>
+      </c>
+      <c r="J31">
+        <v>659551522.327678</v>
+      </c>
+      <c r="K31">
+        <v>634457010.297294</v>
+      </c>
+      <c r="L31">
         <v>283191796.960089</v>
       </c>
-      <c r="I31">
+      <c r="M31">
         <v>13669727363.8558</v>
       </c>
-      <c r="J31">
+      <c r="N31">
         <v>4725925932.34419</v>
-      </c>
-      <c r="K31">
-        <v>9241223562.90646</v>
-      </c>
-      <c r="L31">
-        <v>2639401804.179</v>
-      </c>
-      <c r="M31">
-        <v>659551522.327678</v>
-      </c>
-      <c r="N31">
-        <v>634457010.297294</v>
       </c>
       <c r="O31">
         <v>31890496817.3102</v>
@@ -47570,25 +47570,25 @@
         <v>9454777203.82181</v>
       </c>
       <c r="H32">
+        <v>9302495313.63615</v>
+      </c>
+      <c r="I32">
+        <v>2664556118.52737</v>
+      </c>
+      <c r="J32">
+        <v>664793129.141142</v>
+      </c>
+      <c r="K32">
+        <v>625748946.640962</v>
+      </c>
+      <c r="L32">
         <v>284808140.430627</v>
       </c>
-      <c r="I32">
+      <c r="M32">
         <v>13824655219.9402</v>
       </c>
-      <c r="J32">
+      <c r="N32">
         <v>4732686997.61165</v>
-      </c>
-      <c r="K32">
-        <v>9302495313.63615</v>
-      </c>
-      <c r="L32">
-        <v>2664556118.52737</v>
-      </c>
-      <c r="M32">
-        <v>664793129.141142</v>
-      </c>
-      <c r="N32">
-        <v>625748946.640962</v>
       </c>
       <c r="O32">
         <v>31890262618.7172</v>
@@ -47625,25 +47625,25 @@
         <v>9395517124.677389</v>
       </c>
       <c r="H33">
+        <v>9373948409.791691</v>
+      </c>
+      <c r="I33">
+        <v>2646732847.66306</v>
+      </c>
+      <c r="J33">
+        <v>682338621.894897</v>
+      </c>
+      <c r="K33">
+        <v>604296564.746295</v>
+      </c>
+      <c r="L33">
         <v>285347962.825656</v>
       </c>
-      <c r="I33">
+      <c r="M33">
         <v>14043626377.0767</v>
       </c>
-      <c r="J33">
+      <c r="N33">
         <v>4762313609.50616</v>
-      </c>
-      <c r="K33">
-        <v>9373948409.791691</v>
-      </c>
-      <c r="L33">
-        <v>2646732847.66306</v>
-      </c>
-      <c r="M33">
-        <v>682338621.894897</v>
-      </c>
-      <c r="N33">
-        <v>604296564.746295</v>
       </c>
       <c r="O33">
         <v>32445104855.9939</v>
@@ -47680,25 +47680,25 @@
         <v>9040159058.044941</v>
       </c>
       <c r="H34">
+        <v>8751546317.002251</v>
+      </c>
+      <c r="I34">
+        <v>2549615866.32388</v>
+      </c>
+      <c r="J34">
+        <v>702042920.970094</v>
+      </c>
+      <c r="K34">
+        <v>589091775.6438659</v>
+      </c>
+      <c r="L34">
         <v>259035297.320536</v>
       </c>
-      <c r="I34">
+      <c r="M34">
         <v>12955615043.1657</v>
       </c>
-      <c r="J34">
+      <c r="N34">
         <v>4502495425.80661</v>
-      </c>
-      <c r="K34">
-        <v>8751546317.002251</v>
-      </c>
-      <c r="L34">
-        <v>2549615866.32388</v>
-      </c>
-      <c r="M34">
-        <v>702042920.970094</v>
-      </c>
-      <c r="N34">
-        <v>589091775.6438659</v>
       </c>
       <c r="O34">
         <v>30546893466.5182</v>
@@ -47735,25 +47735,25 @@
         <v>6829505442.54336</v>
       </c>
       <c r="H35">
+        <v>6603234219.15261</v>
+      </c>
+      <c r="I35">
+        <v>1885365500.82691</v>
+      </c>
+      <c r="J35">
+        <v>595540425.205996</v>
+      </c>
+      <c r="K35">
+        <v>541059276.824716</v>
+      </c>
+      <c r="L35">
         <v>198394904.098481</v>
       </c>
-      <c r="I35">
+      <c r="M35">
         <v>8689596251.988171</v>
       </c>
-      <c r="J35">
+      <c r="N35">
         <v>3912717336.07881</v>
-      </c>
-      <c r="K35">
-        <v>6603234219.15261</v>
-      </c>
-      <c r="L35">
-        <v>1885365500.82691</v>
-      </c>
-      <c r="M35">
-        <v>595540425.205996</v>
-      </c>
-      <c r="N35">
-        <v>541059276.824716</v>
       </c>
       <c r="O35">
         <v>22486098691.8059</v>
@@ -47790,25 +47790,25 @@
         <v>7959253887.42906</v>
       </c>
       <c r="H36">
+        <v>7779697146.38698</v>
+      </c>
+      <c r="I36">
+        <v>2157978045.19253</v>
+      </c>
+      <c r="J36">
+        <v>680526686.134938</v>
+      </c>
+      <c r="K36">
+        <v>574640808.655622</v>
+      </c>
+      <c r="L36">
         <v>259909101.68756</v>
       </c>
-      <c r="I36">
+      <c r="M36">
         <v>10281225774.5806</v>
       </c>
-      <c r="J36">
+      <c r="N36">
         <v>4491677742.17573</v>
-      </c>
-      <c r="K36">
-        <v>7779697146.38698</v>
-      </c>
-      <c r="L36">
-        <v>2157978045.19253</v>
-      </c>
-      <c r="M36">
-        <v>680526686.134938</v>
-      </c>
-      <c r="N36">
-        <v>574640808.655622</v>
       </c>
       <c r="O36">
         <v>26333866763.3252</v>
@@ -47845,25 +47845,25 @@
         <v>8528400563.79773</v>
       </c>
       <c r="H37">
+        <v>8309741617.17515</v>
+      </c>
+      <c r="I37">
+        <v>2299339729.68842</v>
+      </c>
+      <c r="J37">
+        <v>711166492.697983</v>
+      </c>
+      <c r="K37">
+        <v>652888015.215705</v>
+      </c>
+      <c r="L37">
         <v>263192458.33337</v>
       </c>
-      <c r="I37">
+      <c r="M37">
         <v>11378682152.8344</v>
       </c>
-      <c r="J37">
+      <c r="N37">
         <v>4823441698.09249</v>
-      </c>
-      <c r="K37">
-        <v>8309741617.17515</v>
-      </c>
-      <c r="L37">
-        <v>2299339729.68842</v>
-      </c>
-      <c r="M37">
-        <v>711166492.697983</v>
-      </c>
-      <c r="N37">
-        <v>652888015.215705</v>
       </c>
       <c r="O37">
         <v>28485932267.5636</v>
@@ -47900,25 +47900,25 @@
         <v>8911158265.376169</v>
       </c>
       <c r="H38">
+        <v>8409314693.74177</v>
+      </c>
+      <c r="I38">
+        <v>2423143577.04036</v>
+      </c>
+      <c r="J38">
+        <v>759298168.764493</v>
+      </c>
+      <c r="K38">
+        <v>673858393.848408</v>
+      </c>
+      <c r="L38">
         <v>298124042.750143</v>
       </c>
-      <c r="I38">
+      <c r="M38">
         <v>11762540033.2728</v>
       </c>
-      <c r="J38">
+      <c r="N38">
         <v>4965054926.22305</v>
-      </c>
-      <c r="K38">
-        <v>8409314693.74177</v>
-      </c>
-      <c r="L38">
-        <v>2423143577.04036</v>
-      </c>
-      <c r="M38">
-        <v>759298168.764493</v>
-      </c>
-      <c r="N38">
-        <v>673858393.848408</v>
       </c>
       <c r="O38">
         <v>29219770011.4446</v>
@@ -47955,25 +47955,25 @@
         <v>8977867715.7199</v>
       </c>
       <c r="H39">
+        <v>8525761820.45254</v>
+      </c>
+      <c r="I39">
+        <v>2442943561.73028</v>
+      </c>
+      <c r="J39">
+        <v>779731167.057803</v>
+      </c>
+      <c r="K39">
+        <v>671061846.872622</v>
+      </c>
+      <c r="L39">
         <v>279370074.902941</v>
       </c>
-      <c r="I39">
+      <c r="M39">
         <v>12076536641.1538</v>
       </c>
-      <c r="J39">
+      <c r="N39">
         <v>4854523789.45125</v>
-      </c>
-      <c r="K39">
-        <v>8525761820.45254</v>
-      </c>
-      <c r="L39">
-        <v>2442943561.73028</v>
-      </c>
-      <c r="M39">
-        <v>779731167.057803</v>
-      </c>
-      <c r="N39">
-        <v>671061846.872622</v>
       </c>
       <c r="O39">
         <v>29697911013.0883</v>
@@ -48010,25 +48010,25 @@
         <v>9495142735.695971</v>
       </c>
       <c r="H40">
+        <v>9204170345.776331</v>
+      </c>
+      <c r="I40">
+        <v>2588906096.24649</v>
+      </c>
+      <c r="J40">
+        <v>767491131.062305</v>
+      </c>
+      <c r="K40">
+        <v>659847147.109975</v>
+      </c>
+      <c r="L40">
         <v>290494123.124202</v>
       </c>
-      <c r="I40">
+      <c r="M40">
         <v>12755477292.6898</v>
       </c>
-      <c r="J40">
+      <c r="N40">
         <v>4771853163.96864</v>
-      </c>
-      <c r="K40">
-        <v>9204170345.776331</v>
-      </c>
-      <c r="L40">
-        <v>2588906096.24649</v>
-      </c>
-      <c r="M40">
-        <v>767491131.062305</v>
-      </c>
-      <c r="N40">
-        <v>659847147.109975</v>
       </c>
       <c r="O40">
         <v>30981154543.3118</v>
@@ -48065,25 +48065,25 @@
         <v>9779243450.47526</v>
       </c>
       <c r="H41">
+        <v>9468911264.114941</v>
+      </c>
+      <c r="I41">
+        <v>2600749599.87583</v>
+      </c>
+      <c r="J41">
+        <v>863921359.609531</v>
+      </c>
+      <c r="K41">
+        <v>682156784.024604</v>
+      </c>
+      <c r="L41">
         <v>291491879.366317</v>
       </c>
-      <c r="I41">
+      <c r="M41">
         <v>13552022010.5766</v>
       </c>
-      <c r="J41">
+      <c r="N41">
         <v>4892084520.58992</v>
-      </c>
-      <c r="K41">
-        <v>9468911264.114941</v>
-      </c>
-      <c r="L41">
-        <v>2600749599.87583</v>
-      </c>
-      <c r="M41">
-        <v>863921359.609531</v>
-      </c>
-      <c r="N41">
-        <v>682156784.024604</v>
       </c>
       <c r="O41">
         <v>32235919973.0086</v>
@@ -48120,25 +48120,25 @@
         <v>9831561324.869539</v>
       </c>
       <c r="H42">
+        <v>9631645062.92061</v>
+      </c>
+      <c r="I42">
+        <v>2640940125.44059</v>
+      </c>
+      <c r="J42">
+        <v>840141814.646948</v>
+      </c>
+      <c r="K42">
+        <v>689429908.583925</v>
+      </c>
+      <c r="L42">
         <v>300662977.099228</v>
       </c>
-      <c r="I42">
+      <c r="M42">
         <v>13848006587.6154</v>
       </c>
-      <c r="J42">
+      <c r="N42">
         <v>4935969824.00465</v>
-      </c>
-      <c r="K42">
-        <v>9631645062.92061</v>
-      </c>
-      <c r="L42">
-        <v>2640940125.44059</v>
-      </c>
-      <c r="M42">
-        <v>840141814.646948</v>
-      </c>
-      <c r="N42">
-        <v>689429908.583925</v>
       </c>
       <c r="O42">
         <v>32953854722.4081</v>
@@ -48175,25 +48175,25 @@
         <v>10023319382.3535</v>
       </c>
       <c r="H43">
+        <v>9860794389.07268</v>
+      </c>
+      <c r="I43">
+        <v>2714384760.17267</v>
+      </c>
+      <c r="J43">
+        <v>893895761.485974</v>
+      </c>
+      <c r="K43">
+        <v>725965132.3480411</v>
+      </c>
+      <c r="L43">
         <v>326380369.483176</v>
       </c>
-      <c r="I43">
+      <c r="M43">
         <v>13969038541.9049</v>
       </c>
-      <c r="J43">
+      <c r="N43">
         <v>5006319144.23146</v>
-      </c>
-      <c r="K43">
-        <v>9860794389.07268</v>
-      </c>
-      <c r="L43">
-        <v>2714384760.17267</v>
-      </c>
-      <c r="M43">
-        <v>893895761.485974</v>
-      </c>
-      <c r="N43">
-        <v>725965132.3480411</v>
       </c>
       <c r="O43">
         <v>33547042208.728</v>
@@ -48230,25 +48230,25 @@
         <v>9957372763.28404</v>
       </c>
       <c r="H44">
+        <v>9995774397.3673</v>
+      </c>
+      <c r="I44">
+        <v>2809704941.53412</v>
+      </c>
+      <c r="J44">
+        <v>843642775.064325</v>
+      </c>
+      <c r="K44">
+        <v>737426645.578622</v>
+      </c>
+      <c r="L44">
         <v>329103944.630933</v>
       </c>
-      <c r="I44">
+      <c r="M44">
         <v>14184182505.4338</v>
       </c>
-      <c r="J44">
+      <c r="N44">
         <v>5127657706.04942</v>
-      </c>
-      <c r="K44">
-        <v>9995774397.3673</v>
-      </c>
-      <c r="L44">
-        <v>2809704941.53412</v>
-      </c>
-      <c r="M44">
-        <v>843642775.064325</v>
-      </c>
-      <c r="N44">
-        <v>737426645.578622</v>
       </c>
       <c r="O44">
         <v>33865278201.378</v>
@@ -48285,25 +48285,25 @@
         <v>9803589030.4484</v>
       </c>
       <c r="H45">
+        <v>9855918237.272301</v>
+      </c>
+      <c r="I45">
+        <v>2831279649.56539</v>
+      </c>
+      <c r="J45">
+        <v>851395686.570052</v>
+      </c>
+      <c r="K45">
+        <v>751168301.356021</v>
+      </c>
+      <c r="L45">
         <v>329481942.963694</v>
       </c>
-      <c r="I45">
+      <c r="M45">
         <v>14217368294.501</v>
       </c>
-      <c r="J45">
+      <c r="N45">
         <v>5103692992.22637</v>
-      </c>
-      <c r="K45">
-        <v>9855918237.272301</v>
-      </c>
-      <c r="L45">
-        <v>2831279649.56539</v>
-      </c>
-      <c r="M45">
-        <v>851395686.570052</v>
-      </c>
-      <c r="N45">
-        <v>751168301.356021</v>
       </c>
       <c r="O45">
         <v>33913025536.772</v>
@@ -48340,25 +48340,25 @@
         <v>9928972184.19998</v>
       </c>
       <c r="H46">
+        <v>9905696662.02993</v>
+      </c>
+      <c r="I46">
+        <v>2840035481.29892</v>
+      </c>
+      <c r="J46">
+        <v>845594283.2959599</v>
+      </c>
+      <c r="K46">
+        <v>768937995.418407</v>
+      </c>
+      <c r="L46">
         <v>329765065.982765</v>
       </c>
-      <c r="I46">
+      <c r="M46">
         <v>14340728727.0078</v>
       </c>
-      <c r="J46">
+      <c r="N46">
         <v>5128629929.85705</v>
-      </c>
-      <c r="K46">
-        <v>9905696662.02993</v>
-      </c>
-      <c r="L46">
-        <v>2840035481.29892</v>
-      </c>
-      <c r="M46">
-        <v>845594283.2959599</v>
-      </c>
-      <c r="N46">
-        <v>768937995.418407</v>
       </c>
       <c r="O46">
         <v>34108396210.9815</v>
@@ -48395,25 +48395,25 @@
         <v>9867369069.79516</v>
       </c>
       <c r="H47">
+        <v>9757754842.734289</v>
+      </c>
+      <c r="I47">
+        <v>2844620189.10678</v>
+      </c>
+      <c r="J47">
+        <v>849125518.797992</v>
+      </c>
+      <c r="K47">
+        <v>756189151.3709739</v>
+      </c>
+      <c r="L47">
         <v>331352453.108025</v>
       </c>
-      <c r="I47">
+      <c r="M47">
         <v>14427291397.8707</v>
       </c>
-      <c r="J47">
+      <c r="N47">
         <v>5185600808.96904</v>
-      </c>
-      <c r="K47">
-        <v>9757754842.734289</v>
-      </c>
-      <c r="L47">
-        <v>2844620189.10678</v>
-      </c>
-      <c r="M47">
-        <v>849125518.797992</v>
-      </c>
-      <c r="N47">
-        <v>756189151.3709739</v>
       </c>
       <c r="O47">
         <v>34192379249.3988</v>
@@ -48450,25 +48450,25 @@
         <v>9754830654.95307</v>
       </c>
       <c r="H48">
+        <v>9826396974.868389</v>
+      </c>
+      <c r="I48">
+        <v>2899110023.87009</v>
+      </c>
+      <c r="J48">
+        <v>906037218.491215</v>
+      </c>
+      <c r="K48">
+        <v>787797748.671479</v>
+      </c>
+      <c r="L48">
         <v>333919948.152034</v>
       </c>
-      <c r="I48">
+      <c r="M48">
         <v>14509191201.7919</v>
       </c>
-      <c r="J48">
+      <c r="N48">
         <v>5161051905.55895</v>
-      </c>
-      <c r="K48">
-        <v>9826396974.868389</v>
-      </c>
-      <c r="L48">
-        <v>2899110023.87009</v>
-      </c>
-      <c r="M48">
-        <v>906037218.491215</v>
-      </c>
-      <c r="N48">
-        <v>787797748.671479</v>
       </c>
       <c r="O48">
         <v>34380992881.4404</v>
@@ -48505,25 +48505,25 @@
         <v>9885576557.927151</v>
       </c>
       <c r="H49">
+        <v>9802193688.219839</v>
+      </c>
+      <c r="I49">
+        <v>2972328366.49374</v>
+      </c>
+      <c r="J49">
+        <v>924570886.805298</v>
+      </c>
+      <c r="K49">
+        <v>757906741.318182</v>
+      </c>
+      <c r="L49">
         <v>355577979.455883</v>
       </c>
-      <c r="I49">
+      <c r="M49">
         <v>14619067088.721</v>
       </c>
-      <c r="J49">
+      <c r="N49">
         <v>5159708314.22753</v>
-      </c>
-      <c r="K49">
-        <v>9802193688.219839</v>
-      </c>
-      <c r="L49">
-        <v>2972328366.49374</v>
-      </c>
-      <c r="M49">
-        <v>924570886.805298</v>
-      </c>
-      <c r="N49">
-        <v>757906741.318182</v>
       </c>
       <c r="O49">
         <v>34554885977.1607</v>
@@ -48560,25 +48560,25 @@
         <v>10192574257.3832</v>
       </c>
       <c r="H50">
+        <v>9880405102.014799</v>
+      </c>
+      <c r="I50">
+        <v>3035233694.04211</v>
+      </c>
+      <c r="J50">
+        <v>920453104.509401</v>
+      </c>
+      <c r="K50">
+        <v>733391326.641223</v>
+      </c>
+      <c r="L50">
         <v>355159646.073993</v>
       </c>
-      <c r="I50">
+      <c r="M50">
         <v>14770156308.4871</v>
       </c>
-      <c r="J50">
+      <c r="N50">
         <v>5245700673.04414</v>
-      </c>
-      <c r="K50">
-        <v>9880405102.014799</v>
-      </c>
-      <c r="L50">
-        <v>3035233694.04211</v>
-      </c>
-      <c r="M50">
-        <v>920453104.509401</v>
-      </c>
-      <c r="N50">
-        <v>733391326.641223</v>
       </c>
       <c r="O50">
         <v>35018940709.6416</v>
@@ -48615,25 +48615,25 @@
         <v>10126622151.8793</v>
       </c>
       <c r="H51">
+        <v>10028786593.9372</v>
+      </c>
+      <c r="I51">
+        <v>3064819097.54026</v>
+      </c>
+      <c r="J51">
+        <v>932985183.0747629</v>
+      </c>
+      <c r="K51">
+        <v>748035297.789098</v>
+      </c>
+      <c r="L51">
         <v>365088482.917033</v>
       </c>
-      <c r="I51">
+      <c r="M51">
         <v>14966481708.2049</v>
       </c>
-      <c r="J51">
+      <c r="N51">
         <v>5382821067.88837</v>
-      </c>
-      <c r="K51">
-        <v>10028786593.9372</v>
-      </c>
-      <c r="L51">
-        <v>3064819097.54026</v>
-      </c>
-      <c r="M51">
-        <v>932985183.0747629</v>
-      </c>
-      <c r="N51">
-        <v>748035297.789098</v>
       </c>
       <c r="O51">
         <v>35597065719.4086</v>
@@ -48670,25 +48670,25 @@
         <v>10272331012.8505</v>
       </c>
       <c r="H52">
+        <v>10152796011.0533</v>
+      </c>
+      <c r="I52">
+        <v>3067307714.65534</v>
+      </c>
+      <c r="J52">
+        <v>938145798.314885</v>
+      </c>
+      <c r="K52">
+        <v>771255399.519868</v>
+      </c>
+      <c r="L52">
         <v>352709502.615337</v>
       </c>
-      <c r="I52">
+      <c r="M52">
         <v>15084100486.4264</v>
       </c>
-      <c r="J52">
+      <c r="N52">
         <v>5398218227.09047</v>
-      </c>
-      <c r="K52">
-        <v>10152796011.0533</v>
-      </c>
-      <c r="L52">
-        <v>3067307714.65534</v>
-      </c>
-      <c r="M52">
-        <v>938145798.314885</v>
-      </c>
-      <c r="N52">
-        <v>771255399.519868</v>
       </c>
       <c r="O52">
         <v>35670555917.3671</v>
@@ -48725,25 +48725,25 @@
         <v>10368387028.3885</v>
       </c>
       <c r="H53">
+        <v>10140690850.9576</v>
+      </c>
+      <c r="I53">
+        <v>3138911344.11779</v>
+      </c>
+      <c r="J53">
+        <v>917980809.096277</v>
+      </c>
+      <c r="K53">
+        <v>754101027.537694</v>
+      </c>
+      <c r="L53">
         <v>363685790.419716</v>
       </c>
-      <c r="I53">
+      <c r="M53">
         <v>15230683978.925</v>
       </c>
-      <c r="J53">
+      <c r="N53">
         <v>5448548575.2106</v>
-      </c>
-      <c r="K53">
-        <v>10140690850.9576</v>
-      </c>
-      <c r="L53">
-        <v>3138911344.11779</v>
-      </c>
-      <c r="M53">
-        <v>917980809.096277</v>
-      </c>
-      <c r="N53">
-        <v>754101027.537694</v>
       </c>
       <c r="O53">
         <v>36052604879.3505</v>
@@ -48780,25 +48780,25 @@
         <v>10353461055.5586</v>
       </c>
       <c r="H54">
+        <v>10187979235.253</v>
+      </c>
+      <c r="I54">
+        <v>3171619932.03647</v>
+      </c>
+      <c r="J54">
+        <v>934825041.505632</v>
+      </c>
+      <c r="K54">
+        <v>800794183.662012</v>
+      </c>
+      <c r="L54">
         <v>376973550.199283</v>
       </c>
-      <c r="I54">
+      <c r="M54">
         <v>15247862083.9897</v>
       </c>
-      <c r="J54">
+      <c r="N54">
         <v>5458707367.38209</v>
-      </c>
-      <c r="K54">
-        <v>10187979235.253</v>
-      </c>
-      <c r="L54">
-        <v>3171619932.03647</v>
-      </c>
-      <c r="M54">
-        <v>934825041.505632</v>
-      </c>
-      <c r="N54">
-        <v>800794183.662012</v>
       </c>
       <c r="O54">
         <v>36015065968.9082</v>
@@ -48835,25 +48835,25 @@
         <v>10441280425.8564</v>
       </c>
       <c r="H55">
+        <v>10315804810.3191</v>
+      </c>
+      <c r="I55">
+        <v>3249775454.59489</v>
+      </c>
+      <c r="J55">
+        <v>921018033.6106451</v>
+      </c>
+      <c r="K55">
+        <v>823556750.31686</v>
+      </c>
+      <c r="L55">
         <v>373793738.743363</v>
       </c>
-      <c r="I55">
+      <c r="M55">
         <v>15296004406.4685</v>
       </c>
-      <c r="J55">
+      <c r="N55">
         <v>5500548213.93868</v>
-      </c>
-      <c r="K55">
-        <v>10315804810.3191</v>
-      </c>
-      <c r="L55">
-        <v>3249775454.59489</v>
-      </c>
-      <c r="M55">
-        <v>921018033.6106451</v>
-      </c>
-      <c r="N55">
-        <v>823556750.31686</v>
       </c>
       <c r="O55">
         <v>36510774567.5591</v>
@@ -48890,25 +48890,25 @@
         <v>10504898339.9799</v>
       </c>
       <c r="H56">
+        <v>10162333383.2025</v>
+      </c>
+      <c r="I56">
+        <v>3272674963.19126</v>
+      </c>
+      <c r="J56">
+        <v>912353305.34647</v>
+      </c>
+      <c r="K56">
+        <v>792615684.7291729</v>
+      </c>
+      <c r="L56">
         <v>402371253.724589</v>
       </c>
-      <c r="I56">
+      <c r="M56">
         <v>15330581562.0568</v>
       </c>
-      <c r="J56">
+      <c r="N56">
         <v>5536325839.27883</v>
-      </c>
-      <c r="K56">
-        <v>10162333383.2025</v>
-      </c>
-      <c r="L56">
-        <v>3272674963.19126</v>
-      </c>
-      <c r="M56">
-        <v>912353305.34647</v>
-      </c>
-      <c r="N56">
-        <v>792615684.7291729</v>
       </c>
       <c r="O56">
         <v>36440850937.1685</v>

--- a/Dados/table_PROD_BR_1_aux.xlsx
+++ b/Dados/table_PROD_BR_1_aux.xlsx
@@ -6586,52 +6586,52 @@
         </is>
       </c>
       <c r="B5">
-        <v>1606962430.182868</v>
+        <v>20729815349.359</v>
       </c>
       <c r="C5">
-        <v>99316168.67999831</v>
+        <v>1281178575.971978</v>
       </c>
       <c r="D5">
-        <v>1976770225.613746</v>
+        <v>25500335910.41732</v>
       </c>
       <c r="E5">
-        <v>141757448.7115089</v>
+        <v>1828671088.378464</v>
       </c>
       <c r="F5">
-        <v>1278439991.998241</v>
+        <v>16491875896.77732</v>
       </c>
       <c r="G5">
-        <v>3496283835.003494</v>
+        <v>45102061471.54507</v>
       </c>
       <c r="H5">
-        <v>2934960487.588606</v>
+        <v>37860990289.89302</v>
       </c>
       <c r="I5">
-        <v>767580863.9054086</v>
+        <v>9901793144.379772</v>
       </c>
       <c r="J5">
-        <v>202879542.1681061</v>
+        <v>2617146093.968569</v>
       </c>
       <c r="K5">
-        <v>193576797.9144181</v>
+        <v>2497140693.095994</v>
       </c>
       <c r="L5">
-        <v>88627699.1573488</v>
+        <v>1143297319.1298</v>
       </c>
       <c r="M5">
-        <v>3825705026.47923</v>
+        <v>49351594841.58207</v>
       </c>
       <c r="N5">
-        <v>1502027990.929463</v>
+        <v>19376161082.99007</v>
       </c>
       <c r="O5">
-        <v>9515358408.142578</v>
+        <v>122748123465.0393</v>
       </c>
       <c r="P5">
-        <v>14618604673.32894</v>
+        <v>188580000285.9434</v>
       </c>
       <c r="Q5">
-        <v>11420986553.05926</v>
+        <v>147330726534.4645</v>
       </c>
     </row>
     <row r="6">
@@ -6641,52 +6641,52 @@
         </is>
       </c>
       <c r="B6">
-        <v>1585281982.717078</v>
+        <v>20450137577.05031</v>
       </c>
       <c r="C6">
-        <v>100004227.2600857</v>
+        <v>1290054531.655105</v>
       </c>
       <c r="D6">
-        <v>1975622414.927575</v>
+        <v>25485529152.56572</v>
       </c>
       <c r="E6">
-        <v>138958470.9983171</v>
+        <v>1792564275.878291</v>
       </c>
       <c r="F6">
-        <v>1298778943.778173</v>
+        <v>16754248374.73843</v>
       </c>
       <c r="G6">
-        <v>3513364056.964151</v>
+        <v>45322396334.83755</v>
       </c>
       <c r="H6">
-        <v>2942908373.004406</v>
+        <v>37963518011.75684</v>
       </c>
       <c r="I6">
-        <v>773354304.8585703</v>
+        <v>9976270532.675558</v>
       </c>
       <c r="J6">
-        <v>206076533.2372507</v>
+        <v>2658387278.760533</v>
       </c>
       <c r="K6">
-        <v>196664593.2656456</v>
+        <v>2536973253.126828</v>
       </c>
       <c r="L6">
-        <v>91491738.99155907</v>
+        <v>1180243432.991112</v>
       </c>
       <c r="M6">
-        <v>3825868129.953123</v>
+        <v>49353698876.39529</v>
       </c>
       <c r="N6">
-        <v>1501153498.482311</v>
+        <v>19364880130.42182</v>
       </c>
       <c r="O6">
-        <v>9537517171.792866</v>
+        <v>123033971516.128</v>
       </c>
       <c r="P6">
-        <v>14636163211.47409</v>
+        <v>188806505428.0158</v>
       </c>
       <c r="Q6">
-        <v>11458235991.28315</v>
+        <v>147811244287.5526</v>
       </c>
     </row>
     <row r="7">
@@ -6696,52 +6696,52 @@
         </is>
       </c>
       <c r="B7">
-        <v>1566966904.243795</v>
+        <v>20213873064.74495</v>
       </c>
       <c r="C7">
-        <v>100597239.114391</v>
+        <v>1297704384.575644</v>
       </c>
       <c r="D7">
-        <v>1963639242.197383</v>
+        <v>25330946224.34624</v>
       </c>
       <c r="E7">
-        <v>141105621.9342702</v>
+        <v>1820262522.952086</v>
       </c>
       <c r="F7">
-        <v>1313899141.950671</v>
+        <v>16949298931.16366</v>
       </c>
       <c r="G7">
-        <v>3519241245.196715</v>
+        <v>45398212063.03763</v>
       </c>
       <c r="H7">
-        <v>2954186386.41784</v>
+        <v>38109004384.79014</v>
       </c>
       <c r="I7">
-        <v>781584507.0946501</v>
+        <v>10082440141.52099</v>
       </c>
       <c r="J7">
-        <v>205848320.5377791</v>
+        <v>2655443334.93735</v>
       </c>
       <c r="K7">
-        <v>199521789.4366192</v>
+        <v>2573831083.732388</v>
       </c>
       <c r="L7">
-        <v>92751878.67327374</v>
+        <v>1196499234.885231</v>
       </c>
       <c r="M7">
-        <v>3833869236.716363</v>
+        <v>49456913153.64109</v>
       </c>
       <c r="N7">
-        <v>1498957803.519489</v>
+        <v>19336555665.40141</v>
       </c>
       <c r="O7">
-        <v>9566719922.396015</v>
+        <v>123410686998.9086</v>
       </c>
       <c r="P7">
-        <v>14652928071.83652</v>
+        <v>189022772126.6912</v>
       </c>
       <c r="Q7">
-        <v>11494251485.39997</v>
+        <v>148275844161.6596</v>
       </c>
     </row>
     <row r="8">
@@ -6751,52 +6751,52 @@
         </is>
       </c>
       <c r="B8">
-        <v>1560015273.867276</v>
+        <v>20124197032.88787</v>
       </c>
       <c r="C8">
-        <v>100322210.1177847</v>
+        <v>1294156510.519423</v>
       </c>
       <c r="D8">
-        <v>1942367287.794484</v>
+        <v>25056538012.54885</v>
       </c>
       <c r="E8">
-        <v>146432896.8515911</v>
+        <v>1888984369.385525</v>
       </c>
       <c r="F8">
-        <v>1329498447.161976</v>
+        <v>17150529968.38949</v>
       </c>
       <c r="G8">
-        <v>3518620841.925836</v>
+        <v>45390208860.84328</v>
       </c>
       <c r="H8">
-        <v>2982603659.288443</v>
+        <v>38475587204.82091</v>
       </c>
       <c r="I8">
-        <v>784704833.402873</v>
+        <v>10122692350.89706</v>
       </c>
       <c r="J8">
-        <v>204710250.4055012</v>
+        <v>2640762230.230966</v>
       </c>
       <c r="K8">
-        <v>201370134.3471184</v>
+        <v>2597674733.077827</v>
       </c>
       <c r="L8">
-        <v>95373145.60790867</v>
+        <v>1230313578.342022</v>
       </c>
       <c r="M8">
-        <v>3844465794.997627</v>
+        <v>49593608755.46938</v>
       </c>
       <c r="N8">
-        <v>1493484340.311441</v>
+        <v>19265947990.01759</v>
       </c>
       <c r="O8">
-        <v>9606712158.36091</v>
+        <v>123926586842.8557</v>
       </c>
       <c r="P8">
-        <v>14685348274.15402</v>
+        <v>189440992736.5869</v>
       </c>
       <c r="Q8">
-        <v>11536475514.3674</v>
+        <v>148820534135.3394</v>
       </c>
     </row>
     <row r="9">
@@ -6806,52 +6806,52 @@
         </is>
       </c>
       <c r="B9">
-        <v>1559449658.438404</v>
+        <v>20116900593.85541</v>
       </c>
       <c r="C9">
-        <v>98838293.79441954</v>
+        <v>1275013989.948012</v>
       </c>
       <c r="D9">
-        <v>1927055585.015235</v>
+        <v>24859017046.69653</v>
       </c>
       <c r="E9">
-        <v>149724054.352484</v>
+        <v>1931440301.147043</v>
       </c>
       <c r="F9">
-        <v>1339156949.212549</v>
+        <v>17275124644.84188</v>
       </c>
       <c r="G9">
-        <v>3514774882.374687</v>
+        <v>45340595982.63347</v>
       </c>
       <c r="H9">
-        <v>3002673391.09306</v>
+        <v>38734486745.10048</v>
       </c>
       <c r="I9">
-        <v>777517908.913808</v>
+        <v>10029981024.98812</v>
       </c>
       <c r="J9">
-        <v>206285370.3742203</v>
+        <v>2661081277.827442</v>
       </c>
       <c r="K9">
-        <v>200517364.43674</v>
+        <v>2586674001.233946</v>
       </c>
       <c r="L9">
-        <v>94867060.95747286</v>
+        <v>1223785086.3514</v>
       </c>
       <c r="M9">
-        <v>3868246083.084463</v>
+        <v>49900374471.78957</v>
       </c>
       <c r="N9">
-        <v>1493567984.871805</v>
+        <v>19267027004.84629</v>
       </c>
       <c r="O9">
-        <v>9643675163.731571</v>
+        <v>124403409612.1373</v>
       </c>
       <c r="P9">
-        <v>14717899704.54466</v>
+        <v>189860906188.6261</v>
       </c>
       <c r="Q9">
-        <v>11570015000.27698</v>
+        <v>149253193503.573</v>
       </c>
     </row>
     <row r="10">
@@ -6861,52 +6861,52 @@
         </is>
       </c>
       <c r="B10">
-        <v>1537087218.166105</v>
+        <v>19828425114.34276</v>
       </c>
       <c r="C10">
-        <v>96495948.47723383</v>
+        <v>1244797735.356316</v>
       </c>
       <c r="D10">
-        <v>1925425880.893919</v>
+        <v>24837993863.53156</v>
       </c>
       <c r="E10">
-        <v>154752781.2977563</v>
+        <v>1996310878.741056</v>
       </c>
       <c r="F10">
-        <v>1355498932.046309</v>
+        <v>17485936223.39738</v>
       </c>
       <c r="G10">
-        <v>3532173542.715218</v>
+        <v>45565038701.02631</v>
       </c>
       <c r="H10">
-        <v>3026063741.27799</v>
+        <v>39036222262.48607</v>
       </c>
       <c r="I10">
-        <v>770992643.7168742</v>
+        <v>9945805103.947678</v>
       </c>
       <c r="J10">
-        <v>208116525.9620625</v>
+        <v>2684703184.910607</v>
       </c>
       <c r="K10">
-        <v>201252225.7483822</v>
+        <v>2596153712.15413</v>
       </c>
       <c r="L10">
-        <v>93545631.03445706</v>
+        <v>1206738640.344496</v>
       </c>
       <c r="M10">
-        <v>3900776458.783278</v>
+        <v>50320016318.30429</v>
       </c>
       <c r="N10">
-        <v>1497912554.086507</v>
+        <v>19323071947.71594</v>
       </c>
       <c r="O10">
-        <v>9698659780.60955</v>
+        <v>125112711169.8632</v>
       </c>
       <c r="P10">
-        <v>14767920541.49087</v>
+        <v>190506174985.2323</v>
       </c>
       <c r="Q10">
-        <v>11639375138.20381</v>
+        <v>150147939282.8291</v>
       </c>
     </row>
     <row r="11">
@@ -6916,52 +6916,52 @@
         </is>
       </c>
       <c r="B11">
-        <v>1512187996.013036</v>
+        <v>19507225148.56817</v>
       </c>
       <c r="C11">
-        <v>94389472.06269598</v>
+        <v>1217624189.608778</v>
       </c>
       <c r="D11">
-        <v>1928341282.617034</v>
+        <v>24875602545.75974</v>
       </c>
       <c r="E11">
-        <v>155103947.1055661</v>
+        <v>2000840917.661803</v>
       </c>
       <c r="F11">
-        <v>1352464351.849611</v>
+        <v>17446790138.85999</v>
       </c>
       <c r="G11">
-        <v>3530299053.634907</v>
+        <v>45540857791.8903</v>
       </c>
       <c r="H11">
-        <v>3035472862.93498</v>
+        <v>39157599931.86125</v>
       </c>
       <c r="I11">
-        <v>763920800.3540754</v>
+        <v>9854578324.567574</v>
       </c>
       <c r="J11">
-        <v>209852256.2345631</v>
+        <v>2707094105.425864</v>
       </c>
       <c r="K11">
-        <v>199693188.5705542</v>
+        <v>2576042132.560149</v>
       </c>
       <c r="L11">
-        <v>91083848.7788745</v>
+        <v>1174981649.247481</v>
       </c>
       <c r="M11">
-        <v>3947130593.360818</v>
+        <v>50917984654.35456</v>
       </c>
       <c r="N11">
-        <v>1502604455.430573</v>
+        <v>19383597475.05439</v>
       </c>
       <c r="O11">
-        <v>9749758005.664438</v>
+        <v>125771878273.0713</v>
       </c>
       <c r="P11">
-        <v>14792245055.31238</v>
+        <v>190819961213.5298</v>
       </c>
       <c r="Q11">
-        <v>11686368755.0899</v>
+        <v>150754156940.6597</v>
       </c>
     </row>
     <row r="12">
@@ -6971,52 +6971,52 @@
         </is>
       </c>
       <c r="B12">
-        <v>1475844385.671403</v>
+        <v>19038392575.16111</v>
       </c>
       <c r="C12">
-        <v>92045061.32158712</v>
+        <v>1187381291.048474</v>
       </c>
       <c r="D12">
-        <v>1951109276.730337</v>
+        <v>25169309669.82135</v>
       </c>
       <c r="E12">
-        <v>153966160.6954196</v>
+        <v>1986163472.970913</v>
       </c>
       <c r="F12">
-        <v>1331128663.17859</v>
+        <v>17171559755.00381</v>
       </c>
       <c r="G12">
-        <v>3528249161.925934</v>
+        <v>45514414188.84455</v>
       </c>
       <c r="H12">
-        <v>3026468698.378728</v>
+        <v>39041446209.08559</v>
       </c>
       <c r="I12">
-        <v>755524032.1539197</v>
+        <v>9746260014.785564</v>
       </c>
       <c r="J12">
-        <v>210593803.0192353</v>
+        <v>2716660058.948135</v>
       </c>
       <c r="K12">
-        <v>201312380.6812045</v>
+        <v>2596929710.787539</v>
       </c>
       <c r="L12">
-        <v>88545512.37606433</v>
+        <v>1142237109.65123</v>
       </c>
       <c r="M12">
-        <v>3990911371.65518</v>
+        <v>51482756694.35182</v>
       </c>
       <c r="N12">
-        <v>1507965011.146966</v>
+        <v>19452748643.79586</v>
       </c>
       <c r="O12">
-        <v>9781320809.411297</v>
+        <v>126179038441.4057</v>
       </c>
       <c r="P12">
-        <v>14785414357.00863</v>
+        <v>190731845205.4114</v>
       </c>
       <c r="Q12">
-        <v>11713059447.8142</v>
+        <v>151098466876.8032</v>
       </c>
     </row>
     <row r="13">
@@ -7026,52 +7026,52 @@
         </is>
       </c>
       <c r="B13">
-        <v>1432983646.995393</v>
+        <v>18485489046.24057</v>
       </c>
       <c r="C13">
-        <v>90521754.53281702</v>
+        <v>1167730633.47334</v>
       </c>
       <c r="D13">
-        <v>1971433005.263093</v>
+        <v>25431485767.8939</v>
       </c>
       <c r="E13">
-        <v>153758334.7804661</v>
+        <v>1983482518.668012</v>
       </c>
       <c r="F13">
-        <v>1312319479.807499</v>
+        <v>16928921289.51674</v>
       </c>
       <c r="G13">
-        <v>3528032574.383875</v>
+        <v>45511620209.55199</v>
       </c>
       <c r="H13">
-        <v>3018990218.592979</v>
+        <v>38944973819.84943</v>
       </c>
       <c r="I13">
-        <v>755846901.9712065</v>
+        <v>9750425035.428564</v>
       </c>
       <c r="J13">
-        <v>210552265.8893807</v>
+        <v>2716124229.973011</v>
       </c>
       <c r="K13">
-        <v>202087251.8693737</v>
+        <v>2606925549.114921</v>
       </c>
       <c r="L13">
-        <v>91223211.83342743</v>
+        <v>1176779432.651214</v>
       </c>
       <c r="M13">
-        <v>4027065378.157786</v>
+        <v>51949143378.23544</v>
       </c>
       <c r="N13">
-        <v>1515006757.835967</v>
+        <v>19543587176.08397</v>
       </c>
       <c r="O13">
-        <v>9820771986.15012</v>
+        <v>126687958621.3365</v>
       </c>
       <c r="P13">
-        <v>14781788207.52939</v>
+        <v>190685067877.1291</v>
       </c>
       <c r="Q13">
-        <v>11742574590.8646</v>
+        <v>151479212222.1534</v>
       </c>
     </row>
     <row r="14">
@@ -7081,52 +7081,52 @@
         </is>
       </c>
       <c r="B14">
-        <v>1424579513.023584</v>
+        <v>18377075718.00423</v>
       </c>
       <c r="C14">
-        <v>88392974.59613244</v>
+        <v>1140269372.290108</v>
       </c>
       <c r="D14">
-        <v>1980280490.997928</v>
+        <v>25545618333.87327</v>
       </c>
       <c r="E14">
-        <v>151907454.605267</v>
+        <v>1959606164.407945</v>
       </c>
       <c r="F14">
-        <v>1289675210.367471</v>
+        <v>16636810213.74037</v>
       </c>
       <c r="G14">
-        <v>3510256130.566798</v>
+        <v>45282304084.3117</v>
       </c>
       <c r="H14">
-        <v>3007613966.99889</v>
+        <v>38798220174.28568</v>
       </c>
       <c r="I14">
-        <v>759653799.0336772</v>
+        <v>9799534007.534437</v>
       </c>
       <c r="J14">
-        <v>208542660.1558259</v>
+        <v>2690200316.010154</v>
       </c>
       <c r="K14">
-        <v>200753976.2803142</v>
+        <v>2589726294.016053</v>
       </c>
       <c r="L14">
-        <v>92481277.42733623</v>
+        <v>1193008478.812637</v>
       </c>
       <c r="M14">
-        <v>4041550508.440587</v>
+        <v>52136001558.88358</v>
       </c>
       <c r="N14">
-        <v>1516048262.91067</v>
+        <v>19557022591.54765</v>
       </c>
       <c r="O14">
-        <v>9826644451.247299</v>
+        <v>126763713421.0902</v>
       </c>
       <c r="P14">
-        <v>14761480094.83768</v>
+        <v>190423093223.4061</v>
       </c>
       <c r="Q14">
-        <v>11728371041.47609</v>
+        <v>151295986435.0416</v>
       </c>
     </row>
     <row r="15">
@@ -7136,52 +7136,52 @@
         </is>
       </c>
       <c r="B15">
-        <v>1411375073.975148</v>
+        <v>18206738454.27941</v>
       </c>
       <c r="C15">
-        <v>86429494.29010111</v>
+        <v>1114940476.342304</v>
       </c>
       <c r="D15">
-        <v>1978463684.337964</v>
+        <v>25522181527.95973</v>
       </c>
       <c r="E15">
-        <v>150413047.3129193</v>
+        <v>1940328310.33666</v>
       </c>
       <c r="F15">
-        <v>1258259506.241954</v>
+        <v>16231547630.52121</v>
       </c>
       <c r="G15">
-        <v>3473565732.182939</v>
+        <v>44808997945.15991</v>
       </c>
       <c r="H15">
-        <v>3010226575.954258</v>
+        <v>38831922829.80993</v>
       </c>
       <c r="I15">
-        <v>759849709.9970539</v>
+        <v>9802061258.961994</v>
       </c>
       <c r="J15">
-        <v>207801447.7905043</v>
+        <v>2680638676.497506</v>
       </c>
       <c r="K15">
-        <v>199519720.4863107</v>
+        <v>2573804394.273408</v>
       </c>
       <c r="L15">
-        <v>94973203.5532268</v>
+        <v>1225154325.836626</v>
       </c>
       <c r="M15">
-        <v>4058434748.525945</v>
+        <v>52353808255.98469</v>
       </c>
       <c r="N15">
-        <v>1515959289.213354</v>
+        <v>19555874830.85227</v>
       </c>
       <c r="O15">
-        <v>9846764695.520653</v>
+        <v>127023264572.2164</v>
       </c>
       <c r="P15">
-        <v>14731705501.67874</v>
+        <v>190039000971.6557</v>
       </c>
       <c r="Q15">
-        <v>11709397934.93701</v>
+        <v>151051233360.6874</v>
       </c>
     </row>
     <row r="16">
@@ -7191,52 +7191,52 @@
         </is>
       </c>
       <c r="B16">
-        <v>1403023470.247206</v>
+        <v>18099002766.18895</v>
       </c>
       <c r="C16">
-        <v>85945634.40028369</v>
+        <v>1108698683.76366</v>
       </c>
       <c r="D16">
-        <v>1954441634.81807</v>
+        <v>25212297089.15311</v>
       </c>
       <c r="E16">
-        <v>147606351.9317218</v>
+        <v>1904121939.919211</v>
       </c>
       <c r="F16">
-        <v>1241212887.517437</v>
+        <v>16011646248.97493</v>
       </c>
       <c r="G16">
-        <v>3429206508.667513</v>
+        <v>44236763961.81092</v>
       </c>
       <c r="H16">
-        <v>3017688523.139956</v>
+        <v>38928181948.50542</v>
       </c>
       <c r="I16">
-        <v>762499362.1193881</v>
+        <v>9836241771.340107</v>
       </c>
       <c r="J16">
-        <v>209555087.9986324</v>
+        <v>2703260635.182358</v>
       </c>
       <c r="K16">
-        <v>194151073.5036832</v>
+        <v>2504548848.197514</v>
       </c>
       <c r="L16">
-        <v>96735662.50733595</v>
+        <v>1247890046.344634</v>
       </c>
       <c r="M16">
-        <v>4056205349.08251</v>
+        <v>52325049003.16438</v>
       </c>
       <c r="N16">
-        <v>1517274067.219474</v>
+        <v>19572835467.13121</v>
       </c>
       <c r="O16">
-        <v>9854109125.570978</v>
+        <v>127118007719.8656</v>
       </c>
       <c r="P16">
-        <v>14686339104.4857</v>
+        <v>189453774447.8655</v>
       </c>
       <c r="Q16">
-        <v>11669305904.51168</v>
+        <v>150534046168.2007</v>
       </c>
     </row>
     <row r="17">
@@ -7246,52 +7246,52 @@
         </is>
       </c>
       <c r="B17">
-        <v>1401880167.376364</v>
+        <v>18084254159.15509</v>
       </c>
       <c r="C17">
-        <v>83018024.4484323</v>
+        <v>1070932515.384777</v>
       </c>
       <c r="D17">
-        <v>1913521448.940701</v>
+        <v>24684426691.33504</v>
       </c>
       <c r="E17">
-        <v>142122727.9277828</v>
+        <v>1833383190.268398</v>
       </c>
       <c r="F17">
-        <v>1242256396.607175</v>
+        <v>16025107516.23255</v>
       </c>
       <c r="G17">
-        <v>3380918597.924091</v>
+        <v>43613849913.22077</v>
       </c>
       <c r="H17">
-        <v>3005784824.16432</v>
+        <v>38774624231.71973</v>
       </c>
       <c r="I17">
-        <v>767071060.1997759</v>
+        <v>9895216676.57711</v>
       </c>
       <c r="J17">
-        <v>205799297.8068848</v>
+        <v>2654810941.708814</v>
       </c>
       <c r="K17">
-        <v>188803732.0302502</v>
+        <v>2435568143.190228</v>
       </c>
       <c r="L17">
-        <v>94152392.35126492</v>
+        <v>1214565861.331318</v>
       </c>
       <c r="M17">
-        <v>4051515929.037144</v>
+        <v>52264555484.57915</v>
       </c>
       <c r="N17">
-        <v>1519996661.845471</v>
+        <v>19607956937.80658</v>
       </c>
       <c r="O17">
-        <v>9833123897.43511</v>
+        <v>126847298276.9129</v>
       </c>
       <c r="P17">
-        <v>14615922662.73557</v>
+        <v>188545402349.2888</v>
       </c>
       <c r="Q17">
-        <v>11599893441.16246</v>
+        <v>149638625390.9958</v>
       </c>
     </row>
     <row r="18">
@@ -7301,52 +7301,52 @@
         </is>
       </c>
       <c r="B18">
-        <v>1399969089.062606</v>
+        <v>18059601248.90762</v>
       </c>
       <c r="C18">
-        <v>80555992.32997756</v>
+        <v>1039172301.05671</v>
       </c>
       <c r="D18">
-        <v>1855770005.482465</v>
+        <v>23939433070.7238</v>
       </c>
       <c r="E18">
-        <v>135541789.1517481</v>
+        <v>1748489080.05755</v>
       </c>
       <c r="F18">
-        <v>1234615149.378673</v>
+        <v>15926535426.98488</v>
       </c>
       <c r="G18">
-        <v>3306482936.342864</v>
+        <v>42653629878.82294</v>
       </c>
       <c r="H18">
-        <v>2988635597.827575</v>
+        <v>38553399211.97572</v>
       </c>
       <c r="I18">
-        <v>768619283.2978318</v>
+        <v>9915188754.54203</v>
       </c>
       <c r="J18">
-        <v>202812592.509343</v>
+        <v>2616282443.370525</v>
       </c>
       <c r="K18">
-        <v>188512553.29656</v>
+        <v>2431811937.525624</v>
       </c>
       <c r="L18">
-        <v>93465418.21893659</v>
+        <v>1205703895.024282</v>
       </c>
       <c r="M18">
-        <v>4055779917.26511</v>
+        <v>52319560932.71992</v>
       </c>
       <c r="N18">
-        <v>1520225083.694947</v>
+        <v>19610903579.66482</v>
       </c>
       <c r="O18">
-        <v>9818050446.110302</v>
+        <v>126652850754.8229</v>
       </c>
       <c r="P18">
-        <v>14524502471.51577</v>
+        <v>187366081882.5535</v>
       </c>
       <c r="Q18">
-        <v>11510842880.53928</v>
+        <v>148489873158.9567</v>
       </c>
     </row>
     <row r="19">
@@ -7356,52 +7356,52 @@
         </is>
       </c>
       <c r="B19">
-        <v>1396554667.440862</v>
+        <v>18015555209.98712</v>
       </c>
       <c r="C19">
-        <v>77086525.66851427</v>
+        <v>994416181.123834</v>
       </c>
       <c r="D19">
-        <v>1801666793.198877</v>
+        <v>23241501632.26551</v>
       </c>
       <c r="E19">
-        <v>129854198.1592275</v>
+        <v>1675119156.254035</v>
       </c>
       <c r="F19">
-        <v>1241711999.464448</v>
+        <v>16018084793.09138</v>
       </c>
       <c r="G19">
-        <v>3250319516.491067</v>
+        <v>41929121762.73477</v>
       </c>
       <c r="H19">
-        <v>2964157883.312398</v>
+        <v>38237636694.72993</v>
       </c>
       <c r="I19">
-        <v>772483688.9837946</v>
+        <v>9965039587.890951</v>
       </c>
       <c r="J19">
-        <v>199754487.516617</v>
+        <v>2576832888.964359</v>
       </c>
       <c r="K19">
-        <v>186110507.1449732</v>
+        <v>2400825542.170155</v>
       </c>
       <c r="L19">
-        <v>90750905.34246692</v>
+        <v>1170686678.917823</v>
       </c>
       <c r="M19">
-        <v>4045346579.928161</v>
+        <v>52184970881.07328</v>
       </c>
       <c r="N19">
-        <v>1524878964.935065</v>
+        <v>19670938647.66234</v>
       </c>
       <c r="O19">
-        <v>9783483017.163475</v>
+        <v>126206930921.4088</v>
       </c>
       <c r="P19">
-        <v>14430357201.0954</v>
+        <v>186151607894.1307</v>
       </c>
       <c r="Q19">
-        <v>11418172663.37701</v>
+        <v>147294427357.5634</v>
       </c>
     </row>
     <row r="20">
@@ -7411,52 +7411,52 @@
         </is>
       </c>
       <c r="B20">
-        <v>1386625029.892113</v>
+        <v>17887462885.60826</v>
       </c>
       <c r="C20">
-        <v>73725553.81381461</v>
+        <v>951059644.1982085</v>
       </c>
       <c r="D20">
-        <v>1753734059.364045</v>
+        <v>22623169365.79618</v>
       </c>
       <c r="E20">
-        <v>127045663.7141272</v>
+        <v>1638889061.912241</v>
       </c>
       <c r="F20">
-        <v>1231016402.262762</v>
+        <v>15880111589.18962</v>
       </c>
       <c r="G20">
-        <v>3185521679.154748</v>
+        <v>41093229661.09625</v>
       </c>
       <c r="H20">
-        <v>2926873648.270752</v>
+        <v>37756670062.69271</v>
       </c>
       <c r="I20">
-        <v>778543393.6247604</v>
+        <v>10043209777.75941</v>
       </c>
       <c r="J20">
-        <v>195057484.4121653</v>
+        <v>2516241548.916932</v>
       </c>
       <c r="K20">
-        <v>187533293.8427297</v>
+        <v>2419179490.571214</v>
       </c>
       <c r="L20">
-        <v>88617539.99704924</v>
+        <v>1143166265.961935</v>
       </c>
       <c r="M20">
-        <v>4041268216.664711</v>
+        <v>52132359994.97477</v>
       </c>
       <c r="N20">
-        <v>1531517642.351837</v>
+        <v>19756577586.3387</v>
       </c>
       <c r="O20">
-        <v>9749411219.164005</v>
+        <v>125767404727.2157</v>
       </c>
       <c r="P20">
-        <v>14321557928.21087</v>
+        <v>184748097273.9202</v>
       </c>
       <c r="Q20">
-        <v>11314797715.96987</v>
+        <v>145960890536.0113</v>
       </c>
     </row>
     <row r="21">
@@ -7466,52 +7466,52 @@
         </is>
       </c>
       <c r="B21">
-        <v>1372217632.8627</v>
+        <v>17701607463.92884</v>
       </c>
       <c r="C21">
-        <v>72968821.76223724</v>
+        <v>941297800.7328603</v>
       </c>
       <c r="D21">
-        <v>1710958303.831089</v>
+        <v>22071362119.42105</v>
       </c>
       <c r="E21">
-        <v>129434061.8317495</v>
+        <v>1669699397.629569</v>
       </c>
       <c r="F21">
-        <v>1192192579.287147</v>
+        <v>15379284272.8042</v>
       </c>
       <c r="G21">
-        <v>3105553766.712224</v>
+        <v>40061643590.58768</v>
       </c>
       <c r="H21">
-        <v>2917034696.453778</v>
+        <v>37629747584.25373</v>
       </c>
       <c r="I21">
-        <v>782215237.5016091</v>
+        <v>10090576563.77076</v>
       </c>
       <c r="J21">
-        <v>196886453.7817818</v>
+        <v>2539835253.784985</v>
       </c>
       <c r="K21">
-        <v>191092739.5851845</v>
+        <v>2465096340.64888</v>
       </c>
       <c r="L21">
-        <v>89246233.8566054</v>
+        <v>1151276416.75021</v>
       </c>
       <c r="M21">
-        <v>4041391808.540929</v>
+        <v>52133954330.17799</v>
       </c>
       <c r="N21">
-        <v>1530253440.650461</v>
+        <v>19740269384.39095</v>
       </c>
       <c r="O21">
-        <v>9748120610.37035</v>
+        <v>125750755873.7775</v>
       </c>
       <c r="P21">
-        <v>14225892009.94527</v>
+        <v>183514006928.294</v>
       </c>
       <c r="Q21">
-        <v>11234174702.5755</v>
+        <v>144920853663.224</v>
       </c>
     </row>
     <row r="22">
@@ -7521,52 +7521,52 @@
         </is>
       </c>
       <c r="B22">
-        <v>1347977277.985763</v>
+        <v>17388906886.01635</v>
       </c>
       <c r="C22">
-        <v>72257479.73962808</v>
+        <v>932121488.6412022</v>
       </c>
       <c r="D22">
-        <v>1693128562.31751</v>
+        <v>21841358453.89587</v>
       </c>
       <c r="E22">
-        <v>131193753.3003733</v>
+        <v>1692399417.574816</v>
       </c>
       <c r="F22">
-        <v>1160171022.173985</v>
+        <v>14966206186.04441</v>
       </c>
       <c r="G22">
-        <v>3056750817.531496</v>
+        <v>39432085546.1563</v>
       </c>
       <c r="H22">
-        <v>2902747475.095938</v>
+        <v>37445442428.73759</v>
       </c>
       <c r="I22">
-        <v>782458078.163988</v>
+        <v>10093709208.31544</v>
       </c>
       <c r="J22">
-        <v>198114740.9191808</v>
+        <v>2555680157.857432</v>
       </c>
       <c r="K22">
-        <v>191831828.4101326</v>
+        <v>2474630586.490711</v>
       </c>
       <c r="L22">
-        <v>90837594.51431671</v>
+        <v>1171804969.234686</v>
       </c>
       <c r="M22">
-        <v>4048607596.544359</v>
+        <v>52227037995.42223</v>
       </c>
       <c r="N22">
-        <v>1527933337.761061</v>
+        <v>19710340057.11769</v>
       </c>
       <c r="O22">
-        <v>9742530651.408978</v>
+        <v>125678645403.1758</v>
       </c>
       <c r="P22">
-        <v>14147258746.92624</v>
+        <v>182499637835.3484</v>
       </c>
       <c r="Q22">
-        <v>11180510536.66509</v>
+        <v>144228585922.9797</v>
       </c>
     </row>
     <row r="23">
@@ -7576,52 +7576,52 @@
         </is>
       </c>
       <c r="B23">
-        <v>1323855374.201186</v>
+        <v>17077734327.1953</v>
       </c>
       <c r="C23">
-        <v>70016630.96144056</v>
+        <v>903214539.4025832</v>
       </c>
       <c r="D23">
-        <v>1691835556.578369</v>
+        <v>21824678679.86096</v>
       </c>
       <c r="E23">
-        <v>135801542.8324144</v>
+        <v>1751839902.538146</v>
       </c>
       <c r="F23">
-        <v>1129363809.439619</v>
+        <v>14568793141.77109</v>
       </c>
       <c r="G23">
-        <v>3027017539.811843</v>
+        <v>39048526263.57278</v>
       </c>
       <c r="H23">
-        <v>2896586008.991805</v>
+        <v>37365959515.99429</v>
       </c>
       <c r="I23">
-        <v>786313437.3472517</v>
+        <v>10143443341.77955</v>
       </c>
       <c r="J23">
-        <v>198661095.4050312</v>
+        <v>2562728130.724903</v>
       </c>
       <c r="K23">
-        <v>192019187.962824</v>
+        <v>2477047524.72043</v>
       </c>
       <c r="L23">
-        <v>91668430.34378836</v>
+        <v>1182522751.43487</v>
       </c>
       <c r="M23">
-        <v>4069802427.695595</v>
+        <v>52500451317.27317</v>
       </c>
       <c r="N23">
-        <v>1525109532.830285</v>
+        <v>19673912973.51068</v>
       </c>
       <c r="O23">
-        <v>9760160120.576582</v>
+        <v>125906065555.4379</v>
       </c>
       <c r="P23">
-        <v>14111033034.58961</v>
+        <v>182032326146.206</v>
       </c>
       <c r="Q23">
-        <v>11170399697.21435</v>
+        <v>144098156094.0652</v>
       </c>
     </row>
     <row r="24">
@@ -7631,52 +7631,52 @@
         </is>
       </c>
       <c r="B24">
-        <v>1312204024.472714</v>
+        <v>16927431915.69802</v>
       </c>
       <c r="C24">
-        <v>69458314.49865237</v>
+        <v>896012257.0326155</v>
       </c>
       <c r="D24">
-        <v>1694634196.952572</v>
+        <v>21860781140.68818</v>
       </c>
       <c r="E24">
-        <v>137925484.9803666</v>
+        <v>1779238756.246729</v>
       </c>
       <c r="F24">
-        <v>1116803450.383828</v>
+        <v>14406764509.95138</v>
       </c>
       <c r="G24">
-        <v>3018821446.815419</v>
+        <v>38942796663.91891</v>
       </c>
       <c r="H24">
-        <v>2905152792.887878</v>
+        <v>37476471028.25362</v>
       </c>
       <c r="I24">
-        <v>790292421.0346043</v>
+        <v>10194772231.3464</v>
       </c>
       <c r="J24">
-        <v>201688292.4287523</v>
+        <v>2601778972.330905</v>
       </c>
       <c r="K24">
-        <v>193556654.4216241</v>
+        <v>2496880842.038951</v>
       </c>
       <c r="L24">
-        <v>92550617.35378043</v>
+        <v>1193902963.863768</v>
       </c>
       <c r="M24">
-        <v>4103692425.754823</v>
+        <v>52937632292.23721</v>
       </c>
       <c r="N24">
-        <v>1522335151.427329</v>
+        <v>19638123453.41255</v>
       </c>
       <c r="O24">
-        <v>9809268355.308792</v>
+        <v>126539561783.4834</v>
       </c>
       <c r="P24">
-        <v>14140293826.59692</v>
+        <v>182409790363.1003</v>
       </c>
       <c r="Q24">
-        <v>11213204033.3431</v>
+        <v>144650332030.126</v>
       </c>
     </row>
     <row r="25">
@@ -7686,52 +7686,52 @@
         </is>
       </c>
       <c r="B25">
-        <v>1298567772.355867</v>
+        <v>16751524263.39068</v>
       </c>
       <c r="C25">
-        <v>69591023.35190862</v>
+        <v>897724201.2396213</v>
       </c>
       <c r="D25">
-        <v>1712757118.60377</v>
+        <v>22094566829.98863</v>
       </c>
       <c r="E25">
-        <v>137956550.4181533</v>
+        <v>1779639500.394177</v>
       </c>
       <c r="F25">
-        <v>1110163351.94003</v>
+        <v>14321107240.02638</v>
       </c>
       <c r="G25">
-        <v>3030468044.313861</v>
+        <v>39093037771.6488</v>
       </c>
       <c r="H25">
-        <v>2914913319.922632</v>
+        <v>37602381827.00195</v>
       </c>
       <c r="I25">
-        <v>786699823.4651415</v>
+        <v>10148427722.70033</v>
       </c>
       <c r="J25">
-        <v>201195969.66842</v>
+        <v>2595428008.722618</v>
       </c>
       <c r="K25">
-        <v>193947764.467271</v>
+        <v>2501926161.627796</v>
       </c>
       <c r="L25">
-        <v>90737207.64265792</v>
+        <v>1170509978.590287</v>
       </c>
       <c r="M25">
-        <v>4155059368.336017</v>
+        <v>53600265851.53462</v>
       </c>
       <c r="N25">
-        <v>1526823462.587265</v>
+        <v>19696022667.37572</v>
       </c>
       <c r="O25">
-        <v>9869376916.089405</v>
+        <v>127314962217.5533</v>
       </c>
       <c r="P25">
-        <v>14198412732.75913</v>
+        <v>183159524252.5928</v>
       </c>
       <c r="Q25">
-        <v>11282284290.17334</v>
+        <v>145541467343.2361</v>
       </c>
     </row>
     <row r="26">
@@ -7741,52 +7741,52 @@
         </is>
       </c>
       <c r="B26">
-        <v>1292001011.378221</v>
+        <v>16666813046.77905</v>
       </c>
       <c r="C26">
-        <v>69133759.21896228</v>
+        <v>891825493.9246135</v>
       </c>
       <c r="D26">
-        <v>1719695262.366649</v>
+        <v>22184068884.52977</v>
       </c>
       <c r="E26">
-        <v>138697048.6099766</v>
+        <v>1789191927.068699</v>
       </c>
       <c r="F26">
-        <v>1096849906.42585</v>
+        <v>14149363792.89346</v>
       </c>
       <c r="G26">
-        <v>3024375976.621438</v>
+        <v>39014450098.41654</v>
       </c>
       <c r="H26">
-        <v>2927501425.470452</v>
+        <v>37764768388.56883</v>
       </c>
       <c r="I26">
-        <v>792437179.222405</v>
+        <v>10222439611.96902</v>
       </c>
       <c r="J26">
-        <v>200756973.5821151</v>
+        <v>2589764959.209285</v>
       </c>
       <c r="K26">
-        <v>192843126.1446242</v>
+        <v>2487676327.265653</v>
       </c>
       <c r="L26">
-        <v>88876021.27319825</v>
+        <v>1146500674.424258</v>
       </c>
       <c r="M26">
-        <v>4201375097.549263</v>
+        <v>54197738758.38549</v>
       </c>
       <c r="N26">
-        <v>1535157228.598652</v>
+        <v>19803528248.92261</v>
       </c>
       <c r="O26">
-        <v>9938947051.84071</v>
+        <v>128212416968.7452</v>
       </c>
       <c r="P26">
-        <v>14255324039.84037</v>
+        <v>183893680113.9407</v>
       </c>
       <c r="Q26">
-        <v>11339289778.5903</v>
+        <v>146276838143.8148</v>
       </c>
     </row>
     <row r="27">
@@ -7796,52 +7796,52 @@
         </is>
       </c>
       <c r="B27">
-        <v>1288998452.566119</v>
+        <v>16628080038.10294</v>
       </c>
       <c r="C27">
-        <v>70709817.80668485</v>
+        <v>912156649.7062346</v>
       </c>
       <c r="D27">
-        <v>1723735384.406176</v>
+        <v>22236186458.83966</v>
       </c>
       <c r="E27">
-        <v>137646635.3166573</v>
+        <v>1775641595.58488</v>
       </c>
       <c r="F27">
-        <v>1088988301.229755</v>
+        <v>14047949085.86384</v>
       </c>
       <c r="G27">
-        <v>3021080138.759273</v>
+        <v>38971933789.99461</v>
       </c>
       <c r="H27">
-        <v>2931911313.996792</v>
+        <v>37821655950.55862</v>
       </c>
       <c r="I27">
-        <v>796855241.289958</v>
+        <v>10279432612.64046</v>
       </c>
       <c r="J27">
-        <v>200806777.6458704</v>
+        <v>2590407431.631729</v>
       </c>
       <c r="K27">
-        <v>194665566.419793</v>
+        <v>2511185806.815331</v>
       </c>
       <c r="L27">
-        <v>89647169.865181</v>
+        <v>1156448491.260835</v>
       </c>
       <c r="M27">
-        <v>4224022261.639156</v>
+        <v>54489887175.14512</v>
       </c>
       <c r="N27">
-        <v>1543142062.806265</v>
+        <v>19906532610.20082</v>
       </c>
       <c r="O27">
-        <v>9981050393.663015</v>
+        <v>128755550078.2529</v>
       </c>
       <c r="P27">
-        <v>14291128984.98841</v>
+        <v>184355563906.3505</v>
       </c>
       <c r="Q27">
-        <v>11369341299.75084</v>
+        <v>146664502766.7859</v>
       </c>
     </row>
     <row r="28">
@@ -7851,52 +7851,52 @@
         </is>
       </c>
       <c r="B28">
-        <v>1293297115.000715</v>
+        <v>16683532783.50922</v>
       </c>
       <c r="C28">
-        <v>71676854.95062283</v>
+        <v>924631428.8630345</v>
       </c>
       <c r="D28">
-        <v>1727108400.229858</v>
+        <v>22279698362.96517</v>
       </c>
       <c r="E28">
-        <v>135007220.480361</v>
+        <v>1741593144.196656</v>
       </c>
       <c r="F28">
-        <v>1083933074.211422</v>
+        <v>13982736657.32734</v>
       </c>
       <c r="G28">
-        <v>3017725549.872264</v>
+        <v>38928659593.3522</v>
       </c>
       <c r="H28">
-        <v>2941744607.653748</v>
+        <v>37948505438.73335</v>
       </c>
       <c r="I28">
-        <v>799034984.0323842</v>
+        <v>10307551294.01776</v>
       </c>
       <c r="J28">
-        <v>200497524.4210291</v>
+        <v>2586418065.031275</v>
       </c>
       <c r="K28">
-        <v>195227893.6484963</v>
+        <v>2518439828.065603</v>
       </c>
       <c r="L28">
-        <v>90774949.09481341</v>
+        <v>1170996843.323093</v>
       </c>
       <c r="M28">
-        <v>4251183456.297542</v>
+        <v>54840266586.2383</v>
       </c>
       <c r="N28">
-        <v>1551590517.736276</v>
+        <v>20015517678.79796</v>
       </c>
       <c r="O28">
-        <v>10030053932.88429</v>
+        <v>129387695734.2073</v>
       </c>
       <c r="P28">
-        <v>14341076597.75727</v>
+        <v>184999888111.0688</v>
       </c>
       <c r="Q28">
-        <v>11405414015.92546</v>
+        <v>147129840805.4385</v>
       </c>
     </row>
     <row r="29">
@@ -7906,52 +7906,52 @@
         </is>
       </c>
       <c r="B29">
-        <v>1293352329.336462</v>
+        <v>16684245048.44036</v>
       </c>
       <c r="C29">
-        <v>71053342.39787595</v>
+        <v>916588116.9325998</v>
       </c>
       <c r="D29">
-        <v>1722756923.674896</v>
+        <v>22223564315.40615</v>
       </c>
       <c r="E29">
-        <v>134919246.7268094</v>
+        <v>1740458282.775841</v>
       </c>
       <c r="F29">
-        <v>1079725524.31469</v>
+        <v>13928459263.6595</v>
       </c>
       <c r="G29">
-        <v>3008455037.114271</v>
+        <v>38809069978.7741</v>
       </c>
       <c r="H29">
-        <v>2942725499.315838</v>
+        <v>37961158941.17431</v>
       </c>
       <c r="I29">
-        <v>811201187.6389616</v>
+        <v>10464495320.5426</v>
       </c>
       <c r="J29">
-        <v>202943975.9776573</v>
+        <v>2617977290.111779</v>
       </c>
       <c r="K29">
-        <v>194517349.616694</v>
+        <v>2509273810.055352</v>
       </c>
       <c r="L29">
-        <v>92315667.67500699</v>
+        <v>1190872113.00759</v>
       </c>
       <c r="M29">
-        <v>4283279138.55506</v>
+        <v>55254300887.36028</v>
       </c>
       <c r="N29">
-        <v>1557590389.746076</v>
+        <v>20092916027.72438</v>
       </c>
       <c r="O29">
-        <v>10084573208.52529</v>
+        <v>130090994389.9763</v>
       </c>
       <c r="P29">
-        <v>14386380574.97603</v>
+        <v>185584309417.1907</v>
       </c>
       <c r="Q29">
-        <v>11443122188.21848</v>
+        <v>147616276228.0184</v>
       </c>
     </row>
     <row r="30">
@@ -7961,52 +7961,52 @@
         </is>
       </c>
       <c r="B30">
-        <v>1291328071.330353</v>
+        <v>16658132120.16155</v>
       </c>
       <c r="C30">
-        <v>72106843.08969009</v>
+        <v>930178275.8570021</v>
       </c>
       <c r="D30">
-        <v>1726693137.569862</v>
+        <v>22274341474.65122</v>
       </c>
       <c r="E30">
-        <v>134348168.6772378</v>
+        <v>1733091375.936368</v>
       </c>
       <c r="F30">
-        <v>1078699377.557031</v>
+        <v>13915221970.4857</v>
       </c>
       <c r="G30">
-        <v>3011847526.893821</v>
+        <v>38852833096.93029</v>
       </c>
       <c r="H30">
-        <v>2948485837.229738</v>
+        <v>38035467300.26363</v>
       </c>
       <c r="I30">
-        <v>820895829.2118832</v>
+        <v>10589556196.83329</v>
       </c>
       <c r="J30">
-        <v>207853934.9982234</v>
+        <v>2681315761.477082</v>
       </c>
       <c r="K30">
-        <v>196716291.6699249</v>
+        <v>2537640162.542031</v>
       </c>
       <c r="L30">
-        <v>93228630.8177065</v>
+        <v>1202649337.548414</v>
       </c>
       <c r="M30">
-        <v>4310934612.478389</v>
+        <v>55611056500.97121</v>
       </c>
       <c r="N30">
-        <v>1563892047.134295</v>
+        <v>20174207408.03241</v>
       </c>
       <c r="O30">
-        <v>10142007183.54016</v>
+        <v>130831892667.6681</v>
       </c>
       <c r="P30">
-        <v>14445182781.76433</v>
+        <v>186342857884.7599</v>
       </c>
       <c r="Q30">
-        <v>11496734032.48198</v>
+        <v>148307869019.0175</v>
       </c>
     </row>
     <row r="31">
@@ -8016,52 +8016,52 @@
         </is>
       </c>
       <c r="B31">
-        <v>1300430879.739195</v>
+        <v>16775558348.63561</v>
       </c>
       <c r="C31">
-        <v>72720597.43582213</v>
+        <v>938095706.9221056</v>
       </c>
       <c r="D31">
-        <v>1733700030.338329</v>
+        <v>22364730391.36444</v>
       </c>
       <c r="E31">
-        <v>134195495.9915963</v>
+        <v>1731121898.291592</v>
       </c>
       <c r="F31">
-        <v>1080305622.320841</v>
+        <v>13935942527.93884</v>
       </c>
       <c r="G31">
-        <v>3020921746.086588</v>
+        <v>38969890524.51698</v>
       </c>
       <c r="H31">
-        <v>2956942015.160421</v>
+        <v>38144551995.56944</v>
       </c>
       <c r="I31">
-        <v>831633008.6916591</v>
+        <v>10728065812.1224</v>
       </c>
       <c r="J31">
-        <v>211644672.4243365</v>
+        <v>2730216274.273941</v>
       </c>
       <c r="K31">
-        <v>199518150.9737271</v>
+        <v>2573784147.56108</v>
       </c>
       <c r="L31">
-        <v>92926138.58246107</v>
+        <v>1198747187.713748</v>
       </c>
       <c r="M31">
-        <v>4361120323.638924</v>
+        <v>56258452174.94212</v>
       </c>
       <c r="N31">
-        <v>1568332478.647142</v>
+        <v>20231488974.54813</v>
       </c>
       <c r="O31">
-        <v>10222116788.11867</v>
+        <v>131865306566.7308</v>
       </c>
       <c r="P31">
-        <v>14543469413.94445</v>
+        <v>187610755439.8834</v>
       </c>
       <c r="Q31">
-        <v>11581779916.97565</v>
+        <v>149404960928.986</v>
       </c>
     </row>
     <row r="32">
@@ -8071,52 +8071,52 @@
         </is>
       </c>
       <c r="B32">
-        <v>1292336624.208962</v>
+        <v>16671142452.29562</v>
       </c>
       <c r="C32">
-        <v>72648809.02505669</v>
+        <v>937169636.4232314</v>
       </c>
       <c r="D32">
-        <v>1742464071.786565</v>
+        <v>22477786526.04669</v>
       </c>
       <c r="E32">
-        <v>137773208.4616512</v>
+        <v>1777274389.1553</v>
       </c>
       <c r="F32">
-        <v>1082348740.33464</v>
+        <v>13962298750.31685</v>
       </c>
       <c r="G32">
-        <v>3035234829.607913</v>
+        <v>39154529301.94208</v>
       </c>
       <c r="H32">
-        <v>2961895971.22745</v>
+        <v>38208458028.83411</v>
       </c>
       <c r="I32">
-        <v>844812003.126972</v>
+        <v>10898074840.33794</v>
       </c>
       <c r="J32">
-        <v>213255770.4139473</v>
+        <v>2750999438.33992</v>
       </c>
       <c r="K32">
-        <v>200607635.1886213</v>
+        <v>2587838493.933214</v>
       </c>
       <c r="L32">
-        <v>92397804.2633191</v>
+        <v>1191931674.996816</v>
       </c>
       <c r="M32">
-        <v>4402776602.045778</v>
+        <v>56795818166.39054</v>
       </c>
       <c r="N32">
-        <v>1570152787.291568</v>
+        <v>20254970956.06123</v>
       </c>
       <c r="O32">
-        <v>10285898573.55766</v>
+        <v>132688091598.8938</v>
       </c>
       <c r="P32">
-        <v>14613470027.37453</v>
+        <v>188513763353.1314</v>
       </c>
       <c r="Q32">
-        <v>11658582811.61068</v>
+        <v>150395718269.7778</v>
       </c>
     </row>
     <row r="33">
@@ -8126,52 +8126,52 @@
         </is>
       </c>
       <c r="B33">
-        <v>1290775856.661009</v>
+        <v>16651008550.92702</v>
       </c>
       <c r="C33">
-        <v>74072095.17247409</v>
+        <v>955530027.7249157</v>
       </c>
       <c r="D33">
-        <v>1755546423.122872</v>
+        <v>22646548858.28505</v>
       </c>
       <c r="E33">
-        <v>140171055.7046766</v>
+        <v>1808206618.590328</v>
       </c>
       <c r="F33">
-        <v>1079617940.256653</v>
+        <v>13927071429.31082</v>
       </c>
       <c r="G33">
-        <v>3049407514.256675</v>
+        <v>39337356933.9111</v>
       </c>
       <c r="H33">
-        <v>2971076970.326589</v>
+        <v>38326892917.213</v>
       </c>
       <c r="I33">
-        <v>853511517.1136928</v>
+        <v>11010298570.76664</v>
       </c>
       <c r="J33">
-        <v>215824729.7320864</v>
+        <v>2784139013.543914</v>
       </c>
       <c r="K33">
-        <v>200957426.4090287</v>
+        <v>2592350800.67647</v>
       </c>
       <c r="L33">
-        <v>91987226.68652226</v>
+        <v>1186635224.256137</v>
       </c>
       <c r="M33">
-        <v>4444079172.631754</v>
+        <v>57328621326.94963</v>
       </c>
       <c r="N33">
-        <v>1573580844.781802</v>
+        <v>20299192897.68525</v>
       </c>
       <c r="O33">
-        <v>10351017887.68147</v>
+        <v>133528130751.091</v>
       </c>
       <c r="P33">
-        <v>14691201258.59916</v>
+        <v>189516496235.9292</v>
       </c>
       <c r="Q33">
-        <v>11734857330.46983</v>
+        <v>151379659563.0608</v>
       </c>
     </row>
     <row r="34">
@@ -8181,52 +8181,52 @@
         </is>
       </c>
       <c r="B34">
-        <v>1287832804.018583</v>
+        <v>16613043171.83972</v>
       </c>
       <c r="C34">
-        <v>75888202.63328007</v>
+        <v>978957813.9693129</v>
       </c>
       <c r="D34">
-        <v>1764828262.489382</v>
+        <v>22766284586.11303</v>
       </c>
       <c r="E34">
-        <v>142278012.0693438</v>
+        <v>1835386355.694535</v>
       </c>
       <c r="F34">
-        <v>1075359317.940309</v>
+        <v>13872135201.42998</v>
       </c>
       <c r="G34">
-        <v>3058353795.132315</v>
+        <v>39452763957.20686</v>
       </c>
       <c r="H34">
-        <v>2963839260.329629</v>
+        <v>38233526458.25222</v>
       </c>
       <c r="I34">
-        <v>859641515.0804064</v>
+        <v>11089375544.53724</v>
       </c>
       <c r="J34">
-        <v>220553830.260054</v>
+        <v>2845144410.354696</v>
       </c>
       <c r="K34">
-        <v>200709148.8086495</v>
+        <v>2589148019.631579</v>
       </c>
       <c r="L34">
-        <v>90879246.73634052</v>
+        <v>1172342282.898793</v>
       </c>
       <c r="M34">
-        <v>4455531639.766994</v>
+        <v>57476358152.99423</v>
       </c>
       <c r="N34">
-        <v>1583705273.51378</v>
+        <v>20429798028.32776</v>
       </c>
       <c r="O34">
-        <v>10374859914.49585</v>
+        <v>133835692896.9965</v>
       </c>
       <c r="P34">
-        <v>14721046513.64675</v>
+        <v>189901500026.0431</v>
       </c>
       <c r="Q34">
-        <v>11758629189.37805</v>
+        <v>151686316542.9768</v>
       </c>
     </row>
     <row r="35">
@@ -8236,52 +8236,52 @@
         </is>
       </c>
       <c r="B35">
-        <v>1266072165.712473</v>
+        <v>16332330937.6909</v>
       </c>
       <c r="C35">
-        <v>76712467.64402764</v>
+        <v>989590832.6079565</v>
       </c>
       <c r="D35">
-        <v>1719721288.104714</v>
+        <v>22184404616.55082</v>
       </c>
       <c r="E35">
-        <v>141412932.7750041</v>
+        <v>1824226832.797553</v>
       </c>
       <c r="F35">
-        <v>1025552130.543139</v>
+        <v>13229622484.00649</v>
       </c>
       <c r="G35">
-        <v>2963398819.066885</v>
+        <v>38227844765.96281</v>
       </c>
       <c r="H35">
-        <v>2870024610.292008</v>
+        <v>37023317472.76691</v>
       </c>
       <c r="I35">
-        <v>837970275.4331074</v>
+        <v>10809816553.08709</v>
       </c>
       <c r="J35">
-        <v>221314870.4952052</v>
+        <v>2854961829.388147</v>
       </c>
       <c r="K35">
-        <v>196378129.9681355</v>
+        <v>2533277876.588948</v>
       </c>
       <c r="L35">
-        <v>88983284.55548783</v>
+        <v>1147884370.765793</v>
       </c>
       <c r="M35">
-        <v>4287010752.971508</v>
+        <v>55302438713.33245</v>
       </c>
       <c r="N35">
-        <v>1606250234.276888</v>
+        <v>20720628022.17186</v>
       </c>
       <c r="O35">
-        <v>10107932157.99234</v>
+        <v>130392324838.1012</v>
       </c>
       <c r="P35">
-        <v>14337403142.7717</v>
+        <v>184952500541.7549</v>
       </c>
       <c r="Q35">
-        <v>11376097458.22685</v>
+        <v>146751657211.1264</v>
       </c>
     </row>
     <row r="36">
@@ -8291,52 +8291,52 @@
         </is>
       </c>
       <c r="B36">
-        <v>1263553849.573467</v>
+        <v>16299844659.49773</v>
       </c>
       <c r="C36">
-        <v>75361995.72939306</v>
+        <v>972169744.9091705</v>
       </c>
       <c r="D36">
-        <v>1673857639.106308</v>
+        <v>21592763544.47137</v>
       </c>
       <c r="E36">
-        <v>136217493.7223105</v>
+        <v>1757205669.017806</v>
       </c>
       <c r="F36">
-        <v>984327755.4030021</v>
+        <v>12697828044.69873</v>
       </c>
       <c r="G36">
-        <v>2869764883.961014</v>
+        <v>37019967003.09708</v>
       </c>
       <c r="H36">
-        <v>2777223378.095803</v>
+        <v>35826181577.43586</v>
       </c>
       <c r="I36">
-        <v>807363561.966949</v>
+        <v>10414989949.37364</v>
       </c>
       <c r="J36">
-        <v>223882406.3804763</v>
+        <v>2888083042.308145</v>
       </c>
       <c r="K36">
-        <v>192635711.0562699</v>
+        <v>2485000672.625881</v>
       </c>
       <c r="L36">
-        <v>88566785.33123672</v>
+        <v>1142511530.772954</v>
       </c>
       <c r="M36">
-        <v>4070410779.643351</v>
+        <v>52508299057.39923</v>
       </c>
       <c r="N36">
-        <v>1608651906.610334</v>
+        <v>20751609595.27331</v>
       </c>
       <c r="O36">
-        <v>9768734529.084421</v>
+        <v>126016675425.189</v>
       </c>
       <c r="P36">
-        <v>13902053262.6189</v>
+        <v>179336487087.7838</v>
       </c>
       <c r="Q36">
-        <v>10941280721.10386</v>
+        <v>141142521302.2399</v>
       </c>
     </row>
     <row r="37">
@@ -8346,52 +8346,52 @@
         </is>
       </c>
       <c r="B37">
-        <v>1276028817.745767</v>
+        <v>16460771748.9204</v>
       </c>
       <c r="C37">
-        <v>73348060.06445608</v>
+        <v>946189974.8314834</v>
       </c>
       <c r="D37">
-        <v>1643780756.032259</v>
+        <v>21204771752.81614</v>
       </c>
       <c r="E37">
-        <v>127081459.4228557</v>
+        <v>1639350826.554839</v>
       </c>
       <c r="F37">
-        <v>959283011.4478943</v>
+        <v>12374750847.67784</v>
       </c>
       <c r="G37">
-        <v>2803493286.967465</v>
+        <v>36165063401.88029</v>
       </c>
       <c r="H37">
-        <v>2699974214.958188</v>
+        <v>34829667372.96062</v>
       </c>
       <c r="I37">
-        <v>780800383.5136192</v>
+        <v>10072324947.32569</v>
       </c>
       <c r="J37">
-        <v>225652622.5668415</v>
+        <v>2910918831.112255</v>
       </c>
       <c r="K37">
-        <v>196589174.6463034</v>
+        <v>2536000352.937314</v>
       </c>
       <c r="L37">
-        <v>87179361.1522381</v>
+        <v>1124613758.863872</v>
       </c>
       <c r="M37">
-        <v>3882462423.553138</v>
+        <v>50083765263.83548</v>
       </c>
       <c r="N37">
-        <v>1621090499.905912</v>
+        <v>20912067448.78627</v>
       </c>
       <c r="O37">
-        <v>9493748680.296238</v>
+        <v>122469357975.8215</v>
       </c>
       <c r="P37">
-        <v>13573270785.00947</v>
+        <v>175095193126.6222</v>
       </c>
       <c r="Q37">
-        <v>10588972106.20555</v>
+        <v>136597740170.0517</v>
       </c>
     </row>
     <row r="38">
@@ -8401,52 +8401,52 @@
         </is>
       </c>
       <c r="B38">
-        <v>1294808513.087819</v>
+        <v>16703029818.83286</v>
       </c>
       <c r="C38">
-        <v>70958069.44442832</v>
+        <v>915359095.8331255</v>
       </c>
       <c r="D38">
-        <v>1618997709.722411</v>
+        <v>20885070455.41911</v>
       </c>
       <c r="E38">
-        <v>120825464.4066795</v>
+        <v>1558648490.846166</v>
       </c>
       <c r="F38">
-        <v>949967942.8710297</v>
+        <v>12254586463.03628</v>
       </c>
       <c r="G38">
-        <v>2760749186.444549</v>
+        <v>35613664505.13468</v>
       </c>
       <c r="H38">
-        <v>2641016619.166145</v>
+        <v>34069114387.24327</v>
       </c>
       <c r="I38">
-        <v>760567215.3249564</v>
+        <v>9811317077.691938</v>
       </c>
       <c r="J38">
-        <v>225950055.1300866</v>
+        <v>2914755711.178117</v>
       </c>
       <c r="K38">
-        <v>200402385.8564509</v>
+        <v>2585190777.548217</v>
       </c>
       <c r="L38">
-        <v>89104184.02637073</v>
+        <v>1149443973.940182</v>
       </c>
       <c r="M38">
-        <v>3728455798.911337</v>
+        <v>48097079805.95625</v>
       </c>
       <c r="N38">
-        <v>1626279689.000889</v>
+        <v>20979007988.11147</v>
       </c>
       <c r="O38">
-        <v>9271775947.416237</v>
+        <v>119605909721.6695</v>
       </c>
       <c r="P38">
-        <v>13327333646.9486</v>
+        <v>171922604045.637</v>
       </c>
       <c r="Q38">
-        <v>10317141260.83353</v>
+        <v>133091122264.7525</v>
       </c>
     </row>
     <row r="39">
@@ -8456,52 +8456,52 @@
         </is>
       </c>
       <c r="B39">
-        <v>1331543142.765314</v>
+        <v>17176906541.67255</v>
       </c>
       <c r="C39">
-        <v>71116859.40159276</v>
+        <v>917407486.2805467</v>
       </c>
       <c r="D39">
-        <v>1639678072.982423</v>
+        <v>21151847141.47326</v>
       </c>
       <c r="E39">
-        <v>113794893.0771276</v>
+        <v>1467954120.694946</v>
       </c>
       <c r="F39">
-        <v>996821814.4921397</v>
+        <v>12859001406.9486</v>
       </c>
       <c r="G39">
-        <v>2821411639.953283</v>
+        <v>36396210155.39735</v>
       </c>
       <c r="H39">
-        <v>2677964301.838365</v>
+        <v>34545739493.7149</v>
       </c>
       <c r="I39">
-        <v>766037662.963336</v>
+        <v>9881885852.227034</v>
       </c>
       <c r="J39">
-        <v>235669430.9513235</v>
+        <v>3040135659.272073</v>
       </c>
       <c r="K39">
-        <v>207067089.232531</v>
+        <v>2671165451.099649</v>
       </c>
       <c r="L39">
-        <v>90857004.40746805</v>
+        <v>1172055356.856338</v>
       </c>
       <c r="M39">
-        <v>3780030041.705995</v>
+        <v>48762387538.00734</v>
       </c>
       <c r="N39">
-        <v>1612404952.731189</v>
+        <v>20800023890.23233</v>
       </c>
       <c r="O39">
-        <v>9370030483.830206</v>
+        <v>120873393241.4097</v>
       </c>
       <c r="P39">
-        <v>13522985266.5488</v>
+        <v>174446509938.4796</v>
       </c>
       <c r="Q39">
-        <v>10488180166.64483</v>
+        <v>135297524149.7184</v>
       </c>
     </row>
     <row r="40">
@@ -8511,52 +8511,52 @@
         </is>
       </c>
       <c r="B40">
-        <v>1363605303.975189</v>
+        <v>17590508421.27995</v>
       </c>
       <c r="C40">
-        <v>72829599.639061</v>
+        <v>939501835.343887</v>
       </c>
       <c r="D40">
-        <v>1689351067.641004</v>
+        <v>21792628772.56895</v>
       </c>
       <c r="E40">
-        <v>109650496.0819023</v>
+        <v>1414491399.456539</v>
       </c>
       <c r="F40">
-        <v>1044862449.52327</v>
+        <v>13478725598.85018</v>
       </c>
       <c r="G40">
-        <v>2916693612.885237</v>
+        <v>37625347606.21956</v>
       </c>
       <c r="H40">
-        <v>2763264260.536091</v>
+        <v>35646108960.91557</v>
       </c>
       <c r="I40">
-        <v>789086894.9943311</v>
+        <v>10179220945.42687</v>
       </c>
       <c r="J40">
-        <v>240878139.0430886</v>
+        <v>3107327993.655842</v>
       </c>
       <c r="K40">
-        <v>212822573.2678615</v>
+        <v>2745411195.155414</v>
       </c>
       <c r="L40">
-        <v>91892942.95358832</v>
+        <v>1185418964.101289</v>
       </c>
       <c r="M40">
-        <v>3913026886.712846</v>
+        <v>50478046838.59571</v>
       </c>
       <c r="N40">
-        <v>1604497105.046042</v>
+        <v>20698012655.09394</v>
       </c>
       <c r="O40">
-        <v>9615468802.553846</v>
+        <v>124039547552.9446</v>
       </c>
       <c r="P40">
-        <v>13895767719.41427</v>
+        <v>179255403580.4442</v>
       </c>
       <c r="Q40">
-        <v>10835772367.43946</v>
+        <v>139781463539.969</v>
       </c>
     </row>
     <row r="41">
@@ -8566,52 +8566,52 @@
         </is>
       </c>
       <c r="B41">
-        <v>1379973131.95039</v>
+        <v>17801653402.16003</v>
       </c>
       <c r="C41">
-        <v>75665837.58402193</v>
+        <v>976089304.8338829</v>
       </c>
       <c r="D41">
-        <v>1727418009.765214</v>
+        <v>22283692325.97126</v>
       </c>
       <c r="E41">
-        <v>111304897.7269831</v>
+        <v>1435833180.678083</v>
       </c>
       <c r="F41">
-        <v>1090330051.519926</v>
+        <v>14065257664.60704</v>
       </c>
       <c r="G41">
-        <v>3004718796.596145</v>
+        <v>38760872476.09027</v>
       </c>
       <c r="H41">
-        <v>2844526175.788503</v>
+        <v>36694387667.67168</v>
       </c>
       <c r="I41">
-        <v>809771330.9665909</v>
+        <v>10446050169.46902</v>
       </c>
       <c r="J41">
-        <v>252855771.9077788</v>
+        <v>3261839457.610346</v>
       </c>
       <c r="K41">
-        <v>214901009.7075964</v>
+        <v>2772223025.227993</v>
       </c>
       <c r="L41">
-        <v>93909349.72330931</v>
+        <v>1211430611.43069</v>
       </c>
       <c r="M41">
-        <v>4052141915.895442</v>
+        <v>52272630715.0512</v>
       </c>
       <c r="N41">
-        <v>1594315413.112071</v>
+        <v>20566668829.14572</v>
       </c>
       <c r="O41">
-        <v>9862420967.101292</v>
+        <v>127225230475.6067</v>
       </c>
       <c r="P41">
-        <v>14247112895.64783</v>
+        <v>183787756353.857</v>
       </c>
       <c r="Q41">
-        <v>11178915000.86206</v>
+        <v>144208003511.1205</v>
       </c>
     </row>
     <row r="42">
@@ -8621,52 +8621,52 @@
         </is>
       </c>
       <c r="B42">
-        <v>1384387035.477096</v>
+        <v>17858592757.65454</v>
       </c>
       <c r="C42">
-        <v>77587162.08715452</v>
+        <v>1000874390.924293</v>
       </c>
       <c r="D42">
-        <v>1762561166.640203</v>
+        <v>22737039049.65861</v>
       </c>
       <c r="E42">
-        <v>112230718.5549635</v>
+        <v>1447776269.359029</v>
       </c>
       <c r="F42">
-        <v>1125232315.074256</v>
+        <v>14515496864.4579</v>
       </c>
       <c r="G42">
-        <v>3077611362.356576</v>
+        <v>39701186574.39983</v>
       </c>
       <c r="H42">
-        <v>2933238887.760644</v>
+        <v>37838781652.1123</v>
       </c>
       <c r="I42">
-        <v>826498060.3114171</v>
+        <v>10661824978.01728</v>
       </c>
       <c r="J42">
-        <v>259589239.0544096</v>
+        <v>3348701183.801884</v>
       </c>
       <c r="K42">
-        <v>216116873.6731251</v>
+        <v>2787907670.383315</v>
       </c>
       <c r="L42">
-        <v>93658413.4366843</v>
+        <v>1208193533.333227</v>
       </c>
       <c r="M42">
-        <v>4200314716.021916</v>
+        <v>54184059836.68272</v>
       </c>
       <c r="N42">
-        <v>1588180983.328684</v>
+        <v>20487534684.94003</v>
       </c>
       <c r="O42">
-        <v>10117597173.58688</v>
+        <v>130517003539.2708</v>
       </c>
       <c r="P42">
-        <v>14579595571.42055</v>
+        <v>188076782871.3251</v>
       </c>
       <c r="Q42">
-        <v>11513369139.17809</v>
+        <v>148522461895.3973</v>
       </c>
     </row>
     <row r="43">
@@ -8676,52 +8676,52 @@
         </is>
       </c>
       <c r="B43">
-        <v>1378432838.660475</v>
+        <v>17781783618.72012</v>
       </c>
       <c r="C43">
-        <v>80678146.83873369</v>
+        <v>1040748094.219665</v>
       </c>
       <c r="D43">
-        <v>1806764283.905996</v>
+        <v>23307259262.38735</v>
       </c>
       <c r="E43">
-        <v>116640439.3205538</v>
+        <v>1504661667.235144</v>
       </c>
       <c r="F43">
-        <v>1157700214.501287</v>
+        <v>14934332767.0666</v>
       </c>
       <c r="G43">
-        <v>3161783084.56657</v>
+        <v>40787001790.90876</v>
       </c>
       <c r="H43">
-        <v>3038178819.722248</v>
+        <v>39192506774.417</v>
       </c>
       <c r="I43">
-        <v>848249721.4173225</v>
+        <v>10942421406.28346</v>
       </c>
       <c r="J43">
-        <v>267827780.050804</v>
+        <v>3454978362.655372</v>
       </c>
       <c r="K43">
-        <v>220510663.3205144</v>
+        <v>2844587556.834636</v>
       </c>
       <c r="L43">
-        <v>97358451.63060512</v>
+        <v>1255924026.034806</v>
       </c>
       <c r="M43">
-        <v>4336609851.136393</v>
+        <v>55942267079.65947</v>
       </c>
       <c r="N43">
-        <v>1601583879.377697</v>
+        <v>20660432043.97229</v>
       </c>
       <c r="O43">
-        <v>10410319166.65558</v>
+        <v>134293117249.857</v>
       </c>
       <c r="P43">
-        <v>14950535089.88263</v>
+        <v>192861902659.4859</v>
       </c>
       <c r="Q43">
-        <v>11873159920.21385</v>
+        <v>153163762970.7587</v>
       </c>
     </row>
     <row r="44">
@@ -8731,52 +8731,52 @@
         </is>
       </c>
       <c r="B44">
-        <v>1366278296.413549</v>
+        <v>17624990023.73478</v>
       </c>
       <c r="C44">
-        <v>82964490.42811427</v>
+        <v>1070241926.522674</v>
       </c>
       <c r="D44">
-        <v>1823860040.287953</v>
+        <v>23527794519.7146</v>
       </c>
       <c r="E44">
-        <v>118253997.715509</v>
+        <v>1525476570.530066</v>
       </c>
       <c r="F44">
-        <v>1169121515.700114</v>
+        <v>15081667552.53147</v>
       </c>
       <c r="G44">
-        <v>3194200044.13169</v>
+        <v>41205180569.29881</v>
       </c>
       <c r="H44">
-        <v>3099711156.144325</v>
+        <v>39986273914.2618</v>
       </c>
       <c r="I44">
-        <v>867149941.3132622</v>
+        <v>11186234242.94108</v>
       </c>
       <c r="J44">
-        <v>273050743.9735898</v>
+        <v>3522354597.259308</v>
       </c>
       <c r="K44">
-        <v>227287938.9080582</v>
+        <v>2932014411.913951</v>
       </c>
       <c r="L44">
-        <v>100033556.5293768</v>
+        <v>1290432879.228961</v>
       </c>
       <c r="M44">
-        <v>4444458410.709824</v>
+        <v>57333513498.15672</v>
       </c>
       <c r="N44">
-        <v>1634808240.891666</v>
+        <v>21089026307.50249</v>
       </c>
       <c r="O44">
-        <v>10646499988.4701</v>
+        <v>137339849851.2643</v>
       </c>
       <c r="P44">
-        <v>15206978329.01534</v>
+        <v>196170020444.2979</v>
       </c>
       <c r="Q44">
-        <v>12105858235.18075</v>
+        <v>156165571233.8317</v>
       </c>
     </row>
     <row r="45">
@@ -8786,52 +8786,52 @@
         </is>
       </c>
       <c r="B45">
-        <v>1347553092.35169</v>
+        <v>17383434891.3368</v>
       </c>
       <c r="C45">
-        <v>85664859.30281244</v>
+        <v>1105076685.00628</v>
       </c>
       <c r="D45">
-        <v>1836206896.570437</v>
+        <v>23687068965.75864</v>
       </c>
       <c r="E45">
-        <v>118460651.4725597</v>
+        <v>1528142403.99602</v>
       </c>
       <c r="F45">
-        <v>1165399449.062934</v>
+        <v>15033652892.91184</v>
       </c>
       <c r="G45">
-        <v>3205731856.408742</v>
+        <v>41353940947.67278</v>
       </c>
       <c r="H45">
-        <v>3132303192.18617</v>
+        <v>40406711179.2016</v>
       </c>
       <c r="I45">
-        <v>885793434.3088365</v>
+        <v>11426735302.58399</v>
       </c>
       <c r="J45">
-        <v>272350943.7462947</v>
+        <v>3513327174.327201</v>
       </c>
       <c r="K45">
-        <v>234047556.6201509</v>
+        <v>3019213480.399947</v>
       </c>
       <c r="L45">
-        <v>102918938.4407971</v>
+        <v>1327654305.886283</v>
       </c>
       <c r="M45">
-        <v>4504610600.864515</v>
+        <v>58109476751.15225</v>
       </c>
       <c r="N45">
-        <v>1658883830.621981</v>
+        <v>21399601415.02355</v>
       </c>
       <c r="O45">
-        <v>10790908496.78874</v>
+        <v>139202719608.5748</v>
       </c>
       <c r="P45">
-        <v>15344193445.54918</v>
+        <v>197940095447.5844</v>
       </c>
       <c r="Q45">
-        <v>12234837584.13471</v>
+        <v>157829404835.3377</v>
       </c>
     </row>
     <row r="46">
@@ -8841,52 +8841,52 @@
         </is>
       </c>
       <c r="B46">
-        <v>1332018193.839209</v>
+        <v>17183034700.5258</v>
       </c>
       <c r="C46">
-        <v>87132298.27412648</v>
+        <v>1124006647.736232</v>
       </c>
       <c r="D46">
-        <v>1845615078.177755</v>
+        <v>23808434508.49304</v>
       </c>
       <c r="E46">
-        <v>118323360.3615828</v>
+        <v>1526371348.664418</v>
       </c>
       <c r="F46">
-        <v>1161709972.368906</v>
+        <v>14986058643.5589</v>
       </c>
       <c r="G46">
-        <v>3212780709.182371</v>
+        <v>41444871148.45258</v>
       </c>
       <c r="H46">
-        <v>3153463572.238882</v>
+        <v>40679680081.88158</v>
       </c>
       <c r="I46">
-        <v>901997110.5421183</v>
+        <v>11635762725.99333</v>
       </c>
       <c r="J46">
-        <v>272800601.6628234</v>
+        <v>3519127761.450422</v>
       </c>
       <c r="K46">
-        <v>240086979.3086599</v>
+        <v>3097122033.081713</v>
       </c>
       <c r="L46">
-        <v>105136493.4905894</v>
+        <v>1356260766.028603</v>
       </c>
       <c r="M46">
-        <v>4543809813.283881</v>
+        <v>58615146591.36207</v>
       </c>
       <c r="N46">
-        <v>1677274504.759767</v>
+        <v>21636841111.40099</v>
       </c>
       <c r="O46">
-        <v>10894569075.28672</v>
+        <v>140539941071.1987</v>
       </c>
       <c r="P46">
-        <v>15439367978.3083</v>
+        <v>199167846920.1771</v>
       </c>
       <c r="Q46">
-        <v>12324938786.21874</v>
+        <v>158991710342.2217</v>
       </c>
     </row>
     <row r="47">
@@ -8896,52 +8896,52 @@
         </is>
       </c>
       <c r="B47">
-        <v>1316756541.119009</v>
+        <v>16986159380.43521</v>
       </c>
       <c r="C47">
-        <v>87359242.96796857</v>
+        <v>1126934234.286795</v>
       </c>
       <c r="D47">
-        <v>1843010479.778081</v>
+        <v>23774835189.13725</v>
       </c>
       <c r="E47">
-        <v>117195987.8105012</v>
+        <v>1511828242.755466</v>
       </c>
       <c r="F47">
-        <v>1146296406.417224</v>
+        <v>14787223642.78219</v>
       </c>
       <c r="G47">
-        <v>3193862116.973775</v>
+        <v>41200821308.9617</v>
       </c>
       <c r="H47">
-        <v>3143888064.941614</v>
+        <v>40556156037.74683</v>
       </c>
       <c r="I47">
-        <v>909652030.1561675</v>
+        <v>11734511189.01456</v>
       </c>
       <c r="J47">
-        <v>269397305.8555628</v>
+        <v>3475225245.53676</v>
       </c>
       <c r="K47">
-        <v>242620849.5512547</v>
+        <v>3129808959.211186</v>
       </c>
       <c r="L47">
-        <v>105219220.6705115</v>
+        <v>1357327946.649598</v>
       </c>
       <c r="M47">
-        <v>4577355498.143349</v>
+        <v>59047885926.0492</v>
       </c>
       <c r="N47">
-        <v>1688943020.948427</v>
+        <v>21787364970.23471</v>
       </c>
       <c r="O47">
-        <v>10937075990.26689</v>
+        <v>141088280274.4428</v>
       </c>
       <c r="P47">
-        <v>15447694648.35967</v>
+        <v>199275260963.8397</v>
       </c>
       <c r="Q47">
-        <v>12336775865.62172</v>
+        <v>159144408666.5202</v>
       </c>
     </row>
     <row r="48">
@@ -8951,52 +8951,52 @@
         </is>
       </c>
       <c r="B48">
-        <v>1298215098.378171</v>
+        <v>16746974769.0784</v>
       </c>
       <c r="C48">
-        <v>89476979.08729845</v>
+        <v>1154253030.22615</v>
       </c>
       <c r="D48">
-        <v>1832952449.272601</v>
+        <v>23645086595.61655</v>
       </c>
       <c r="E48">
-        <v>119431574.9258437</v>
+        <v>1540667316.543384</v>
       </c>
       <c r="F48">
-        <v>1134740899.686905</v>
+        <v>14638157605.96108</v>
       </c>
       <c r="G48">
-        <v>3176601902.972649</v>
+        <v>40978164548.34717</v>
       </c>
       <c r="H48">
-        <v>3130276947.743368</v>
+        <v>40380572625.88945</v>
       </c>
       <c r="I48">
-        <v>914536598.7096205</v>
+        <v>11797522123.3541</v>
       </c>
       <c r="J48">
-        <v>274354733.4172651</v>
+        <v>3539176061.082719</v>
       </c>
       <c r="K48">
-        <v>246254535.7546673</v>
+        <v>3176683511.235209</v>
       </c>
       <c r="L48">
-        <v>105324894.2642952</v>
+        <v>1358691136.009408</v>
       </c>
       <c r="M48">
-        <v>4603168486.648848</v>
+        <v>59380873477.77013</v>
       </c>
       <c r="N48">
-        <v>1690868398.085838</v>
+        <v>21812202335.30731</v>
       </c>
       <c r="O48">
-        <v>10964784594.6239</v>
+        <v>141445721270.6483</v>
       </c>
       <c r="P48">
-        <v>15439601595.97472</v>
+        <v>199170860588.0739</v>
       </c>
       <c r="Q48">
-        <v>12345193205.24642</v>
+        <v>159252992347.6788</v>
       </c>
     </row>
     <row r="49">
@@ -9006,52 +9006,52 @@
         </is>
       </c>
       <c r="B49">
-        <v>1277122126.170314</v>
+        <v>16474875427.59705</v>
       </c>
       <c r="C49">
-        <v>90471658.41153002</v>
+        <v>1167084393.508737</v>
       </c>
       <c r="D49">
-        <v>1836147464.666982</v>
+        <v>23686302294.20407</v>
       </c>
       <c r="E49">
-        <v>120320043.5486089</v>
+        <v>1552128561.777056</v>
       </c>
       <c r="F49">
-        <v>1133665216.882944</v>
+        <v>14624281297.78998</v>
       </c>
       <c r="G49">
-        <v>3180604383.510065</v>
+        <v>41029796547.27984</v>
       </c>
       <c r="H49">
-        <v>3127552817.789745</v>
+        <v>40345431349.48772</v>
       </c>
       <c r="I49">
-        <v>927220826.2232332</v>
+        <v>11961148658.27971</v>
       </c>
       <c r="J49">
-        <v>280648402.3142658</v>
+        <v>3620364389.85403</v>
       </c>
       <c r="K49">
-        <v>245479433.8891369</v>
+        <v>3166684697.169866</v>
       </c>
       <c r="L49">
-        <v>107649413.0205447</v>
+        <v>1388677427.965027</v>
       </c>
       <c r="M49">
-        <v>4639914869.949095</v>
+        <v>59854901822.34332</v>
       </c>
       <c r="N49">
-        <v>1694042728.392934</v>
+        <v>21853151196.26885</v>
       </c>
       <c r="O49">
-        <v>11022508491.57895</v>
+        <v>142190359541.3685</v>
       </c>
       <c r="P49">
-        <v>15480235001.25933</v>
+        <v>199695031516.2454</v>
       </c>
       <c r="Q49">
-        <v>12401420733.67554</v>
+        <v>159978327464.4145</v>
       </c>
     </row>
     <row r="50">
@@ -9061,52 +9061,52 @@
         </is>
       </c>
       <c r="B50">
-        <v>1262501312.86089</v>
+        <v>16286266935.90548</v>
       </c>
       <c r="C50">
-        <v>93053028.28182143</v>
+        <v>1200384064.835496</v>
       </c>
       <c r="D50">
-        <v>1843635266.755431</v>
+        <v>23782894941.14507</v>
       </c>
       <c r="E50">
-        <v>121167590.595795</v>
+        <v>1563061918.685755</v>
       </c>
       <c r="F50">
-        <v>1142004036.793427</v>
+        <v>14731852074.63521</v>
       </c>
       <c r="G50">
-        <v>3199859922.426475</v>
+        <v>41278192999.30153</v>
       </c>
       <c r="H50">
-        <v>3131717119.486147</v>
+        <v>40399150841.3713</v>
       </c>
       <c r="I50">
-        <v>942703281.5486966</v>
+        <v>12160872331.97819</v>
       </c>
       <c r="J50">
-        <v>286655117.2915866</v>
+        <v>3697851013.061467</v>
       </c>
       <c r="K50">
-        <v>244796413.6376707</v>
+        <v>3157873735.925952</v>
       </c>
       <c r="L50">
-        <v>110186910.2038942</v>
+        <v>1421411141.630236</v>
       </c>
       <c r="M50">
-        <v>4688169500.559446</v>
+        <v>60477386557.21686</v>
       </c>
       <c r="N50">
-        <v>1704299519.276125</v>
+        <v>21985463798.66201</v>
       </c>
       <c r="O50">
-        <v>11108527862.00357</v>
+        <v>143300009419.846</v>
       </c>
       <c r="P50">
-        <v>15570889097.29093</v>
+        <v>200864469355.053</v>
       </c>
       <c r="Q50">
-        <v>12493901354.95002</v>
+        <v>161171327478.8553</v>
       </c>
     </row>
     <row r="51">
@@ -9116,52 +9116,52 @@
         </is>
       </c>
       <c r="B51">
-        <v>1247231272.088166</v>
+        <v>16089283409.93734</v>
       </c>
       <c r="C51">
-        <v>93991963.54963145</v>
+        <v>1212496329.790246</v>
       </c>
       <c r="D51">
-        <v>1852038294.654904</v>
+        <v>23891294001.04826</v>
       </c>
       <c r="E51">
-        <v>120606988.4841656</v>
+        <v>1555830151.445737</v>
       </c>
       <c r="F51">
-        <v>1155824056.347383</v>
+        <v>14910130326.88125</v>
       </c>
       <c r="G51">
-        <v>3222461303.036084</v>
+        <v>41569750809.16549</v>
       </c>
       <c r="H51">
-        <v>3153196799.421396</v>
+        <v>40676238712.536</v>
       </c>
       <c r="I51">
-        <v>961362965.9133604</v>
+        <v>12401582260.28235</v>
       </c>
       <c r="J51">
-        <v>293840692.2142365</v>
+        <v>3790544929.563651</v>
       </c>
       <c r="K51">
-        <v>244235965.136762</v>
+        <v>3150643950.264229</v>
       </c>
       <c r="L51">
-        <v>112895104.3158858</v>
+        <v>1456346845.674927</v>
       </c>
       <c r="M51">
-        <v>4733426031.409797</v>
+        <v>61061195805.18638</v>
       </c>
       <c r="N51">
-        <v>1723088130.834738</v>
+        <v>22227836887.76812</v>
       </c>
       <c r="O51">
-        <v>11222045689.24617</v>
+        <v>144764389391.2756</v>
       </c>
       <c r="P51">
-        <v>15691738264.37042</v>
+        <v>202423423610.3785</v>
       </c>
       <c r="Q51">
-        <v>12608523757.13163</v>
+        <v>162649956466.9981</v>
       </c>
     </row>
     <row r="52">
@@ -9171,52 +9171,52 @@
         </is>
       </c>
       <c r="B52">
-        <v>1231822402.414624</v>
+        <v>15890508991.14865</v>
       </c>
       <c r="C52">
-        <v>94882809.16567212</v>
+        <v>1223988238.23717</v>
       </c>
       <c r="D52">
-        <v>1879815981.131222</v>
+        <v>24249626156.59276</v>
       </c>
       <c r="E52">
-        <v>121872241.5224423</v>
+        <v>1572151915.639506</v>
       </c>
       <c r="F52">
-        <v>1167147822.381612</v>
+        <v>15056206908.7228</v>
       </c>
       <c r="G52">
-        <v>3263718854.200949</v>
+        <v>42101973219.19224</v>
       </c>
       <c r="H52">
-        <v>3178375474.177531</v>
+        <v>41001043616.89015</v>
       </c>
       <c r="I52">
-        <v>976364897.8082932</v>
+        <v>12595107181.72698</v>
       </c>
       <c r="J52">
-        <v>296825773.059359</v>
+        <v>3829052472.465731</v>
       </c>
       <c r="K52">
-        <v>243481238.115571</v>
+        <v>3140907971.690866</v>
       </c>
       <c r="L52">
-        <v>114402579.0411177</v>
+        <v>1475793269.630419</v>
       </c>
       <c r="M52">
-        <v>4778657974.79939</v>
+        <v>61644687874.91213</v>
       </c>
       <c r="N52">
-        <v>1743630161.884943</v>
+        <v>22492829088.31577</v>
       </c>
       <c r="O52">
-        <v>11331738098.8862</v>
+        <v>146179421475.632</v>
       </c>
       <c r="P52">
-        <v>15827279355.50178</v>
+        <v>204171903685.9729</v>
       </c>
       <c r="Q52">
-        <v>12737424212.16109</v>
+        <v>164312772336.8781</v>
       </c>
     </row>
     <row r="53">
@@ -9226,52 +9226,52 @@
         </is>
       </c>
       <c r="B53">
-        <v>1220879068.180143</v>
+        <v>15749339979.52385</v>
       </c>
       <c r="C53">
-        <v>95798163.30423844</v>
+        <v>1235796306.624676</v>
       </c>
       <c r="D53">
-        <v>1893330239.6865</v>
+        <v>24423960091.95586</v>
       </c>
       <c r="E53">
-        <v>123048361.3722993</v>
+        <v>1587323861.702661</v>
       </c>
       <c r="F53">
-        <v>1184821804.179462</v>
+        <v>15284201273.91507</v>
       </c>
       <c r="G53">
-        <v>3296998568.5425</v>
+        <v>42531281534.19826</v>
       </c>
       <c r="H53">
-        <v>3199042091.473891</v>
+        <v>41267642980.01319</v>
       </c>
       <c r="I53">
-        <v>989792529.3756158</v>
+        <v>12768323628.94544</v>
       </c>
       <c r="J53">
-        <v>296116818.3955084</v>
+        <v>3819906957.302059</v>
       </c>
       <c r="K53">
-        <v>242752485.6561813</v>
+        <v>3131507064.964739</v>
       </c>
       <c r="L53">
-        <v>114468519.7198727</v>
+        <v>1476643904.386358</v>
       </c>
       <c r="M53">
-        <v>4822604283.780319</v>
+        <v>62211595260.76612</v>
       </c>
       <c r="N53">
-        <v>1763899777.69859</v>
+        <v>22754307132.31181</v>
       </c>
       <c r="O53">
-        <v>11428676506.09998</v>
+        <v>147429926928.6897</v>
       </c>
       <c r="P53">
-        <v>15946554142.82262</v>
+        <v>205710548442.4118</v>
       </c>
       <c r="Q53">
-        <v>12847306777.22401</v>
+        <v>165730257426.1898</v>
       </c>
     </row>
     <row r="54">
@@ -9281,52 +9281,52 @@
         </is>
       </c>
       <c r="B54">
-        <v>1208078144.216968</v>
+        <v>15584208060.39888</v>
       </c>
       <c r="C54">
-        <v>96782317.70287061</v>
+        <v>1248491898.367031</v>
       </c>
       <c r="D54">
-        <v>1911556001.387927</v>
+        <v>24659072417.90426</v>
       </c>
       <c r="E54">
-        <v>123213359.9629369</v>
+        <v>1589452343.521886</v>
       </c>
       <c r="F54">
-        <v>1187102123.297074</v>
+        <v>15313617390.53226</v>
       </c>
       <c r="G54">
-        <v>3318653802.350809</v>
+        <v>42810634050.32544</v>
       </c>
       <c r="H54">
-        <v>3222698540.274104</v>
+        <v>41572811169.53593</v>
       </c>
       <c r="I54">
-        <v>999733550.4534768</v>
+        <v>12896562800.84985</v>
       </c>
       <c r="J54">
-        <v>297590047.1578125</v>
+        <v>3838911608.335782</v>
       </c>
       <c r="K54">
-        <v>246109472.2504156</v>
+        <v>3174812192.030361</v>
       </c>
       <c r="L54">
-        <v>115839918.6995972</v>
+        <v>1494334951.224803</v>
       </c>
       <c r="M54">
-        <v>4849155924.926964</v>
+        <v>62554111431.55784</v>
       </c>
       <c r="N54">
-        <v>1779668675.266534</v>
+        <v>22957725910.93829</v>
       </c>
       <c r="O54">
-        <v>11510796129.0289</v>
+        <v>148489270064.4729</v>
       </c>
       <c r="P54">
-        <v>16037528075.59668</v>
+        <v>206884112175.1972</v>
       </c>
       <c r="Q54">
-        <v>12933941337.41358</v>
+        <v>166847843252.6352</v>
       </c>
     </row>
     <row r="55">
@@ -9336,52 +9336,52 @@
         </is>
       </c>
       <c r="B55">
-        <v>1198483921.714005</v>
+        <v>15460442590.11066</v>
       </c>
       <c r="C55">
-        <v>99179010.27211374</v>
+        <v>1279409232.510267</v>
       </c>
       <c r="D55">
-        <v>1933251037.566127</v>
+        <v>24938938384.60303</v>
       </c>
       <c r="E55">
-        <v>126626859.4570776</v>
+        <v>1633486486.996301</v>
       </c>
       <c r="F55">
-        <v>1182162888.634637</v>
+        <v>15249901263.38682</v>
       </c>
       <c r="G55">
-        <v>3341219795.929955</v>
+        <v>43101735367.49643</v>
       </c>
       <c r="H55">
-        <v>3247399505.883498</v>
+        <v>41891453625.89713</v>
       </c>
       <c r="I55">
-        <v>1014411074.82842</v>
+        <v>13085902865.28662</v>
       </c>
       <c r="J55">
-        <v>294962490.1410497</v>
+        <v>3805016122.819541</v>
       </c>
       <c r="K55">
-        <v>252851868.7440712</v>
+        <v>3261789106.798519</v>
       </c>
       <c r="L55">
-        <v>116836729.9238158</v>
+        <v>1507193816.017224</v>
       </c>
       <c r="M55">
-        <v>4879182788.976574</v>
+        <v>62941457977.79781</v>
       </c>
       <c r="N55">
-        <v>1790222360.03023</v>
+        <v>23093868444.38997</v>
       </c>
       <c r="O55">
-        <v>11595866818.52766</v>
+        <v>149586681959.0068</v>
       </c>
       <c r="P55">
-        <v>16135570536.17162</v>
+        <v>208148859916.6139</v>
       </c>
       <c r="Q55">
-        <v>13030027524.50357</v>
+        <v>168087355066.0961</v>
       </c>
     </row>
     <row r="56">
@@ -9391,52 +9391,52 @@
         </is>
       </c>
       <c r="B56">
-        <v>1199419276.398112</v>
+        <v>15472508665.53564</v>
       </c>
       <c r="C56">
-        <v>100590165.0781309</v>
+        <v>1297613129.507889</v>
       </c>
       <c r="D56">
-        <v>1940417752.605939</v>
+        <v>25031389008.61662</v>
       </c>
       <c r="E56">
-        <v>125717192.0508241</v>
+        <v>1621751777.455631</v>
       </c>
       <c r="F56">
-        <v>1191126568.165895</v>
+        <v>15365532729.34004</v>
       </c>
       <c r="G56">
-        <v>3357851677.900789</v>
+        <v>43316286644.92017</v>
       </c>
       <c r="H56">
-        <v>3247667513.873904</v>
+        <v>41894910928.97337</v>
       </c>
       <c r="I56">
-        <v>1029301753.51907</v>
+        <v>13277992620.39601</v>
       </c>
       <c r="J56">
-        <v>292239841.6284574</v>
+        <v>3769893957.0071</v>
       </c>
       <c r="K56">
-        <v>255147740.4474773</v>
+        <v>3291405851.772457</v>
       </c>
       <c r="L56">
-        <v>120616934.5871307</v>
+        <v>1555958456.173986</v>
       </c>
       <c r="M56">
-        <v>4892719431.180414</v>
+        <v>63116080662.22735</v>
       </c>
       <c r="N56">
-        <v>1799411770.216249</v>
+        <v>23212411835.78962</v>
       </c>
       <c r="O56">
-        <v>11637104985.4527</v>
+        <v>150118654312.3399</v>
       </c>
       <c r="P56">
-        <v>16194375939.7516</v>
+        <v>208907449622.7957</v>
       </c>
       <c r="Q56">
-        <v>13074927958.55011</v>
+        <v>168666570665.2965</v>
       </c>
     </row>
   </sheetData>
@@ -9564,52 +9564,52 @@
         </is>
       </c>
       <c r="B5">
-        <v>1495637998.147074</v>
+        <v>19293730176.09726</v>
       </c>
       <c r="C5">
-        <v>92163028.97349598</v>
+        <v>1188903073.758098</v>
       </c>
       <c r="D5">
-        <v>1891091370.575777</v>
+        <v>24395078680.42752</v>
       </c>
       <c r="E5">
-        <v>136679097.8972124</v>
+        <v>1763160362.874041</v>
       </c>
       <c r="F5">
-        <v>1203752964.221705</v>
+        <v>15528413238.46</v>
       </c>
       <c r="G5">
-        <v>3323686461.66819</v>
+        <v>42875555355.51965</v>
       </c>
       <c r="H5">
-        <v>2848528760.633636</v>
+        <v>36746021012.1739</v>
       </c>
       <c r="I5">
-        <v>735735453.7183744</v>
+        <v>9490987352.96703</v>
       </c>
       <c r="J5">
-        <v>196314208.2441752</v>
+        <v>2532453286.34986</v>
       </c>
       <c r="K5">
-        <v>186885016.5152293</v>
+        <v>2410816713.046457</v>
       </c>
       <c r="L5">
-        <v>85489946.32590047</v>
+        <v>1102820307.604116</v>
       </c>
       <c r="M5">
-        <v>3683054002.368647</v>
+        <v>47511396630.55554</v>
       </c>
       <c r="N5">
-        <v>1396938180.821205</v>
+        <v>18020502532.59354</v>
       </c>
       <c r="O5">
-        <v>9132945568.627167</v>
+        <v>117814997835.2905</v>
       </c>
       <c r="P5">
-        <v>13952270028.44243</v>
+        <v>179984283366.9073</v>
       </c>
       <c r="Q5">
-        <v>10974203903.14825</v>
+        <v>141567230350.6124</v>
       </c>
     </row>
     <row r="6">
@@ -9619,52 +9619,52 @@
         </is>
       </c>
       <c r="B6">
-        <v>1474290750.529244</v>
+        <v>19018350681.82726</v>
       </c>
       <c r="C6">
-        <v>92601960.60361826</v>
+        <v>1194565291.786676</v>
       </c>
       <c r="D6">
-        <v>1883392964.711319</v>
+        <v>24295769244.77601</v>
       </c>
       <c r="E6">
-        <v>133161855.5362393</v>
+        <v>1717787936.417487</v>
       </c>
       <c r="F6">
-        <v>1220095825.789829</v>
+        <v>15739236152.6888</v>
       </c>
       <c r="G6">
-        <v>3329252606.641006</v>
+        <v>42947358625.66898</v>
       </c>
       <c r="H6">
-        <v>2849013014.098999</v>
+        <v>36752267881.87709</v>
       </c>
       <c r="I6">
-        <v>739792701.8624411</v>
+        <v>9543325854.02549</v>
       </c>
       <c r="J6">
-        <v>198690356.8239832</v>
+        <v>2563105603.029383</v>
       </c>
       <c r="K6">
-        <v>189084567.159738</v>
+        <v>2439190916.36062</v>
       </c>
       <c r="L6">
-        <v>87776423.9812423</v>
+        <v>1132315869.358026</v>
       </c>
       <c r="M6">
-        <v>3675725122.707302</v>
+        <v>47416854082.92419</v>
       </c>
       <c r="N6">
-        <v>1392552700.997606</v>
+        <v>17963929842.86912</v>
       </c>
       <c r="O6">
-        <v>9132634887.631311</v>
+        <v>117810990050.4439</v>
       </c>
       <c r="P6">
-        <v>13936178244.80156</v>
+        <v>179776699357.9402</v>
       </c>
       <c r="Q6">
-        <v>10981558369.29347</v>
+        <v>141662102963.8857</v>
       </c>
     </row>
     <row r="7">
@@ -9674,52 +9674,52 @@
         </is>
       </c>
       <c r="B7">
-        <v>1466322076.842185</v>
+        <v>18915554791.26418</v>
       </c>
       <c r="C7">
-        <v>92796858.35740989</v>
+        <v>1197079472.810588</v>
       </c>
       <c r="D7">
-        <v>1877354462.314765</v>
+        <v>24217872563.86047</v>
       </c>
       <c r="E7">
-        <v>135488538.2340986</v>
+        <v>1747802143.219872</v>
       </c>
       <c r="F7">
-        <v>1238257373.355951</v>
+        <v>15973520116.29176</v>
       </c>
       <c r="G7">
-        <v>3343897232.262224</v>
+        <v>43136274296.18269</v>
       </c>
       <c r="H7">
-        <v>2864877821.150534</v>
+        <v>36956923892.84189</v>
       </c>
       <c r="I7">
-        <v>748532554.5061331</v>
+        <v>9656069953.129116</v>
       </c>
       <c r="J7">
-        <v>199184361.6314949</v>
+        <v>2569478265.046285</v>
       </c>
       <c r="K7">
-        <v>192376744.6297528</v>
+        <v>2481660005.723811</v>
       </c>
       <c r="L7">
-        <v>89196148.19932109</v>
+        <v>1150630311.771242</v>
       </c>
       <c r="M7">
-        <v>3691246485.161293</v>
+        <v>47617079658.58068</v>
       </c>
       <c r="N7">
-        <v>1397815077.21232</v>
+        <v>18031814496.03893</v>
       </c>
       <c r="O7">
-        <v>9183229192.490849</v>
+        <v>118463656583.1319</v>
       </c>
       <c r="P7">
-        <v>13993448501.59526</v>
+        <v>180515485670.5788</v>
       </c>
       <c r="Q7">
-        <v>11040115199.34143</v>
+        <v>142417486071.5045</v>
       </c>
     </row>
     <row r="8">
@@ -9729,52 +9729,52 @@
         </is>
       </c>
       <c r="B8">
-        <v>1466667143.216158</v>
+        <v>18920006147.48845</v>
       </c>
       <c r="C8">
-        <v>93338978.86491662</v>
+        <v>1204072827.357424</v>
       </c>
       <c r="D8">
-        <v>1861493131.584463</v>
+        <v>24013261397.43957</v>
       </c>
       <c r="E8">
-        <v>140772363.2015939</v>
+        <v>1815963485.300562</v>
       </c>
       <c r="F8">
-        <v>1258685584.116005</v>
+        <v>16237044035.09646</v>
       </c>
       <c r="G8">
-        <v>3354290057.766978</v>
+        <v>43270341745.19402</v>
       </c>
       <c r="H8">
-        <v>2899384243.726229</v>
+        <v>37402056744.06835</v>
       </c>
       <c r="I8">
-        <v>752920655.7431184</v>
+        <v>9712676459.086227</v>
       </c>
       <c r="J8">
-        <v>198650163.8508998</v>
+        <v>2562587113.676608</v>
       </c>
       <c r="K8">
-        <v>194443059.0490328</v>
+        <v>2508315461.732523</v>
       </c>
       <c r="L8">
-        <v>91726819.45664656</v>
+        <v>1183275970.990741</v>
       </c>
       <c r="M8">
-        <v>3709169617.785881</v>
+        <v>47848288069.43787</v>
       </c>
       <c r="N8">
-        <v>1398925237.801656</v>
+        <v>18046135567.64137</v>
       </c>
       <c r="O8">
-        <v>9245219797.413464</v>
+        <v>119263335386.6337</v>
       </c>
       <c r="P8">
-        <v>14066176998.3966</v>
+        <v>181453683279.3162</v>
       </c>
       <c r="Q8">
-        <v>11108857797.92214</v>
+        <v>143304265593.1956</v>
       </c>
     </row>
     <row r="9">
@@ -9784,52 +9784,52 @@
         </is>
       </c>
       <c r="B9">
-        <v>1474984930.969078</v>
+        <v>19027305609.5011</v>
       </c>
       <c r="C9">
-        <v>92762624.56894244</v>
+        <v>1196637856.939358</v>
       </c>
       <c r="D9">
-        <v>1856467777.415314</v>
+        <v>23948434328.65755</v>
       </c>
       <c r="E9">
-        <v>144601037.8342366</v>
+        <v>1865353388.061652</v>
       </c>
       <c r="F9">
-        <v>1275737895.00227</v>
+        <v>16457018845.52929</v>
       </c>
       <c r="G9">
-        <v>3369569334.820764</v>
+        <v>43467444419.18785</v>
       </c>
       <c r="H9">
-        <v>2929662509.152517</v>
+        <v>37792646368.06747</v>
       </c>
       <c r="I9">
-        <v>750336327.1674545</v>
+        <v>9679338620.460163</v>
       </c>
       <c r="J9">
-        <v>201190107.4422444</v>
+        <v>2595352386.004953</v>
       </c>
       <c r="K9">
-        <v>194582416.702915</v>
+        <v>2510113175.467604</v>
       </c>
       <c r="L9">
-        <v>92040548.65388933</v>
+        <v>1187323077.635172</v>
       </c>
       <c r="M9">
-        <v>3748452421.260798</v>
+        <v>48355036234.26431</v>
       </c>
       <c r="N9">
-        <v>1411064340.391909</v>
+        <v>18202729991.05563</v>
       </c>
       <c r="O9">
-        <v>9327328670.771729</v>
+        <v>120322539852.9553</v>
       </c>
       <c r="P9">
-        <v>14171882936.56157</v>
+        <v>182817289881.6443</v>
       </c>
       <c r="Q9">
-        <v>11193793116.54669</v>
+        <v>144399931203.4523</v>
       </c>
     </row>
     <row r="10">
@@ -9839,52 +9839,52 @@
         </is>
       </c>
       <c r="B10">
-        <v>1465399439.015062</v>
+        <v>18903652763.2943</v>
       </c>
       <c r="C10">
-        <v>91962989.9408523</v>
+        <v>1186322570.236995</v>
       </c>
       <c r="D10">
-        <v>1865595128.46738</v>
+        <v>24066177157.2292</v>
       </c>
       <c r="E10">
-        <v>150228611.4704027</v>
+        <v>1937949087.968194</v>
       </c>
       <c r="F10">
-        <v>1302280054.778915</v>
+        <v>16799412706.648</v>
       </c>
       <c r="G10">
-        <v>3410066784.65755</v>
+        <v>43989861522.0824</v>
       </c>
       <c r="H10">
-        <v>2964469142.993697</v>
+        <v>38241651944.6187</v>
       </c>
       <c r="I10">
-        <v>748152081.6448178</v>
+        <v>9651161853.218151</v>
       </c>
       <c r="J10">
-        <v>203736923.7692729</v>
+        <v>2628206316.62362</v>
       </c>
       <c r="K10">
-        <v>196377851.5017849</v>
+        <v>2533274284.373025</v>
       </c>
       <c r="L10">
-        <v>91338232.2274047</v>
+        <v>1178263195.733521</v>
       </c>
       <c r="M10">
-        <v>3799146769.619025</v>
+        <v>49008993328.08543</v>
       </c>
       <c r="N10">
-        <v>1428426034.507185</v>
+        <v>18426695845.14268</v>
       </c>
       <c r="O10">
-        <v>9431647036.263187</v>
+        <v>121668246767.7951</v>
       </c>
       <c r="P10">
-        <v>14307113259.9358</v>
+        <v>184561761053.1718</v>
       </c>
       <c r="Q10">
-        <v>11321949554.18615</v>
+        <v>146053149249.0013</v>
       </c>
     </row>
     <row r="11">
@@ -9894,52 +9894,52 @@
         </is>
       </c>
       <c r="B11">
-        <v>1444047140.619648</v>
+        <v>18628208113.99347</v>
       </c>
       <c r="C11">
-        <v>90808878.93615817</v>
+        <v>1171434538.27644</v>
       </c>
       <c r="D11">
-        <v>1865901909.442534</v>
+        <v>24070134631.80869</v>
       </c>
       <c r="E11">
-        <v>150799412.8611166</v>
+        <v>1945312425.908404</v>
       </c>
       <c r="F11">
-        <v>1302722179.325314</v>
+        <v>16805116113.29655</v>
       </c>
       <c r="G11">
-        <v>3410232380.565123</v>
+        <v>43991997709.29008</v>
       </c>
       <c r="H11">
-        <v>2972240679.269812</v>
+        <v>38341904762.58057</v>
       </c>
       <c r="I11">
-        <v>742352951.5553073</v>
+        <v>9576353075.063463</v>
       </c>
       <c r="J11">
-        <v>205351037.9943643</v>
+        <v>2649028390.127299</v>
       </c>
       <c r="K11">
-        <v>194414541.5308493</v>
+        <v>2507947585.747956</v>
       </c>
       <c r="L11">
-        <v>88942876.11395945</v>
+        <v>1147363101.870077</v>
       </c>
       <c r="M11">
-        <v>3843833483.198715</v>
+        <v>49585451933.26342</v>
       </c>
       <c r="N11">
-        <v>1427739051.296265</v>
+        <v>18417833761.72181</v>
       </c>
       <c r="O11">
-        <v>9474874620.959272</v>
+        <v>122225882610.3746</v>
       </c>
       <c r="P11">
-        <v>14329154142.14404</v>
+        <v>184846088433.6582</v>
       </c>
       <c r="Q11">
-        <v>11368425074.11417</v>
+        <v>146652683456.0728</v>
       </c>
     </row>
     <row r="12">
@@ -9949,52 +9949,52 @@
         </is>
       </c>
       <c r="B12">
-        <v>1408230894.461137</v>
+        <v>18166178538.54866</v>
       </c>
       <c r="C12">
-        <v>88312100.56512451</v>
+        <v>1139226097.290106</v>
       </c>
       <c r="D12">
-        <v>1885179758.034803</v>
+        <v>24318818878.64896</v>
       </c>
       <c r="E12">
-        <v>149954833.6273111</v>
+        <v>1934417353.792313</v>
       </c>
       <c r="F12">
-        <v>1279650717.048213</v>
+        <v>16507494249.92196</v>
       </c>
       <c r="G12">
-        <v>3403097409.275453</v>
+        <v>43899956579.65334</v>
       </c>
       <c r="H12">
-        <v>2958847363.919579</v>
+        <v>38169130994.56256</v>
       </c>
       <c r="I12">
-        <v>733674558.821396</v>
+        <v>9464401808.796009</v>
       </c>
       <c r="J12">
-        <v>206028023.1933677</v>
+        <v>2657761499.194443</v>
       </c>
       <c r="K12">
-        <v>195865010.0635691</v>
+        <v>2526658629.820042</v>
       </c>
       <c r="L12">
-        <v>86356757.2690565</v>
+        <v>1114002168.770829</v>
       </c>
       <c r="M12">
-        <v>3882900547.256183</v>
+        <v>50089417059.60476</v>
       </c>
       <c r="N12">
-        <v>1431561490.050452</v>
+        <v>18467143221.65083</v>
       </c>
       <c r="O12">
-        <v>9495233750.573601</v>
+        <v>122488515382.3995</v>
       </c>
       <c r="P12">
-        <v>14306562054.31019</v>
+        <v>184554650500.6015</v>
       </c>
       <c r="Q12">
-        <v>11380412912.52954</v>
+        <v>146807326571.6311</v>
       </c>
     </row>
     <row r="13">
@@ -10004,52 +10004,52 @@
         </is>
       </c>
       <c r="B13">
-        <v>1365299264.331352</v>
+        <v>17612360509.87444</v>
       </c>
       <c r="C13">
-        <v>86826477.30774236</v>
+        <v>1120061557.269876</v>
       </c>
       <c r="D13">
-        <v>1901801782.481241</v>
+        <v>24533242994.00801</v>
       </c>
       <c r="E13">
-        <v>149605212.8245873</v>
+        <v>1929907245.437176</v>
       </c>
       <c r="F13">
-        <v>1257601574.572516</v>
+        <v>16223060311.98546</v>
       </c>
       <c r="G13">
-        <v>3395835047.186087</v>
+        <v>43806272108.70052</v>
       </c>
       <c r="H13">
-        <v>2945275001.961221</v>
+        <v>37994047525.29975</v>
       </c>
       <c r="I13">
-        <v>732439799.1174526</v>
+        <v>9448473408.615139</v>
       </c>
       <c r="J13">
-        <v>205374874.764697</v>
+        <v>2649335884.464592</v>
       </c>
       <c r="K13">
-        <v>196349416.5405046</v>
+        <v>2532907473.372509</v>
       </c>
       <c r="L13">
-        <v>88642964.85736316</v>
+        <v>1143494246.659985</v>
       </c>
       <c r="M13">
-        <v>3910223726.057924</v>
+        <v>50441886066.14722</v>
       </c>
       <c r="N13">
-        <v>1432548481.350149</v>
+        <v>18479875409.41692</v>
       </c>
       <c r="O13">
-        <v>9510854264.649311</v>
+        <v>122690020013.9761</v>
       </c>
       <c r="P13">
-        <v>14271988576.16675</v>
+        <v>184108652632.5511</v>
       </c>
       <c r="Q13">
-        <v>11385497865.62788</v>
+        <v>146872922466.5997</v>
       </c>
     </row>
     <row r="14">
@@ -10059,52 +10059,52 @@
         </is>
       </c>
       <c r="B14">
-        <v>1356512354.590195</v>
+        <v>17499009374.21352</v>
       </c>
       <c r="C14">
-        <v>84879217.58251056</v>
+        <v>1094941906.814386</v>
       </c>
       <c r="D14">
-        <v>1914352094.697034</v>
+        <v>24695142021.59174</v>
       </c>
       <c r="E14">
-        <v>147915230.9381479</v>
+        <v>1908106479.102108</v>
       </c>
       <c r="F14">
-        <v>1234256998.219609</v>
+        <v>15921915277.03296</v>
       </c>
       <c r="G14">
-        <v>3381403541.437302</v>
+        <v>43620105684.54119</v>
       </c>
       <c r="H14">
-        <v>2935583048.147716</v>
+        <v>37869021321.10554</v>
       </c>
       <c r="I14">
-        <v>736879694.3836527</v>
+        <v>9505748057.54912</v>
       </c>
       <c r="J14">
-        <v>204239895.5780929</v>
+        <v>2634694652.957398</v>
       </c>
       <c r="K14">
-        <v>195174646.486792</v>
+        <v>2517752939.679616</v>
       </c>
       <c r="L14">
-        <v>90235568.61660671</v>
+        <v>1164038835.154227</v>
       </c>
       <c r="M14">
-        <v>3924331100.340911</v>
+        <v>50623871194.39776</v>
       </c>
       <c r="N14">
-        <v>1428102190.805165</v>
+        <v>18422518261.38663</v>
       </c>
       <c r="O14">
-        <v>9514546144.358936</v>
+        <v>122737645262.2303</v>
       </c>
       <c r="P14">
-        <v>14252462040.38643</v>
+        <v>183856760320.985</v>
       </c>
       <c r="Q14">
-        <v>11377611926.37447</v>
+        <v>146771193850.2306</v>
       </c>
     </row>
     <row r="15">
@@ -10114,52 +10114,52 @@
         </is>
       </c>
       <c r="B15">
-        <v>1342971024.766054</v>
+        <v>17324326219.4821</v>
       </c>
       <c r="C15">
-        <v>83020006.18174389</v>
+        <v>1070958079.744496</v>
       </c>
       <c r="D15">
-        <v>1909038396.551764</v>
+        <v>24626595315.51776</v>
       </c>
       <c r="E15">
-        <v>146291433.9356744</v>
+        <v>1887159497.7702</v>
       </c>
       <c r="F15">
-        <v>1200492019.358713</v>
+        <v>15486347049.7274</v>
       </c>
       <c r="G15">
-        <v>3338841856.027896</v>
+        <v>43071059942.75986</v>
       </c>
       <c r="H15">
-        <v>2937584269.568412</v>
+        <v>37894837077.43251</v>
       </c>
       <c r="I15">
-        <v>736718402.1177238</v>
+        <v>9503667387.318638</v>
       </c>
       <c r="J15">
-        <v>203269152.6921256</v>
+        <v>2622172069.728421</v>
       </c>
       <c r="K15">
-        <v>193940877.4596878</v>
+        <v>2501837319.229973</v>
       </c>
       <c r="L15">
-        <v>92703960.81690858</v>
+        <v>1195881094.538121</v>
       </c>
       <c r="M15">
-        <v>3937457362.465269</v>
+        <v>50793199975.80197</v>
       </c>
       <c r="N15">
-        <v>1429275665.546381</v>
+        <v>18437656085.54832</v>
       </c>
       <c r="O15">
-        <v>9530949690.666508</v>
+        <v>122949251009.5979</v>
       </c>
       <c r="P15">
-        <v>14212762571.46046</v>
+        <v>183344637171.8399</v>
       </c>
       <c r="Q15">
-        <v>11347811920.33111</v>
+        <v>146386773772.2714</v>
       </c>
     </row>
     <row r="16">
@@ -10169,52 +10169,52 @@
         </is>
       </c>
       <c r="B16">
-        <v>1331981148.049339</v>
+        <v>17182556809.83647</v>
       </c>
       <c r="C16">
-        <v>82664309.5082147</v>
+        <v>1066369592.65597</v>
       </c>
       <c r="D16">
-        <v>1881688066.503857</v>
+        <v>24273776057.89976</v>
       </c>
       <c r="E16">
-        <v>143270764.7323319</v>
+        <v>1848192865.047082</v>
       </c>
       <c r="F16">
-        <v>1180507329.432479</v>
+        <v>15228544549.67898</v>
       </c>
       <c r="G16">
-        <v>3288130470.176883</v>
+        <v>42416883065.28179</v>
       </c>
       <c r="H16">
-        <v>2944142284.323642</v>
+        <v>37979435467.77498</v>
       </c>
       <c r="I16">
-        <v>737579891.5388223</v>
+        <v>9514780600.850807</v>
       </c>
       <c r="J16">
-        <v>204361744.5606788</v>
+        <v>2636266504.832756</v>
       </c>
       <c r="K16">
-        <v>188352328.7531176</v>
+        <v>2429745040.915216</v>
       </c>
       <c r="L16">
-        <v>94375003.60993418</v>
+        <v>1217437546.568151</v>
       </c>
       <c r="M16">
-        <v>3932681152.771826</v>
+        <v>50731586870.75655</v>
       </c>
       <c r="N16">
-        <v>1426498734.671415</v>
+        <v>18401833677.26126</v>
       </c>
       <c r="O16">
-        <v>9527991140.229435</v>
+        <v>122911085708.9597</v>
       </c>
       <c r="P16">
-        <v>14148102758.45566</v>
+        <v>182510525584.078</v>
       </c>
       <c r="Q16">
-        <v>11295247872.12497</v>
+        <v>145708697550.4121</v>
       </c>
     </row>
     <row r="17">
@@ -10224,52 +10224,52 @@
         </is>
       </c>
       <c r="B17">
-        <v>1336155758.779061</v>
+        <v>17236409288.24988</v>
       </c>
       <c r="C17">
-        <v>79877486.92269941</v>
+        <v>1030419581.302822</v>
       </c>
       <c r="D17">
-        <v>1844376310.639971</v>
+        <v>23792454407.25563</v>
       </c>
       <c r="E17">
-        <v>137909778.1214173</v>
+        <v>1779036137.766284</v>
       </c>
       <c r="F17">
-        <v>1185433999.581995</v>
+        <v>15292098594.60774</v>
       </c>
       <c r="G17">
-        <v>3247597575.266084</v>
+        <v>41894008720.93248</v>
       </c>
       <c r="H17">
-        <v>2934352937.073934</v>
+        <v>37853152888.25375</v>
       </c>
       <c r="I17">
-        <v>741610734.2717321</v>
+        <v>9566778472.105345</v>
       </c>
       <c r="J17">
-        <v>200938222.3552575</v>
+        <v>2592103068.382822</v>
       </c>
       <c r="K17">
-        <v>182740637.9044194</v>
+        <v>2357354228.96701</v>
       </c>
       <c r="L17">
-        <v>91789821.34098718</v>
+        <v>1184088695.298735</v>
       </c>
       <c r="M17">
-        <v>3933656340.283605</v>
+        <v>50744166789.65851</v>
       </c>
       <c r="N17">
-        <v>1433311238.073053</v>
+        <v>18489714971.14239</v>
       </c>
       <c r="O17">
-        <v>9518399931.302988</v>
+        <v>122787359113.8085</v>
       </c>
       <c r="P17">
-        <v>14102153265.34813</v>
+        <v>181917777122.9909</v>
       </c>
       <c r="Q17">
-        <v>11240896447.15503</v>
+        <v>145007564168.2999</v>
       </c>
     </row>
     <row r="18">
@@ -10279,52 +10279,52 @@
         </is>
       </c>
       <c r="B18">
-        <v>1337829943.029869</v>
+        <v>17258006265.08532</v>
       </c>
       <c r="C18">
-        <v>77386885.49990873</v>
+        <v>998290822.9488226</v>
       </c>
       <c r="D18">
-        <v>1785722231.306827</v>
+        <v>23035816783.85807</v>
       </c>
       <c r="E18">
-        <v>131330630.4252133</v>
+        <v>1694165132.485251</v>
       </c>
       <c r="F18">
-        <v>1178436856.683515</v>
+        <v>15201835451.21734</v>
       </c>
       <c r="G18">
-        <v>3172876603.915463</v>
+        <v>40930108190.50948</v>
       </c>
       <c r="H18">
-        <v>2914396899.451916</v>
+        <v>37595720002.92972</v>
       </c>
       <c r="I18">
-        <v>741460820.4426905</v>
+        <v>9564844583.710707</v>
       </c>
       <c r="J18">
-        <v>198013349.5902862</v>
+        <v>2554372209.714692</v>
       </c>
       <c r="K18">
-        <v>181396969.0934329</v>
+        <v>2340020901.305285</v>
       </c>
       <c r="L18">
-        <v>90883112.25431143</v>
+        <v>1172392148.080617</v>
       </c>
       <c r="M18">
-        <v>3937620542.853914</v>
+        <v>50795305002.8155</v>
       </c>
       <c r="N18">
-        <v>1438357756.700408</v>
+        <v>18554815061.43526</v>
       </c>
       <c r="O18">
-        <v>9502129450.386959</v>
+        <v>122577469909.9918</v>
       </c>
       <c r="P18">
-        <v>14012835997.33229</v>
+        <v>180765584365.5865</v>
       </c>
       <c r="Q18">
-        <v>11145765185.3477</v>
+        <v>143780370890.9854</v>
       </c>
     </row>
     <row r="19">
@@ -10334,52 +10334,52 @@
         </is>
       </c>
       <c r="B19">
-        <v>1340512684.99416</v>
+        <v>17292613636.42466</v>
       </c>
       <c r="C19">
-        <v>74330009.26809885</v>
+        <v>958857119.5584751</v>
       </c>
       <c r="D19">
-        <v>1737669957.729841</v>
+        <v>22415942454.71494</v>
       </c>
       <c r="E19">
-        <v>125792887.3232317</v>
+        <v>1622728246.469688</v>
       </c>
       <c r="F19">
-        <v>1189676046.113485</v>
+        <v>15346820994.86396</v>
       </c>
       <c r="G19">
-        <v>3127468900.434656</v>
+        <v>40344348815.60706</v>
       </c>
       <c r="H19">
-        <v>2892231382.095919</v>
+        <v>37309784829.03735</v>
       </c>
       <c r="I19">
-        <v>745322911.6420907</v>
+        <v>9614665560.18297</v>
       </c>
       <c r="J19">
-        <v>195577862.4310406</v>
+        <v>2522954425.360423</v>
       </c>
       <c r="K19">
-        <v>178431301.5195971</v>
+        <v>2301763789.602802</v>
       </c>
       <c r="L19">
-        <v>88374468.08580814</v>
+        <v>1140030638.306925</v>
       </c>
       <c r="M19">
-        <v>3932403185.12449</v>
+        <v>50728001088.10592</v>
       </c>
       <c r="N19">
-        <v>1444871847.101674</v>
+        <v>18638846827.61159</v>
       </c>
       <c r="O19">
-        <v>9477212958.000618</v>
+        <v>122256047158.208</v>
       </c>
       <c r="P19">
-        <v>13945194543.42943</v>
+        <v>179893009610.2397</v>
       </c>
       <c r="Q19">
-        <v>11071435543.24779</v>
+        <v>142821518507.8965</v>
       </c>
     </row>
     <row r="20">
@@ -10389,52 +10389,52 @@
         </is>
       </c>
       <c r="B20">
-        <v>1338789934.918791</v>
+        <v>17270390160.45241</v>
       </c>
       <c r="C20">
-        <v>70819421.51367153</v>
+        <v>913570537.5263628</v>
       </c>
       <c r="D20">
-        <v>1692287949.884021</v>
+        <v>21830514553.50387</v>
       </c>
       <c r="E20">
-        <v>123012263.9808352</v>
+        <v>1586858205.352774</v>
       </c>
       <c r="F20">
-        <v>1182591632.522968</v>
+        <v>15255432059.54628</v>
       </c>
       <c r="G20">
-        <v>3068711267.901495</v>
+        <v>39586375355.92929</v>
       </c>
       <c r="H20">
-        <v>2856620234.214585</v>
+        <v>36850401021.36815</v>
       </c>
       <c r="I20">
-        <v>751705833.6938369</v>
+        <v>9697005254.650497</v>
       </c>
       <c r="J20">
-        <v>191290589.9761067</v>
+        <v>2467648610.691777</v>
       </c>
       <c r="K20">
-        <v>180060487.6633757</v>
+        <v>2322780290.857547</v>
       </c>
       <c r="L20">
-        <v>86297222.72086079</v>
+        <v>1113234173.099104</v>
       </c>
       <c r="M20">
-        <v>3929288490.125025</v>
+        <v>50687821522.61282</v>
       </c>
       <c r="N20">
-        <v>1452972049.19847</v>
+        <v>18743339434.66027</v>
       </c>
       <c r="O20">
-        <v>9448234907.592258</v>
+        <v>121882230307.9401</v>
       </c>
       <c r="P20">
-        <v>13855736110.41255</v>
+        <v>178738995824.3219</v>
       </c>
       <c r="Q20">
-        <v>10977676903.57442</v>
+        <v>141612032056.1101</v>
       </c>
     </row>
     <row r="21">
@@ -10444,52 +10444,52 @@
         </is>
       </c>
       <c r="B21">
-        <v>1325309912.363556</v>
+        <v>17096497869.48987</v>
       </c>
       <c r="C21">
-        <v>69961847.60443228</v>
+        <v>902507834.0971766</v>
       </c>
       <c r="D21">
-        <v>1649545130.807225</v>
+        <v>21279132187.4132</v>
       </c>
       <c r="E21">
-        <v>125237516.4394933</v>
+        <v>1615563962.069464</v>
       </c>
       <c r="F21">
-        <v>1143980446.619148</v>
+        <v>14757347761.387</v>
       </c>
       <c r="G21">
-        <v>2988724941.470298</v>
+        <v>38554551744.96685</v>
       </c>
       <c r="H21">
-        <v>2844567623.696587</v>
+        <v>36694922345.68597</v>
       </c>
       <c r="I21">
-        <v>753001986.7927686</v>
+        <v>9713725629.626715</v>
       </c>
       <c r="J21">
-        <v>192405167.6326413</v>
+        <v>2482026662.461072</v>
       </c>
       <c r="K21">
-        <v>183230287.4788993</v>
+        <v>2363670708.477801</v>
       </c>
       <c r="L21">
-        <v>86939487.472278</v>
+        <v>1121519388.392386</v>
       </c>
       <c r="M21">
-        <v>3925163926.492376</v>
+        <v>50634614651.75165</v>
       </c>
       <c r="N21">
-        <v>1446794261.630057</v>
+        <v>18663645975.02773</v>
       </c>
       <c r="O21">
-        <v>9432102741.195606</v>
+        <v>121674125361.4233</v>
       </c>
       <c r="P21">
-        <v>13746137595.02946</v>
+        <v>177325174975.8801</v>
       </c>
       <c r="Q21">
-        <v>10887093933.56357</v>
+        <v>140443511742.9701</v>
       </c>
     </row>
     <row r="22">
@@ -10499,52 +10499,52 @@
         </is>
       </c>
       <c r="B22">
-        <v>1303820995.183814</v>
+        <v>16819290837.8712</v>
       </c>
       <c r="C22">
-        <v>69038527.3526988</v>
+        <v>890597002.8498145</v>
       </c>
       <c r="D22">
-        <v>1630643164.503507</v>
+        <v>21035296822.09524</v>
       </c>
       <c r="E22">
-        <v>126798910.0618537</v>
+        <v>1635705939.797912</v>
       </c>
       <c r="F22">
-        <v>1112424213.963407</v>
+        <v>14350272360.12795</v>
       </c>
       <c r="G22">
-        <v>2938904815.881467</v>
+        <v>37911872124.87093</v>
       </c>
       <c r="H22">
-        <v>2829468907.7293</v>
+        <v>36500148909.70796</v>
       </c>
       <c r="I22">
-        <v>752877950.9251548</v>
+        <v>9712125566.934498</v>
       </c>
       <c r="J22">
-        <v>193431611.7981119</v>
+        <v>2495267792.195643</v>
       </c>
       <c r="K22">
-        <v>184326652.25832</v>
+        <v>2377813814.132328</v>
       </c>
       <c r="L22">
-        <v>88327377.09852475</v>
+        <v>1139423164.570969</v>
       </c>
       <c r="M22">
-        <v>3929551914.133689</v>
+        <v>50691219692.32458</v>
       </c>
       <c r="N22">
-        <v>1442268865.844993</v>
+        <v>18605268369.40041</v>
       </c>
       <c r="O22">
-        <v>9420253279.788094</v>
+        <v>121521267309.2664</v>
       </c>
       <c r="P22">
-        <v>13662979090.85337</v>
+        <v>176252430272.0085</v>
       </c>
       <c r="Q22">
-        <v>10828561852.72604</v>
+        <v>139688447900.166</v>
       </c>
     </row>
     <row r="23">
@@ -10554,52 +10554,52 @@
         </is>
       </c>
       <c r="B23">
-        <v>1278320963.108912</v>
+        <v>16490340424.10497</v>
       </c>
       <c r="C23">
-        <v>66555879.52718192</v>
+        <v>858570845.9006467</v>
       </c>
       <c r="D23">
-        <v>1624581339.587837</v>
+        <v>20957099280.68309</v>
       </c>
       <c r="E23">
-        <v>130784593.0450897</v>
+        <v>1687121250.281658</v>
       </c>
       <c r="F23">
-        <v>1077681881.7611</v>
+        <v>13902096274.71819</v>
       </c>
       <c r="G23">
-        <v>2899603693.921208</v>
+        <v>37404887651.58358</v>
       </c>
       <c r="H23">
-        <v>2816355847.895463</v>
+        <v>36330990437.85148</v>
       </c>
       <c r="I23">
-        <v>754830332.5321584</v>
+        <v>9737311289.664843</v>
       </c>
       <c r="J23">
-        <v>192916105.4837197</v>
+        <v>2488617760.739985</v>
       </c>
       <c r="K23">
-        <v>184085727.0715399</v>
+        <v>2374705879.222865</v>
       </c>
       <c r="L23">
-        <v>88875899.82414909</v>
+        <v>1146499107.731523</v>
       </c>
       <c r="M23">
-        <v>3940789556.413908</v>
+        <v>50836185277.73942</v>
       </c>
       <c r="N23">
-        <v>1435248512.948997</v>
+        <v>18514705817.04206</v>
       </c>
       <c r="O23">
-        <v>9413101982.169937</v>
+        <v>121429015569.9922</v>
       </c>
       <c r="P23">
-        <v>13591026639.20005</v>
+        <v>175324243645.6807</v>
       </c>
       <c r="Q23">
-        <v>10788581263.318</v>
+        <v>139172698296.8022</v>
       </c>
     </row>
     <row r="24">
@@ -10609,52 +10609,52 @@
         </is>
       </c>
       <c r="B24">
-        <v>1264773593.706193</v>
+        <v>16315579358.8099</v>
       </c>
       <c r="C24">
-        <v>65924819.55038463</v>
+        <v>850430172.1999617</v>
       </c>
       <c r="D24">
-        <v>1625682449.191576</v>
+        <v>20971303594.57132</v>
       </c>
       <c r="E24">
-        <v>132441375.3650883</v>
+        <v>1708493742.209639</v>
       </c>
       <c r="F24">
-        <v>1063741561.471477</v>
+        <v>13722266142.98206</v>
       </c>
       <c r="G24">
-        <v>2887790205.578526</v>
+        <v>37252493651.96298</v>
       </c>
       <c r="H24">
-        <v>2821614879.134626</v>
+        <v>36398831940.83669</v>
       </c>
       <c r="I24">
-        <v>757597217.0614958</v>
+        <v>9773004100.093296</v>
       </c>
       <c r="J24">
-        <v>195008789.4267744</v>
+        <v>2515613383.605391</v>
       </c>
       <c r="K24">
-        <v>184798388.8112605</v>
+        <v>2383899215.66526</v>
       </c>
       <c r="L24">
-        <v>89787117.64061576</v>
+        <v>1158253817.563943</v>
       </c>
       <c r="M24">
-        <v>3967850136.633342</v>
+        <v>51185266762.57011</v>
       </c>
       <c r="N24">
-        <v>1430299170.952637</v>
+        <v>18450859305.28901</v>
       </c>
       <c r="O24">
-        <v>9446955699.660751</v>
+        <v>121865728525.6237</v>
       </c>
       <c r="P24">
-        <v>13599519498.94547</v>
+        <v>175433801536.3965</v>
       </c>
       <c r="Q24">
-        <v>10814659616.64602</v>
+        <v>139509109054.7337</v>
       </c>
     </row>
     <row r="25">
@@ -10664,52 +10664,52 @@
         </is>
       </c>
       <c r="B25">
-        <v>1248933860.118147</v>
+        <v>16111246795.5241</v>
       </c>
       <c r="C25">
-        <v>65725252.69902714</v>
+        <v>847855759.81745</v>
       </c>
       <c r="D25">
-        <v>1633300292.717775</v>
+        <v>21069573776.0593</v>
       </c>
       <c r="E25">
-        <v>131791964.7676157</v>
+        <v>1700116345.502242</v>
       </c>
       <c r="F25">
-        <v>1051317409.445656</v>
+        <v>13561994581.84897</v>
       </c>
       <c r="G25">
-        <v>2882134919.630075</v>
+        <v>37179540463.22796</v>
       </c>
       <c r="H25">
-        <v>2821602459.669874</v>
+        <v>36398671729.74137</v>
       </c>
       <c r="I25">
-        <v>752916615.7314458</v>
+        <v>9712624342.935652</v>
       </c>
       <c r="J25">
-        <v>193480118.7321385</v>
+        <v>2495893531.644586</v>
       </c>
       <c r="K25">
-        <v>184045404.2851279</v>
+        <v>2374185715.27815</v>
       </c>
       <c r="L25">
-        <v>87402743.61810754</v>
+        <v>1127495392.673587</v>
       </c>
       <c r="M25">
-        <v>4000845047.565886</v>
+        <v>51610901113.59994</v>
       </c>
       <c r="N25">
-        <v>1427674453.973468</v>
+        <v>18417000456.25773</v>
       </c>
       <c r="O25">
-        <v>9467966843.576048</v>
+        <v>122136772282.131</v>
       </c>
       <c r="P25">
-        <v>13599035623.32427</v>
+        <v>175427559540.8831</v>
       </c>
       <c r="Q25">
-        <v>10835024565.61454</v>
+        <v>139771816896.4276</v>
       </c>
     </row>
     <row r="26">
@@ -10719,52 +10719,52 @@
         </is>
       </c>
       <c r="B26">
-        <v>1238119150.578154</v>
+        <v>15971737042.45819</v>
       </c>
       <c r="C26">
-        <v>65160179.76590676</v>
+        <v>840566318.9801972</v>
       </c>
       <c r="D26">
-        <v>1632448015.320254</v>
+        <v>21058579397.63128</v>
       </c>
       <c r="E26">
-        <v>132275382.6427242</v>
+        <v>1706352436.091143</v>
       </c>
       <c r="F26">
-        <v>1034432810.749274</v>
+        <v>13344183258.66564</v>
       </c>
       <c r="G26">
-        <v>2864316388.478159</v>
+        <v>36949681411.36826</v>
       </c>
       <c r="H26">
-        <v>2823409813.372967</v>
+        <v>36421986592.51128</v>
       </c>
       <c r="I26">
-        <v>755548800.6516817</v>
+        <v>9746579528.406694</v>
       </c>
       <c r="J26">
-        <v>191471715.8029471</v>
+        <v>2469985133.858018</v>
       </c>
       <c r="K26">
-        <v>181497370.3139928</v>
+        <v>2341316077.050507</v>
       </c>
       <c r="L26">
-        <v>85056649.19604468</v>
+        <v>1097230774.628976</v>
       </c>
       <c r="M26">
-        <v>4025113773.02175</v>
+        <v>51923967671.98058</v>
       </c>
       <c r="N26">
-        <v>1426243527.152373</v>
+        <v>18398541500.26561</v>
       </c>
       <c r="O26">
-        <v>9488341649.511757</v>
+        <v>122399607278.7017</v>
       </c>
       <c r="P26">
-        <v>13590777188.56807</v>
+        <v>175321025732.5281</v>
       </c>
       <c r="Q26">
-        <v>10841357861.6415</v>
+        <v>139853516415.1753</v>
       </c>
     </row>
     <row r="27">
@@ -10774,52 +10774,52 @@
         </is>
       </c>
       <c r="B27">
-        <v>1237360983.358366</v>
+        <v>15961956685.32292</v>
       </c>
       <c r="C27">
-        <v>66563392.77469927</v>
+        <v>858667766.7936206</v>
       </c>
       <c r="D27">
-        <v>1639127568.171186</v>
+        <v>21144745629.40829</v>
       </c>
       <c r="E27">
-        <v>131684956.6581226</v>
+        <v>1698735940.889782</v>
       </c>
       <c r="F27">
-        <v>1029336952.491269</v>
+        <v>13278446687.13737</v>
       </c>
       <c r="G27">
-        <v>2866712870.095276</v>
+        <v>36980596024.22906</v>
       </c>
       <c r="H27">
-        <v>2828293476.265247</v>
+        <v>36484985843.82169</v>
       </c>
       <c r="I27">
-        <v>758528017.2249842</v>
+        <v>9785011422.202295</v>
       </c>
       <c r="J27">
-        <v>192129742.6147953</v>
+        <v>2478473679.730859</v>
       </c>
       <c r="K27">
-        <v>183559458.9938264</v>
+        <v>2367917021.020361</v>
       </c>
       <c r="L27">
-        <v>85642026.20837308</v>
+        <v>1104782138.088013</v>
       </c>
       <c r="M27">
-        <v>4050998075.220705</v>
+        <v>52257875170.3471</v>
       </c>
       <c r="N27">
-        <v>1435966978.283567</v>
+        <v>18523974019.85802</v>
       </c>
       <c r="O27">
-        <v>9535117774.811497</v>
+        <v>123003019295.0683</v>
       </c>
       <c r="P27">
-        <v>13639191628.26514</v>
+        <v>175945572004.6203</v>
       </c>
       <c r="Q27">
-        <v>10880221640.41483</v>
+        <v>140354859161.3513</v>
       </c>
     </row>
     <row r="28">
@@ -10829,52 +10829,52 @@
         </is>
       </c>
       <c r="B28">
-        <v>1241843443.335081</v>
+        <v>16019780419.02254</v>
       </c>
       <c r="C28">
-        <v>67537218.02108237</v>
+        <v>871230112.4719626</v>
       </c>
       <c r="D28">
-        <v>1642335745.743354</v>
+        <v>21186131120.08927</v>
       </c>
       <c r="E28">
-        <v>129437447.6180896</v>
+        <v>1669743074.273356</v>
       </c>
       <c r="F28">
-        <v>1024176456.338835</v>
+        <v>13211876286.77097</v>
       </c>
       <c r="G28">
-        <v>2863486867.721361</v>
+        <v>36938980593.60556</v>
       </c>
       <c r="H28">
-        <v>2836317390.33861</v>
+        <v>36588494335.36806</v>
       </c>
       <c r="I28">
-        <v>760129158.0084136</v>
+        <v>9805666138.308535</v>
       </c>
       <c r="J28">
-        <v>192388214.2319182</v>
+        <v>2481807963.591745</v>
       </c>
       <c r="K28">
-        <v>183774871.8286814</v>
+        <v>2370695846.589991</v>
       </c>
       <c r="L28">
-        <v>86545685.34468898</v>
+        <v>1116439340.946488</v>
       </c>
       <c r="M28">
-        <v>4077832047.121695</v>
+        <v>52604033407.86987</v>
       </c>
       <c r="N28">
-        <v>1443634307.47707</v>
+        <v>18622882566.45421</v>
       </c>
       <c r="O28">
-        <v>9580621674.351074</v>
+        <v>123590019599.1289</v>
       </c>
       <c r="P28">
-        <v>13685951985.40752</v>
+        <v>176548780611.757</v>
       </c>
       <c r="Q28">
-        <v>10913928549.25068</v>
+        <v>140789678285.3337</v>
       </c>
     </row>
     <row r="29">
@@ -10884,52 +10884,52 @@
         </is>
       </c>
       <c r="B29">
-        <v>1241590403.147282</v>
+        <v>16016516200.59994</v>
       </c>
       <c r="C29">
-        <v>67298661.38000615</v>
+        <v>868152731.8020793</v>
       </c>
       <c r="D29">
-        <v>1640316183.255976</v>
+        <v>21160078764.00209</v>
       </c>
       <c r="E29">
-        <v>129562328.5477784</v>
+        <v>1671354038.266342</v>
       </c>
       <c r="F29">
-        <v>1019391035.246518</v>
+        <v>13150144354.68008</v>
       </c>
       <c r="G29">
-        <v>2856568208.430278</v>
+        <v>36849729888.75059</v>
       </c>
       <c r="H29">
-        <v>2837037397.492076</v>
+        <v>36597782427.64779</v>
       </c>
       <c r="I29">
-        <v>771579633.5894734</v>
+        <v>9953377273.304207</v>
       </c>
       <c r="J29">
-        <v>195101333.0338468</v>
+        <v>2516807196.136624</v>
       </c>
       <c r="K29">
-        <v>183727390.7952356</v>
+        <v>2370083341.25854</v>
       </c>
       <c r="L29">
-        <v>88287732.10036108</v>
+        <v>1138911744.094658</v>
       </c>
       <c r="M29">
-        <v>4110108332.56676</v>
+        <v>53020397490.11121</v>
       </c>
       <c r="N29">
-        <v>1449887399.619093</v>
+        <v>18703547455.0863</v>
       </c>
       <c r="O29">
-        <v>9635729219.196846</v>
+        <v>124300906927.6393</v>
       </c>
       <c r="P29">
-        <v>13733887830.77441</v>
+        <v>177167153016.9898</v>
       </c>
       <c r="Q29">
-        <v>10954122295.90767</v>
+        <v>141308177617.2089</v>
       </c>
     </row>
     <row r="30">
@@ -10939,52 +10939,52 @@
         </is>
       </c>
       <c r="B30">
-        <v>1241153675.842506</v>
+        <v>16010882418.36833</v>
       </c>
       <c r="C30">
-        <v>68225396.74141365</v>
+        <v>880107617.9642361</v>
       </c>
       <c r="D30">
-        <v>1642310141.184696</v>
+        <v>21185800821.28258</v>
       </c>
       <c r="E30">
-        <v>128984283.4542421</v>
+        <v>1663897256.559724</v>
       </c>
       <c r="F30">
-        <v>1018683139.575513</v>
+        <v>13141012500.52412</v>
       </c>
       <c r="G30">
-        <v>2858202960.955865</v>
+        <v>36870818196.33066</v>
       </c>
       <c r="H30">
-        <v>2843855718.890245</v>
+        <v>36685738773.68417</v>
       </c>
       <c r="I30">
-        <v>780786755.3034286</v>
+        <v>10072149143.41423</v>
       </c>
       <c r="J30">
-        <v>199770967.6488139</v>
+        <v>2577045482.6697</v>
       </c>
       <c r="K30">
-        <v>185646747.9469174</v>
+        <v>2394843048.515235</v>
       </c>
       <c r="L30">
-        <v>89566508.92654985</v>
+        <v>1155407965.152493</v>
       </c>
       <c r="M30">
-        <v>4138554833.758093</v>
+        <v>53387357355.4794</v>
       </c>
       <c r="N30">
-        <v>1455184847.321428</v>
+        <v>18771884530.44643</v>
       </c>
       <c r="O30">
-        <v>9693366379.795475</v>
+        <v>125044426299.3616</v>
       </c>
       <c r="P30">
-        <v>13792723016.59385</v>
+        <v>177926126914.0606</v>
       </c>
       <c r="Q30">
-        <v>11006817984.50336</v>
+        <v>141987952000.0934</v>
       </c>
     </row>
     <row r="31">
@@ -10994,52 +10994,52 @@
         </is>
       </c>
       <c r="B31">
-        <v>1248563563.215599</v>
+        <v>16106469965.48123</v>
       </c>
       <c r="C31">
-        <v>68611967.6690049</v>
+        <v>885094382.9301633</v>
       </c>
       <c r="D31">
-        <v>1645984832.688061</v>
+        <v>21233204341.67599</v>
       </c>
       <c r="E31">
-        <v>128654658.7369868</v>
+        <v>1659645097.707129</v>
       </c>
       <c r="F31">
-        <v>1018245513.247991</v>
+        <v>13135367120.89908</v>
       </c>
       <c r="G31">
-        <v>2861496972.342044</v>
+        <v>36913310943.21236</v>
       </c>
       <c r="H31">
-        <v>2851946603.195865</v>
+        <v>36790111181.22665</v>
       </c>
       <c r="I31">
-        <v>792412594.796867</v>
+        <v>10222122472.87959</v>
       </c>
       <c r="J31">
-        <v>202403265.2816361</v>
+        <v>2611002122.133105</v>
       </c>
       <c r="K31">
-        <v>188263744.5933234</v>
+        <v>2428602305.253872</v>
       </c>
       <c r="L31">
-        <v>89215362.96688831</v>
+        <v>1150878182.272859</v>
       </c>
       <c r="M31">
-        <v>4177699646.583763</v>
+        <v>53892325440.93054</v>
       </c>
       <c r="N31">
-        <v>1456201554.820516</v>
+        <v>18785000057.18466</v>
       </c>
       <c r="O31">
-        <v>9758142772.238857</v>
+        <v>125880041761.8813</v>
       </c>
       <c r="P31">
-        <v>13868203307.7965</v>
+        <v>178899822670.5749</v>
       </c>
       <c r="Q31">
-        <v>11074222826.7935</v>
+        <v>142857474465.6361</v>
       </c>
     </row>
     <row r="32">
@@ -11049,52 +11049,52 @@
         </is>
       </c>
       <c r="B32">
-        <v>1242442055.946856</v>
+        <v>16027502521.71444</v>
       </c>
       <c r="C32">
-        <v>68688474.12332</v>
+        <v>886081316.190828</v>
       </c>
       <c r="D32">
-        <v>1656032846.726533</v>
+        <v>21362823722.77228</v>
       </c>
       <c r="E32">
-        <v>131653161.6314156</v>
+        <v>1698325785.045262</v>
       </c>
       <c r="F32">
-        <v>1021219603.316388</v>
+        <v>13173732882.7814</v>
       </c>
       <c r="G32">
-        <v>2877594085.797656</v>
+        <v>37120963706.78976</v>
       </c>
       <c r="H32">
-        <v>2859392893.605025</v>
+        <v>36886168327.50482</v>
       </c>
       <c r="I32">
-        <v>805534750.5742505</v>
+        <v>10391398282.40783</v>
       </c>
       <c r="J32">
-        <v>203823776.3535123</v>
+        <v>2629326714.960309</v>
       </c>
       <c r="K32">
-        <v>189682688.9560003</v>
+        <v>2446906687.532403</v>
       </c>
       <c r="L32">
-        <v>88649013.17768419</v>
+        <v>1143572269.992126</v>
       </c>
       <c r="M32">
-        <v>4218802253.725793</v>
+        <v>54422549073.06273</v>
       </c>
       <c r="N32">
-        <v>1456671912.517897</v>
+        <v>18791067671.48087</v>
       </c>
       <c r="O32">
-        <v>9822557288.910162</v>
+        <v>126710989026.9411</v>
       </c>
       <c r="P32">
-        <v>13942593430.65467</v>
+        <v>179859455255.4453</v>
       </c>
       <c r="Q32">
-        <v>11154830449.01224</v>
+        <v>143897312792.2579</v>
       </c>
     </row>
     <row r="33">
@@ -11104,52 +11104,52 @@
         </is>
       </c>
       <c r="B33">
-        <v>1241928561.831959</v>
+        <v>16020878447.63227</v>
       </c>
       <c r="C33">
-        <v>70505194.99836493</v>
+        <v>909517015.4789076</v>
       </c>
       <c r="D33">
-        <v>1671843689.785504</v>
+        <v>21566783598.233</v>
       </c>
       <c r="E33">
-        <v>134373240.3241457</v>
+        <v>1733414800.181479</v>
       </c>
       <c r="F33">
-        <v>1023220773.862402</v>
+        <v>13199547982.82499</v>
       </c>
       <c r="G33">
-        <v>2899942898.970417</v>
+        <v>37409263396.71838</v>
       </c>
       <c r="H33">
-        <v>2876112566.066193</v>
+        <v>37101852102.25389</v>
       </c>
       <c r="I33">
-        <v>815783282.1064099</v>
+        <v>10523604339.17269</v>
       </c>
       <c r="J33">
-        <v>206570802.928047</v>
+        <v>2664763357.771806</v>
       </c>
       <c r="K33">
-        <v>191096332.6962868</v>
+        <v>2465142691.7821</v>
       </c>
       <c r="L33">
-        <v>88609973.66142146</v>
+        <v>1143068660.232337</v>
       </c>
       <c r="M33">
-        <v>4268681441.554964</v>
+        <v>55065990596.05904</v>
       </c>
       <c r="N33">
-        <v>1464222393.322133</v>
+        <v>18888468873.85552</v>
       </c>
       <c r="O33">
-        <v>9911076792.335457</v>
+        <v>127852890621.1274</v>
       </c>
       <c r="P33">
-        <v>14052948253.13783</v>
+        <v>181283032465.478</v>
       </c>
       <c r="Q33">
-        <v>11258187324.32232</v>
+        <v>145230616483.7579</v>
       </c>
     </row>
     <row r="34">
@@ -11159,52 +11159,52 @@
         </is>
       </c>
       <c r="B34">
-        <v>1236147289.677323</v>
+        <v>15946300036.83747</v>
       </c>
       <c r="C34">
-        <v>71332964.24560037</v>
+        <v>920195238.7682449</v>
       </c>
       <c r="D34">
-        <v>1665173883.857735</v>
+        <v>21480743101.76479</v>
       </c>
       <c r="E34">
-        <v>135058641.825077</v>
+        <v>1742256479.543493</v>
       </c>
       <c r="F34">
-        <v>1011608267.059344</v>
+        <v>13049746645.06554</v>
       </c>
       <c r="G34">
-        <v>2883173756.987757</v>
+        <v>37192941465.14206</v>
       </c>
       <c r="H34">
-        <v>2844962451.585122</v>
+        <v>36700015625.44807</v>
       </c>
       <c r="I34">
-        <v>814114055.9397676</v>
+        <v>10502071321.623</v>
       </c>
       <c r="J34">
-        <v>209850771.1099438</v>
+        <v>2707074947.318275</v>
       </c>
       <c r="K34">
-        <v>190993364.6230051</v>
+        <v>2463814403.636765</v>
       </c>
       <c r="L34">
-        <v>86238553.78209144</v>
+        <v>1112477343.78898</v>
       </c>
       <c r="M34">
-        <v>4229294470.872555</v>
+        <v>54557898674.25596</v>
       </c>
       <c r="N34">
-        <v>1451918812.209832</v>
+        <v>18729752677.50683</v>
       </c>
       <c r="O34">
-        <v>9827372480.122318</v>
+        <v>126773104993.5779</v>
       </c>
       <c r="P34">
-        <v>13946693526.7874</v>
+        <v>179912346495.5574</v>
       </c>
       <c r="Q34">
-        <v>11172388871.11815</v>
+        <v>144123816437.4241</v>
       </c>
     </row>
     <row r="35">
@@ -11214,52 +11214,52 @@
         </is>
       </c>
       <c r="B35">
-        <v>1205474794.201439</v>
+        <v>15550624845.19856</v>
       </c>
       <c r="C35">
-        <v>70416038.71972632</v>
+        <v>908366899.4844697</v>
       </c>
       <c r="D35">
-        <v>1554397400.144826</v>
+        <v>20051726461.86826</v>
       </c>
       <c r="E35">
-        <v>131178479.4236735</v>
+        <v>1692202384.565389</v>
       </c>
       <c r="F35">
-        <v>930716378.8819983</v>
+        <v>12006241287.57778</v>
       </c>
       <c r="G35">
-        <v>2686708297.170224</v>
+        <v>34658537033.4959</v>
       </c>
       <c r="H35">
-        <v>2640634986.051502</v>
+        <v>34064191320.06437</v>
       </c>
       <c r="I35">
-        <v>755323709.225577</v>
+        <v>9743675849.009943</v>
       </c>
       <c r="J35">
-        <v>205183357.6738024</v>
+        <v>2646865313.992051</v>
       </c>
       <c r="K35">
-        <v>183736307.7312924</v>
+        <v>2370198369.733672</v>
       </c>
       <c r="L35">
-        <v>79661947.26535918</v>
+        <v>1027639119.723133</v>
       </c>
       <c r="M35">
-        <v>3844249027.541221</v>
+        <v>49590812455.28175</v>
       </c>
       <c r="N35">
-        <v>1389692039.146802</v>
+        <v>17927027304.99374</v>
       </c>
       <c r="O35">
-        <v>9098481374.635555</v>
+        <v>117370409732.7987</v>
       </c>
       <c r="P35">
-        <v>12990664466.00722</v>
+        <v>167579571611.4931</v>
       </c>
       <c r="Q35">
-        <v>10315835685.39362</v>
+        <v>133074280341.5777</v>
       </c>
     </row>
     <row r="36">
@@ -11269,52 +11269,52 @@
         </is>
       </c>
       <c r="B36">
-        <v>1201819067.796517</v>
+        <v>15503465974.57507</v>
       </c>
       <c r="C36">
-        <v>68418932.88030414</v>
+        <v>882604234.1559235</v>
       </c>
       <c r="D36">
-        <v>1493809262.989364</v>
+        <v>19270139492.5628</v>
       </c>
       <c r="E36">
-        <v>125488290.1689624</v>
+        <v>1618798943.179615</v>
       </c>
       <c r="F36">
-        <v>881989041.9130701</v>
+        <v>11377658640.6786</v>
       </c>
       <c r="G36">
-        <v>2569705527.951701</v>
+        <v>33149201310.57694</v>
       </c>
       <c r="H36">
-        <v>2522867821.275859</v>
+        <v>32544994894.45859</v>
       </c>
       <c r="I36">
-        <v>716163320.5638989</v>
+        <v>9238506835.274296</v>
       </c>
       <c r="J36">
-        <v>206123829.7409885</v>
+        <v>2658997403.658752</v>
       </c>
       <c r="K36">
-        <v>179752242.0179456</v>
+        <v>2318803922.031498</v>
       </c>
       <c r="L36">
-        <v>77726144.80569299</v>
+        <v>1002667267.99344</v>
       </c>
       <c r="M36">
-        <v>3569870925.682683</v>
+        <v>46051334941.30661</v>
       </c>
       <c r="N36">
-        <v>1370483604.594534</v>
+        <v>17679238499.26949</v>
       </c>
       <c r="O36">
-        <v>8642987888.681602</v>
+        <v>111494543763.9927</v>
       </c>
       <c r="P36">
-        <v>12414512484.42982</v>
+        <v>160147211049.1447</v>
       </c>
       <c r="Q36">
-        <v>9764483667.233076</v>
+        <v>125961839307.3067</v>
       </c>
     </row>
     <row r="37">
@@ -11324,52 +11324,52 @@
         </is>
       </c>
       <c r="B37">
-        <v>1214959428.177704</v>
+        <v>15672976623.49238</v>
       </c>
       <c r="C37">
-        <v>65851992.37608036</v>
+        <v>849490701.6514367</v>
       </c>
       <c r="D37">
-        <v>1464930463.63805</v>
+        <v>18897602980.93084</v>
       </c>
       <c r="E37">
-        <v>115865206.0257396</v>
+        <v>1494661157.732041</v>
       </c>
       <c r="F37">
-        <v>856064814.3488879</v>
+        <v>11043236105.10065</v>
       </c>
       <c r="G37">
-        <v>2502712476.388757</v>
+        <v>32284990945.41497</v>
       </c>
       <c r="H37">
-        <v>2440259234.619397</v>
+        <v>31479344126.59022</v>
       </c>
       <c r="I37">
-        <v>689448378.8034235</v>
+        <v>8893884086.564163</v>
       </c>
       <c r="J37">
-        <v>208486693.3240954</v>
+        <v>2689478343.880831</v>
       </c>
       <c r="K37">
-        <v>183627993.7800841</v>
+        <v>2368801119.763085</v>
       </c>
       <c r="L37">
-        <v>76013136.85513875</v>
+        <v>980569465.4312899</v>
       </c>
       <c r="M37">
-        <v>3363411506.527812</v>
+        <v>43388008434.20879</v>
       </c>
       <c r="N37">
-        <v>1375081640.857731</v>
+        <v>17738553167.06474</v>
       </c>
       <c r="O37">
-        <v>8336328584.767682</v>
+        <v>107538638743.5031</v>
       </c>
       <c r="P37">
-        <v>12054000489.33414</v>
+        <v>155496606312.4105</v>
       </c>
       <c r="Q37">
-        <v>9387946283.443569</v>
+        <v>121104507056.422</v>
       </c>
     </row>
     <row r="38">
@@ -11379,52 +11379,52 @@
         </is>
       </c>
       <c r="B38">
-        <v>1237698468.890496</v>
+        <v>15966310248.6874</v>
       </c>
       <c r="C38">
-        <v>65212648.72588098</v>
+        <v>841243168.5638647</v>
       </c>
       <c r="D38">
-        <v>1466946251.512892</v>
+        <v>18923606644.51632</v>
       </c>
       <c r="E38">
-        <v>111503109.1801536</v>
+        <v>1438390108.423981</v>
       </c>
       <c r="F38">
-        <v>857491858.2982619</v>
+        <v>11061644972.04758</v>
       </c>
       <c r="G38">
-        <v>2501153867.717189</v>
+        <v>32264884893.55174</v>
       </c>
       <c r="H38">
-        <v>2409948066.773148</v>
+        <v>31088330061.37361</v>
       </c>
       <c r="I38">
-        <v>679915722.0770388</v>
+        <v>8770912814.7938</v>
       </c>
       <c r="J38">
-        <v>212013055.6747805</v>
+        <v>2734968418.204669</v>
       </c>
       <c r="K38">
-        <v>189002301.1330123</v>
+        <v>2438129684.615858</v>
       </c>
       <c r="L38">
-        <v>79033846.78151235</v>
+        <v>1019536623.481509</v>
       </c>
       <c r="M38">
-        <v>3262583448.556738</v>
+        <v>42087326486.38193</v>
       </c>
       <c r="N38">
-        <v>1410384929.148055</v>
+        <v>18193965586.00991</v>
       </c>
       <c r="O38">
-        <v>8242881370.144285</v>
+        <v>106333169674.8613</v>
       </c>
       <c r="P38">
-        <v>11981733706.75197</v>
+        <v>154564364817.1004</v>
       </c>
       <c r="Q38">
-        <v>9254616461.931906</v>
+        <v>119384552358.9216</v>
       </c>
     </row>
     <row r="39">
@@ -11434,52 +11434,52 @@
         </is>
       </c>
       <c r="B39">
-        <v>1286233306.751479</v>
+        <v>16592409657.09408</v>
       </c>
       <c r="C39">
-        <v>67947371.86685738</v>
+        <v>876521097.0824602</v>
       </c>
       <c r="D39">
-        <v>1554750125.812848</v>
+        <v>20056276622.98574</v>
       </c>
       <c r="E39">
-        <v>108169875.0176419</v>
+        <v>1395391387.727581</v>
       </c>
       <c r="F39">
-        <v>937268681.9695301</v>
+        <v>12090765997.40694</v>
       </c>
       <c r="G39">
-        <v>2668136054.666877</v>
+        <v>34418955105.20272</v>
       </c>
       <c r="H39">
-        <v>2559307100.750437</v>
+        <v>33015061599.68063</v>
       </c>
       <c r="I39">
-        <v>722701162.6880995</v>
+        <v>9322844998.676483</v>
       </c>
       <c r="J39">
-        <v>227315667.2095659</v>
+        <v>2932372107.0034</v>
       </c>
       <c r="K39">
-        <v>199069481.8882014</v>
+        <v>2567996316.357798</v>
       </c>
       <c r="L39">
-        <v>85320951.55626506</v>
+        <v>1100640275.075819</v>
       </c>
       <c r="M39">
-        <v>3526272768.735929</v>
+        <v>45488918716.69349</v>
       </c>
       <c r="N39">
-        <v>1484175930.649313</v>
+        <v>19145869505.37614</v>
       </c>
       <c r="O39">
-        <v>8804163063.477812</v>
+        <v>113573703518.8638</v>
       </c>
       <c r="P39">
-        <v>12758532424.89617</v>
+        <v>164585068281.1606</v>
       </c>
       <c r="Q39">
-        <v>9902802235.93911</v>
+        <v>127746148843.6145</v>
       </c>
     </row>
     <row r="40">
@@ -11489,52 +11489,52 @@
         </is>
       </c>
       <c r="B40">
-        <v>1320308289.703498</v>
+        <v>17031976937.17512</v>
       </c>
       <c r="C40">
-        <v>70112370.95752503</v>
+        <v>904449585.352073</v>
       </c>
       <c r="D40">
-        <v>1618397123.797568</v>
+        <v>20877322896.98862</v>
       </c>
       <c r="E40">
-        <v>105447407.884776</v>
+        <v>1360271561.713611</v>
       </c>
       <c r="F40">
-        <v>992038463.6525183</v>
+        <v>12797296181.11749</v>
       </c>
       <c r="G40">
-        <v>2785995366.292387</v>
+        <v>35939340225.17179</v>
       </c>
       <c r="H40">
-        <v>2669829615.923005</v>
+        <v>34440802045.40676</v>
       </c>
       <c r="I40">
-        <v>756276508.7235974</v>
+        <v>9755966962.534407</v>
       </c>
       <c r="J40">
-        <v>233886090.5119525</v>
+        <v>3017130567.604187</v>
       </c>
       <c r="K40">
-        <v>205829328.3535764</v>
+        <v>2655198335.761135</v>
       </c>
       <c r="L40">
-        <v>87680447.46567608</v>
+        <v>1131077772.307221</v>
       </c>
       <c r="M40">
-        <v>3718461841.547292</v>
+        <v>47968157755.96007</v>
       </c>
       <c r="N40">
-        <v>1505823970.757216</v>
+        <v>19425129222.76808</v>
       </c>
       <c r="O40">
-        <v>9177787803.282314</v>
+        <v>118393462662.3419</v>
       </c>
       <c r="P40">
-        <v>13284091459.2782</v>
+        <v>171364779824.6888</v>
       </c>
       <c r="Q40">
-        <v>10370278751.35181</v>
+        <v>133776595892.4383</v>
       </c>
     </row>
     <row r="41">
@@ -11544,52 +11544,52 @@
         </is>
       </c>
       <c r="B41">
-        <v>1338160406.878538</v>
+        <v>17262269248.73314</v>
       </c>
       <c r="C41">
-        <v>73361006.21528599</v>
+        <v>946356980.1771892</v>
       </c>
       <c r="D41">
-        <v>1661378821.535144</v>
+        <v>21431786797.80336</v>
       </c>
       <c r="E41">
-        <v>108204037.5101184</v>
+        <v>1395832083.880528</v>
       </c>
       <c r="F41">
-        <v>1039661594.733123</v>
+        <v>13411634572.05729</v>
       </c>
       <c r="G41">
-        <v>2882605459.993671</v>
+        <v>37185610433.91837</v>
       </c>
       <c r="H41">
-        <v>2759502412.441619</v>
+        <v>35597581120.49689</v>
       </c>
       <c r="I41">
-        <v>779841141.5698423</v>
+        <v>10059950726.25097</v>
       </c>
       <c r="J41">
-        <v>245870994.9740403</v>
+        <v>3171735835.16512</v>
       </c>
       <c r="K41">
-        <v>208000499.8912152</v>
+        <v>2683206448.596677</v>
       </c>
       <c r="L41">
-        <v>89892208.48899527</v>
+        <v>1159609489.508039</v>
       </c>
       <c r="M41">
-        <v>3886390009.436756</v>
+        <v>50134431121.73415</v>
       </c>
       <c r="N41">
-        <v>1510874078.093775</v>
+        <v>19490275607.4097</v>
       </c>
       <c r="O41">
-        <v>9480371344.896244</v>
+        <v>122296790349.1615</v>
       </c>
       <c r="P41">
-        <v>13701137211.76845</v>
+        <v>176744670031.813</v>
       </c>
       <c r="Q41">
-        <v>10762210518.30714</v>
+        <v>138832515686.1622</v>
       </c>
     </row>
     <row r="42">
@@ -11599,52 +11599,52 @@
         </is>
       </c>
       <c r="B42">
-        <v>1341112528.838454</v>
+        <v>17300351622.01606</v>
       </c>
       <c r="C42">
-        <v>75096813.60159348</v>
+        <v>968748895.4605559</v>
       </c>
       <c r="D42">
-        <v>1696766734.271511</v>
+        <v>21888290872.10249</v>
       </c>
       <c r="E42">
-        <v>109392724.2867829</v>
+        <v>1411166143.299499</v>
       </c>
       <c r="F42">
-        <v>1073825701.767997</v>
+        <v>13852351552.80716</v>
       </c>
       <c r="G42">
-        <v>2955081973.927884</v>
+        <v>38120557463.66971</v>
       </c>
       <c r="H42">
-        <v>2854016789.236031</v>
+        <v>36816816581.1448</v>
       </c>
       <c r="I42">
-        <v>796676752.4498205</v>
+        <v>10277130106.60268</v>
       </c>
       <c r="J42">
-        <v>252649170.4284376</v>
+        <v>3259174298.526845</v>
       </c>
       <c r="K42">
-        <v>209083028.7370577</v>
+        <v>2697171070.708045</v>
       </c>
       <c r="L42">
-        <v>90080327.36119115</v>
+        <v>1162036222.959366</v>
       </c>
       <c r="M42">
-        <v>4047316899.563733</v>
+        <v>52210388004.37216</v>
       </c>
       <c r="N42">
-        <v>1507909785.227339</v>
+        <v>19452036229.43268</v>
       </c>
       <c r="O42">
-        <v>9757732753.003611</v>
+        <v>125874752513.7466</v>
       </c>
       <c r="P42">
-        <v>14053927255.76995</v>
+        <v>181295661599.4323</v>
       </c>
       <c r="Q42">
-        <v>11114824614.34296</v>
+        <v>143381237525.0242</v>
       </c>
     </row>
     <row r="43">
@@ -11654,52 +11654,52 @@
         </is>
       </c>
       <c r="B43">
-        <v>1332405298.249249</v>
+        <v>17188028347.41532</v>
       </c>
       <c r="C43">
-        <v>77177728.93016052</v>
+        <v>995592703.1990708</v>
       </c>
       <c r="D43">
-        <v>1740612841.890585</v>
+        <v>22453905660.38855</v>
       </c>
       <c r="E43">
-        <v>113319700.8163255</v>
+        <v>1461824140.5306</v>
       </c>
       <c r="F43">
-        <v>1105346329.127886</v>
+        <v>14258967645.74973</v>
       </c>
       <c r="G43">
-        <v>3036456600.764957</v>
+        <v>39170290149.86794</v>
       </c>
       <c r="H43">
-        <v>2957932308.089561</v>
+        <v>38157326774.35533</v>
       </c>
       <c r="I43">
-        <v>817465643.6456125</v>
+        <v>10545306803.0284</v>
       </c>
       <c r="J43">
-        <v>260916222.1913003</v>
+        <v>3365819266.267775</v>
       </c>
       <c r="K43">
-        <v>213443670.8496517</v>
+        <v>2753423353.960507</v>
       </c>
       <c r="L43">
-        <v>93720138.01650345</v>
+        <v>1208989780.412894</v>
       </c>
       <c r="M43">
-        <v>4195050484.772921</v>
+        <v>54116151253.57068</v>
       </c>
       <c r="N43">
-        <v>1520617533.449556</v>
+        <v>19615966181.49927</v>
       </c>
       <c r="O43">
-        <v>10059146001.0151</v>
+        <v>129762983413.0948</v>
       </c>
       <c r="P43">
-        <v>14428007900.02931</v>
+        <v>186121301910.3781</v>
       </c>
       <c r="Q43">
-        <v>11481264930.314</v>
+        <v>148108317601.0506</v>
       </c>
     </row>
     <row r="44">
@@ -11709,52 +11709,52 @@
         </is>
       </c>
       <c r="B44">
-        <v>1317977220.275294</v>
+        <v>17001906141.55129</v>
       </c>
       <c r="C44">
-        <v>79363030.40418957</v>
+        <v>1023783092.214046</v>
       </c>
       <c r="D44">
-        <v>1759253657.020622</v>
+        <v>22694372175.56602</v>
       </c>
       <c r="E44">
-        <v>115144012.140077</v>
+        <v>1485357756.606993</v>
       </c>
       <c r="F44">
-        <v>1117650464.884203</v>
+        <v>14417690997.00623</v>
       </c>
       <c r="G44">
-        <v>3071411164.449092</v>
+        <v>39621204021.39329</v>
       </c>
       <c r="H44">
-        <v>3019284071.900944</v>
+        <v>38948764527.52218</v>
       </c>
       <c r="I44">
-        <v>834747408.548316</v>
+        <v>10768241570.27328</v>
       </c>
       <c r="J44">
-        <v>266749138.5777707</v>
+        <v>3441063887.653242</v>
       </c>
       <c r="K44">
-        <v>219667824.5319983</v>
+        <v>2833714936.462778</v>
       </c>
       <c r="L44">
-        <v>96703288.97327314</v>
+        <v>1247472427.755224</v>
       </c>
       <c r="M44">
-        <v>4305636657.467054</v>
+        <v>55542712881.325</v>
       </c>
       <c r="N44">
-        <v>1548473197.727696</v>
+        <v>19975304250.68728</v>
       </c>
       <c r="O44">
-        <v>10291261587.72705</v>
+        <v>132757274481.679</v>
       </c>
       <c r="P44">
-        <v>14680649972.45144</v>
+        <v>189380384644.6236</v>
       </c>
       <c r="Q44">
-        <v>11717496265.47517</v>
+        <v>151155701824.6298</v>
       </c>
     </row>
     <row r="45">
@@ -11764,52 +11764,52 @@
         </is>
       </c>
       <c r="B45">
-        <v>1299311055.516215</v>
+        <v>16761112616.15918</v>
       </c>
       <c r="C45">
-        <v>81621706.76800947</v>
+        <v>1052920017.307322</v>
       </c>
       <c r="D45">
-        <v>1763625224.966962</v>
+        <v>22750765402.07381</v>
       </c>
       <c r="E45">
-        <v>115044944.8491298</v>
+        <v>1484079788.553775</v>
       </c>
       <c r="F45">
-        <v>1111086420.943088</v>
+        <v>14333014830.16583</v>
       </c>
       <c r="G45">
-        <v>3071378297.527189</v>
+        <v>39620780038.10075</v>
       </c>
       <c r="H45">
-        <v>3048900703.087004</v>
+        <v>39330819069.82236</v>
       </c>
       <c r="I45">
-        <v>852323206.1711884</v>
+        <v>10994969359.60833</v>
       </c>
       <c r="J45">
-        <v>265917935.548352</v>
+        <v>3430341368.57374</v>
       </c>
       <c r="K45">
-        <v>224865934.7164083</v>
+        <v>2900770557.841667</v>
       </c>
       <c r="L45">
-        <v>99676104.41004454</v>
+        <v>1285821746.889575</v>
       </c>
       <c r="M45">
-        <v>4355397613.824589</v>
+        <v>56184629218.3372</v>
       </c>
       <c r="N45">
-        <v>1562848241.979585</v>
+        <v>20160742321.53664</v>
       </c>
       <c r="O45">
-        <v>10409929739.73717</v>
+        <v>134288093642.6095</v>
       </c>
       <c r="P45">
-        <v>14780619092.78057</v>
+        <v>190669986296.8694</v>
       </c>
       <c r="Q45">
-        <v>11818783690.87473</v>
+        <v>152462309612.2841</v>
       </c>
     </row>
     <row r="46">
@@ -11819,52 +11819,52 @@
         </is>
       </c>
       <c r="B46">
-        <v>1287269784.308636</v>
+        <v>16605780217.58141</v>
       </c>
       <c r="C46">
-        <v>82970010.7203068</v>
+        <v>1070313138.291958</v>
       </c>
       <c r="D46">
-        <v>1773344123.907498</v>
+        <v>22876139198.40672</v>
       </c>
       <c r="E46">
-        <v>114781400.49561</v>
+        <v>1480680066.393369</v>
       </c>
       <c r="F46">
-        <v>1109981405.204291</v>
+        <v>14318760127.13536</v>
       </c>
       <c r="G46">
-        <v>3081076940.327706</v>
+        <v>39745892530.22741</v>
       </c>
       <c r="H46">
-        <v>3070125402.678631</v>
+        <v>39604617694.55434</v>
       </c>
       <c r="I46">
-        <v>868039649.5592563</v>
+        <v>11197711479.31441</v>
       </c>
       <c r="J46">
-        <v>266190123.0340504</v>
+        <v>3433852587.13925</v>
       </c>
       <c r="K46">
-        <v>230775353.9914632</v>
+        <v>2977002066.489876</v>
       </c>
       <c r="L46">
-        <v>101914105.8825517</v>
+        <v>1314691965.884917</v>
       </c>
       <c r="M46">
-        <v>4394319244.0751</v>
+        <v>56686718248.56879</v>
       </c>
       <c r="N46">
-        <v>1578454932.999729</v>
+        <v>20362068635.6965</v>
       </c>
       <c r="O46">
-        <v>10509818812.22078</v>
+        <v>135576662677.6481</v>
       </c>
       <c r="P46">
-        <v>14878165536.85712</v>
+        <v>191928335425.4569</v>
       </c>
       <c r="Q46">
-        <v>11910526713.66621</v>
+        <v>153645794606.2941</v>
       </c>
     </row>
     <row r="47">
@@ -11874,52 +11874,52 @@
         </is>
       </c>
       <c r="B47">
-        <v>1274166272.451589</v>
+        <v>16436744914.6255</v>
       </c>
       <c r="C47">
-        <v>83899235.52345657</v>
+        <v>1082300138.25259</v>
       </c>
       <c r="D47">
-        <v>1774339741.405599</v>
+        <v>22888982664.13223</v>
       </c>
       <c r="E47">
-        <v>113538397.9452326</v>
+        <v>1464645333.4935</v>
       </c>
       <c r="F47">
-        <v>1097536446.010314</v>
+        <v>14158220153.53305</v>
       </c>
       <c r="G47">
-        <v>3069313820.884603</v>
+        <v>39594148289.41138</v>
       </c>
       <c r="H47">
-        <v>3062524754.599952</v>
+        <v>39506569334.33938</v>
       </c>
       <c r="I47">
-        <v>878043770.1547335</v>
+        <v>11326764634.99606</v>
       </c>
       <c r="J47">
-        <v>262753204.1475812</v>
+        <v>3389516333.503798</v>
       </c>
       <c r="K47">
-        <v>233362677.4250402</v>
+        <v>3010378538.783018</v>
       </c>
       <c r="L47">
-        <v>102318074.3038182</v>
+        <v>1319903158.519255</v>
       </c>
       <c r="M47">
-        <v>4431422908.501648</v>
+        <v>57165355519.67126</v>
       </c>
       <c r="N47">
-        <v>1593251148.810071</v>
+        <v>20552939819.64992</v>
       </c>
       <c r="O47">
-        <v>10563676537.94284</v>
+        <v>136271427339.4627</v>
       </c>
       <c r="P47">
-        <v>14907156631.27904</v>
+        <v>192302320543.4996</v>
       </c>
       <c r="Q47">
-        <v>11937421135.71356</v>
+        <v>153992732650.7049</v>
       </c>
     </row>
     <row r="48">
@@ -11929,52 +11929,52 @@
         </is>
       </c>
       <c r="B48">
-        <v>1257049516.866942</v>
+        <v>16215938767.58356</v>
       </c>
       <c r="C48">
-        <v>86179866.55979332</v>
+        <v>1111720278.621334</v>
       </c>
       <c r="D48">
-        <v>1762896055.949615</v>
+        <v>22741359121.75003</v>
       </c>
       <c r="E48">
-        <v>115304910.877484</v>
+        <v>1487433350.319543</v>
       </c>
       <c r="F48">
-        <v>1087596748.183782</v>
+        <v>14029998051.57079</v>
       </c>
       <c r="G48">
-        <v>3051977581.570674</v>
+        <v>39370510802.2617</v>
       </c>
       <c r="H48">
-        <v>3049279902.560895</v>
+        <v>39335710743.03555</v>
       </c>
       <c r="I48">
-        <v>884773009.0841956</v>
+        <v>11413571817.18612</v>
       </c>
       <c r="J48">
-        <v>267628307.3775168</v>
+        <v>3452405165.169967</v>
       </c>
       <c r="K48">
-        <v>237537187.5548087</v>
+        <v>3064229719.457032</v>
       </c>
       <c r="L48">
-        <v>102651699.9860534</v>
+        <v>1324206929.820089</v>
       </c>
       <c r="M48">
-        <v>4453336195.978141</v>
+        <v>57448036928.11802</v>
       </c>
       <c r="N48">
-        <v>1594830695.675569</v>
+        <v>20573315974.21484</v>
       </c>
       <c r="O48">
-        <v>10590036998.21718</v>
+        <v>136611477277.0016</v>
       </c>
       <c r="P48">
-        <v>14899064096.6548</v>
+        <v>192197926846.8469</v>
       </c>
       <c r="Q48">
-        <v>11944532184.12623</v>
+        <v>154084465175.2284</v>
       </c>
     </row>
     <row r="49">
@@ -11984,52 +11984,52 @@
         </is>
       </c>
       <c r="B49">
-        <v>1235254512.355714</v>
+        <v>15934783209.38872</v>
       </c>
       <c r="C49">
-        <v>87413473.49421121</v>
+        <v>1127633808.075325</v>
       </c>
       <c r="D49">
-        <v>1765968565.201777</v>
+        <v>22780994491.10293</v>
       </c>
       <c r="E49">
-        <v>116044938.1705925</v>
+        <v>1496979702.400644</v>
       </c>
       <c r="F49">
-        <v>1088161720.633545</v>
+        <v>14037286196.17273</v>
       </c>
       <c r="G49">
-        <v>3057588697.500126</v>
+        <v>39442894197.75163</v>
       </c>
       <c r="H49">
-        <v>3044907723.855222</v>
+        <v>39279309637.73236</v>
       </c>
       <c r="I49">
-        <v>895649256.4290485</v>
+        <v>11553875407.93473</v>
       </c>
       <c r="J49">
-        <v>273354923.4511883</v>
+        <v>3526278512.520329</v>
       </c>
       <c r="K49">
-        <v>237738589.2039388</v>
+        <v>3066827800.730811</v>
       </c>
       <c r="L49">
-        <v>104691495.1734311</v>
+        <v>1350520287.737261</v>
       </c>
       <c r="M49">
-        <v>4485782534.000668</v>
+        <v>57866594688.60861</v>
       </c>
       <c r="N49">
-        <v>1598661186.209859</v>
+        <v>20622729302.10719</v>
       </c>
       <c r="O49">
-        <v>10640785708.32336</v>
+        <v>137266135637.3713</v>
       </c>
       <c r="P49">
-        <v>14933628918.1792</v>
+        <v>192643813044.5116</v>
       </c>
       <c r="Q49">
-        <v>11995021724.44019</v>
+        <v>154735780245.2785</v>
       </c>
     </row>
     <row r="50">
@@ -12039,52 +12039,52 @@
         </is>
       </c>
       <c r="B50">
-        <v>1215907445.315349</v>
+        <v>15685206044.568</v>
       </c>
       <c r="C50">
-        <v>89614337.31080011</v>
+        <v>1156024951.309321</v>
       </c>
       <c r="D50">
-        <v>1767052313.608211</v>
+        <v>22794974845.54592</v>
       </c>
       <c r="E50">
-        <v>116893984.8255707</v>
+        <v>1507932404.249862</v>
       </c>
       <c r="F50">
-        <v>1091560228.790021</v>
+        <v>14081126951.39128</v>
       </c>
       <c r="G50">
-        <v>3065120864.534603</v>
+        <v>39540059152.49638</v>
       </c>
       <c r="H50">
-        <v>3043482946.592073</v>
+        <v>39260930011.03774</v>
       </c>
       <c r="I50">
-        <v>909168462.4079239</v>
+        <v>11728273165.06222</v>
       </c>
       <c r="J50">
-        <v>277716144.5223563</v>
+        <v>3582538264.338396</v>
       </c>
       <c r="K50">
-        <v>236006663.5142552</v>
+        <v>3044485959.333892</v>
       </c>
       <c r="L50">
-        <v>106684773.7675248</v>
+        <v>1376233581.60107</v>
       </c>
       <c r="M50">
-        <v>4520496806.272625</v>
+        <v>58314408800.91686</v>
       </c>
       <c r="N50">
-        <v>1601408653.904306</v>
+        <v>20658171635.36555</v>
       </c>
       <c r="O50">
-        <v>10694964450.98106</v>
+        <v>137965041417.6557</v>
       </c>
       <c r="P50">
-        <v>14975992760.83102</v>
+        <v>193190306614.7201</v>
       </c>
       <c r="Q50">
-        <v>12051991887.84384</v>
+        <v>155470695353.1855</v>
       </c>
     </row>
     <row r="51">
@@ -12094,52 +12094,52 @@
         </is>
       </c>
       <c r="B51">
-        <v>1199814663.763798</v>
+        <v>15477609162.55299</v>
       </c>
       <c r="C51">
-        <v>90120086.92405747</v>
+        <v>1162549121.320341</v>
       </c>
       <c r="D51">
-        <v>1777929985.552753</v>
+        <v>22935296813.63052</v>
       </c>
       <c r="E51">
-        <v>116741278.2065178</v>
+        <v>1505962488.86408</v>
       </c>
       <c r="F51">
-        <v>1104516491.449383</v>
+        <v>14248262739.69704</v>
       </c>
       <c r="G51">
-        <v>3089307842.132712</v>
+        <v>39852071163.51199</v>
       </c>
       <c r="H51">
-        <v>3067297517.45656</v>
+        <v>39568137975.18963</v>
       </c>
       <c r="I51">
-        <v>927201132.8924278</v>
+        <v>11960894614.31232</v>
       </c>
       <c r="J51">
-        <v>285543945.6143269</v>
+        <v>3683516898.424817</v>
       </c>
       <c r="K51">
-        <v>235629699.068659</v>
+        <v>3039623117.985701</v>
       </c>
       <c r="L51">
-        <v>109303701.7303491</v>
+        <v>1410017752.321504</v>
       </c>
       <c r="M51">
-        <v>4565276933.800127</v>
+        <v>58892072446.02164</v>
       </c>
       <c r="N51">
-        <v>1621592198.49002</v>
+        <v>20918539360.52126</v>
       </c>
       <c r="O51">
-        <v>10811845129.05247</v>
+        <v>139472802164.7769</v>
       </c>
       <c r="P51">
-        <v>15100967634.94898</v>
+        <v>194802482490.8419</v>
       </c>
       <c r="Q51">
-        <v>12170257070.96481</v>
+        <v>156996316215.4461</v>
       </c>
     </row>
     <row r="52">
@@ -12149,52 +12149,52 @@
         </is>
       </c>
       <c r="B52">
-        <v>1185464035.282279</v>
+        <v>15292486055.1414</v>
       </c>
       <c r="C52">
-        <v>90956548.2040257</v>
+        <v>1173339471.831932</v>
       </c>
       <c r="D52">
-        <v>1806804477.847625</v>
+        <v>23307777764.23436</v>
       </c>
       <c r="E52">
-        <v>118045443.4463852</v>
+        <v>1522786220.458369</v>
       </c>
       <c r="F52">
-        <v>1115330898.547938</v>
+        <v>14387768591.26841</v>
       </c>
       <c r="G52">
-        <v>3131137368.045974</v>
+        <v>40391672047.79307</v>
       </c>
       <c r="H52">
-        <v>3092988488.79198</v>
+        <v>39899551505.41654</v>
       </c>
       <c r="I52">
-        <v>940751619.614298</v>
+        <v>12135695893.02444</v>
       </c>
       <c r="J52">
-        <v>288174808.2282385</v>
+        <v>3717455026.144277</v>
       </c>
       <c r="K52">
-        <v>234421959.1846393</v>
+        <v>3024043273.481847</v>
       </c>
       <c r="L52">
-        <v>110714358.9589021</v>
+        <v>1428215230.569838</v>
       </c>
       <c r="M52">
-        <v>4610779496.809066</v>
+        <v>59479055508.83695</v>
       </c>
       <c r="N52">
-        <v>1642032409.752266</v>
+        <v>21182218085.80424</v>
       </c>
       <c r="O52">
-        <v>10919863141.33939</v>
+        <v>140866234523.2781</v>
       </c>
       <c r="P52">
-        <v>15236464544.66764</v>
+        <v>196550392626.2126</v>
       </c>
       <c r="Q52">
-        <v>12298253740.67419</v>
+        <v>158647473254.6971</v>
       </c>
     </row>
     <row r="53">
@@ -12204,52 +12204,52 @@
         </is>
       </c>
       <c r="B53">
-        <v>1175126546.798352</v>
+        <v>15159132453.69874</v>
       </c>
       <c r="C53">
-        <v>91628766.23819572</v>
+        <v>1182011084.472725</v>
       </c>
       <c r="D53">
-        <v>1825894710.388929</v>
+        <v>23554041764.01719</v>
       </c>
       <c r="E53">
-        <v>119419964.2149265</v>
+        <v>1540517538.372552</v>
       </c>
       <c r="F53">
-        <v>1132929596.785298</v>
+        <v>14614791798.53035</v>
       </c>
       <c r="G53">
-        <v>3169873037.62735</v>
+        <v>40891362185.39281</v>
       </c>
       <c r="H53">
-        <v>3119092180.32014</v>
+        <v>40236289126.12981</v>
       </c>
       <c r="I53">
-        <v>953964222.6870748</v>
+        <v>12306138472.66327</v>
       </c>
       <c r="J53">
-        <v>287655846.0471141</v>
+        <v>3710760414.007772</v>
       </c>
       <c r="K53">
-        <v>233808055.9759435</v>
+        <v>3016123922.089672</v>
       </c>
       <c r="L53">
-        <v>111350395.1822698</v>
+        <v>1436420097.85128</v>
       </c>
       <c r="M53">
-        <v>4662110340.619394</v>
+        <v>60141223393.99019</v>
       </c>
       <c r="N53">
-        <v>1665624039.071494</v>
+        <v>21486550104.02227</v>
       </c>
       <c r="O53">
-        <v>11033605079.90343</v>
+        <v>142333505530.7543</v>
       </c>
       <c r="P53">
-        <v>15378604664.32913</v>
+        <v>198384000169.8458</v>
       </c>
       <c r="Q53">
-        <v>12426503683.27702</v>
+        <v>160301897514.2735</v>
       </c>
     </row>
     <row r="54">
@@ -12259,52 +12259,52 @@
         </is>
       </c>
       <c r="B54">
-        <v>1165603450.536989</v>
+        <v>15036284511.92715</v>
       </c>
       <c r="C54">
-        <v>92693879.4598119</v>
+        <v>1195751045.031574</v>
       </c>
       <c r="D54">
-        <v>1843942519.710855</v>
+        <v>23786858504.27003</v>
       </c>
       <c r="E54">
-        <v>119430206.9203479</v>
+        <v>1540649669.272488</v>
       </c>
       <c r="F54">
-        <v>1138011739.570572</v>
+        <v>14680351440.46038</v>
       </c>
       <c r="G54">
-        <v>3194078345.661587</v>
+        <v>41203610659.03447</v>
       </c>
       <c r="H54">
-        <v>3141747813.06535</v>
+        <v>40528546788.54301</v>
       </c>
       <c r="I54">
-        <v>965523227.7812845</v>
+        <v>12455249638.37857</v>
       </c>
       <c r="J54">
-        <v>290142286.9937446</v>
+        <v>3742835502.219306</v>
       </c>
       <c r="K54">
-        <v>237881729.0054593</v>
+        <v>3068674304.170425</v>
       </c>
       <c r="L54">
-        <v>113073630.4864537</v>
+        <v>1458649833.275253</v>
       </c>
       <c r="M54">
-        <v>4692328474.841867</v>
+        <v>60531037325.46009</v>
       </c>
       <c r="N54">
-        <v>1685162872.592943</v>
+        <v>21738601056.44896</v>
       </c>
       <c r="O54">
-        <v>11125860034.7671</v>
+        <v>143523594448.4956</v>
       </c>
       <c r="P54">
-        <v>15485541830.96568</v>
+        <v>199763489619.4573</v>
       </c>
       <c r="Q54">
-        <v>12521701877.34929</v>
+        <v>161529954217.8059</v>
       </c>
     </row>
     <row r="55">
@@ -12314,52 +12314,52 @@
         </is>
       </c>
       <c r="B55">
-        <v>1154990134.250763</v>
+        <v>14899372731.83485</v>
       </c>
       <c r="C55">
-        <v>95084525.11581814</v>
+        <v>1226590373.994054</v>
       </c>
       <c r="D55">
-        <v>1863689443.17856</v>
+        <v>24041593817.00343</v>
       </c>
       <c r="E55">
-        <v>122758332.915676</v>
+        <v>1583582494.612221</v>
       </c>
       <c r="F55">
-        <v>1132765702.669525</v>
+        <v>14612677564.43687</v>
       </c>
       <c r="G55">
-        <v>3214298003.879579</v>
+        <v>41464444250.04657</v>
       </c>
       <c r="H55">
-        <v>3161692302.369681</v>
+        <v>40785830700.56889</v>
       </c>
       <c r="I55">
-        <v>979132308.5301689</v>
+        <v>12630806780.03918</v>
       </c>
       <c r="J55">
-        <v>287636314.448166</v>
+        <v>3710508456.381341</v>
       </c>
       <c r="K55">
-        <v>243920150.7043211</v>
+        <v>3146569944.085742</v>
       </c>
       <c r="L55">
-        <v>113758965.621309</v>
+        <v>1467490656.514887</v>
       </c>
       <c r="M55">
-        <v>4717000041.422618</v>
+        <v>60849300534.35178</v>
       </c>
       <c r="N55">
-        <v>1690985809.131738</v>
+        <v>21813716937.79942</v>
       </c>
       <c r="O55">
-        <v>11194125892.228</v>
+        <v>144404224009.7413</v>
       </c>
       <c r="P55">
-        <v>15563414030.35835</v>
+        <v>200768040991.6227</v>
       </c>
       <c r="Q55">
-        <v>12603679121.35453</v>
+        <v>162587460665.4735</v>
       </c>
     </row>
     <row r="56">
@@ -12369,52 +12369,52 @@
         </is>
       </c>
       <c r="B56">
-        <v>1155889368.918871</v>
+        <v>14910972859.05343</v>
       </c>
       <c r="C56">
-        <v>96320637.03194539</v>
+        <v>1242536217.712095</v>
       </c>
       <c r="D56">
-        <v>1871432802.817061</v>
+        <v>24141483156.34009</v>
       </c>
       <c r="E56">
-        <v>121869483.0469566</v>
+        <v>1572116331.30574</v>
       </c>
       <c r="F56">
-        <v>1143126252.765097</v>
+        <v>14746328660.66976</v>
       </c>
       <c r="G56">
-        <v>3232749175.661061</v>
+        <v>41702464366.02769</v>
       </c>
       <c r="H56">
-        <v>3162928578.884078</v>
+        <v>40801778667.60461</v>
       </c>
       <c r="I56">
-        <v>995067901.6712375</v>
+        <v>12836375931.55896</v>
       </c>
       <c r="J56">
-        <v>285773691.9306706</v>
+        <v>3686480625.905651</v>
       </c>
       <c r="K56">
-        <v>245633402.9419672</v>
+        <v>3168670897.951377</v>
       </c>
       <c r="L56">
-        <v>117548183.7395482</v>
+        <v>1516371570.240172</v>
       </c>
       <c r="M56">
-        <v>4735467129.86716</v>
+        <v>61087525975.28636</v>
       </c>
       <c r="N56">
-        <v>1701852219.20478</v>
+        <v>21953893627.74167</v>
       </c>
       <c r="O56">
-        <v>11244271108.23944</v>
+        <v>145051097296.2888</v>
       </c>
       <c r="P56">
-        <v>15632909652.81937</v>
+        <v>201664534521.3699</v>
       </c>
       <c r="Q56">
-        <v>12657619880.95617</v>
+        <v>163283296464.3347</v>
       </c>
     </row>
   </sheetData>

--- a/Dados/table_PROD_BR_1_aux.xlsx
+++ b/Dados/table_PROD_BR_1_aux.xlsx
@@ -6595,16 +6595,16 @@
         <v>25500335910.41732</v>
       </c>
       <c r="E5">
-        <v>1828671088.378464</v>
+        <v>1828671088.378465</v>
       </c>
       <c r="F5">
-        <v>16491875896.77732</v>
+        <v>16491875896.77731</v>
       </c>
       <c r="G5">
-        <v>45102061471.54507</v>
+        <v>45102061471.54508</v>
       </c>
       <c r="H5">
-        <v>37860990289.89302</v>
+        <v>37860990289.89301</v>
       </c>
       <c r="I5">
         <v>9901793144.379772</v>
@@ -6619,7 +6619,7 @@
         <v>1143297319.1298</v>
       </c>
       <c r="M5">
-        <v>49351594841.58207</v>
+        <v>49351594841.58206</v>
       </c>
       <c r="N5">
         <v>19376161082.99007</v>
@@ -6674,7 +6674,7 @@
         <v>1180243432.991112</v>
       </c>
       <c r="M6">
-        <v>49353698876.39529</v>
+        <v>49353698876.39528</v>
       </c>
       <c r="N6">
         <v>19364880130.42182</v>
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>20213873064.74495</v>
+        <v>20213873064.74496</v>
       </c>
       <c r="C7">
         <v>1297704384.575644</v>
@@ -6705,7 +6705,7 @@
         <v>25330946224.34624</v>
       </c>
       <c r="E7">
-        <v>1820262522.952086</v>
+        <v>1820262522.952085</v>
       </c>
       <c r="F7">
         <v>16949298931.16366</v>
@@ -6763,7 +6763,7 @@
         <v>1888984369.385525</v>
       </c>
       <c r="F8">
-        <v>17150529968.38949</v>
+        <v>17150529968.38948</v>
       </c>
       <c r="G8">
         <v>45390208860.84328</v>
@@ -6790,7 +6790,7 @@
         <v>19265947990.01759</v>
       </c>
       <c r="O8">
-        <v>123926586842.8557</v>
+        <v>123926586842.8558</v>
       </c>
       <c r="P8">
         <v>189440992736.5869</v>
@@ -6851,7 +6851,7 @@
         <v>189860906188.6261</v>
       </c>
       <c r="Q9">
-        <v>149253193503.573</v>
+        <v>149253193503.5731</v>
       </c>
     </row>
     <row r="10">
@@ -6958,7 +6958,7 @@
         <v>125771878273.0713</v>
       </c>
       <c r="P11">
-        <v>190819961213.5298</v>
+        <v>190819961213.5297</v>
       </c>
       <c r="Q11">
         <v>150754156940.6597</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>19038392575.16111</v>
+        <v>19038392575.1611</v>
       </c>
       <c r="C12">
         <v>1187381291.048474</v>
@@ -6986,7 +6986,7 @@
         <v>17171559755.00381</v>
       </c>
       <c r="G12">
-        <v>45514414188.84455</v>
+        <v>45514414188.84454</v>
       </c>
       <c r="H12">
         <v>39041446209.08559</v>
@@ -6995,7 +6995,7 @@
         <v>9746260014.785564</v>
       </c>
       <c r="J12">
-        <v>2716660058.948135</v>
+        <v>2716660058.948136</v>
       </c>
       <c r="K12">
         <v>2596929710.787539</v>
@@ -7007,7 +7007,7 @@
         <v>51482756694.35182</v>
       </c>
       <c r="N12">
-        <v>19452748643.79586</v>
+        <v>19452748643.79585</v>
       </c>
       <c r="O12">
         <v>126179038441.4057</v>
@@ -7035,7 +7035,7 @@
         <v>25431485767.8939</v>
       </c>
       <c r="E13">
-        <v>1983482518.668012</v>
+        <v>1983482518.668013</v>
       </c>
       <c r="F13">
         <v>16928921289.51674</v>
@@ -7047,7 +7047,7 @@
         <v>38944973819.84943</v>
       </c>
       <c r="I13">
-        <v>9750425035.428564</v>
+        <v>9750425035.428566</v>
       </c>
       <c r="J13">
         <v>2716124229.973011</v>
@@ -7102,13 +7102,13 @@
         <v>38798220174.28568</v>
       </c>
       <c r="I14">
-        <v>9799534007.534437</v>
+        <v>9799534007.534435</v>
       </c>
       <c r="J14">
-        <v>2690200316.010154</v>
+        <v>2690200316.010153</v>
       </c>
       <c r="K14">
-        <v>2589726294.016053</v>
+        <v>2589726294.016054</v>
       </c>
       <c r="L14">
         <v>1193008478.812637</v>
@@ -7136,7 +7136,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>18206738454.27941</v>
+        <v>18206738454.2794</v>
       </c>
       <c r="C15">
         <v>1114940476.342304</v>
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>18099002766.18895</v>
+        <v>18099002766.18896</v>
       </c>
       <c r="C16">
         <v>1108698683.76366</v>
@@ -7206,10 +7206,10 @@
         <v>16011646248.97493</v>
       </c>
       <c r="G16">
-        <v>44236763961.81092</v>
+        <v>44236763961.81091</v>
       </c>
       <c r="H16">
-        <v>38928181948.50542</v>
+        <v>38928181948.50543</v>
       </c>
       <c r="I16">
         <v>9836241771.340107</v>
@@ -7261,10 +7261,10 @@
         <v>16025107516.23255</v>
       </c>
       <c r="G17">
-        <v>43613849913.22077</v>
+        <v>43613849913.22078</v>
       </c>
       <c r="H17">
-        <v>38774624231.71973</v>
+        <v>38774624231.71972</v>
       </c>
       <c r="I17">
         <v>9895216676.57711</v>
@@ -7304,7 +7304,7 @@
         <v>18059601248.90762</v>
       </c>
       <c r="C18">
-        <v>1039172301.05671</v>
+        <v>1039172301.056711</v>
       </c>
       <c r="D18">
         <v>23939433070.7238</v>
@@ -7359,7 +7359,7 @@
         <v>18015555209.98712</v>
       </c>
       <c r="C19">
-        <v>994416181.123834</v>
+        <v>994416181.1238341</v>
       </c>
       <c r="D19">
         <v>23241501632.26551</v>
@@ -7392,7 +7392,7 @@
         <v>52184970881.07328</v>
       </c>
       <c r="N19">
-        <v>19670938647.66234</v>
+        <v>19670938647.66233</v>
       </c>
       <c r="O19">
         <v>126206930921.4088</v>
@@ -7414,7 +7414,7 @@
         <v>17887462885.60826</v>
       </c>
       <c r="C20">
-        <v>951059644.1982085</v>
+        <v>951059644.1982086</v>
       </c>
       <c r="D20">
         <v>22623169365.79618</v>
@@ -7429,7 +7429,7 @@
         <v>41093229661.09625</v>
       </c>
       <c r="H20">
-        <v>37756670062.69271</v>
+        <v>37756670062.6927</v>
       </c>
       <c r="I20">
         <v>10043209777.75941</v>
@@ -7444,10 +7444,10 @@
         <v>1143166265.961935</v>
       </c>
       <c r="M20">
-        <v>52132359994.97477</v>
+        <v>52132359994.97478</v>
       </c>
       <c r="N20">
-        <v>19756577586.3387</v>
+        <v>19756577586.33869</v>
       </c>
       <c r="O20">
         <v>125767404727.2157</v>
@@ -7469,7 +7469,7 @@
         <v>17701607463.92884</v>
       </c>
       <c r="C21">
-        <v>941297800.7328603</v>
+        <v>941297800.7328604</v>
       </c>
       <c r="D21">
         <v>22071362119.42105</v>
@@ -7484,7 +7484,7 @@
         <v>40061643590.58768</v>
       </c>
       <c r="H21">
-        <v>37629747584.25373</v>
+        <v>37629747584.25374</v>
       </c>
       <c r="I21">
         <v>10090576563.77076</v>
@@ -7551,7 +7551,7 @@
         <v>2474630586.490711</v>
       </c>
       <c r="L22">
-        <v>1171804969.234686</v>
+        <v>1171804969.234685</v>
       </c>
       <c r="M22">
         <v>52227037995.42223</v>
@@ -7609,7 +7609,7 @@
         <v>1182522751.43487</v>
       </c>
       <c r="M23">
-        <v>52500451317.27317</v>
+        <v>52500451317.27318</v>
       </c>
       <c r="N23">
         <v>19673912973.51068</v>
@@ -7621,7 +7621,7 @@
         <v>182032326146.206</v>
       </c>
       <c r="Q23">
-        <v>144098156094.0652</v>
+        <v>144098156094.0651</v>
       </c>
     </row>
     <row r="24">
@@ -7634,10 +7634,10 @@
         <v>16927431915.69802</v>
       </c>
       <c r="C24">
-        <v>896012257.0326155</v>
+        <v>896012257.0326157</v>
       </c>
       <c r="D24">
-        <v>21860781140.68818</v>
+        <v>21860781140.68819</v>
       </c>
       <c r="E24">
         <v>1779238756.246729</v>
@@ -7664,7 +7664,7 @@
         <v>1193902963.863768</v>
       </c>
       <c r="M24">
-        <v>52937632292.23721</v>
+        <v>52937632292.23722</v>
       </c>
       <c r="N24">
         <v>19638123453.41255</v>
@@ -7713,7 +7713,7 @@
         <v>2595428008.722618</v>
       </c>
       <c r="K25">
-        <v>2501926161.627796</v>
+        <v>2501926161.627797</v>
       </c>
       <c r="L25">
         <v>1170509978.590287</v>
@@ -7774,7 +7774,7 @@
         <v>1146500674.424258</v>
       </c>
       <c r="M26">
-        <v>54197738758.38549</v>
+        <v>54197738758.3855</v>
       </c>
       <c r="N26">
         <v>19803528248.92261</v>
@@ -7799,7 +7799,7 @@
         <v>16628080038.10294</v>
       </c>
       <c r="C27">
-        <v>912156649.7062346</v>
+        <v>912156649.7062347</v>
       </c>
       <c r="D27">
         <v>22236186458.83966</v>
@@ -7811,7 +7811,7 @@
         <v>14047949085.86384</v>
       </c>
       <c r="G27">
-        <v>38971933789.99461</v>
+        <v>38971933789.99462</v>
       </c>
       <c r="H27">
         <v>37821655950.55862</v>
@@ -7878,7 +7878,7 @@
         <v>2586418065.031275</v>
       </c>
       <c r="K28">
-        <v>2518439828.065603</v>
+        <v>2518439828.065602</v>
       </c>
       <c r="L28">
         <v>1170996843.323093</v>
@@ -7912,7 +7912,7 @@
         <v>916588116.9325998</v>
       </c>
       <c r="D29">
-        <v>22223564315.40615</v>
+        <v>22223564315.40616</v>
       </c>
       <c r="E29">
         <v>1740458282.775841</v>
@@ -7964,13 +7964,13 @@
         <v>16658132120.16155</v>
       </c>
       <c r="C30">
-        <v>930178275.8570021</v>
+        <v>930178275.857002</v>
       </c>
       <c r="D30">
         <v>22274341474.65122</v>
       </c>
       <c r="E30">
-        <v>1733091375.936368</v>
+        <v>1733091375.936367</v>
       </c>
       <c r="F30">
         <v>13915221970.4857</v>
@@ -7994,7 +7994,7 @@
         <v>1202649337.548414</v>
       </c>
       <c r="M30">
-        <v>55611056500.97121</v>
+        <v>55611056500.97122</v>
       </c>
       <c r="N30">
         <v>20174207408.03241</v>
@@ -8019,7 +8019,7 @@
         <v>16775558348.63561</v>
       </c>
       <c r="C31">
-        <v>938095706.9221056</v>
+        <v>938095706.9221053</v>
       </c>
       <c r="D31">
         <v>22364730391.36444</v>
@@ -8043,13 +8043,13 @@
         <v>2730216274.273941</v>
       </c>
       <c r="K31">
-        <v>2573784147.56108</v>
+        <v>2573784147.561079</v>
       </c>
       <c r="L31">
         <v>1198747187.713748</v>
       </c>
       <c r="M31">
-        <v>56258452174.94212</v>
+        <v>56258452174.94211</v>
       </c>
       <c r="N31">
         <v>20231488974.54813</v>
@@ -8061,7 +8061,7 @@
         <v>187610755439.8834</v>
       </c>
       <c r="Q31">
-        <v>149404960928.986</v>
+        <v>149404960928.9859</v>
       </c>
     </row>
     <row r="32">
@@ -8101,7 +8101,7 @@
         <v>2587838493.933214</v>
       </c>
       <c r="L32">
-        <v>1191931674.996816</v>
+        <v>1191931674.996817</v>
       </c>
       <c r="M32">
         <v>56795818166.39054</v>
@@ -8129,7 +8129,7 @@
         <v>16651008550.92702</v>
       </c>
       <c r="C33">
-        <v>955530027.7249157</v>
+        <v>955530027.7249156</v>
       </c>
       <c r="D33">
         <v>22646548858.28505</v>
@@ -8141,7 +8141,7 @@
         <v>13927071429.31082</v>
       </c>
       <c r="G33">
-        <v>39337356933.9111</v>
+        <v>39337356933.91111</v>
       </c>
       <c r="H33">
         <v>38326892917.213</v>
@@ -8150,10 +8150,10 @@
         <v>11010298570.76664</v>
       </c>
       <c r="J33">
-        <v>2784139013.543914</v>
+        <v>2784139013.543915</v>
       </c>
       <c r="K33">
-        <v>2592350800.67647</v>
+        <v>2592350800.676471</v>
       </c>
       <c r="L33">
         <v>1186635224.256137</v>
@@ -8168,7 +8168,7 @@
         <v>133528130751.091</v>
       </c>
       <c r="P33">
-        <v>189516496235.9292</v>
+        <v>189516496235.9291</v>
       </c>
       <c r="Q33">
         <v>151379659563.0608</v>
@@ -8184,7 +8184,7 @@
         <v>16613043171.83972</v>
       </c>
       <c r="C34">
-        <v>978957813.9693129</v>
+        <v>978957813.969313</v>
       </c>
       <c r="D34">
         <v>22766284586.11303</v>
@@ -8193,7 +8193,7 @@
         <v>1835386355.694535</v>
       </c>
       <c r="F34">
-        <v>13872135201.42998</v>
+        <v>13872135201.42999</v>
       </c>
       <c r="G34">
         <v>39452763957.20686</v>
@@ -8214,7 +8214,7 @@
         <v>1172342282.898793</v>
       </c>
       <c r="M34">
-        <v>57476358152.99423</v>
+        <v>57476358152.99422</v>
       </c>
       <c r="N34">
         <v>20429798028.32776</v>
@@ -8251,16 +8251,16 @@
         <v>13229622484.00649</v>
       </c>
       <c r="G35">
-        <v>38227844765.96281</v>
+        <v>38227844765.96282</v>
       </c>
       <c r="H35">
-        <v>37023317472.76691</v>
+        <v>37023317472.7669</v>
       </c>
       <c r="I35">
         <v>10809816553.08709</v>
       </c>
       <c r="J35">
-        <v>2854961829.388147</v>
+        <v>2854961829.388146</v>
       </c>
       <c r="K35">
         <v>2533277876.588948</v>
@@ -8272,7 +8272,7 @@
         <v>55302438713.33245</v>
       </c>
       <c r="N35">
-        <v>20720628022.17186</v>
+        <v>20720628022.17185</v>
       </c>
       <c r="O35">
         <v>130392324838.1012</v>
@@ -8309,7 +8309,7 @@
         <v>37019967003.09708</v>
       </c>
       <c r="H36">
-        <v>35826181577.43586</v>
+        <v>35826181577.43587</v>
       </c>
       <c r="I36">
         <v>10414989949.37364</v>
@@ -8404,7 +8404,7 @@
         <v>16703029818.83286</v>
       </c>
       <c r="C38">
-        <v>915359095.8331255</v>
+        <v>915359095.8331254</v>
       </c>
       <c r="D38">
         <v>20885070455.41911</v>
@@ -8422,7 +8422,7 @@
         <v>34069114387.24327</v>
       </c>
       <c r="I38">
-        <v>9811317077.691938</v>
+        <v>9811317077.69194</v>
       </c>
       <c r="J38">
         <v>2914755711.178117</v>
@@ -8440,7 +8440,7 @@
         <v>20979007988.11147</v>
       </c>
       <c r="O38">
-        <v>119605909721.6695</v>
+        <v>119605909721.6694</v>
       </c>
       <c r="P38">
         <v>171922604045.637</v>
@@ -8477,7 +8477,7 @@
         <v>34545739493.7149</v>
       </c>
       <c r="I39">
-        <v>9881885852.227034</v>
+        <v>9881885852.227036</v>
       </c>
       <c r="J39">
         <v>3040135659.272073</v>
@@ -8514,7 +8514,7 @@
         <v>17590508421.27995</v>
       </c>
       <c r="C40">
-        <v>939501835.343887</v>
+        <v>939501835.3438869</v>
       </c>
       <c r="D40">
         <v>21792628772.56895</v>
@@ -8569,7 +8569,7 @@
         <v>17801653402.16003</v>
       </c>
       <c r="C41">
-        <v>976089304.8338829</v>
+        <v>976089304.8338828</v>
       </c>
       <c r="D41">
         <v>22283692325.97126</v>
@@ -8599,7 +8599,7 @@
         <v>1211430611.43069</v>
       </c>
       <c r="M41">
-        <v>52272630715.0512</v>
+        <v>52272630715.05121</v>
       </c>
       <c r="N41">
         <v>20566668829.14572</v>
@@ -8627,7 +8627,7 @@
         <v>1000874390.924293</v>
       </c>
       <c r="D42">
-        <v>22737039049.65861</v>
+        <v>22737039049.65862</v>
       </c>
       <c r="E42">
         <v>1447776269.359029</v>
@@ -8636,16 +8636,16 @@
         <v>14515496864.4579</v>
       </c>
       <c r="G42">
-        <v>39701186574.39983</v>
+        <v>39701186574.39984</v>
       </c>
       <c r="H42">
-        <v>37838781652.1123</v>
+        <v>37838781652.11231</v>
       </c>
       <c r="I42">
         <v>10661824978.01728</v>
       </c>
       <c r="J42">
-        <v>3348701183.801884</v>
+        <v>3348701183.801883</v>
       </c>
       <c r="K42">
         <v>2787907670.383315</v>
@@ -8666,7 +8666,7 @@
         <v>188076782871.3251</v>
       </c>
       <c r="Q42">
-        <v>148522461895.3973</v>
+        <v>148522461895.3974</v>
       </c>
     </row>
     <row r="43">
@@ -8694,7 +8694,7 @@
         <v>40787001790.90876</v>
       </c>
       <c r="H43">
-        <v>39192506774.417</v>
+        <v>39192506774.41701</v>
       </c>
       <c r="I43">
         <v>10942421406.28346</v>
@@ -8709,7 +8709,7 @@
         <v>1255924026.034806</v>
       </c>
       <c r="M43">
-        <v>55942267079.65947</v>
+        <v>55942267079.65946</v>
       </c>
       <c r="N43">
         <v>20660432043.97229</v>
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="B44">
-        <v>17624990023.73478</v>
+        <v>17624990023.73479</v>
       </c>
       <c r="C44">
         <v>1070241926.522674</v>
@@ -8798,7 +8798,7 @@
         <v>1528142403.99602</v>
       </c>
       <c r="F45">
-        <v>15033652892.91184</v>
+        <v>15033652892.91185</v>
       </c>
       <c r="G45">
         <v>41353940947.67278</v>
@@ -8819,7 +8819,7 @@
         <v>1327654305.886283</v>
       </c>
       <c r="M45">
-        <v>58109476751.15225</v>
+        <v>58109476751.15224</v>
       </c>
       <c r="N45">
         <v>21399601415.02355</v>
@@ -8841,7 +8841,7 @@
         </is>
       </c>
       <c r="B46">
-        <v>17183034700.5258</v>
+        <v>17183034700.52579</v>
       </c>
       <c r="C46">
         <v>1124006647.736232</v>
@@ -8899,7 +8899,7 @@
         <v>16986159380.43521</v>
       </c>
       <c r="C47">
-        <v>1126934234.286795</v>
+        <v>1126934234.286794</v>
       </c>
       <c r="D47">
         <v>23774835189.13725</v>
@@ -8920,7 +8920,7 @@
         <v>11734511189.01456</v>
       </c>
       <c r="J47">
-        <v>3475225245.53676</v>
+        <v>3475225245.536761</v>
       </c>
       <c r="K47">
         <v>3129808959.211186</v>
@@ -8984,7 +8984,7 @@
         <v>1358691136.009408</v>
       </c>
       <c r="M48">
-        <v>59380873477.77013</v>
+        <v>59380873477.77014</v>
       </c>
       <c r="N48">
         <v>21812202335.30731</v>
@@ -9018,7 +9018,7 @@
         <v>1552128561.777056</v>
       </c>
       <c r="F49">
-        <v>14624281297.78998</v>
+        <v>14624281297.78997</v>
       </c>
       <c r="G49">
         <v>41029796547.27984</v>
@@ -9030,7 +9030,7 @@
         <v>11961148658.27971</v>
       </c>
       <c r="J49">
-        <v>3620364389.85403</v>
+        <v>3620364389.854029</v>
       </c>
       <c r="K49">
         <v>3166684697.169866</v>
@@ -9039,7 +9039,7 @@
         <v>1388677427.965027</v>
       </c>
       <c r="M49">
-        <v>59854901822.34332</v>
+        <v>59854901822.34333</v>
       </c>
       <c r="N49">
         <v>21853151196.26885</v>
@@ -9097,7 +9097,7 @@
         <v>60477386557.21686</v>
       </c>
       <c r="N50">
-        <v>21985463798.66201</v>
+        <v>21985463798.66202</v>
       </c>
       <c r="O50">
         <v>143300009419.846</v>
@@ -9143,19 +9143,19 @@
         <v>3790544929.563651</v>
       </c>
       <c r="K51">
-        <v>3150643950.264229</v>
+        <v>3150643950.26423</v>
       </c>
       <c r="L51">
         <v>1456346845.674927</v>
       </c>
       <c r="M51">
-        <v>61061195805.18638</v>
+        <v>61061195805.18639</v>
       </c>
       <c r="N51">
         <v>22227836887.76812</v>
       </c>
       <c r="O51">
-        <v>144764389391.2756</v>
+        <v>144764389391.2757</v>
       </c>
       <c r="P51">
         <v>202423423610.3785</v>
@@ -9238,7 +9238,7 @@
         <v>1587323861.702661</v>
       </c>
       <c r="F53">
-        <v>15284201273.91507</v>
+        <v>15284201273.91506</v>
       </c>
       <c r="G53">
         <v>42531281534.19826</v>
@@ -9247,10 +9247,10 @@
         <v>41267642980.01319</v>
       </c>
       <c r="I53">
-        <v>12768323628.94544</v>
+        <v>12768323628.94545</v>
       </c>
       <c r="J53">
-        <v>3819906957.302059</v>
+        <v>3819906957.302058</v>
       </c>
       <c r="K53">
         <v>3131507064.964739</v>
@@ -9259,7 +9259,7 @@
         <v>1476643904.386358</v>
       </c>
       <c r="M53">
-        <v>62211595260.76612</v>
+        <v>62211595260.76611</v>
       </c>
       <c r="N53">
         <v>22754307132.31181</v>
@@ -9320,7 +9320,7 @@
         <v>22957725910.93829</v>
       </c>
       <c r="O54">
-        <v>148489270064.4729</v>
+        <v>148489270064.4728</v>
       </c>
       <c r="P54">
         <v>206884112175.1972</v>
@@ -9406,7 +9406,7 @@
         <v>15365532729.34004</v>
       </c>
       <c r="G56">
-        <v>43316286644.92017</v>
+        <v>43316286644.92018</v>
       </c>
       <c r="H56">
         <v>41894910928.97337</v>
@@ -9424,7 +9424,7 @@
         <v>1555958456.173986</v>
       </c>
       <c r="M56">
-        <v>63116080662.22735</v>
+        <v>63116080662.22734</v>
       </c>
       <c r="N56">
         <v>23212411835.78962</v>
@@ -9436,7 +9436,7 @@
         <v>208907449622.7957</v>
       </c>
       <c r="Q56">
-        <v>168666570665.2965</v>
+        <v>168666570665.2964</v>
       </c>
     </row>
   </sheetData>
@@ -9603,13 +9603,13 @@
         <v>18020502532.59354</v>
       </c>
       <c r="O5">
-        <v>117814997835.2905</v>
+        <v>117814997835.2904</v>
       </c>
       <c r="P5">
         <v>179984283366.9073</v>
       </c>
       <c r="Q5">
-        <v>141567230350.6124</v>
+        <v>141567230350.6125</v>
       </c>
     </row>
     <row r="6">
@@ -9643,7 +9643,7 @@
         <v>9543325854.02549</v>
       </c>
       <c r="J6">
-        <v>2563105603.029383</v>
+        <v>2563105603.029384</v>
       </c>
       <c r="K6">
         <v>2439190916.36062</v>
@@ -9661,10 +9661,10 @@
         <v>117810990050.4439</v>
       </c>
       <c r="P6">
-        <v>179776699357.9402</v>
+        <v>179776699357.9401</v>
       </c>
       <c r="Q6">
-        <v>141662102963.8857</v>
+        <v>141662102963.8858</v>
       </c>
     </row>
     <row r="7">
@@ -9692,7 +9692,7 @@
         <v>43136274296.18269</v>
       </c>
       <c r="H7">
-        <v>36956923892.84189</v>
+        <v>36956923892.84188</v>
       </c>
       <c r="I7">
         <v>9656069953.129116</v>
@@ -9707,13 +9707,13 @@
         <v>1150630311.771242</v>
       </c>
       <c r="M7">
-        <v>47617079658.58068</v>
+        <v>47617079658.58069</v>
       </c>
       <c r="N7">
         <v>18031814496.03893</v>
       </c>
       <c r="O7">
-        <v>118463656583.1319</v>
+        <v>118463656583.132</v>
       </c>
       <c r="P7">
         <v>180515485670.5788</v>
@@ -9729,7 +9729,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>18920006147.48845</v>
+        <v>18920006147.48844</v>
       </c>
       <c r="C8">
         <v>1204072827.357424</v>
@@ -9747,7 +9747,7 @@
         <v>43270341745.19402</v>
       </c>
       <c r="H8">
-        <v>37402056744.06835</v>
+        <v>37402056744.06834</v>
       </c>
       <c r="I8">
         <v>9712676459.086227</v>
@@ -9771,7 +9771,7 @@
         <v>119263335386.6337</v>
       </c>
       <c r="P8">
-        <v>181453683279.3162</v>
+        <v>181453683279.3161</v>
       </c>
       <c r="Q8">
         <v>143304265593.1956</v>
@@ -9826,7 +9826,7 @@
         <v>120322539852.9553</v>
       </c>
       <c r="P9">
-        <v>182817289881.6443</v>
+        <v>182817289881.6442</v>
       </c>
       <c r="Q9">
         <v>144399931203.4523</v>
@@ -9860,7 +9860,7 @@
         <v>38241651944.6187</v>
       </c>
       <c r="I10">
-        <v>9651161853.218151</v>
+        <v>9651161853.218149</v>
       </c>
       <c r="J10">
         <v>2628206316.62362</v>
@@ -9915,7 +9915,7 @@
         <v>38341904762.58057</v>
       </c>
       <c r="I11">
-        <v>9576353075.063463</v>
+        <v>9576353075.063465</v>
       </c>
       <c r="J11">
         <v>2649028390.127299</v>
@@ -9936,7 +9936,7 @@
         <v>122225882610.3746</v>
       </c>
       <c r="P11">
-        <v>184846088433.6582</v>
+        <v>184846088433.6581</v>
       </c>
       <c r="Q11">
         <v>146652683456.0728</v>
@@ -9991,7 +9991,7 @@
         <v>122488515382.3995</v>
       </c>
       <c r="P12">
-        <v>184554650500.6015</v>
+        <v>184554650500.6014</v>
       </c>
       <c r="Q12">
         <v>146807326571.6311</v>
@@ -10016,7 +10016,7 @@
         <v>1929907245.437176</v>
       </c>
       <c r="F13">
-        <v>16223060311.98546</v>
+        <v>16223060311.98545</v>
       </c>
       <c r="G13">
         <v>43806272108.70052</v>
@@ -10153,7 +10153,7 @@
         <v>18437656085.54832</v>
       </c>
       <c r="O15">
-        <v>122949251009.5979</v>
+        <v>122949251009.598</v>
       </c>
       <c r="P15">
         <v>183344637171.8399</v>
@@ -10242,7 +10242,7 @@
         <v>41894008720.93248</v>
       </c>
       <c r="H17">
-        <v>37853152888.25375</v>
+        <v>37853152888.25374</v>
       </c>
       <c r="I17">
         <v>9566778472.105345</v>
@@ -10260,7 +10260,7 @@
         <v>50744166789.65851</v>
       </c>
       <c r="N17">
-        <v>18489714971.14239</v>
+        <v>18489714971.14238</v>
       </c>
       <c r="O17">
         <v>122787359113.8085</v>
@@ -10300,7 +10300,7 @@
         <v>37595720002.92972</v>
       </c>
       <c r="I18">
-        <v>9564844583.710707</v>
+        <v>9564844583.710709</v>
       </c>
       <c r="J18">
         <v>2554372209.714692</v>
@@ -10312,7 +10312,7 @@
         <v>1172392148.080617</v>
       </c>
       <c r="M18">
-        <v>50795305002.8155</v>
+        <v>50795305002.81549</v>
       </c>
       <c r="N18">
         <v>18554815061.43526</v>
@@ -10337,7 +10337,7 @@
         <v>17292613636.42466</v>
       </c>
       <c r="C19">
-        <v>958857119.5584751</v>
+        <v>958857119.5584753</v>
       </c>
       <c r="D19">
         <v>22415942454.71494</v>
@@ -10355,7 +10355,7 @@
         <v>37309784829.03735</v>
       </c>
       <c r="I19">
-        <v>9614665560.18297</v>
+        <v>9614665560.182972</v>
       </c>
       <c r="J19">
         <v>2522954425.360423</v>
@@ -10367,7 +10367,7 @@
         <v>1140030638.306925</v>
       </c>
       <c r="M19">
-        <v>50728001088.10592</v>
+        <v>50728001088.10593</v>
       </c>
       <c r="N19">
         <v>18638846827.61159</v>
@@ -10425,10 +10425,10 @@
         <v>50687821522.61282</v>
       </c>
       <c r="N20">
-        <v>18743339434.66027</v>
+        <v>18743339434.66026</v>
       </c>
       <c r="O20">
-        <v>121882230307.9401</v>
+        <v>121882230307.9402</v>
       </c>
       <c r="P20">
         <v>178738995824.3219</v>
@@ -10450,7 +10450,7 @@
         <v>902507834.0971766</v>
       </c>
       <c r="D21">
-        <v>21279132187.4132</v>
+        <v>21279132187.41321</v>
       </c>
       <c r="E21">
         <v>1615563962.069464</v>
@@ -10468,7 +10468,7 @@
         <v>9713725629.626715</v>
       </c>
       <c r="J21">
-        <v>2482026662.461072</v>
+        <v>2482026662.461073</v>
       </c>
       <c r="K21">
         <v>2363670708.477801</v>
@@ -10502,7 +10502,7 @@
         <v>16819290837.8712</v>
       </c>
       <c r="C22">
-        <v>890597002.8498145</v>
+        <v>890597002.8498144</v>
       </c>
       <c r="D22">
         <v>21035296822.09524</v>
@@ -10517,7 +10517,7 @@
         <v>37911872124.87093</v>
       </c>
       <c r="H22">
-        <v>36500148909.70796</v>
+        <v>36500148909.70797</v>
       </c>
       <c r="I22">
         <v>9712125566.934498</v>
@@ -10532,7 +10532,7 @@
         <v>1139423164.570969</v>
       </c>
       <c r="M22">
-        <v>50691219692.32458</v>
+        <v>50691219692.32459</v>
       </c>
       <c r="N22">
         <v>18605268369.40041</v>
@@ -10587,7 +10587,7 @@
         <v>1146499107.731523</v>
       </c>
       <c r="M23">
-        <v>50836185277.73942</v>
+        <v>50836185277.73941</v>
       </c>
       <c r="N23">
         <v>18514705817.04206</v>
@@ -10612,13 +10612,13 @@
         <v>16315579358.8099</v>
       </c>
       <c r="C24">
-        <v>850430172.1999617</v>
+        <v>850430172.1999618</v>
       </c>
       <c r="D24">
         <v>20971303594.57132</v>
       </c>
       <c r="E24">
-        <v>1708493742.209639</v>
+        <v>1708493742.20964</v>
       </c>
       <c r="F24">
         <v>13722266142.98206</v>
@@ -10645,13 +10645,13 @@
         <v>51185266762.57011</v>
       </c>
       <c r="N24">
-        <v>18450859305.28901</v>
+        <v>18450859305.28902</v>
       </c>
       <c r="O24">
         <v>121865728525.6237</v>
       </c>
       <c r="P24">
-        <v>175433801536.3965</v>
+        <v>175433801536.3966</v>
       </c>
       <c r="Q24">
         <v>139509109054.7337</v>
@@ -10667,7 +10667,7 @@
         <v>16111246795.5241</v>
       </c>
       <c r="C25">
-        <v>847855759.81745</v>
+        <v>847855759.8174502</v>
       </c>
       <c r="D25">
         <v>21069573776.0593</v>
@@ -10685,7 +10685,7 @@
         <v>36398671729.74137</v>
       </c>
       <c r="I25">
-        <v>9712624342.935652</v>
+        <v>9712624342.93565</v>
       </c>
       <c r="J25">
         <v>2495893531.644586</v>
@@ -10697,7 +10697,7 @@
         <v>1127495392.673587</v>
       </c>
       <c r="M25">
-        <v>51610901113.59994</v>
+        <v>51610901113.59993</v>
       </c>
       <c r="N25">
         <v>18417000456.25773</v>
@@ -10719,7 +10719,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>15971737042.45819</v>
+        <v>15971737042.45818</v>
       </c>
       <c r="C26">
         <v>840566318.9801972</v>
@@ -10740,16 +10740,16 @@
         <v>36421986592.51128</v>
       </c>
       <c r="I26">
-        <v>9746579528.406694</v>
+        <v>9746579528.406693</v>
       </c>
       <c r="J26">
         <v>2469985133.858018</v>
       </c>
       <c r="K26">
-        <v>2341316077.050507</v>
+        <v>2341316077.050508</v>
       </c>
       <c r="L26">
-        <v>1097230774.628976</v>
+        <v>1097230774.628977</v>
       </c>
       <c r="M26">
         <v>51923967671.98058</v>
@@ -10795,7 +10795,7 @@
         <v>36484985843.82169</v>
       </c>
       <c r="I27">
-        <v>9785011422.202295</v>
+        <v>9785011422.202297</v>
       </c>
       <c r="J27">
         <v>2478473679.730859</v>
@@ -10807,7 +10807,7 @@
         <v>1104782138.088013</v>
       </c>
       <c r="M27">
-        <v>52257875170.3471</v>
+        <v>52257875170.34709</v>
       </c>
       <c r="N27">
         <v>18523974019.85802</v>
@@ -10853,7 +10853,7 @@
         <v>9805666138.308535</v>
       </c>
       <c r="J28">
-        <v>2481807963.591745</v>
+        <v>2481807963.591744</v>
       </c>
       <c r="K28">
         <v>2370695846.589991</v>
@@ -10911,7 +10911,7 @@
         <v>2516807196.136624</v>
       </c>
       <c r="K29">
-        <v>2370083341.25854</v>
+        <v>2370083341.258539</v>
       </c>
       <c r="L29">
         <v>1138911744.094658</v>
@@ -10920,7 +10920,7 @@
         <v>53020397490.11121</v>
       </c>
       <c r="N29">
-        <v>18703547455.0863</v>
+        <v>18703547455.08631</v>
       </c>
       <c r="O29">
         <v>124300906927.6393</v>
@@ -10948,7 +10948,7 @@
         <v>21185800821.28258</v>
       </c>
       <c r="E30">
-        <v>1663897256.559724</v>
+        <v>1663897256.559723</v>
       </c>
       <c r="F30">
         <v>13141012500.52412</v>
@@ -10994,7 +10994,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>16106469965.48123</v>
+        <v>16106469965.48122</v>
       </c>
       <c r="C31">
         <v>885094382.9301633</v>
@@ -11003,7 +11003,7 @@
         <v>21233204341.67599</v>
       </c>
       <c r="E31">
-        <v>1659645097.707129</v>
+        <v>1659645097.70713</v>
       </c>
       <c r="F31">
         <v>13135367120.89908</v>
@@ -11052,13 +11052,13 @@
         <v>16027502521.71444</v>
       </c>
       <c r="C32">
-        <v>886081316.190828</v>
+        <v>886081316.1908281</v>
       </c>
       <c r="D32">
         <v>21362823722.77228</v>
       </c>
       <c r="E32">
-        <v>1698325785.045262</v>
+        <v>1698325785.045261</v>
       </c>
       <c r="F32">
         <v>13173732882.7814</v>
@@ -11110,7 +11110,7 @@
         <v>909517015.4789076</v>
       </c>
       <c r="D33">
-        <v>21566783598.233</v>
+        <v>21566783598.23301</v>
       </c>
       <c r="E33">
         <v>1733414800.181479</v>
@@ -11128,7 +11128,7 @@
         <v>10523604339.17269</v>
       </c>
       <c r="J33">
-        <v>2664763357.771806</v>
+        <v>2664763357.771807</v>
       </c>
       <c r="K33">
         <v>2465142691.7821</v>
@@ -11162,7 +11162,7 @@
         <v>15946300036.83747</v>
       </c>
       <c r="C34">
-        <v>920195238.7682449</v>
+        <v>920195238.768245</v>
       </c>
       <c r="D34">
         <v>21480743101.76479</v>
@@ -11195,7 +11195,7 @@
         <v>54557898674.25596</v>
       </c>
       <c r="N34">
-        <v>18729752677.50683</v>
+        <v>18729752677.50684</v>
       </c>
       <c r="O34">
         <v>126773104993.5779</v>
@@ -11204,7 +11204,7 @@
         <v>179912346495.5574</v>
       </c>
       <c r="Q34">
-        <v>144123816437.4241</v>
+        <v>144123816437.4242</v>
       </c>
     </row>
     <row r="35">
@@ -11229,7 +11229,7 @@
         <v>12006241287.57778</v>
       </c>
       <c r="G35">
-        <v>34658537033.4959</v>
+        <v>34658537033.49589</v>
       </c>
       <c r="H35">
         <v>34064191320.06437</v>
@@ -11272,7 +11272,7 @@
         <v>15503465974.57507</v>
       </c>
       <c r="C36">
-        <v>882604234.1559235</v>
+        <v>882604234.1559234</v>
       </c>
       <c r="D36">
         <v>19270139492.5628</v>
@@ -11327,7 +11327,7 @@
         <v>15672976623.49238</v>
       </c>
       <c r="C37">
-        <v>849490701.6514367</v>
+        <v>849490701.6514368</v>
       </c>
       <c r="D37">
         <v>18897602980.93084</v>
@@ -11385,7 +11385,7 @@
         <v>841243168.5638647</v>
       </c>
       <c r="D38">
-        <v>18923606644.51632</v>
+        <v>18923606644.51631</v>
       </c>
       <c r="E38">
         <v>1438390108.423981</v>
@@ -11452,7 +11452,7 @@
         <v>34418955105.20272</v>
       </c>
       <c r="H39">
-        <v>33015061599.68063</v>
+        <v>33015061599.68064</v>
       </c>
       <c r="I39">
         <v>9322844998.676483</v>
@@ -11467,7 +11467,7 @@
         <v>1100640275.075819</v>
       </c>
       <c r="M39">
-        <v>45488918716.69349</v>
+        <v>45488918716.69348</v>
       </c>
       <c r="N39">
         <v>19145869505.37614</v>
@@ -11547,7 +11547,7 @@
         <v>17262269248.73314</v>
       </c>
       <c r="C41">
-        <v>946356980.1771892</v>
+        <v>946356980.1771894</v>
       </c>
       <c r="D41">
         <v>21431786797.80336</v>
@@ -11559,7 +11559,7 @@
         <v>13411634572.05729</v>
       </c>
       <c r="G41">
-        <v>37185610433.91837</v>
+        <v>37185610433.91836</v>
       </c>
       <c r="H41">
         <v>35597581120.49689</v>
@@ -11571,7 +11571,7 @@
         <v>3171735835.16512</v>
       </c>
       <c r="K41">
-        <v>2683206448.596677</v>
+        <v>2683206448.596676</v>
       </c>
       <c r="L41">
         <v>1159609489.508039</v>
@@ -11589,7 +11589,7 @@
         <v>176744670031.813</v>
       </c>
       <c r="Q41">
-        <v>138832515686.1622</v>
+        <v>138832515686.1621</v>
       </c>
     </row>
     <row r="42">
@@ -11669,7 +11669,7 @@
         <v>14258967645.74973</v>
       </c>
       <c r="G43">
-        <v>39170290149.86794</v>
+        <v>39170290149.86795</v>
       </c>
       <c r="H43">
         <v>38157326774.35533</v>
@@ -11727,7 +11727,7 @@
         <v>39621204021.39329</v>
       </c>
       <c r="H44">
-        <v>38948764527.52218</v>
+        <v>38948764527.52219</v>
       </c>
       <c r="I44">
         <v>10768241570.27328</v>
@@ -11745,13 +11745,13 @@
         <v>55542712881.325</v>
       </c>
       <c r="N44">
-        <v>19975304250.68728</v>
+        <v>19975304250.68729</v>
       </c>
       <c r="O44">
         <v>132757274481.679</v>
       </c>
       <c r="P44">
-        <v>189380384644.6236</v>
+        <v>189380384644.6235</v>
       </c>
       <c r="Q44">
         <v>151155701824.6298</v>
@@ -11779,7 +11779,7 @@
         <v>14333014830.16583</v>
       </c>
       <c r="G45">
-        <v>39620780038.10075</v>
+        <v>39620780038.10074</v>
       </c>
       <c r="H45">
         <v>39330819069.82236</v>
@@ -11889,7 +11889,7 @@
         <v>14158220153.53305</v>
       </c>
       <c r="G47">
-        <v>39594148289.41138</v>
+        <v>39594148289.41137</v>
       </c>
       <c r="H47">
         <v>39506569334.33938</v>
@@ -12045,7 +12045,7 @@
         <v>1156024951.309321</v>
       </c>
       <c r="D50">
-        <v>22794974845.54592</v>
+        <v>22794974845.54593</v>
       </c>
       <c r="E50">
         <v>1507932404.249862</v>
@@ -12069,7 +12069,7 @@
         <v>3044485959.333892</v>
       </c>
       <c r="L50">
-        <v>1376233581.60107</v>
+        <v>1376233581.601069</v>
       </c>
       <c r="M50">
         <v>58314408800.91686</v>
@@ -12112,7 +12112,7 @@
         <v>39852071163.51199</v>
       </c>
       <c r="H51">
-        <v>39568137975.18963</v>
+        <v>39568137975.18962</v>
       </c>
       <c r="I51">
         <v>11960894614.31232</v>
@@ -12121,10 +12121,10 @@
         <v>3683516898.424817</v>
       </c>
       <c r="K51">
-        <v>3039623117.985701</v>
+        <v>3039623117.985702</v>
       </c>
       <c r="L51">
-        <v>1410017752.321504</v>
+        <v>1410017752.321503</v>
       </c>
       <c r="M51">
         <v>58892072446.02164</v>
@@ -12243,7 +12243,7 @@
         <v>21486550104.02227</v>
       </c>
       <c r="O53">
-        <v>142333505530.7543</v>
+        <v>142333505530.7542</v>
       </c>
       <c r="P53">
         <v>198384000169.8458</v>
@@ -12262,7 +12262,7 @@
         <v>15036284511.92715</v>
       </c>
       <c r="C54">
-        <v>1195751045.031574</v>
+        <v>1195751045.031573</v>
       </c>
       <c r="D54">
         <v>23786858504.27003</v>
@@ -12292,7 +12292,7 @@
         <v>1458649833.275253</v>
       </c>
       <c r="M54">
-        <v>60531037325.46009</v>
+        <v>60531037325.4601</v>
       </c>
       <c r="N54">
         <v>21738601056.44896</v>
@@ -12375,7 +12375,7 @@
         <v>1242536217.712095</v>
       </c>
       <c r="D56">
-        <v>24141483156.34009</v>
+        <v>24141483156.3401</v>
       </c>
       <c r="E56">
         <v>1572116331.30574</v>
@@ -12405,7 +12405,7 @@
         <v>61087525975.28636</v>
       </c>
       <c r="N56">
-        <v>21953893627.74167</v>
+        <v>21953893627.74166</v>
       </c>
       <c r="O56">
         <v>145051097296.2888</v>
